--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA8E090-04C2-4142-846E-33EA0462A624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="130">
   <si>
     <t>Funcionário</t>
   </si>
@@ -408,31 +420,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,14 +462,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -481,112 +486,375 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
-  <dimension ref="A1:G81"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G80"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
-    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
-    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
-    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
-    <col max="6" min="6" style="1" width="26.28515625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="3.7109375" customWidth="true"/>
-    <col max="16384" min="8" style="1" width="12.140625"/>
+    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -609,7 +877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -619,11 +887,11 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>45326</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>9391.78</v>
+      <c r="E2" s="5">
+        <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
@@ -632,7 +900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -642,10 +910,10 @@
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>45346</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5">
         <v>5418</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -655,7 +923,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -665,11 +933,11 @@
       <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>45350</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1264.87</v>
+      <c r="E4" s="5">
+        <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>16</v>
@@ -678,7 +946,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -688,10 +956,10 @@
       <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>45356</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5">
         <v>5418</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -701,7 +969,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -711,10 +979,10 @@
       <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>45362</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5">
         <v>384</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -724,7 +992,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -734,10 +1002,10 @@
       <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>45364</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5">
         <v>816</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -747,7 +1015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -757,10 +1025,10 @@
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>45378</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5">
         <v>816</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -770,7 +1038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -780,10 +1048,10 @@
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>45463</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5">
         <v>1674.52</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -793,7 +1061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -803,10 +1071,10 @@
       <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>45493</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5">
         <v>873.6</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -816,7 +1084,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -826,10 +1094,10 @@
       <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>45523</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5">
         <v>873.6</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -839,7 +1107,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -849,10 +1117,10 @@
       <c r="C12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>45600</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5">
         <v>2000</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -862,7 +1130,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -872,10 +1140,10 @@
       <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>45607</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5">
         <v>3204.34</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -885,7 +1153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -895,11 +1163,11 @@
       <c r="C14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>45608</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4439.9</v>
+      <c r="E14" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -908,7 +1176,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>27</v>
       </c>
@@ -918,10 +1186,10 @@
       <c r="C15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>45614</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="5">
         <v>2000</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -931,7 +1199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
@@ -941,11 +1209,11 @@
       <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>45615</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>1216.86</v>
+      <c r="E16" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>10</v>
@@ -954,7 +1222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
@@ -964,10 +1232,10 @@
       <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>45617</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="5">
         <v>1843.87</v>
       </c>
       <c r="F17" s="3" t="s">
@@ -977,7 +1245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -987,11 +1255,11 @@
       <c r="C18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>45622</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1216.86</v>
+      <c r="E18" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>10</v>
@@ -1000,7 +1268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
@@ -1010,11 +1278,11 @@
       <c r="C19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>45622</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>4439.9</v>
+      <c r="E19" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>10</v>
@@ -1023,7 +1291,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1033,10 +1301,10 @@
       <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>45624</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="5">
         <v>1843.88</v>
       </c>
       <c r="F20" s="3" t="s">
@@ -1046,7 +1314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1056,11 +1324,11 @@
       <c r="C21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>45688</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>1118.4</v>
+      <c r="E21" s="5">
+        <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>10</v>
@@ -1069,7 +1337,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
@@ -1079,10 +1347,10 @@
       <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>45695</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="5">
         <v>3296.8</v>
       </c>
       <c r="F22" s="3" t="s">
@@ -1092,7 +1360,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
@@ -1102,10 +1370,10 @@
       <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>45699</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="5">
         <v>2330</v>
       </c>
       <c r="F23" s="3" t="s">
@@ -1115,7 +1383,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1125,10 +1393,10 @@
       <c r="C24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>45702</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="5">
         <v>3296.8</v>
       </c>
       <c r="F24" s="3" t="s">
@@ -1138,7 +1406,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
@@ -1148,10 +1416,10 @@
       <c r="C25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>45705</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="5">
         <v>2541</v>
       </c>
       <c r="F25" s="3" t="s">
@@ -1161,7 +1429,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>27</v>
       </c>
@@ -1171,10 +1439,10 @@
       <c r="C26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>45709</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="5">
         <v>3296.8</v>
       </c>
       <c r="F26" s="3" t="s">
@@ -1184,7 +1452,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
@@ -1194,10 +1462,10 @@
       <c r="C27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>45712</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="5">
         <v>2541</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -1207,7 +1475,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1217,10 +1485,10 @@
       <c r="C28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>45726</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="5">
         <v>2541</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -1230,7 +1498,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
@@ -1240,10 +1508,10 @@
       <c r="C29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4">
         <v>45727</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="5">
         <v>7562.78</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -1253,7 +1521,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>31</v>
       </c>
@@ -1263,10 +1531,10 @@
       <c r="C30" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>45734</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="5">
         <v>1154.56</v>
       </c>
       <c r="F30" s="3" t="s">
@@ -1276,7 +1544,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>27</v>
       </c>
@@ -1286,10 +1554,10 @@
       <c r="C31" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>45734</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="5">
         <v>7562.78</v>
       </c>
       <c r="F31" s="3" t="s">
@@ -1299,7 +1567,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>27</v>
       </c>
@@ -1309,10 +1577,10 @@
       <c r="C32" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>45740</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="5">
         <v>2541</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -1322,7 +1590,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
@@ -1332,10 +1600,10 @@
       <c r="C33" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>45741</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="5">
         <v>1154.56</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -1345,7 +1613,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>27</v>
       </c>
@@ -1355,10 +1623,10 @@
       <c r="C34" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>45741</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="5">
         <v>7562.78</v>
       </c>
       <c r="F34" s="3" t="s">
@@ -1368,7 +1636,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>31</v>
       </c>
@@ -1378,10 +1646,10 @@
       <c r="C35" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4">
         <v>45748</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="5">
         <v>1154.56</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -1391,7 +1659,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>27</v>
       </c>
@@ -1401,10 +1669,10 @@
       <c r="C36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4">
         <v>45748</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="5">
         <v>7562.76</v>
       </c>
       <c r="F36" s="3" t="s">
@@ -1414,7 +1682,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
@@ -1424,10 +1692,10 @@
       <c r="C37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4">
         <v>45755</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="5">
         <v>1154.56</v>
       </c>
       <c r="F37" s="3" t="s">
@@ -1437,7 +1705,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
@@ -1447,10 +1715,10 @@
       <c r="C38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="4">
         <v>45761</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="5">
         <v>6169.53</v>
       </c>
       <c r="F38" s="3" t="s">
@@ -1460,7 +1728,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>31</v>
       </c>
@@ -1470,10 +1738,10 @@
       <c r="C39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="4">
         <v>45768</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="5">
         <v>3850</v>
       </c>
       <c r="F39" s="3" t="s">
@@ -1483,7 +1751,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -1493,10 +1761,10 @@
       <c r="C40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="4">
         <v>45775</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="5">
         <v>3850</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -1506,7 +1774,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>31</v>
       </c>
@@ -1516,10 +1784,10 @@
       <c r="C41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="4">
         <v>45775</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="5">
         <v>6089.41</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -1529,7 +1797,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>31</v>
       </c>
@@ -1539,10 +1807,10 @@
       <c r="C42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="4">
         <v>45782</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="5">
         <v>3800</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -1552,7 +1820,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>31</v>
       </c>
@@ -1562,10 +1830,10 @@
       <c r="C43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="4">
         <v>45789</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="5">
         <v>3800</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -1575,7 +1843,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>71</v>
       </c>
@@ -1585,10 +1853,10 @@
       <c r="C44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="4">
         <v>45789</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="5">
         <v>1143.54</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -1598,7 +1866,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -1608,10 +1876,10 @@
       <c r="C45" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="4">
         <v>45796</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="5">
         <v>2287.06</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -1621,7 +1889,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>13</v>
       </c>
@@ -1631,10 +1899,10 @@
       <c r="C46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="4">
         <v>45874</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="5">
         <v>1326</v>
       </c>
       <c r="F46" s="3"/>
@@ -1642,7 +1910,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>27</v>
       </c>
@@ -1652,10 +1920,10 @@
       <c r="C47" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="4">
         <v>45896</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="5">
         <v>4572.62</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -1665,7 +1933,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>27</v>
       </c>
@@ -1675,10 +1943,10 @@
       <c r="C48" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="4">
         <v>45910</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="5">
         <v>3663.84</v>
       </c>
       <c r="F48" s="3" t="s">
@@ -1688,7 +1956,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>27</v>
       </c>
@@ -1698,10 +1966,10 @@
       <c r="C49" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="4">
         <v>45910</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="5">
         <v>873.63</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -1711,7 +1979,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>27</v>
       </c>
@@ -1721,10 +1989,10 @@
       <c r="C50" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="4">
         <v>45917</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="5">
         <v>700</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -1734,7 +2002,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>27</v>
       </c>
@@ -1744,10 +2012,10 @@
       <c r="C51" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="4">
         <v>45924</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="5">
         <v>700</v>
       </c>
       <c r="F51" s="3" t="s">
@@ -1757,7 +2025,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>27</v>
       </c>
@@ -1767,10 +2035,10 @@
       <c r="C52" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="4">
         <v>45924</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="5">
         <v>3663.84</v>
       </c>
       <c r="F52" s="3" t="s">
@@ -1780,7 +2048,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>85</v>
       </c>
@@ -1790,10 +2058,10 @@
       <c r="C53" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="4">
         <v>45947</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E53" s="5">
         <v>3867.34</v>
       </c>
       <c r="F53" s="3" t="s">
@@ -1803,7 +2071,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>85</v>
       </c>
@@ -1813,10 +2081,10 @@
       <c r="C54" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="4">
         <v>45954</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E54" s="5">
         <v>2144.59</v>
       </c>
       <c r="F54" s="3" t="s">
@@ -1826,7 +2094,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>85</v>
       </c>
@@ -1836,10 +2104,10 @@
       <c r="C55" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="4">
         <v>45961</v>
       </c>
-      <c r="E55" s="5" t="n">
+      <c r="E55" s="5">
         <v>2144.59</v>
       </c>
       <c r="F55" s="3" t="s">
@@ -1849,7 +2117,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>85</v>
       </c>
@@ -1859,10 +2127,10 @@
       <c r="C56" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="4">
         <v>45968</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="5">
         <v>2144.59</v>
       </c>
       <c r="F56" s="3" t="s">
@@ -1872,7 +2140,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>71</v>
       </c>
@@ -1882,10 +2150,10 @@
       <c r="C57" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="4">
         <v>45980</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="5">
         <v>4480</v>
       </c>
       <c r="F57" s="3" t="s">
@@ -1895,7 +2163,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>85</v>
       </c>
@@ -1905,10 +2173,10 @@
       <c r="C58" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="4">
         <v>45980</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="5">
         <v>48213.84</v>
       </c>
       <c r="F58" s="3"/>
@@ -1916,7 +2184,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>85</v>
       </c>
@@ -1926,18 +2194,18 @@
       <c r="C59" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="4">
         <v>45987</v>
       </c>
-      <c r="E59" s="5" t="n">
-        <v>33844.16</v>
+      <c r="E59" s="5">
+        <v>33844.160000000003</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>71</v>
       </c>
@@ -1947,10 +2215,10 @@
       <c r="C60" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="4">
         <v>45989</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="5">
         <v>3220</v>
       </c>
       <c r="F60" s="3"/>
@@ -1958,7 +2226,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>85</v>
       </c>
@@ -1968,10 +2236,10 @@
       <c r="C61" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="4">
         <v>45994</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="5">
         <v>48208.79</v>
       </c>
       <c r="F61" s="3"/>
@@ -1979,7 +2247,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>98</v>
       </c>
@@ -1989,11 +2257,11 @@
       <c r="C62" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="4">
         <v>46085</v>
       </c>
-      <c r="E62" s="5" t="n">
-        <v>2089.57</v>
+      <c r="E62" s="5">
+        <v>2089.5700000000002</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>16</v>
@@ -2002,7 +2270,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>98</v>
       </c>
@@ -2012,10 +2280,10 @@
       <c r="C63" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="4">
         <v>46087</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="5">
         <v>4736.72</v>
       </c>
       <c r="F63" s="3" t="s">
@@ -2025,7 +2293,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>13</v>
       </c>
@@ -2035,10 +2303,10 @@
       <c r="C64" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="4">
         <v>46090</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="5">
         <v>806.34</v>
       </c>
       <c r="F64" s="3" t="s">
@@ -2048,7 +2316,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>98</v>
       </c>
@@ -2058,11 +2326,11 @@
       <c r="C65" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="4">
         <v>46092</v>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>2089.57</v>
+      <c r="E65" s="5">
+        <v>2089.5700000000002</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>16</v>
@@ -2071,7 +2339,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>13</v>
       </c>
@@ -2081,10 +2349,10 @@
       <c r="C66" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="4">
         <v>46097</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="5">
         <v>503.28</v>
       </c>
       <c r="F66" s="3" t="s">
@@ -2094,7 +2362,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>98</v>
       </c>
@@ -2104,10 +2372,10 @@
       <c r="C67" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="4">
         <v>46099</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="5">
         <v>7584.01</v>
       </c>
       <c r="F67" s="3"/>
@@ -2115,7 +2383,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>98</v>
       </c>
@@ -2125,10 +2393,10 @@
       <c r="C68" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="4">
         <v>46099</v>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E68" s="5">
         <v>2089.56</v>
       </c>
       <c r="F68" s="3" t="s">
@@ -2138,7 +2406,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>85</v>
       </c>
@@ -2148,10 +2416,10 @@
       <c r="C69" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="4">
         <v>46104</v>
       </c>
-      <c r="E69" s="5" t="n">
+      <c r="E69" s="5">
         <v>3636</v>
       </c>
       <c r="F69" s="3" t="s">
@@ -2161,7 +2429,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>13</v>
       </c>
@@ -2171,10 +2439,10 @@
       <c r="C70" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="4">
         <v>46104</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="5">
         <v>927</v>
       </c>
       <c r="F70" s="3" t="s">
@@ -2184,7 +2452,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>13</v>
       </c>
@@ -2194,10 +2462,10 @@
       <c r="C71" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="4">
         <v>46104</v>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E71" s="5">
         <v>503.28</v>
       </c>
       <c r="F71" s="3" t="s">
@@ -2207,7 +2475,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>13</v>
       </c>
@@ -2217,10 +2485,10 @@
       <c r="C72" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="4">
         <v>46104</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E72" s="5">
         <v>863.1</v>
       </c>
       <c r="F72" s="3" t="s">
@@ -2230,7 +2498,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>13</v>
       </c>
@@ -2240,10 +2508,10 @@
       <c r="C73" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="4">
         <v>46104</v>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="5">
         <v>760.74</v>
       </c>
       <c r="F73" s="3" t="s">
@@ -2253,7 +2521,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>27</v>
       </c>
@@ -2263,10 +2531,10 @@
       <c r="C74" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="4">
         <v>46105</v>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E74" s="5">
         <v>1812.31</v>
       </c>
       <c r="F74" s="3" t="s">
@@ -2276,7 +2544,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>98</v>
       </c>
@@ -2286,10 +2554,10 @@
       <c r="C75" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="4">
         <v>46105</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E75" s="5">
         <v>4434.51</v>
       </c>
       <c r="F75" s="3" t="s">
@@ -2299,7 +2567,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>7</v>
       </c>
@@ -2309,10 +2577,10 @@
       <c r="C76" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="4">
         <v>46105</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="5">
         <v>5466.66</v>
       </c>
       <c r="F76" s="3" t="s">
@@ -2322,7 +2590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>7</v>
       </c>
@@ -2332,18 +2600,18 @@
       <c r="C77" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="4">
         <v>46106</v>
       </c>
-      <c r="E77" s="5" t="n">
-        <v>9832.7</v>
+      <c r="E77" s="5">
+        <v>9832.7000000000007</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>13</v>
       </c>
@@ -2353,11 +2621,11 @@
       <c r="C78" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="4">
         <v>46106</v>
       </c>
-      <c r="E78" s="5" t="n">
-        <v>264.09</v>
+      <c r="E78" s="5">
+        <v>264.08999999999997</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>16</v>
@@ -2366,7 +2634,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>98</v>
       </c>
@@ -2376,10 +2644,10 @@
       <c r="C79" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="4">
         <v>46106</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E79" s="5">
         <v>4646.53</v>
       </c>
       <c r="F79" s="3"/>
@@ -2387,7 +2655,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>71</v>
       </c>
@@ -2397,10 +2665,10 @@
       <c r="C80" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="4">
         <v>46106</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="E80" s="5">
         <v>5826.6</v>
       </c>
       <c r="F80" s="3" t="s">
@@ -2410,18 +2678,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="81" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="8" t="n">
-        <v>361138.06</v>
-      </c>
-      <c r="F81" s="7"/>
-      <c r="G81" s="9"/>
-    </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,31 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA8E090-04C2-4142-846E-33EA0462A624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr refMode="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>Funcionário</t>
   </si>
@@ -192,24 +180,24 @@
     <t>01003589.1</t>
   </si>
   <si>
+    <t>01003589.2</t>
+  </si>
+  <si>
     <t>MED-K COMERCIO LTDA</t>
   </si>
   <si>
     <t>01003592.2</t>
   </si>
   <si>
-    <t>01003589.2</t>
-  </si>
-  <si>
     <t>01003504.6</t>
   </si>
   <si>
+    <t>01003589.3</t>
+  </si>
+  <si>
     <t>01003592.3</t>
   </si>
   <si>
-    <t>01003589.3</t>
-  </si>
-  <si>
     <t>01003592.4</t>
   </si>
   <si>
@@ -321,129 +309,181 @@
     <t>01005217.3</t>
   </si>
   <si>
+    <t>DENTAL SORRISO LTDA</t>
+  </si>
+  <si>
+    <t>01005781.1</t>
+  </si>
+  <si>
     <t>MARCOS DUTRA</t>
   </si>
   <si>
     <t>VITAL DISTRIBUIDORA LTDA</t>
   </si>
   <si>
-    <t>01005759.1</t>
+    <t>01005759.2</t>
   </si>
   <si>
     <t>PI</t>
   </si>
   <si>
+    <t>01005781.2</t>
+  </si>
+  <si>
+    <t>01005759.3</t>
+  </si>
+  <si>
+    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005839.1</t>
+  </si>
+  <si>
+    <t>01005781.3</t>
+  </si>
+  <si>
+    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01005878.1</t>
+  </si>
+  <si>
     <t>R7 DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
   </si>
   <si>
-    <t>01005645.4</t>
+    <t>01005876.1</t>
   </si>
   <si>
     <t>MA</t>
   </si>
   <si>
-    <t>DENTAL SORRISO LTDA</t>
-  </si>
-  <si>
-    <t>01005781.1</t>
-  </si>
-  <si>
-    <t>01005759.2</t>
-  </si>
-  <si>
-    <t>01005781.2</t>
-  </si>
-  <si>
-    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005839.1</t>
-  </si>
-  <si>
-    <t>01005759.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
-  </si>
-  <si>
-    <t>01005686.5</t>
+    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01005683.3</t>
+  </si>
+  <si>
+    <t>01005839.2</t>
+  </si>
+  <si>
+    <t>JMC COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01005822.2</t>
+  </si>
+  <si>
+    <t>DISTRIMEDICA COM PROD MED E ODONT LTDA</t>
+  </si>
+  <si>
+    <t>01005820.1</t>
+  </si>
+  <si>
+    <t>01005755.3</t>
+  </si>
+  <si>
+    <t>QUALIMMED - COM. ATAC. DE MED. E MAT. HOSPITALAR</t>
+  </si>
+  <si>
+    <t>01005765.4</t>
+  </si>
+  <si>
+    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
+  </si>
+  <si>
+    <t>01005881.1</t>
   </si>
   <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01005779.3</t>
-  </si>
-  <si>
-    <t>01005781.3</t>
-  </si>
-  <si>
-    <t>01005863.1</t>
-  </si>
-  <si>
-    <t>01005782.3</t>
-  </si>
-  <si>
-    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
-  </si>
-  <si>
-    <t>01005878.1</t>
-  </si>
-  <si>
-    <t>01005876.1</t>
-  </si>
-  <si>
-    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01005683.3</t>
-  </si>
-  <si>
-    <t>JMC COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01005822.2</t>
-  </si>
-  <si>
-    <t>01005840.2</t>
-  </si>
-  <si>
-    <t>01005839.2</t>
-  </si>
-  <si>
-    <t>DISTRIMEDICA COM PROD MED E ODONT LTDA</t>
-  </si>
-  <si>
-    <t>01005820.1</t>
+    <t>01005863.2</t>
+  </si>
+  <si>
+    <t>01005913.1</t>
+  </si>
+  <si>
+    <t>01005820.2</t>
+  </si>
+  <si>
+    <t>MAIS SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>01005742.5</t>
+  </si>
+  <si>
+    <t>01005755.4</t>
+  </si>
+  <si>
+    <t>F F MELO SILVA MATERIAL MEDICO HOSPITALAR E ODONT</t>
+  </si>
+  <si>
+    <t>01005954.1</t>
+  </si>
+  <si>
+    <t>01005876.2</t>
+  </si>
+  <si>
+    <t>01005878.2</t>
+  </si>
+  <si>
+    <t>01005923.1</t>
+  </si>
+  <si>
+    <t>01005840.3</t>
+  </si>
+  <si>
+    <t>01005839.3</t>
+  </si>
+  <si>
+    <t>ESTRELA COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01005908.1</t>
+  </si>
+  <si>
+    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
+  </si>
+  <si>
+    <t>01005792.3</t>
+  </si>
+  <si>
+    <t>01005836.3</t>
+  </si>
+  <si>
+    <t>MEDZ DISTRIBUIDORA HOSPITALAR E MEDICA LTDA</t>
+  </si>
+  <si>
+    <t>01005967.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
+    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -462,8 +502,14 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -486,375 +532,112 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA0A0A0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA0A0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+  <cellXfs count="10">
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G80"/>
-  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
+  <dimension ref="A1:G92"/>
+  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="3.7109375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="12.140625" style="1"/>
+    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
+    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
+    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
+    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
+    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
+    <col max="6" min="6" style="1" width="26.28515625" customWidth="true"/>
+    <col max="7" min="7" style="1" width="3.7109375" customWidth="true"/>
+    <col max="16384" min="8" style="1" width="12.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -877,7 +660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -887,11 +670,11 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="4" t="n">
         <v>45326</v>
       </c>
-      <c r="E2" s="5">
-        <v>9391.7800000000007</v>
+      <c r="E2" s="5" t="n">
+        <v>9391.78</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
@@ -900,7 +683,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -910,10 +693,10 @@
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="4" t="n">
         <v>45346</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="5" t="n">
         <v>5418</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -923,7 +706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -933,11 +716,11 @@
       <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="4" t="n">
         <v>45350</v>
       </c>
-      <c r="E4" s="5">
-        <v>1264.8699999999999</v>
+      <c r="E4" s="5" t="n">
+        <v>1264.87</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>16</v>
@@ -946,7 +729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -956,10 +739,10 @@
       <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="4" t="n">
         <v>45356</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="5" t="n">
         <v>5418</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -969,7 +752,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -979,10 +762,10 @@
       <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="4" t="n">
         <v>45362</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="5" t="n">
         <v>384</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -992,7 +775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1002,10 +785,10 @@
       <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="n">
         <v>45364</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5" t="n">
         <v>816</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -1015,7 +798,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1025,10 +808,10 @@
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="4" t="n">
         <v>45378</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="5" t="n">
         <v>816</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -1038,7 +821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -1048,10 +831,10 @@
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="4" t="n">
         <v>45463</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5" t="n">
         <v>1674.52</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -1061,7 +844,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1071,10 +854,10 @@
       <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="4" t="n">
         <v>45493</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="5" t="n">
         <v>873.6</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -1084,7 +867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -1094,10 +877,10 @@
       <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="4" t="n">
         <v>45523</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5" t="n">
         <v>873.6</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -1107,7 +890,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1117,10 +900,10 @@
       <c r="C12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="4" t="n">
         <v>45600</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -1130,7 +913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -1140,10 +923,10 @@
       <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="4" t="n">
         <v>45607</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="5" t="n">
         <v>3204.34</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -1153,7 +936,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -1163,11 +946,11 @@
       <c r="C14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="4" t="n">
         <v>45608</v>
       </c>
-      <c r="E14" s="5">
-        <v>4439.8999999999996</v>
+      <c r="E14" s="5" t="n">
+        <v>4439.9</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -1176,7 +959,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A15" s="3" t="s">
         <v>27</v>
       </c>
@@ -1186,10 +969,10 @@
       <c r="C15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="4" t="n">
         <v>45614</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -1199,7 +982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
@@ -1209,11 +992,11 @@
       <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="4" t="n">
         <v>45615</v>
       </c>
-      <c r="E16" s="5">
-        <v>1216.8599999999999</v>
+      <c r="E16" s="5" t="n">
+        <v>1216.86</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>10</v>
@@ -1222,7 +1005,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
@@ -1232,10 +1015,10 @@
       <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="4" t="n">
         <v>45617</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="5" t="n">
         <v>1843.87</v>
       </c>
       <c r="F17" s="3" t="s">
@@ -1245,7 +1028,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1255,11 +1038,11 @@
       <c r="C18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E18" s="5">
-        <v>1216.8599999999999</v>
+      <c r="E18" s="5" t="n">
+        <v>1216.86</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>10</v>
@@ -1268,7 +1051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
@@ -1278,11 +1061,11 @@
       <c r="C19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E19" s="5">
-        <v>4439.8999999999996</v>
+      <c r="E19" s="5" t="n">
+        <v>4439.9</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>10</v>
@@ -1291,7 +1074,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1301,10 +1084,10 @@
       <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="4" t="n">
         <v>45624</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="5" t="n">
         <v>1843.88</v>
       </c>
       <c r="F20" s="3" t="s">
@@ -1314,7 +1097,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1324,11 +1107,11 @@
       <c r="C21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="4" t="n">
         <v>45688</v>
       </c>
-      <c r="E21" s="5">
-        <v>1118.4000000000001</v>
+      <c r="E21" s="5" t="n">
+        <v>1118.4</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>10</v>
@@ -1337,7 +1120,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
@@ -1347,10 +1130,10 @@
       <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="4" t="n">
         <v>45695</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="F22" s="3" t="s">
@@ -1360,7 +1143,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
@@ -1370,10 +1153,10 @@
       <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="4" t="n">
         <v>45699</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="5" t="n">
         <v>2330</v>
       </c>
       <c r="F23" s="3" t="s">
@@ -1383,7 +1166,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1393,10 +1176,10 @@
       <c r="C24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="4" t="n">
         <v>45702</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="F24" s="3" t="s">
@@ -1406,7 +1189,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
@@ -1416,10 +1199,10 @@
       <c r="C25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="4" t="n">
         <v>45705</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="F25" s="3" t="s">
@@ -1429,7 +1212,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A26" s="3" t="s">
         <v>27</v>
       </c>
@@ -1439,10 +1222,10 @@
       <c r="C26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="4" t="n">
         <v>45709</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="F26" s="3" t="s">
@@ -1452,7 +1235,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
@@ -1462,10 +1245,10 @@
       <c r="C27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="4" t="n">
         <v>45712</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -1475,7 +1258,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1485,10 +1268,10 @@
       <c r="C28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="4" t="n">
         <v>45726</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -1498,7 +1281,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
@@ -1508,10 +1291,10 @@
       <c r="C29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="4" t="n">
         <v>45727</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -1521,53 +1304,53 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>45734</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>7562.78</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="D30" s="4">
-        <v>45734</v>
-      </c>
-      <c r="E30" s="5">
-        <v>1154.56</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="4" t="n">
         <v>45734</v>
       </c>
-      <c r="E31" s="5">
-        <v>7562.78</v>
+      <c r="E31" s="5" t="n">
+        <v>1154.56</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A32" s="3" t="s">
         <v>27</v>
       </c>
@@ -1577,10 +1360,10 @@
       <c r="C32" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="4" t="n">
         <v>45740</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -1590,66 +1373,66 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A33" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E33" s="5">
-        <v>1154.56</v>
+      <c r="E33" s="5" t="n">
+        <v>7562.78</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A34" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E34" s="5">
-        <v>7562.78</v>
+      <c r="E34" s="5" t="n">
+        <v>1154.56</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -1659,7 +1442,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A36" s="3" t="s">
         <v>27</v>
       </c>
@@ -1669,10 +1452,10 @@
       <c r="C36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="5" t="n">
         <v>7562.76</v>
       </c>
       <c r="F36" s="3" t="s">
@@ -1682,20 +1465,20 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="4" t="n">
         <v>45755</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="F37" s="3" t="s">
@@ -1705,7 +1488,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
@@ -1715,10 +1498,10 @@
       <c r="C38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="4" t="n">
         <v>45761</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="5" t="n">
         <v>6169.53</v>
       </c>
       <c r="F38" s="3" t="s">
@@ -1728,7 +1511,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A39" s="3" t="s">
         <v>31</v>
       </c>
@@ -1738,10 +1521,10 @@
       <c r="C39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="4" t="n">
         <v>45768</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="5" t="n">
         <v>3850</v>
       </c>
       <c r="F39" s="3" t="s">
@@ -1751,7 +1534,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -1761,10 +1544,10 @@
       <c r="C40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="5" t="n">
         <v>3850</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -1774,7 +1557,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A41" s="3" t="s">
         <v>31</v>
       </c>
@@ -1784,10 +1567,10 @@
       <c r="C41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="5" t="n">
         <v>6089.41</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -1797,7 +1580,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A42" s="3" t="s">
         <v>31</v>
       </c>
@@ -1807,10 +1590,10 @@
       <c r="C42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="5" t="n">
         <v>3800</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -1820,7 +1603,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A43" s="3" t="s">
         <v>31</v>
       </c>
@@ -1830,10 +1613,10 @@
       <c r="C43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="5" t="n">
         <v>3800</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -1843,7 +1626,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A44" s="3" t="s">
         <v>71</v>
       </c>
@@ -1853,10 +1636,10 @@
       <c r="C44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="5" t="n">
         <v>1143.54</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -1866,7 +1649,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -1876,10 +1659,10 @@
       <c r="C45" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="4" t="n">
         <v>45796</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="5" t="n">
         <v>2287.06</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -1889,7 +1672,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A46" s="3" t="s">
         <v>13</v>
       </c>
@@ -1899,10 +1682,10 @@
       <c r="C46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="4" t="n">
         <v>45874</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="5" t="n">
         <v>1326</v>
       </c>
       <c r="F46" s="3"/>
@@ -1910,7 +1693,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A47" s="3" t="s">
         <v>27</v>
       </c>
@@ -1920,10 +1703,10 @@
       <c r="C47" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="4" t="n">
         <v>45896</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="5" t="n">
         <v>4572.62</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -1933,7 +1716,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A48" s="3" t="s">
         <v>27</v>
       </c>
@@ -1943,10 +1726,10 @@
       <c r="C48" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="4" t="n">
         <v>45910</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="5" t="n">
         <v>3663.84</v>
       </c>
       <c r="F48" s="3" t="s">
@@ -1956,7 +1739,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A49" s="3" t="s">
         <v>27</v>
       </c>
@@ -1966,10 +1749,10 @@
       <c r="C49" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="4" t="n">
         <v>45910</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="5" t="n">
         <v>873.63</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -1979,7 +1762,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A50" s="3" t="s">
         <v>27</v>
       </c>
@@ -1989,10 +1772,10 @@
       <c r="C50" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="4" t="n">
         <v>45917</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="5" t="n">
         <v>700</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -2002,7 +1785,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A51" s="3" t="s">
         <v>27</v>
       </c>
@@ -2012,10 +1795,10 @@
       <c r="C51" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="4" t="n">
         <v>45924</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="5" t="n">
         <v>700</v>
       </c>
       <c r="F51" s="3" t="s">
@@ -2025,7 +1808,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A52" s="3" t="s">
         <v>27</v>
       </c>
@@ -2035,10 +1818,10 @@
       <c r="C52" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="4" t="n">
         <v>45924</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="5" t="n">
         <v>3663.84</v>
       </c>
       <c r="F52" s="3" t="s">
@@ -2048,7 +1831,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A53" s="3" t="s">
         <v>85</v>
       </c>
@@ -2058,10 +1841,10 @@
       <c r="C53" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="4" t="n">
         <v>45947</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="5" t="n">
         <v>3867.34</v>
       </c>
       <c r="F53" s="3" t="s">
@@ -2071,7 +1854,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A54" s="3" t="s">
         <v>85</v>
       </c>
@@ -2081,10 +1864,10 @@
       <c r="C54" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="4" t="n">
         <v>45954</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="F54" s="3" t="s">
@@ -2094,7 +1877,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A55" s="3" t="s">
         <v>85</v>
       </c>
@@ -2104,10 +1887,10 @@
       <c r="C55" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="4" t="n">
         <v>45961</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="F55" s="3" t="s">
@@ -2117,7 +1900,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A56" s="3" t="s">
         <v>85</v>
       </c>
@@ -2127,10 +1910,10 @@
       <c r="C56" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="4" t="n">
         <v>45968</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="F56" s="3" t="s">
@@ -2140,7 +1923,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A57" s="3" t="s">
         <v>71</v>
       </c>
@@ -2150,10 +1933,10 @@
       <c r="C57" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="4" t="n">
         <v>45980</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="5" t="n">
         <v>4480</v>
       </c>
       <c r="F57" s="3" t="s">
@@ -2163,7 +1946,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A58" s="3" t="s">
         <v>85</v>
       </c>
@@ -2173,10 +1956,10 @@
       <c r="C58" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="4" t="n">
         <v>45980</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="5" t="n">
         <v>48213.84</v>
       </c>
       <c r="F58" s="3"/>
@@ -2184,7 +1967,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A59" s="3" t="s">
         <v>85</v>
       </c>
@@ -2194,18 +1977,18 @@
       <c r="C59" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="4" t="n">
         <v>45987</v>
       </c>
-      <c r="E59" s="5">
-        <v>33844.160000000003</v>
+      <c r="E59" s="5" t="n">
+        <v>33844.16</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A60" s="3" t="s">
         <v>71</v>
       </c>
@@ -2215,10 +1998,10 @@
       <c r="C60" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="4" t="n">
         <v>45989</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="5" t="n">
         <v>3220</v>
       </c>
       <c r="F60" s="3"/>
@@ -2226,7 +2009,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A61" s="3" t="s">
         <v>85</v>
       </c>
@@ -2236,10 +2019,10 @@
       <c r="C61" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="4" t="n">
         <v>45994</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="5" t="n">
         <v>48208.79</v>
       </c>
       <c r="F61" s="3"/>
@@ -2247,67 +2030,67 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="4" t="n">
+        <v>46090</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>806.34</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A63" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D62" s="4">
-        <v>46085</v>
-      </c>
-      <c r="E62" s="5">
-        <v>2089.5700000000002</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" s="3" t="s">
+      <c r="B63" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="4" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>2089.57</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D63" s="4">
-        <v>46087</v>
-      </c>
-      <c r="E63" s="5">
-        <v>4736.72</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A64" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D64" s="4">
-        <v>46090</v>
-      </c>
-      <c r="E64" s="5">
-        <v>806.34</v>
+        <v>104</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>46097</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>503.28</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>16</v>
@@ -2316,122 +2099,122 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A65" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>2089.56</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A66" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>7584.01</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D65" s="4">
-        <v>46092</v>
-      </c>
-      <c r="E65" s="5">
-        <v>2089.5700000000002</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C66" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D66" s="4">
-        <v>46097</v>
-      </c>
-      <c r="E66" s="5">
+      <c r="D67" s="4" t="n">
+        <v>46104</v>
+      </c>
+      <c r="E67" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G66" s="3" t="s">
+      <c r="F67" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B67" s="3" t="s">
+    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D67" s="4">
-        <v>46099</v>
-      </c>
-      <c r="E67" s="5">
-        <v>7584.01</v>
-      </c>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>1812.31</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A69" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D68" s="4">
-        <v>46099</v>
-      </c>
-      <c r="E68" s="5">
-        <v>2089.56</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>4434.51</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D69" s="4">
-        <v>46104</v>
-      </c>
-      <c r="E69" s="5">
-        <v>3636</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A70" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>114</v>
@@ -2439,193 +2222,187 @@
       <c r="C70" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D70" s="4">
-        <v>46104</v>
-      </c>
-      <c r="E70" s="5">
-        <v>927</v>
+      <c r="D70" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>5466.66</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A71" s="3" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D71" s="4">
-        <v>46104</v>
-      </c>
-      <c r="E71" s="5">
-        <v>503.28</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="D71" s="4" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>4646.53</v>
+      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A72" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D72" s="4">
-        <v>46104</v>
-      </c>
-      <c r="E72" s="5">
-        <v>863.1</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>9832.7</v>
+      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A73" s="3" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D73" s="4">
-        <v>46104</v>
-      </c>
-      <c r="E73" s="5">
-        <v>760.74</v>
+        <v>120</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>5826.6</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A74" s="3" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>119</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D74" s="4">
-        <v>46105</v>
-      </c>
-      <c r="E74" s="5">
-        <v>1812.31</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>6120</v>
+      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A75" s="3" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D75" s="4">
-        <v>46105</v>
-      </c>
-      <c r="E75" s="5">
-        <v>4434.51</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A76" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D76" s="4">
-        <v>46105</v>
-      </c>
-      <c r="E76" s="5">
-        <v>5466.66</v>
+        <v>125</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>46108</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>1470</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A77" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D77" s="4">
-        <v>46106</v>
-      </c>
-      <c r="E77" s="5">
-        <v>9832.7000000000007</v>
-      </c>
-      <c r="F77" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>46111</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>863.1</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G77" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A78" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D78" s="4">
-        <v>46106</v>
-      </c>
-      <c r="E78" s="5">
-        <v>264.08999999999997</v>
+        <v>128</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>46111</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>863.1</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>16</v>
@@ -2634,51 +2411,309 @@
         <v>44</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A79" s="3" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>46111</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>5826.6</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A80" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>46111</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>19163.32</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A81" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>6120</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A82" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>11536.57</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A83" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>4434.51</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A84" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D79" s="4">
-        <v>46106</v>
-      </c>
-      <c r="E79" s="5">
-        <v>4646.53</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D80" s="4">
-        <v>46106</v>
-      </c>
-      <c r="E80" s="5">
-        <v>5826.6</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="C84" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>1452.13</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>1854</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A86" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>264.08</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A87" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>4646.54</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A88" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>10146.52</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A89" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>5408.64</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="90" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A90" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>4434.4</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A91" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>3704.66</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="92" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A92" s="6"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="8" t="n">
+        <v>448319.01</v>
+      </c>
+      <c r="F92" s="7"/>
+      <c r="G92" s="9"/>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="default" cellComments="none"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B5608D-1CAA-4C4F-8892-5D66095BE44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="151">
   <si>
     <t>Funcionário</t>
   </si>
@@ -243,12 +255,6 @@
     <t>01003847.3</t>
   </si>
   <si>
-    <t>CAMEDIC COMERCIAL E SERVIÇOS DE PROD MED HOSP EIRE</t>
-  </si>
-  <si>
-    <t>01004413.1BP</t>
-  </si>
-  <si>
     <t>ISA COMERCIO VAREJISTA DE PRODUTOS HOSPITALARES LT</t>
   </si>
   <si>
@@ -288,25 +294,25 @@
     <t>01004900.4</t>
   </si>
   <si>
+    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
+  </si>
+  <si>
+    <t>01005217.1BPBP</t>
+  </si>
+  <si>
     <t>BR MEDICAMENTOS LTDA</t>
   </si>
   <si>
     <t>01005075.3</t>
   </si>
   <si>
-    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
-  </si>
-  <si>
-    <t>01005217.1BPBP</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
     <t>01005144.3</t>
   </si>
   <si>
-    <t>01005217.3</t>
+    <t>01005217.3BP</t>
   </si>
   <si>
     <t>DENTAL SORRISO LTDA</t>
@@ -372,118 +378,135 @@
     <t>01005822.2</t>
   </si>
   <si>
+    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
+  </si>
+  <si>
+    <t>01005881.1</t>
+  </si>
+  <si>
     <t>DISTRIMEDICA COM PROD MED E ODONT LTDA</t>
   </si>
   <si>
-    <t>01005820.1</t>
-  </si>
-  <si>
-    <t>01005755.3</t>
+    <t>01005820.2</t>
+  </si>
+  <si>
+    <t>01005755.4</t>
+  </si>
+  <si>
+    <t>01005876.2</t>
+  </si>
+  <si>
+    <t>01005878.2</t>
+  </si>
+  <si>
+    <t>01005839.3</t>
+  </si>
+  <si>
+    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
+  </si>
+  <si>
+    <t>01005792.3</t>
+  </si>
+  <si>
+    <t>01005836.3</t>
+  </si>
+  <si>
+    <t>01005934.1</t>
   </si>
   <si>
     <t>QUALIMMED - COM. ATAC. DE MED. E MAT. HOSPITALAR</t>
   </si>
   <si>
-    <t>01005765.4</t>
-  </si>
-  <si>
-    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
-  </si>
-  <si>
-    <t>01005881.1</t>
+    <t>01005765.5</t>
   </si>
   <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01005863.2</t>
-  </si>
-  <si>
-    <t>01005913.1</t>
-  </si>
-  <si>
-    <t>01005820.2</t>
-  </si>
-  <si>
-    <t>MAIS SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>01005742.5</t>
-  </si>
-  <si>
-    <t>01005755.4</t>
-  </si>
-  <si>
-    <t>F F MELO SILVA MATERIAL MEDICO HOSPITALAR E ODONT</t>
-  </si>
-  <si>
-    <t>01005954.1</t>
-  </si>
-  <si>
-    <t>01005876.2</t>
-  </si>
-  <si>
-    <t>01005878.2</t>
-  </si>
-  <si>
-    <t>01005923.1</t>
-  </si>
-  <si>
-    <t>01005840.3</t>
-  </si>
-  <si>
-    <t>01005839.3</t>
-  </si>
-  <si>
-    <t>ESTRELA COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
-  </si>
-  <si>
-    <t>01005908.1</t>
-  </si>
-  <si>
-    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
-  </si>
-  <si>
-    <t>01005792.3</t>
-  </si>
-  <si>
-    <t>01005836.3</t>
+    <t>01005844.3</t>
+  </si>
+  <si>
+    <t>01005940.1</t>
+  </si>
+  <si>
+    <t>01005820.3</t>
+  </si>
+  <si>
+    <t>01005822.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDALAB COMERCIO DE ARTIGOS LABORAT E HOSP LTDA - </t>
+  </si>
+  <si>
+    <t>01005915.2</t>
+  </si>
+  <si>
+    <t>01005863.3</t>
+  </si>
+  <si>
+    <t>01005913.2</t>
+  </si>
+  <si>
+    <t>01005881.2</t>
+  </si>
+  <si>
+    <t>01005878.3</t>
+  </si>
+  <si>
+    <t>01005876.3</t>
+  </si>
+  <si>
+    <t>01005951.1</t>
+  </si>
+  <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
+  </si>
+  <si>
+    <t>01005955.1</t>
   </si>
   <si>
     <t>MEDZ DISTRIBUIDORA HOSPITALAR E MEDICA LTDA</t>
   </si>
   <si>
-    <t>01005967.1</t>
+    <t>01005967.2</t>
+  </si>
+  <si>
+    <t>01005923.2</t>
+  </si>
+  <si>
+    <t>01005968.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,14 +525,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -532,112 +549,375 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
-  <dimension ref="A1:G92"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G96"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
-    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
-    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
-    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
-    <col max="6" min="6" style="1" width="26.28515625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="3.7109375" customWidth="true"/>
-    <col max="16384" min="8" style="1" width="12.140625"/>
+    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -660,7 +940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -670,11 +950,11 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>45326</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>9391.78</v>
+      <c r="E2" s="5">
+        <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
@@ -683,7 +963,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -693,10 +973,10 @@
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>45346</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5">
         <v>5418</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -706,7 +986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -716,11 +996,11 @@
       <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>45350</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1264.87</v>
+      <c r="E4" s="5">
+        <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>16</v>
@@ -729,7 +1009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -739,10 +1019,10 @@
       <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>45356</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5">
         <v>5418</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -752,7 +1032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -762,10 +1042,10 @@
       <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>45362</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5">
         <v>384</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -775,7 +1055,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -785,10 +1065,10 @@
       <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>45364</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5">
         <v>816</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -798,7 +1078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -808,10 +1088,10 @@
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>45378</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5">
         <v>816</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -821,7 +1101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -831,10 +1111,10 @@
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>45463</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5">
         <v>1674.52</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -844,7 +1124,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -854,10 +1134,10 @@
       <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>45493</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5">
         <v>873.6</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -867,7 +1147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -877,10 +1157,10 @@
       <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>45523</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5">
         <v>873.6</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -890,7 +1170,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -900,10 +1180,10 @@
       <c r="C12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>45600</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5">
         <v>2000</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -913,7 +1193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -923,10 +1203,10 @@
       <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>45607</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5">
         <v>3204.34</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -936,7 +1216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -946,11 +1226,11 @@
       <c r="C14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>45608</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4439.9</v>
+      <c r="E14" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -959,7 +1239,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>27</v>
       </c>
@@ -969,10 +1249,10 @@
       <c r="C15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>45614</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="5">
         <v>2000</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -982,7 +1262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
@@ -992,11 +1272,11 @@
       <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>45615</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>1216.86</v>
+      <c r="E16" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>10</v>
@@ -1005,7 +1285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
@@ -1015,10 +1295,10 @@
       <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>45617</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="5">
         <v>1843.87</v>
       </c>
       <c r="F17" s="3" t="s">
@@ -1028,7 +1308,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1038,11 +1318,11 @@
       <c r="C18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>45622</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1216.86</v>
+      <c r="E18" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>10</v>
@@ -1051,7 +1331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
@@ -1061,11 +1341,11 @@
       <c r="C19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>45622</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>4439.9</v>
+      <c r="E19" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>10</v>
@@ -1074,7 +1354,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1084,10 +1364,10 @@
       <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>45624</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="5">
         <v>1843.88</v>
       </c>
       <c r="F20" s="3" t="s">
@@ -1097,7 +1377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1107,11 +1387,11 @@
       <c r="C21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>45688</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>1118.4</v>
+      <c r="E21" s="5">
+        <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>10</v>
@@ -1120,7 +1400,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
@@ -1130,10 +1410,10 @@
       <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>45695</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="5">
         <v>3296.8</v>
       </c>
       <c r="F22" s="3" t="s">
@@ -1143,7 +1423,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
@@ -1153,10 +1433,10 @@
       <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>45699</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="5">
         <v>2330</v>
       </c>
       <c r="F23" s="3" t="s">
@@ -1166,7 +1446,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1176,10 +1456,10 @@
       <c r="C24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>45702</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="5">
         <v>3296.8</v>
       </c>
       <c r="F24" s="3" t="s">
@@ -1189,7 +1469,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
@@ -1199,10 +1479,10 @@
       <c r="C25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>45705</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="5">
         <v>2541</v>
       </c>
       <c r="F25" s="3" t="s">
@@ -1212,7 +1492,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>27</v>
       </c>
@@ -1222,10 +1502,10 @@
       <c r="C26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>45709</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="5">
         <v>3296.8</v>
       </c>
       <c r="F26" s="3" t="s">
@@ -1235,7 +1515,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
@@ -1245,10 +1525,10 @@
       <c r="C27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>45712</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="5">
         <v>2541</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -1258,7 +1538,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1268,10 +1548,10 @@
       <c r="C28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>45726</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="5">
         <v>2541</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -1281,7 +1561,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
@@ -1291,10 +1571,10 @@
       <c r="C29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4">
         <v>45727</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="5">
         <v>7562.78</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -1304,7 +1584,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>27</v>
       </c>
@@ -1314,10 +1594,10 @@
       <c r="C30" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>45734</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="5">
         <v>7562.78</v>
       </c>
       <c r="F30" s="3" t="s">
@@ -1327,7 +1607,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
@@ -1337,10 +1617,10 @@
       <c r="C31" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>45734</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="5">
         <v>1154.56</v>
       </c>
       <c r="F31" s="3" t="s">
@@ -1350,7 +1630,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>27</v>
       </c>
@@ -1360,10 +1640,10 @@
       <c r="C32" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>45740</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="5">
         <v>2541</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -1373,7 +1653,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>27</v>
       </c>
@@ -1383,10 +1663,10 @@
       <c r="C33" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>45741</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="5">
         <v>7562.78</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -1396,7 +1676,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>31</v>
       </c>
@@ -1406,10 +1686,10 @@
       <c r="C34" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>45741</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="5">
         <v>1154.56</v>
       </c>
       <c r="F34" s="3" t="s">
@@ -1419,7 +1699,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>31</v>
       </c>
@@ -1429,10 +1709,10 @@
       <c r="C35" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4">
         <v>45748</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="5">
         <v>1154.56</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -1442,7 +1722,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>27</v>
       </c>
@@ -1452,10 +1732,10 @@
       <c r="C36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4">
         <v>45748</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="5">
         <v>7562.76</v>
       </c>
       <c r="F36" s="3" t="s">
@@ -1465,7 +1745,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
@@ -1475,10 +1755,10 @@
       <c r="C37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4">
         <v>45755</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="5">
         <v>1154.56</v>
       </c>
       <c r="F37" s="3" t="s">
@@ -1488,7 +1768,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
@@ -1498,10 +1778,10 @@
       <c r="C38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="4">
         <v>45761</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="5">
         <v>6169.53</v>
       </c>
       <c r="F38" s="3" t="s">
@@ -1511,7 +1791,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>31</v>
       </c>
@@ -1521,10 +1801,10 @@
       <c r="C39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="4">
         <v>45768</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="5">
         <v>3850</v>
       </c>
       <c r="F39" s="3" t="s">
@@ -1534,7 +1814,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -1544,10 +1824,10 @@
       <c r="C40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="4">
         <v>45775</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="5">
         <v>3850</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -1557,7 +1837,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>31</v>
       </c>
@@ -1567,10 +1847,10 @@
       <c r="C41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="4">
         <v>45775</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="5">
         <v>6089.41</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -1580,7 +1860,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>31</v>
       </c>
@@ -1590,10 +1870,10 @@
       <c r="C42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="4">
         <v>45782</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="5">
         <v>3800</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -1603,7 +1883,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>31</v>
       </c>
@@ -1613,10 +1893,10 @@
       <c r="C43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="4">
         <v>45789</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="5">
         <v>3800</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -1626,7 +1906,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>71</v>
       </c>
@@ -1636,10 +1916,10 @@
       <c r="C44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="4">
         <v>45789</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="5">
         <v>1143.54</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -1649,7 +1929,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -1659,10 +1939,10 @@
       <c r="C45" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="4">
         <v>45796</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="5">
         <v>2287.06</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -1672,9 +1952,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>76</v>
@@ -1682,32 +1962,34 @@
       <c r="C46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="4" t="n">
-        <v>45874</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>1326</v>
-      </c>
-      <c r="F46" s="3"/>
+      <c r="D46" s="4">
+        <v>45896</v>
+      </c>
+      <c r="E46" s="5">
+        <v>4572.62</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G46" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>45896</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>4572.62</v>
+      <c r="D47" s="4">
+        <v>45910</v>
+      </c>
+      <c r="E47" s="5">
+        <v>3663.84</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>16</v>
@@ -1716,21 +1998,21 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D48" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="D48" s="4">
         <v>45910</v>
       </c>
-      <c r="E48" s="5" t="n">
-        <v>3663.84</v>
+      <c r="E48" s="5">
+        <v>873.63</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>16</v>
@@ -1739,21 +2021,21 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>45910</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>873.63</v>
+        <v>80</v>
+      </c>
+      <c r="D49" s="4">
+        <v>45917</v>
+      </c>
+      <c r="E49" s="5">
+        <v>700</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>16</v>
@@ -1762,20 +2044,20 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>45917</v>
-      </c>
-      <c r="E50" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="D50" s="4">
+        <v>45924</v>
+      </c>
+      <c r="E50" s="5">
         <v>700</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -1785,21 +2067,21 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D51" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="D51" s="4">
         <v>45924</v>
       </c>
-      <c r="E51" s="5" t="n">
-        <v>700</v>
+      <c r="E51" s="5">
+        <v>3663.84</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>16</v>
@@ -1808,44 +2090,44 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="4">
+        <v>45947</v>
+      </c>
+      <c r="E52" s="5">
+        <v>3867.34</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D52" s="4" t="n">
-        <v>45924</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>3663.84</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A53" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>45947</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>3867.34</v>
+      <c r="D53" s="4">
+        <v>45954</v>
+      </c>
+      <c r="E53" s="5">
+        <v>2144.59</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>16</v>
@@ -1854,20 +2136,20 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>45954</v>
-      </c>
-      <c r="E54" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="D54" s="4">
+        <v>45961</v>
+      </c>
+      <c r="E54" s="5">
         <v>2144.59</v>
       </c>
       <c r="F54" s="3" t="s">
@@ -1877,20 +2159,20 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>45961</v>
-      </c>
-      <c r="E55" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="D55" s="4">
+        <v>45968</v>
+      </c>
+      <c r="E55" s="5">
         <v>2144.59</v>
       </c>
       <c r="F55" s="3" t="s">
@@ -1900,30 +2182,28 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D56" s="4" t="n">
-        <v>45968</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>2144.59</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="D56" s="4">
+        <v>45980</v>
+      </c>
+      <c r="E56" s="5">
+        <v>48213.84</v>
+      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>71</v>
       </c>
@@ -1933,10 +2213,10 @@
       <c r="C57" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="4">
         <v>45980</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="5">
         <v>4480</v>
       </c>
       <c r="F57" s="3" t="s">
@@ -1946,229 +2226,231 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>45980</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>48213.84</v>
+      <c r="D58" s="4">
+        <v>45987</v>
+      </c>
+      <c r="E58" s="5">
+        <v>33844.160000000003</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>45987</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>33844.16</v>
+        <v>94</v>
+      </c>
+      <c r="D59" s="4">
+        <v>45989</v>
+      </c>
+      <c r="E59" s="5">
+        <v>3220</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>45989</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>3220</v>
+        <v>95</v>
+      </c>
+      <c r="D60" s="4">
+        <v>45994</v>
+      </c>
+      <c r="E60" s="5">
+        <v>38740.53</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="4" t="n">
-        <v>45994</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>48208.79</v>
-      </c>
-      <c r="F61" s="3"/>
+      <c r="D61" s="4">
+        <v>46090</v>
+      </c>
+      <c r="E61" s="5">
+        <v>806.34</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G61" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D62" s="4">
+        <v>46092</v>
+      </c>
+      <c r="E62" s="5">
+        <v>2089.5700000000002</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>46090</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>806.34</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A63" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="B63" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D63" s="4" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>2089.57</v>
+      <c r="D63" s="4">
+        <v>46097</v>
+      </c>
+      <c r="E63" s="5">
+        <v>503.28</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G63" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A64" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B64" s="3" t="s">
+      <c r="D64" s="4">
+        <v>46099</v>
+      </c>
+      <c r="E64" s="5">
+        <v>2089.56</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="B65" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>46097</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>503.28</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A65" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="4">
         <v>46099</v>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>2089.56</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="E65" s="5">
+        <v>7584.01</v>
+      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="D66" s="4">
+        <v>46104</v>
+      </c>
+      <c r="E66" s="5">
+        <v>503.28</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>7584.01</v>
-      </c>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A67" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D67" s="4" t="n">
-        <v>46104</v>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>503.28</v>
+      <c r="D67" s="4">
+        <v>46105</v>
+      </c>
+      <c r="E67" s="5">
+        <v>1812.31</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>109</v>
@@ -2176,87 +2458,85 @@
       <c r="C68" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="4">
         <v>46105</v>
       </c>
-      <c r="E68" s="5" t="n">
-        <v>1812.31</v>
+      <c r="E68" s="5">
+        <v>4434.51</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D69" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="D69" s="4">
         <v>46105</v>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>4434.51</v>
+      <c r="E69" s="5">
+        <v>5466.66</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" s="4">
+        <v>46106</v>
+      </c>
+      <c r="E70" s="5">
+        <v>4646.53</v>
+      </c>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C70" s="3" t="s">
+      <c r="B71" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>46105</v>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>5466.66</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A71" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="4">
         <v>46106</v>
       </c>
-      <c r="E71" s="5" t="n">
-        <v>4646.53</v>
+      <c r="E71" s="5">
+        <v>9832.7000000000007</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>7</v>
       </c>
@@ -2266,18 +2546,20 @@
       <c r="C72" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D72" s="4" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>9832.7</v>
-      </c>
-      <c r="F72" s="3"/>
+      <c r="D72" s="4">
+        <v>46108</v>
+      </c>
+      <c r="E72" s="5">
+        <v>1470</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G72" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>71</v>
       </c>
@@ -2287,10 +2569,10 @@
       <c r="C73" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D73" s="4" t="n">
-        <v>46106</v>
-      </c>
-      <c r="E73" s="5" t="n">
+      <c r="D73" s="4">
+        <v>46111</v>
+      </c>
+      <c r="E73" s="5">
         <v>5826.6</v>
       </c>
       <c r="F73" s="3" t="s">
@@ -2300,7 +2582,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>71</v>
       </c>
@@ -2310,10 +2592,10 @@
       <c r="C74" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="E74" s="5" t="n">
+      <c r="D74" s="4">
+        <v>46112</v>
+      </c>
+      <c r="E74" s="5">
         <v>6120</v>
       </c>
       <c r="F74" s="3"/>
@@ -2321,268 +2603,268 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D75" s="4">
+        <v>46112</v>
+      </c>
+      <c r="E75" s="5">
+        <v>4434.51</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D76" s="4">
+        <v>46112</v>
+      </c>
+      <c r="E76" s="5">
+        <v>1452.13</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D77" s="4">
+        <v>46113</v>
+      </c>
+      <c r="E77" s="5">
+        <v>4646.54</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D78" s="4">
+        <v>46113</v>
+      </c>
+      <c r="E78" s="5">
+        <v>5408.64</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D79" s="4">
+        <v>46113</v>
+      </c>
+      <c r="E79" s="5">
+        <v>4434.3999999999996</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D80" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E80" s="5">
+        <v>3013.43</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="E75" s="5" t="n">
+      <c r="B81" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D81" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E81" s="5">
         <v>12150</v>
-      </c>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A76" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>1470</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A77" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>46111</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>863.1</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A78" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>46111</v>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>863.1</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A79" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>46111</v>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>5826.6</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A80" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>46111</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>19163.32</v>
-      </c>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A81" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>6120</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>11536.57</v>
+        <v>132</v>
+      </c>
+      <c r="D82" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E82" s="5">
+        <v>1057.26</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D83" s="4">
+        <v>46115</v>
+      </c>
+      <c r="E83" s="5">
+        <v>2570.4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D84" s="4">
+        <v>46116</v>
+      </c>
+      <c r="E84" s="5">
+        <v>5826.6</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D83" s="4" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>4434.51</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A84" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C84" s="3" t="s">
+      <c r="D85" s="4">
+        <v>46116</v>
+      </c>
+      <c r="E85" s="5">
+        <v>9832.7000000000007</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D84" s="4" t="n">
-        <v>46112</v>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>1452.13</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A85" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C85" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D85" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>1854</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A86" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>264.08</v>
+      <c r="D86" s="4">
+        <v>46118</v>
+      </c>
+      <c r="E86" s="5">
+        <v>870.4</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>16</v>
@@ -2591,129 +2873,235 @@
         <v>44</v>
       </c>
     </row>
-    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D87" s="4">
+        <v>46118</v>
+      </c>
+      <c r="E87" s="5">
+        <v>863.1</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D87" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>4646.54</v>
-      </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A88" s="3" t="s">
+      <c r="D88" s="4">
+        <v>46118</v>
+      </c>
+      <c r="E88" s="5">
+        <v>863.1</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B89" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D89" s="4">
+        <v>46118</v>
+      </c>
+      <c r="E89" s="5">
+        <v>1470</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D88" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>10146.52</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="89" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A89" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B89" s="3" t="s">
+      <c r="D90" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E90" s="5">
+        <v>1452.14</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="D91" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E91" s="5">
+        <v>4434.51</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D89" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>5408.64</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="90" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A90" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C90" s="3" t="s">
+      <c r="D92" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E92" s="5">
+        <v>1265.78</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D90" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>4434.4</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="91" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A91" s="3" t="s">
+      <c r="B93" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D93" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E93" s="5">
+        <v>6319.14</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>3704.66</v>
-      </c>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3" t="s">
+      <c r="B94" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D94" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E94" s="5">
+        <v>2311.84</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="92" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A92" s="6"/>
-      <c r="B92" s="7"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="8" t="n">
-        <v>448319.01</v>
-      </c>
-      <c r="F92" s="7"/>
-      <c r="G92" s="9"/>
+    <row r="95" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D95" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E95" s="5">
+        <v>1854</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D96" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E96" s="5">
+        <v>1150.8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,31 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B5608D-1CAA-4C4F-8892-5D66095BE44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr refMode="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>Funcionário</t>
   </si>
@@ -390,9 +378,6 @@
     <t>01005820.2</t>
   </si>
   <si>
-    <t>01005755.4</t>
-  </si>
-  <si>
     <t>01005876.2</t>
   </si>
   <si>
@@ -402,111 +387,115 @@
     <t>01005839.3</t>
   </si>
   <si>
+    <t>01005934.1</t>
+  </si>
+  <si>
+    <t>QUALIMMED - COM. ATAC. DE MED. E MAT. HOSPITALAR</t>
+  </si>
+  <si>
+    <t>01005765.5</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01005940.1</t>
+  </si>
+  <si>
+    <t>01005820.3</t>
+  </si>
+  <si>
+    <t>01005822.3</t>
+  </si>
+  <si>
+    <t>01005913.2</t>
+  </si>
+  <si>
+    <t>01005881.2</t>
+  </si>
+  <si>
+    <t>01005878.3</t>
+  </si>
+  <si>
+    <t>01005876.3</t>
+  </si>
+  <si>
+    <t>01005951.1</t>
+  </si>
+  <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
+  </si>
+  <si>
+    <t>01005955.1</t>
+  </si>
+  <si>
+    <t>01005923.2</t>
+  </si>
+  <si>
+    <t>01005968.1</t>
+  </si>
+  <si>
+    <t>01005934.2</t>
+  </si>
+  <si>
+    <t>01005820.4</t>
+  </si>
+  <si>
+    <t>C DE CARVALHO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01005935.2</t>
+  </si>
+  <si>
     <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
   </si>
   <si>
-    <t>01005792.3</t>
-  </si>
-  <si>
-    <t>01005836.3</t>
-  </si>
-  <si>
-    <t>01005934.1</t>
-  </si>
-  <si>
-    <t>QUALIMMED - COM. ATAC. DE MED. E MAT. HOSPITALAR</t>
-  </si>
-  <si>
-    <t>01005765.5</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01005844.3</t>
-  </si>
-  <si>
-    <t>01005940.1</t>
-  </si>
-  <si>
-    <t>01005820.3</t>
-  </si>
-  <si>
-    <t>01005822.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIDALAB COMERCIO DE ARTIGOS LABORAT E HOSP LTDA - </t>
-  </si>
-  <si>
-    <t>01005915.2</t>
-  </si>
-  <si>
-    <t>01005863.3</t>
-  </si>
-  <si>
-    <t>01005913.2</t>
-  </si>
-  <si>
-    <t>01005881.2</t>
-  </si>
-  <si>
-    <t>01005878.3</t>
-  </si>
-  <si>
-    <t>01005876.3</t>
-  </si>
-  <si>
-    <t>01005951.1</t>
-  </si>
-  <si>
-    <t>KELLEN</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
-  </si>
-  <si>
-    <t>01005955.1</t>
-  </si>
-  <si>
-    <t>MEDZ DISTRIBUIDORA HOSPITALAR E MEDICA LTDA</t>
-  </si>
-  <si>
-    <t>01005967.2</t>
-  </si>
-  <si>
-    <t>01005923.2</t>
-  </si>
-  <si>
-    <t>01005968.1</t>
+    <t>01005979.1</t>
+  </si>
+  <si>
+    <t>01005983.1</t>
+  </si>
+  <si>
+    <t>01005940.2</t>
+  </si>
+  <si>
+    <t>FARMAGUEDES COMERCIO DE PROD FARMAC. MED E HOSP LT</t>
+  </si>
+  <si>
+    <t>01005900.3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
+    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -525,8 +514,14 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -549,375 +544,112 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA0A0A0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA0A0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+  <cellXfs count="10">
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G96"/>
-  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
+  <dimension ref="A1:G97"/>
+  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="3.7109375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="12.140625" style="1"/>
+    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
+    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
+    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
+    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
+    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
+    <col max="6" min="6" style="1" width="26.28515625" customWidth="true"/>
+    <col max="7" min="7" style="1" width="3.7109375" customWidth="true"/>
+    <col max="16384" min="8" style="1" width="12.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -940,7 +672,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -950,11 +682,11 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="4" t="n">
         <v>45326</v>
       </c>
-      <c r="E2" s="5">
-        <v>9391.7800000000007</v>
+      <c r="E2" s="5" t="n">
+        <v>9391.78</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
@@ -963,7 +695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -973,10 +705,10 @@
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="4" t="n">
         <v>45346</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="5" t="n">
         <v>5418</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -986,7 +718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -996,11 +728,11 @@
       <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="4" t="n">
         <v>45350</v>
       </c>
-      <c r="E4" s="5">
-        <v>1264.8699999999999</v>
+      <c r="E4" s="5" t="n">
+        <v>1264.87</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>16</v>
@@ -1009,7 +741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -1019,10 +751,10 @@
       <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="4" t="n">
         <v>45356</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="5" t="n">
         <v>5418</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -1032,7 +764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -1042,10 +774,10 @@
       <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="4" t="n">
         <v>45362</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="5" t="n">
         <v>384</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -1055,7 +787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1065,10 +797,10 @@
       <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="n">
         <v>45364</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5" t="n">
         <v>816</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -1078,7 +810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1088,10 +820,10 @@
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="4" t="n">
         <v>45378</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="5" t="n">
         <v>816</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -1101,7 +833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -1111,10 +843,10 @@
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="4" t="n">
         <v>45463</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5" t="n">
         <v>1674.52</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -1124,7 +856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1134,10 +866,10 @@
       <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="4" t="n">
         <v>45493</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="5" t="n">
         <v>873.6</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -1147,7 +879,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -1157,10 +889,10 @@
       <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="4" t="n">
         <v>45523</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5" t="n">
         <v>873.6</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -1170,7 +902,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1180,10 +912,10 @@
       <c r="C12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="4" t="n">
         <v>45600</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -1193,7 +925,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -1203,10 +935,10 @@
       <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="4" t="n">
         <v>45607</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="5" t="n">
         <v>3204.34</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -1216,7 +948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -1226,11 +958,11 @@
       <c r="C14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="4" t="n">
         <v>45608</v>
       </c>
-      <c r="E14" s="5">
-        <v>4439.8999999999996</v>
+      <c r="E14" s="5" t="n">
+        <v>4439.9</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -1239,7 +971,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A15" s="3" t="s">
         <v>27</v>
       </c>
@@ -1249,10 +981,10 @@
       <c r="C15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="4" t="n">
         <v>45614</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -1262,7 +994,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
@@ -1272,11 +1004,11 @@
       <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="4" t="n">
         <v>45615</v>
       </c>
-      <c r="E16" s="5">
-        <v>1216.8599999999999</v>
+      <c r="E16" s="5" t="n">
+        <v>1216.86</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>10</v>
@@ -1285,7 +1017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
@@ -1295,10 +1027,10 @@
       <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="4" t="n">
         <v>45617</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="5" t="n">
         <v>1843.87</v>
       </c>
       <c r="F17" s="3" t="s">
@@ -1308,7 +1040,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1318,11 +1050,11 @@
       <c r="C18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E18" s="5">
-        <v>1216.8599999999999</v>
+      <c r="E18" s="5" t="n">
+        <v>1216.86</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>10</v>
@@ -1331,7 +1063,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
@@ -1341,11 +1073,11 @@
       <c r="C19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E19" s="5">
-        <v>4439.8999999999996</v>
+      <c r="E19" s="5" t="n">
+        <v>4439.9</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>10</v>
@@ -1354,7 +1086,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1364,10 +1096,10 @@
       <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="4" t="n">
         <v>45624</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="5" t="n">
         <v>1843.88</v>
       </c>
       <c r="F20" s="3" t="s">
@@ -1377,7 +1109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1387,11 +1119,11 @@
       <c r="C21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="4" t="n">
         <v>45688</v>
       </c>
-      <c r="E21" s="5">
-        <v>1118.4000000000001</v>
+      <c r="E21" s="5" t="n">
+        <v>1118.4</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>10</v>
@@ -1400,7 +1132,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
@@ -1410,10 +1142,10 @@
       <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="4" t="n">
         <v>45695</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="F22" s="3" t="s">
@@ -1423,7 +1155,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
@@ -1433,10 +1165,10 @@
       <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="4" t="n">
         <v>45699</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="5" t="n">
         <v>2330</v>
       </c>
       <c r="F23" s="3" t="s">
@@ -1446,7 +1178,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1456,10 +1188,10 @@
       <c r="C24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="4" t="n">
         <v>45702</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="F24" s="3" t="s">
@@ -1469,7 +1201,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
@@ -1479,10 +1211,10 @@
       <c r="C25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="4" t="n">
         <v>45705</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="F25" s="3" t="s">
@@ -1492,7 +1224,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A26" s="3" t="s">
         <v>27</v>
       </c>
@@ -1502,10 +1234,10 @@
       <c r="C26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="4" t="n">
         <v>45709</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="5" t="n">
         <v>3296.8</v>
       </c>
       <c r="F26" s="3" t="s">
@@ -1515,7 +1247,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
@@ -1525,10 +1257,10 @@
       <c r="C27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="4" t="n">
         <v>45712</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -1538,7 +1270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1548,10 +1280,10 @@
       <c r="C28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="4" t="n">
         <v>45726</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -1561,7 +1293,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
@@ -1571,10 +1303,10 @@
       <c r="C29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="4" t="n">
         <v>45727</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -1584,7 +1316,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A30" s="3" t="s">
         <v>27</v>
       </c>
@@ -1594,10 +1326,10 @@
       <c r="C30" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="4" t="n">
         <v>45734</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="F30" s="3" t="s">
@@ -1607,7 +1339,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
@@ -1617,10 +1349,10 @@
       <c r="C31" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="4" t="n">
         <v>45734</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="F31" s="3" t="s">
@@ -1630,7 +1362,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A32" s="3" t="s">
         <v>27</v>
       </c>
@@ -1640,10 +1372,10 @@
       <c r="C32" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="4" t="n">
         <v>45740</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="5" t="n">
         <v>2541</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -1653,7 +1385,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A33" s="3" t="s">
         <v>27</v>
       </c>
@@ -1663,10 +1395,10 @@
       <c r="C33" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="5" t="n">
         <v>7562.78</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -1676,7 +1408,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A34" s="3" t="s">
         <v>31</v>
       </c>
@@ -1686,10 +1418,10 @@
       <c r="C34" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="F34" s="3" t="s">
@@ -1699,7 +1431,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A35" s="3" t="s">
         <v>31</v>
       </c>
@@ -1709,10 +1441,10 @@
       <c r="C35" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -1722,7 +1454,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A36" s="3" t="s">
         <v>27</v>
       </c>
@@ -1732,10 +1464,10 @@
       <c r="C36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="5" t="n">
         <v>7562.76</v>
       </c>
       <c r="F36" s="3" t="s">
@@ -1745,7 +1477,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
@@ -1755,10 +1487,10 @@
       <c r="C37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="4" t="n">
         <v>45755</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="5" t="n">
         <v>1154.56</v>
       </c>
       <c r="F37" s="3" t="s">
@@ -1768,7 +1500,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
@@ -1778,10 +1510,10 @@
       <c r="C38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="4" t="n">
         <v>45761</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="5" t="n">
         <v>6169.53</v>
       </c>
       <c r="F38" s="3" t="s">
@@ -1791,7 +1523,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A39" s="3" t="s">
         <v>31</v>
       </c>
@@ -1801,10 +1533,10 @@
       <c r="C39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="4" t="n">
         <v>45768</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="5" t="n">
         <v>3850</v>
       </c>
       <c r="F39" s="3" t="s">
@@ -1814,7 +1546,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -1824,10 +1556,10 @@
       <c r="C40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="5" t="n">
         <v>3850</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -1837,7 +1569,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A41" s="3" t="s">
         <v>31</v>
       </c>
@@ -1847,10 +1579,10 @@
       <c r="C41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="5" t="n">
         <v>6089.41</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -1860,7 +1592,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A42" s="3" t="s">
         <v>31</v>
       </c>
@@ -1870,10 +1602,10 @@
       <c r="C42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="5" t="n">
         <v>3800</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -1883,7 +1615,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A43" s="3" t="s">
         <v>31</v>
       </c>
@@ -1893,10 +1625,10 @@
       <c r="C43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="5" t="n">
         <v>3800</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -1906,7 +1638,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A44" s="3" t="s">
         <v>71</v>
       </c>
@@ -1916,10 +1648,10 @@
       <c r="C44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="5" t="n">
         <v>1143.54</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -1929,7 +1661,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -1939,10 +1671,10 @@
       <c r="C45" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="4" t="n">
         <v>45796</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="5" t="n">
         <v>2287.06</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -1952,7 +1684,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A46" s="3" t="s">
         <v>27</v>
       </c>
@@ -1962,10 +1694,10 @@
       <c r="C46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="4" t="n">
         <v>45896</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="5" t="n">
         <v>4572.62</v>
       </c>
       <c r="F46" s="3" t="s">
@@ -1975,7 +1707,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A47" s="3" t="s">
         <v>27</v>
       </c>
@@ -1985,10 +1717,10 @@
       <c r="C47" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="4" t="n">
         <v>45910</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="5" t="n">
         <v>3663.84</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -1998,7 +1730,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A48" s="3" t="s">
         <v>27</v>
       </c>
@@ -2008,10 +1740,10 @@
       <c r="C48" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="4" t="n">
         <v>45910</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="5" t="n">
         <v>873.63</v>
       </c>
       <c r="F48" s="3" t="s">
@@ -2021,7 +1753,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A49" s="3" t="s">
         <v>27</v>
       </c>
@@ -2031,10 +1763,10 @@
       <c r="C49" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="4" t="n">
         <v>45917</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="5" t="n">
         <v>700</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -2044,7 +1776,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A50" s="3" t="s">
         <v>27</v>
       </c>
@@ -2054,10 +1786,10 @@
       <c r="C50" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="4" t="n">
         <v>45924</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="5" t="n">
         <v>700</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -2067,7 +1799,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A51" s="3" t="s">
         <v>27</v>
       </c>
@@ -2077,10 +1809,10 @@
       <c r="C51" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="4" t="n">
         <v>45924</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="5" t="n">
         <v>3663.84</v>
       </c>
       <c r="F51" s="3" t="s">
@@ -2090,7 +1822,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A52" s="3" t="s">
         <v>83</v>
       </c>
@@ -2100,10 +1832,10 @@
       <c r="C52" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="4" t="n">
         <v>45947</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="5" t="n">
         <v>3867.34</v>
       </c>
       <c r="F52" s="3" t="s">
@@ -2113,7 +1845,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A53" s="3" t="s">
         <v>83</v>
       </c>
@@ -2123,10 +1855,10 @@
       <c r="C53" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="4" t="n">
         <v>45954</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="F53" s="3" t="s">
@@ -2136,7 +1868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A54" s="3" t="s">
         <v>83</v>
       </c>
@@ -2146,10 +1878,10 @@
       <c r="C54" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="4" t="n">
         <v>45961</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="F54" s="3" t="s">
@@ -2159,7 +1891,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A55" s="3" t="s">
         <v>83</v>
       </c>
@@ -2169,10 +1901,10 @@
       <c r="C55" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="4" t="n">
         <v>45968</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E55" s="5" t="n">
         <v>2144.59</v>
       </c>
       <c r="F55" s="3" t="s">
@@ -2182,7 +1914,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A56" s="3" t="s">
         <v>83</v>
       </c>
@@ -2192,10 +1924,10 @@
       <c r="C56" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="4" t="n">
         <v>45980</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="5" t="n">
         <v>48213.84</v>
       </c>
       <c r="F56" s="3"/>
@@ -2203,7 +1935,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A57" s="3" t="s">
         <v>71</v>
       </c>
@@ -2213,10 +1945,10 @@
       <c r="C57" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="4" t="n">
         <v>45980</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="5" t="n">
         <v>4480</v>
       </c>
       <c r="F57" s="3" t="s">
@@ -2226,7 +1958,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A58" s="3" t="s">
         <v>83</v>
       </c>
@@ -2236,18 +1968,18 @@
       <c r="C58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="4" t="n">
         <v>45987</v>
       </c>
-      <c r="E58" s="5">
-        <v>33844.160000000003</v>
+      <c r="E58" s="5" t="n">
+        <v>33844.16</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A59" s="3" t="s">
         <v>71</v>
       </c>
@@ -2257,10 +1989,10 @@
       <c r="C59" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="4" t="n">
         <v>45989</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="5" t="n">
         <v>3220</v>
       </c>
       <c r="F59" s="3"/>
@@ -2268,7 +2000,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A60" s="3" t="s">
         <v>83</v>
       </c>
@@ -2278,10 +2010,10 @@
       <c r="C60" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="4" t="n">
         <v>45994</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="5" t="n">
         <v>38740.53</v>
       </c>
       <c r="F60" s="3"/>
@@ -2289,7 +2021,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A61" s="3" t="s">
         <v>13</v>
       </c>
@@ -2299,10 +2031,10 @@
       <c r="C61" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="4" t="n">
         <v>46090</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="5" t="n">
         <v>806.34</v>
       </c>
       <c r="F61" s="3" t="s">
@@ -2312,7 +2044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A62" s="3" t="s">
         <v>98</v>
       </c>
@@ -2322,11 +2054,11 @@
       <c r="C62" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="4" t="n">
         <v>46092</v>
       </c>
-      <c r="E62" s="5">
-        <v>2089.5700000000002</v>
+      <c r="E62" s="5" t="n">
+        <v>2089.57</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>16</v>
@@ -2335,7 +2067,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A63" s="3" t="s">
         <v>13</v>
       </c>
@@ -2345,10 +2077,10 @@
       <c r="C63" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="4" t="n">
         <v>46097</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="5" t="n">
         <v>503.28</v>
       </c>
       <c r="F63" s="3" t="s">
@@ -2358,7 +2090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A64" s="3" t="s">
         <v>98</v>
       </c>
@@ -2368,10 +2100,10 @@
       <c r="C64" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="5" t="n">
         <v>2089.56</v>
       </c>
       <c r="F64" s="3" t="s">
@@ -2381,7 +2113,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A65" s="3" t="s">
         <v>98</v>
       </c>
@@ -2391,10 +2123,10 @@
       <c r="C65" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E65" s="5" t="n">
         <v>7584.01</v>
       </c>
       <c r="F65" s="3"/>
@@ -2402,7 +2134,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A66" s="3" t="s">
         <v>13</v>
       </c>
@@ -2412,10 +2144,10 @@
       <c r="C66" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="4" t="n">
         <v>46104</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E66" s="5" t="n">
         <v>503.28</v>
       </c>
       <c r="F66" s="3" t="s">
@@ -2425,7 +2157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A67" s="3" t="s">
         <v>27</v>
       </c>
@@ -2435,10 +2167,10 @@
       <c r="C67" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E67" s="5" t="n">
         <v>1812.31</v>
       </c>
       <c r="F67" s="3" t="s">
@@ -2448,7 +2180,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A68" s="3" t="s">
         <v>98</v>
       </c>
@@ -2458,10 +2190,10 @@
       <c r="C68" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E68" s="5" t="n">
         <v>4434.51</v>
       </c>
       <c r="F68" s="3" t="s">
@@ -2471,7 +2203,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A69" s="3" t="s">
         <v>7</v>
       </c>
@@ -2481,10 +2213,10 @@
       <c r="C69" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="5" t="n">
         <v>5466.66</v>
       </c>
       <c r="F69" s="3" t="s">
@@ -2494,7 +2226,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A70" s="3" t="s">
         <v>98</v>
       </c>
@@ -2504,10 +2236,10 @@
       <c r="C70" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="4" t="n">
         <v>46106</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E70" s="5" t="n">
         <v>4646.53</v>
       </c>
       <c r="F70" s="3"/>
@@ -2515,7 +2247,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A71" s="3" t="s">
         <v>7</v>
       </c>
@@ -2525,18 +2257,18 @@
       <c r="C71" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="4" t="n">
         <v>46106</v>
       </c>
-      <c r="E71" s="5">
-        <v>9832.7000000000007</v>
+      <c r="E71" s="5" t="n">
+        <v>9832.7</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A72" s="3" t="s">
         <v>7</v>
       </c>
@@ -2546,10 +2278,10 @@
       <c r="C72" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="4" t="n">
         <v>46108</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="5" t="n">
         <v>1470</v>
       </c>
       <c r="F72" s="3" t="s">
@@ -2559,7 +2291,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A73" s="3" t="s">
         <v>71</v>
       </c>
@@ -2569,10 +2301,10 @@
       <c r="C73" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73" s="4" t="n">
         <v>46111</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E73" s="5" t="n">
         <v>5826.6</v>
       </c>
       <c r="F73" s="3" t="s">
@@ -2582,97 +2314,99 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A74" s="3" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="4" t="n">
         <v>46112</v>
       </c>
-      <c r="E74" s="5">
-        <v>6120</v>
-      </c>
-      <c r="F74" s="3"/>
+      <c r="E74" s="5" t="n">
+        <v>4434.51</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G74" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A75" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="4" t="n">
         <v>46112</v>
       </c>
-      <c r="E75" s="5">
-        <v>4434.51</v>
+      <c r="E75" s="5" t="n">
+        <v>1452.13</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A76" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D76" s="4">
-        <v>46112</v>
-      </c>
-      <c r="E76" s="5">
-        <v>1452.13</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="D76" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>4646.54</v>
+      </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A77" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D77" s="4">
-        <v>46113</v>
-      </c>
-      <c r="E77" s="5">
-        <v>4646.54</v>
-      </c>
-      <c r="F77" s="3"/>
+      <c r="D77" s="4" t="n">
+        <v>46114</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>3013.43</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G77" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A78" s="3" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>125</v>
@@ -2680,101 +2414,99 @@
       <c r="C78" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D78" s="4">
-        <v>46113</v>
-      </c>
-      <c r="E78" s="5">
-        <v>5408.64</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="D78" s="4" t="n">
+        <v>46114</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>12150</v>
+      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A79" s="3" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D79" s="4">
-        <v>46113</v>
-      </c>
-      <c r="E79" s="5">
-        <v>4434.3999999999996</v>
+        <v>128</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>2570.4</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A80" s="3" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D80" s="4">
-        <v>46114</v>
-      </c>
-      <c r="E80" s="5">
-        <v>3013.43</v>
+        <v>129</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>46116</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>5826.6</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A81" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D81" s="4">
-        <v>46114</v>
-      </c>
-      <c r="E81" s="5">
-        <v>12150</v>
+      <c r="D81" s="4" t="n">
+        <v>46116</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>9832.7</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A82" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D82" s="4">
-        <v>46114</v>
-      </c>
-      <c r="E82" s="5">
-        <v>1057.26</v>
+      <c r="D82" s="4" t="n">
+        <v>46118</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>863.1</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>16</v>
@@ -2783,134 +2515,136 @@
         <v>44</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A83" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>46118</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A84" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D83" s="4">
-        <v>46115</v>
-      </c>
-      <c r="E83" s="5">
-        <v>2570.4</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G83" s="3" t="s">
+      <c r="D84" s="4" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>1452.14</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C84" s="3" t="s">
+    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A85" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D84" s="4">
-        <v>46116</v>
-      </c>
-      <c r="E84" s="5">
-        <v>5826.6</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="4" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>4434.51</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A86" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D85" s="4">
-        <v>46116</v>
-      </c>
-      <c r="E85" s="5">
-        <v>9832.7000000000007</v>
-      </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B86" s="3" t="s">
+      <c r="D86" s="4" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>1265.78</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A87" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="B87" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="D86" s="4">
-        <v>46118</v>
-      </c>
-      <c r="E86" s="5">
-        <v>870.4</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D87" s="4">
-        <v>46118</v>
-      </c>
-      <c r="E87" s="5">
-        <v>863.1</v>
+      <c r="D87" s="4" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>6319.14</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A88" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D88" s="4">
-        <v>46118</v>
-      </c>
-      <c r="E88" s="5">
-        <v>863.1</v>
+      <c r="D88" s="4" t="n">
+        <v>46120</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>1854</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>16</v>
@@ -2919,101 +2653,101 @@
         <v>44</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A89" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D89" s="4">
-        <v>46118</v>
-      </c>
-      <c r="E89" s="5">
-        <v>1470</v>
+      <c r="D89" s="4" t="n">
+        <v>46120</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>1150.8</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A90" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D90" s="4">
-        <v>46119</v>
-      </c>
-      <c r="E90" s="5">
-        <v>1452.14</v>
+      <c r="D90" s="4" t="n">
+        <v>46121</v>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>3013.43</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="91" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A91" s="3" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D91" s="4">
-        <v>46119</v>
-      </c>
-      <c r="E91" s="5">
-        <v>4434.51</v>
+      <c r="D91" s="4" t="n">
+        <v>46121</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>5826.6</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A92" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D92" s="4">
-        <v>46119</v>
-      </c>
-      <c r="E92" s="5">
-        <v>1265.78</v>
+        <v>144</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>46121</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>3284.65</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A93" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>145</v>
@@ -3021,87 +2755,100 @@
       <c r="C93" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D93" s="4">
-        <v>46119</v>
-      </c>
-      <c r="E93" s="5">
-        <v>6319.14</v>
+      <c r="D93" s="4" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>3316.11</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A94" s="3" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D94" s="4">
-        <v>46120</v>
-      </c>
-      <c r="E94" s="5">
-        <v>2311.84</v>
-      </c>
-      <c r="F94" s="3"/>
+      <c r="D94" s="4" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>10282.5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G94" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A95" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D95" s="4">
-        <v>46120</v>
-      </c>
-      <c r="E95" s="5">
-        <v>1854</v>
+        <v>148</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>2570.4</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A96" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D96" s="4">
-        <v>46120</v>
-      </c>
-      <c r="E96" s="5">
-        <v>1150.8</v>
+      <c r="D96" s="4" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>1610.5</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>44</v>
       </c>
     </row>
+    <row r="97" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A97" s="6"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="8" t="n">
+        <v>431176.55</v>
+      </c>
+      <c r="F97" s="7"/>
+      <c r="G97" s="9"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="default" cellComments="none"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
   <si>
     <t>Funcionário</t>
   </si>
@@ -252,15 +252,6 @@
     <t>01004522.2</t>
   </si>
   <si>
-    <t>01004617.1</t>
-  </si>
-  <si>
-    <t>01004617.2</t>
-  </si>
-  <si>
-    <t>01004617.3</t>
-  </si>
-  <si>
     <t>01004522.3</t>
   </si>
   <si>
@@ -282,18 +273,18 @@
     <t>01004900.4</t>
   </si>
   <si>
+    <t>BR MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005075.3</t>
+  </si>
+  <si>
     <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
   </si>
   <si>
     <t>01005217.1BPBP</t>
   </si>
   <si>
-    <t>BR MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005075.3</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
@@ -408,33 +399,27 @@
     <t>01005822.3</t>
   </si>
   <si>
-    <t>01005913.2</t>
-  </si>
-  <si>
     <t>01005881.2</t>
   </si>
   <si>
     <t>01005878.3</t>
   </si>
   <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
+  </si>
+  <si>
+    <t>01005955.1</t>
+  </si>
+  <si>
+    <t>01005951.1</t>
+  </si>
+  <si>
     <t>01005876.3</t>
   </si>
   <si>
-    <t>01005951.1</t>
-  </si>
-  <si>
-    <t>KELLEN</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
-  </si>
-  <si>
-    <t>01005955.1</t>
-  </si>
-  <si>
-    <t>01005923.2</t>
-  </si>
-  <si>
     <t>01005968.1</t>
   </si>
   <si>
@@ -444,10 +429,10 @@
     <t>01005820.4</t>
   </si>
   <si>
-    <t>C DE CARVALHO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01005935.2</t>
+    <t>01005940.2</t>
+  </si>
+  <si>
+    <t>01005983.1</t>
   </si>
   <si>
     <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
@@ -456,16 +441,34 @@
     <t>01005979.1</t>
   </si>
   <si>
-    <t>01005983.1</t>
-  </si>
-  <si>
-    <t>01005940.2</t>
+    <t>01005863.4</t>
+  </si>
+  <si>
+    <t>01005913.3</t>
   </si>
   <si>
     <t>FARMAGUEDES COMERCIO DE PROD FARMAC. MED E HOSP LT</t>
   </si>
   <si>
-    <t>01005900.3</t>
+    <t>01005950.2</t>
+  </si>
+  <si>
+    <t>01005822.4</t>
+  </si>
+  <si>
+    <t>01005955.2</t>
+  </si>
+  <si>
+    <t>01005951.2</t>
+  </si>
+  <si>
+    <t>01005876.4</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA PARNAIBA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006002.1</t>
   </si>
 </sst>
 </file>
@@ -636,7 +639,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
@@ -1741,10 +1744,10 @@
         <v>79</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>45910</v>
+        <v>45924</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>873.63</v>
+        <v>3663.84</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>16</v>
@@ -1755,88 +1758,88 @@
     </row>
     <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A49" s="3" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>45917</v>
+        <v>45947</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>700</v>
+        <v>3867.34</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A50" s="3" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>45924</v>
+        <v>45954</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>700</v>
+        <v>2144.59</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A51" s="3" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>45924</v>
+        <v>45961</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>3663.84</v>
+        <v>2144.59</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A52" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>85</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>45947</v>
+        <v>45968</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>3867.34</v>
+        <v>2144.59</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>16</v>
@@ -1847,224 +1850,222 @@
     </row>
     <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A53" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>45954</v>
+        <v>45980</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2144.59</v>
+        <v>4480</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A54" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>45961</v>
+        <v>45980</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2144.59</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>48213.84</v>
+      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A55" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>45968</v>
+        <v>45987</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2144.59</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>33844.16</v>
+      </c>
+      <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A56" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>45980</v>
+        <v>45989</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>48213.84</v>
+        <v>3220</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A57" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>92</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>45980</v>
+        <v>45994</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>4480</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>38740.53</v>
+      </c>
+      <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A58" s="3" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>45987</v>
+        <v>46090</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>33844.16</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>806.34</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G58" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A59" s="3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>45989</v>
+        <v>46092</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>3220</v>
-      </c>
-      <c r="F59" s="3"/>
+        <v>2089.57</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G59" s="3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A60" s="3" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>45994</v>
+        <v>46097</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>38740.53</v>
-      </c>
-      <c r="F60" s="3"/>
+        <v>503.28</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G60" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A61" s="3" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>46090</v>
+        <v>46099</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>806.34</v>
+        <v>2089.56</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A62" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>7584.01</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>46092</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>2089.57</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
@@ -2072,13 +2073,13 @@
         <v>13</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>503.28</v>
@@ -2092,115 +2093,113 @@
     </row>
     <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A64" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2089.56</v>
+        <v>1812.31</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A65" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>7584.01</v>
-      </c>
-      <c r="F65" s="3"/>
+        <v>4434.51</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G65" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A66" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>503.28</v>
+        <v>5466.66</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A67" s="3" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1812.31</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>4646.53</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A68" s="3" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>4434.51</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>9832.7</v>
+      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
@@ -2208,354 +2207,358 @@
         <v>7</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>5466.66</v>
+        <v>1470</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A70" s="3" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>4646.53</v>
-      </c>
-      <c r="F70" s="3"/>
+        <v>5826.6</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G70" s="3" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A71" s="3" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>9832.7</v>
-      </c>
-      <c r="F71" s="3"/>
+        <v>4434.51</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G71" s="3" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A72" s="3" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1470</v>
+        <v>1452.13</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A73" s="3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>5826.6</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>4646.54</v>
+      </c>
+      <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A74" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>4434.51</v>
+        <v>3013.43</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A75" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1452.13</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>12150</v>
+      </c>
+      <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A76" s="3" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>4646.54</v>
-      </c>
-      <c r="F76" s="3"/>
+        <v>2570.4</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G76" s="3" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A77" s="3" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3013.43</v>
+        <v>5826.6</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A78" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>12150</v>
+        <v>9832.7</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A79" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>46115</v>
+        <v>46118</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2570.4</v>
+        <v>1470</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A80" s="3" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>46116</v>
+        <v>46119</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>5826.6</v>
+        <v>1452.14</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A81" s="3" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>46116</v>
+        <v>46119</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>9832.7</v>
-      </c>
-      <c r="F81" s="3"/>
+        <v>6319.14</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G81" s="3" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A82" s="3" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>863.1</v>
+        <v>1265.78</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
     </row>
     <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A83" s="3" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1470</v>
+        <v>4434.51</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A84" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1452.14</v>
+        <v>1150.8</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>44</v>
@@ -2563,290 +2566,311 @@
     </row>
     <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A85" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>46121</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>3013.43</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>4434.51</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A86" s="3" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1265.78</v>
+        <v>5826.6</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A87" s="3" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>6319.14</v>
+        <v>2570.4</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>111</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A88" s="3" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>139</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1854</v>
+        <v>10282.5</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
     </row>
     <row r="89" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A89" s="3" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1150.8</v>
+        <v>3316.11</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A90" s="3" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>3013.43</v>
+        <v>863.1</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A91" s="3" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>5826.6</v>
+        <v>863.1</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A92" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>46121</v>
+        <v>46126</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>3284.65</v>
+        <v>707.78</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A93" s="3" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>3316.11</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>10</v>
-      </c>
+        <v>9832.7</v>
+      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A94" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>147</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>10282.5</v>
+        <v>3150</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="95" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A95" s="3" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>148</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2570.4</v>
+        <v>1265.78</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
     </row>
     <row r="96" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A96" s="3" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="D96" s="4" t="n">
+        <v>46126</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>4434.51</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A97" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D96" s="4" t="n">
-        <v>46122</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>1610.5</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="97" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A97" s="6"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="8" t="n">
-        <v>431176.55</v>
-      </c>
-      <c r="F97" s="7"/>
-      <c r="G97" s="9"/>
+      <c r="C97" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>46126</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A98" s="6"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="8" t="n">
+        <v>444507.64</v>
+      </c>
+      <c r="F98" s="7"/>
+      <c r="G98" s="9"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD670C15-506C-4B5C-B46B-A5C4F0919AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="152">
   <si>
     <t>Funcionário</t>
   </si>
@@ -474,31 +486,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,14 +528,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -547,112 +552,375 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
-  <dimension ref="A1:G98"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G97"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
-    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
-    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
-    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
-    <col max="6" min="6" style="1" width="26.28515625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="3.7109375" customWidth="true"/>
-    <col max="16384" min="8" style="1" width="12.140625"/>
+    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -675,7 +943,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -685,11 +953,11 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>45326</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>9391.78</v>
+      <c r="E2" s="5">
+        <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
@@ -698,7 +966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -708,10 +976,10 @@
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>45346</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5">
         <v>5418</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -721,7 +989,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -731,11 +999,11 @@
       <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>45350</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1264.87</v>
+      <c r="E4" s="5">
+        <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>16</v>
@@ -744,7 +1012,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -754,10 +1022,10 @@
       <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>45356</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5">
         <v>5418</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -767,7 +1035,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -777,10 +1045,10 @@
       <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>45362</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5">
         <v>384</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -790,7 +1058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -800,10 +1068,10 @@
       <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>45364</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5">
         <v>816</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -813,7 +1081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -823,10 +1091,10 @@
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>45378</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5">
         <v>816</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -836,7 +1104,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -846,10 +1114,10 @@
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>45463</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5">
         <v>1674.52</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -859,7 +1127,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -869,10 +1137,10 @@
       <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>45493</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5">
         <v>873.6</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -882,7 +1150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -892,10 +1160,10 @@
       <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>45523</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5">
         <v>873.6</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -905,7 +1173,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -915,10 +1183,10 @@
       <c r="C12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>45600</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5">
         <v>2000</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -928,7 +1196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -938,10 +1206,10 @@
       <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>45607</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5">
         <v>3204.34</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -951,7 +1219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -961,11 +1229,11 @@
       <c r="C14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>45608</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4439.9</v>
+      <c r="E14" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -974,7 +1242,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>27</v>
       </c>
@@ -984,10 +1252,10 @@
       <c r="C15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>45614</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="5">
         <v>2000</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -997,7 +1265,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
@@ -1007,11 +1275,11 @@
       <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>45615</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>1216.86</v>
+      <c r="E16" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>10</v>
@@ -1020,7 +1288,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>27</v>
       </c>
@@ -1030,10 +1298,10 @@
       <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>45617</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="5">
         <v>1843.87</v>
       </c>
       <c r="F17" s="3" t="s">
@@ -1043,7 +1311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1053,11 +1321,11 @@
       <c r="C18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>45622</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1216.86</v>
+      <c r="E18" s="5">
+        <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>10</v>
@@ -1066,7 +1334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
@@ -1076,11 +1344,11 @@
       <c r="C19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>45622</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>4439.9</v>
+      <c r="E19" s="5">
+        <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>10</v>
@@ -1089,7 +1357,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1099,10 +1367,10 @@
       <c r="C20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>45624</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="5">
         <v>1843.88</v>
       </c>
       <c r="F20" s="3" t="s">
@@ -1112,7 +1380,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1122,11 +1390,11 @@
       <c r="C21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>45688</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>1118.4</v>
+      <c r="E21" s="5">
+        <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>10</v>
@@ -1135,7 +1403,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
@@ -1145,10 +1413,10 @@
       <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>45695</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="5">
         <v>3296.8</v>
       </c>
       <c r="F22" s="3" t="s">
@@ -1158,7 +1426,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
@@ -1168,10 +1436,10 @@
       <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>45699</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="5">
         <v>2330</v>
       </c>
       <c r="F23" s="3" t="s">
@@ -1181,7 +1449,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1191,10 +1459,10 @@
       <c r="C24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>45702</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="5">
         <v>3296.8</v>
       </c>
       <c r="F24" s="3" t="s">
@@ -1204,7 +1472,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
@@ -1214,10 +1482,10 @@
       <c r="C25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>45705</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="5">
         <v>2541</v>
       </c>
       <c r="F25" s="3" t="s">
@@ -1227,7 +1495,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>27</v>
       </c>
@@ -1237,10 +1505,10 @@
       <c r="C26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>45709</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="5">
         <v>3296.8</v>
       </c>
       <c r="F26" s="3" t="s">
@@ -1250,7 +1518,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
@@ -1260,10 +1528,10 @@
       <c r="C27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>45712</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="5">
         <v>2541</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -1273,7 +1541,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1283,10 +1551,10 @@
       <c r="C28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>45726</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="5">
         <v>2541</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -1296,7 +1564,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
@@ -1306,10 +1574,10 @@
       <c r="C29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4">
         <v>45727</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="5">
         <v>7562.78</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -1319,7 +1587,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>27</v>
       </c>
@@ -1329,10 +1597,10 @@
       <c r="C30" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>45734</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="5">
         <v>7562.78</v>
       </c>
       <c r="F30" s="3" t="s">
@@ -1342,7 +1610,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
@@ -1352,10 +1620,10 @@
       <c r="C31" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>45734</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="5">
         <v>1154.56</v>
       </c>
       <c r="F31" s="3" t="s">
@@ -1365,7 +1633,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>27</v>
       </c>
@@ -1375,10 +1643,10 @@
       <c r="C32" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>45740</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="5">
         <v>2541</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -1388,7 +1656,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>27</v>
       </c>
@@ -1398,10 +1666,10 @@
       <c r="C33" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>45741</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="5">
         <v>7562.78</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -1411,7 +1679,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>31</v>
       </c>
@@ -1421,10 +1689,10 @@
       <c r="C34" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>45741</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="5">
         <v>1154.56</v>
       </c>
       <c r="F34" s="3" t="s">
@@ -1434,7 +1702,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>31</v>
       </c>
@@ -1444,10 +1712,10 @@
       <c r="C35" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4">
         <v>45748</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="5">
         <v>1154.56</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -1457,7 +1725,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>27</v>
       </c>
@@ -1467,10 +1735,10 @@
       <c r="C36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4">
         <v>45748</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="5">
         <v>7562.76</v>
       </c>
       <c r="F36" s="3" t="s">
@@ -1480,7 +1748,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
@@ -1490,10 +1758,10 @@
       <c r="C37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4">
         <v>45755</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="5">
         <v>1154.56</v>
       </c>
       <c r="F37" s="3" t="s">
@@ -1503,7 +1771,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
@@ -1513,10 +1781,10 @@
       <c r="C38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="4">
         <v>45761</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="5">
         <v>6169.53</v>
       </c>
       <c r="F38" s="3" t="s">
@@ -1526,7 +1794,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>31</v>
       </c>
@@ -1536,10 +1804,10 @@
       <c r="C39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="4">
         <v>45768</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="5">
         <v>3850</v>
       </c>
       <c r="F39" s="3" t="s">
@@ -1549,7 +1817,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -1559,10 +1827,10 @@
       <c r="C40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="4">
         <v>45775</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="5">
         <v>3850</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -1572,7 +1840,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>31</v>
       </c>
@@ -1582,10 +1850,10 @@
       <c r="C41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="4">
         <v>45775</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="5">
         <v>6089.41</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -1595,7 +1863,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>31</v>
       </c>
@@ -1605,10 +1873,10 @@
       <c r="C42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="4">
         <v>45782</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="5">
         <v>3800</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -1618,7 +1886,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>31</v>
       </c>
@@ -1628,10 +1896,10 @@
       <c r="C43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="4">
         <v>45789</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="5">
         <v>3800</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -1641,7 +1909,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>71</v>
       </c>
@@ -1651,10 +1919,10 @@
       <c r="C44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="4">
         <v>45789</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="5">
         <v>1143.54</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -1664,7 +1932,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -1674,10 +1942,10 @@
       <c r="C45" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="4">
         <v>45796</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="5">
         <v>2287.06</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -1687,7 +1955,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>27</v>
       </c>
@@ -1697,10 +1965,10 @@
       <c r="C46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="4">
         <v>45896</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="5">
         <v>4572.62</v>
       </c>
       <c r="F46" s="3" t="s">
@@ -1710,7 +1978,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>27</v>
       </c>
@@ -1720,10 +1988,10 @@
       <c r="C47" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="4">
         <v>45910</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="5">
         <v>3663.84</v>
       </c>
       <c r="F47" s="3" t="s">
@@ -1733,7 +2001,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>27</v>
       </c>
@@ -1743,10 +2011,10 @@
       <c r="C48" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="4">
         <v>45924</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="5">
         <v>3663.84</v>
       </c>
       <c r="F48" s="3" t="s">
@@ -1756,7 +2024,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>80</v>
       </c>
@@ -1766,10 +2034,10 @@
       <c r="C49" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="4">
         <v>45947</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="5">
         <v>3867.34</v>
       </c>
       <c r="F49" s="3" t="s">
@@ -1779,7 +2047,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>80</v>
       </c>
@@ -1789,10 +2057,10 @@
       <c r="C50" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="4">
         <v>45954</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="5">
         <v>2144.59</v>
       </c>
       <c r="F50" s="3" t="s">
@@ -1802,7 +2070,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>80</v>
       </c>
@@ -1812,10 +2080,10 @@
       <c r="C51" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="4">
         <v>45961</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="5">
         <v>2144.59</v>
       </c>
       <c r="F51" s="3" t="s">
@@ -1825,7 +2093,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>80</v>
       </c>
@@ -1835,10 +2103,10 @@
       <c r="C52" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="4">
         <v>45968</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="5">
         <v>2144.59</v>
       </c>
       <c r="F52" s="3" t="s">
@@ -1848,7 +2116,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>71</v>
       </c>
@@ -1858,10 +2126,10 @@
       <c r="C53" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="4">
         <v>45980</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E53" s="5">
         <v>4480</v>
       </c>
       <c r="F53" s="3" t="s">
@@ -1871,7 +2139,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>80</v>
       </c>
@@ -1881,10 +2149,10 @@
       <c r="C54" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="4">
         <v>45980</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E54" s="5">
         <v>48213.84</v>
       </c>
       <c r="F54" s="3"/>
@@ -1892,7 +2160,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>80</v>
       </c>
@@ -1902,18 +2170,18 @@
       <c r="C55" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="4">
         <v>45987</v>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>33844.16</v>
+      <c r="E55" s="5">
+        <v>33844.160000000003</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>71</v>
       </c>
@@ -1923,10 +2191,10 @@
       <c r="C56" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="4">
         <v>45989</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="5">
         <v>3220</v>
       </c>
       <c r="F56" s="3"/>
@@ -1934,7 +2202,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>80</v>
       </c>
@@ -1944,10 +2212,10 @@
       <c r="C57" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="4">
         <v>45994</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="5">
         <v>38740.53</v>
       </c>
       <c r="F57" s="3"/>
@@ -1955,7 +2223,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>13</v>
       </c>
@@ -1965,10 +2233,10 @@
       <c r="C58" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="4">
         <v>46090</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="5">
         <v>806.34</v>
       </c>
       <c r="F58" s="3" t="s">
@@ -1978,7 +2246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>95</v>
       </c>
@@ -1988,11 +2256,11 @@
       <c r="C59" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="4">
         <v>46092</v>
       </c>
-      <c r="E59" s="5" t="n">
-        <v>2089.57</v>
+      <c r="E59" s="5">
+        <v>2089.5700000000002</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>16</v>
@@ -2001,7 +2269,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>13</v>
       </c>
@@ -2011,10 +2279,10 @@
       <c r="C60" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="4">
         <v>46097</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="5">
         <v>503.28</v>
       </c>
       <c r="F60" s="3" t="s">
@@ -2024,7 +2292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>95</v>
       </c>
@@ -2034,10 +2302,10 @@
       <c r="C61" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="4">
         <v>46099</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="5">
         <v>2089.56</v>
       </c>
       <c r="F61" s="3" t="s">
@@ -2047,7 +2315,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>95</v>
       </c>
@@ -2057,10 +2325,10 @@
       <c r="C62" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="4">
         <v>46099</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E62" s="5">
         <v>7584.01</v>
       </c>
       <c r="F62" s="3"/>
@@ -2068,7 +2336,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>13</v>
       </c>
@@ -2078,10 +2346,10 @@
       <c r="C63" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="4">
         <v>46104</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="5">
         <v>503.28</v>
       </c>
       <c r="F63" s="3" t="s">
@@ -2091,7 +2359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>27</v>
       </c>
@@ -2101,10 +2369,10 @@
       <c r="C64" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="4">
         <v>46105</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="5">
         <v>1812.31</v>
       </c>
       <c r="F64" s="3" t="s">
@@ -2114,7 +2382,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>95</v>
       </c>
@@ -2124,10 +2392,10 @@
       <c r="C65" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="4">
         <v>46105</v>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E65" s="5">
         <v>4434.51</v>
       </c>
       <c r="F65" s="3" t="s">
@@ -2137,7 +2405,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>7</v>
       </c>
@@ -2147,10 +2415,10 @@
       <c r="C66" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="4">
         <v>46105</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="5">
         <v>5466.66</v>
       </c>
       <c r="F66" s="3" t="s">
@@ -2160,7 +2428,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>95</v>
       </c>
@@ -2170,10 +2438,10 @@
       <c r="C67" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="4">
         <v>46106</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="5">
         <v>4646.53</v>
       </c>
       <c r="F67" s="3"/>
@@ -2181,7 +2449,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>7</v>
       </c>
@@ -2191,18 +2459,18 @@
       <c r="C68" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="4">
         <v>46106</v>
       </c>
-      <c r="E68" s="5" t="n">
-        <v>9832.7</v>
+      <c r="E68" s="5">
+        <v>9832.7000000000007</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>7</v>
       </c>
@@ -2212,10 +2480,10 @@
       <c r="C69" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="4">
         <v>46108</v>
       </c>
-      <c r="E69" s="5" t="n">
+      <c r="E69" s="5">
         <v>1470</v>
       </c>
       <c r="F69" s="3" t="s">
@@ -2225,7 +2493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>71</v>
       </c>
@@ -2235,10 +2503,10 @@
       <c r="C70" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="4">
         <v>46111</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="5">
         <v>5826.6</v>
       </c>
       <c r="F70" s="3" t="s">
@@ -2248,7 +2516,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>95</v>
       </c>
@@ -2258,10 +2526,10 @@
       <c r="C71" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="4">
         <v>46112</v>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E71" s="5">
         <v>4434.51</v>
       </c>
       <c r="F71" s="3" t="s">
@@ -2271,7 +2539,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>27</v>
       </c>
@@ -2281,10 +2549,10 @@
       <c r="C72" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="4">
         <v>46112</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E72" s="5">
         <v>1452.13</v>
       </c>
       <c r="F72" s="3" t="s">
@@ -2294,7 +2562,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>95</v>
       </c>
@@ -2304,10 +2572,10 @@
       <c r="C73" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="4">
         <v>46113</v>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="5">
         <v>4646.54</v>
       </c>
       <c r="F73" s="3"/>
@@ -2315,7 +2583,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>95</v>
       </c>
@@ -2325,10 +2593,10 @@
       <c r="C74" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="4">
         <v>46114</v>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E74" s="5">
         <v>3013.43</v>
       </c>
       <c r="F74" s="3" t="s">
@@ -2338,7 +2606,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>13</v>
       </c>
@@ -2348,10 +2616,10 @@
       <c r="C75" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="4">
         <v>46114</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E75" s="5">
         <v>12150</v>
       </c>
       <c r="F75" s="3"/>
@@ -2359,7 +2627,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>13</v>
       </c>
@@ -2369,10 +2637,10 @@
       <c r="C76" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="4">
         <v>46115</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="5">
         <v>2570.4</v>
       </c>
       <c r="F76" s="3" t="s">
@@ -2382,7 +2650,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>71</v>
       </c>
@@ -2392,10 +2660,10 @@
       <c r="C77" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="4">
         <v>46116</v>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="E77" s="5">
         <v>5826.6</v>
       </c>
       <c r="F77" s="3" t="s">
@@ -2405,7 +2673,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>7</v>
       </c>
@@ -2415,18 +2683,18 @@
       <c r="C78" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="4">
         <v>46116</v>
       </c>
-      <c r="E78" s="5" t="n">
-        <v>9832.7</v>
+      <c r="E78" s="5">
+        <v>9832.7000000000007</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>7</v>
       </c>
@@ -2436,10 +2704,10 @@
       <c r="C79" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="4">
         <v>46118</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E79" s="5">
         <v>1470</v>
       </c>
       <c r="F79" s="3" t="s">
@@ -2449,7 +2717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>27</v>
       </c>
@@ -2459,10 +2727,10 @@
       <c r="C80" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="4">
         <v>46119</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="E80" s="5">
         <v>1452.14</v>
       </c>
       <c r="F80" s="3" t="s">
@@ -2472,7 +2740,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>130</v>
       </c>
@@ -2482,10 +2750,10 @@
       <c r="C81" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" s="4">
         <v>46119</v>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E81" s="5">
         <v>6319.14</v>
       </c>
       <c r="F81" s="3" t="s">
@@ -2495,7 +2763,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>95</v>
       </c>
@@ -2505,10 +2773,10 @@
       <c r="C82" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="4">
         <v>46119</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E82" s="5">
         <v>1265.78</v>
       </c>
       <c r="F82" s="3" t="s">
@@ -2518,7 +2786,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>95</v>
       </c>
@@ -2528,10 +2796,10 @@
       <c r="C83" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="D83" s="4">
         <v>46119</v>
       </c>
-      <c r="E83" s="5" t="n">
+      <c r="E83" s="5">
         <v>4434.51</v>
       </c>
       <c r="F83" s="3" t="s">
@@ -2541,7 +2809,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>13</v>
       </c>
@@ -2551,10 +2819,10 @@
       <c r="C84" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="D84" s="4">
         <v>46120</v>
       </c>
-      <c r="E84" s="5" t="n">
+      <c r="E84" s="5">
         <v>1150.8</v>
       </c>
       <c r="F84" s="3" t="s">
@@ -2564,7 +2832,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>95</v>
       </c>
@@ -2574,10 +2842,10 @@
       <c r="C85" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" s="4">
         <v>46121</v>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E85" s="5">
         <v>3013.43</v>
       </c>
       <c r="F85" s="3" t="s">
@@ -2587,7 +2855,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>71</v>
       </c>
@@ -2597,10 +2865,10 @@
       <c r="C86" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="D86" s="4">
         <v>46121</v>
       </c>
-      <c r="E86" s="5" t="n">
+      <c r="E86" s="5">
         <v>5826.6</v>
       </c>
       <c r="F86" s="3" t="s">
@@ -2610,7 +2878,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>13</v>
       </c>
@@ -2620,10 +2888,10 @@
       <c r="C87" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="D87" s="4">
         <v>46122</v>
       </c>
-      <c r="E87" s="5" t="n">
+      <c r="E87" s="5">
         <v>2570.4</v>
       </c>
       <c r="F87" s="3" t="s">
@@ -2633,7 +2901,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="88" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>130</v>
       </c>
@@ -2643,10 +2911,10 @@
       <c r="C88" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="4">
         <v>46122</v>
       </c>
-      <c r="E88" s="5" t="n">
+      <c r="E88" s="5">
         <v>10282.5</v>
       </c>
       <c r="F88" s="3" t="s">
@@ -2656,7 +2924,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="89" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="89" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>95</v>
       </c>
@@ -2666,10 +2934,10 @@
       <c r="C89" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D89" s="4" t="n">
+      <c r="D89" s="4">
         <v>46122</v>
       </c>
-      <c r="E89" s="5" t="n">
+      <c r="E89" s="5">
         <v>3316.11</v>
       </c>
       <c r="F89" s="3" t="s">
@@ -2679,7 +2947,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="90" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="90" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>13</v>
       </c>
@@ -2689,10 +2957,10 @@
       <c r="C90" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D90" s="4" t="n">
+      <c r="D90" s="4">
         <v>46125</v>
       </c>
-      <c r="E90" s="5" t="n">
+      <c r="E90" s="5">
         <v>863.1</v>
       </c>
       <c r="F90" s="3" t="s">
@@ -2702,7 +2970,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="91" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="91" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>13</v>
       </c>
@@ -2712,10 +2980,10 @@
       <c r="C91" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D91" s="4" t="n">
+      <c r="D91" s="4">
         <v>46125</v>
       </c>
-      <c r="E91" s="5" t="n">
+      <c r="E91" s="5">
         <v>863.1</v>
       </c>
       <c r="F91" s="3" t="s">
@@ -2725,7 +2993,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="92" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="92" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>27</v>
       </c>
@@ -2735,10 +3003,10 @@
       <c r="C92" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D92" s="4" t="n">
+      <c r="D92" s="4">
         <v>46126</v>
       </c>
-      <c r="E92" s="5" t="n">
+      <c r="E92" s="5">
         <v>707.78</v>
       </c>
       <c r="F92" s="3" t="s">
@@ -2748,7 +3016,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="93" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="93" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>7</v>
       </c>
@@ -2758,18 +3026,18 @@
       <c r="C93" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D93" s="4" t="n">
+      <c r="D93" s="4">
         <v>46126</v>
       </c>
-      <c r="E93" s="5" t="n">
-        <v>9832.7</v>
+      <c r="E93" s="5">
+        <v>9832.7000000000007</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="94" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="94" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>130</v>
       </c>
@@ -2779,10 +3047,10 @@
       <c r="C94" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="D94" s="4">
         <v>46126</v>
       </c>
-      <c r="E94" s="5" t="n">
+      <c r="E94" s="5">
         <v>3150</v>
       </c>
       <c r="F94" s="3" t="s">
@@ -2792,7 +3060,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="95" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="95" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>95</v>
       </c>
@@ -2802,10 +3070,10 @@
       <c r="C95" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D95" s="4" t="n">
+      <c r="D95" s="4">
         <v>46126</v>
       </c>
-      <c r="E95" s="5" t="n">
+      <c r="E95" s="5">
         <v>1265.78</v>
       </c>
       <c r="F95" s="3" t="s">
@@ -2815,7 +3083,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="96" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="96" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>95</v>
       </c>
@@ -2825,10 +3093,10 @@
       <c r="C96" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D96" s="4" t="n">
+      <c r="D96" s="4">
         <v>46126</v>
       </c>
-      <c r="E96" s="5" t="n">
+      <c r="E96" s="5">
         <v>4434.51</v>
       </c>
       <c r="F96" s="3" t="s">
@@ -2838,7 +3106,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="97" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="97" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>71</v>
       </c>
@@ -2848,10 +3116,10 @@
       <c r="C97" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D97" s="4" t="n">
+      <c r="D97" s="4">
         <v>46126</v>
       </c>
-      <c r="E97" s="5" t="n">
+      <c r="E97" s="5">
         <v>2100</v>
       </c>
       <c r="F97" s="3" t="s">
@@ -2861,18 +3129,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="98" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A98" s="6"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="8" t="n">
-        <v>444507.64</v>
-      </c>
-      <c r="F98" s="7"/>
-      <c r="G98" s="9"/>
-    </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD670C15-506C-4B5C-B46B-A5C4F0919AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEABD749-DD46-4010-93BE-1326886C3F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="149">
   <si>
     <t>Funcionário</t>
   </si>
@@ -42,6 +53,9 @@
     <t>Vr.Líquido</t>
   </si>
   <si>
+    <t>Dias Atraso</t>
+  </si>
+  <si>
     <t>Conta/Caixa</t>
   </si>
   <si>
@@ -312,135 +326,111 @@
     <t>01005781.1</t>
   </si>
   <si>
+    <t>01005781.2</t>
+  </si>
+  <si>
     <t>MARCOS DUTRA</t>
   </si>
   <si>
+    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005839.1</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>01005781.3</t>
+  </si>
+  <si>
+    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01005878.1</t>
+  </si>
+  <si>
+    <t>R7 DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005876.1</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01005683.3</t>
+  </si>
+  <si>
+    <t>01005839.2</t>
+  </si>
+  <si>
+    <t>JMC COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01005822.2</t>
+  </si>
+  <si>
+    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
+  </si>
+  <si>
+    <t>01005881.1</t>
+  </si>
+  <si>
+    <t>DISTRIMEDICA COM PROD MED E ODONT LTDA</t>
+  </si>
+  <si>
+    <t>01005820.2</t>
+  </si>
+  <si>
+    <t>01005876.2</t>
+  </si>
+  <si>
+    <t>01005878.2</t>
+  </si>
+  <si>
+    <t>01005839.3</t>
+  </si>
+  <si>
     <t>VITAL DISTRIBUIDORA LTDA</t>
   </si>
   <si>
-    <t>01005759.2</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>01005781.2</t>
-  </si>
-  <si>
-    <t>01005759.3</t>
-  </si>
-  <si>
-    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005839.1</t>
-  </si>
-  <si>
-    <t>01005781.3</t>
-  </si>
-  <si>
-    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
-  </si>
-  <si>
-    <t>01005878.1</t>
-  </si>
-  <si>
-    <t>R7 DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005876.1</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01005683.3</t>
-  </si>
-  <si>
-    <t>01005839.2</t>
-  </si>
-  <si>
-    <t>JMC COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01005822.2</t>
-  </si>
-  <si>
-    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
-  </si>
-  <si>
-    <t>01005881.1</t>
-  </si>
-  <si>
-    <t>DISTRIMEDICA COM PROD MED E ODONT LTDA</t>
-  </si>
-  <si>
-    <t>01005820.2</t>
-  </si>
-  <si>
-    <t>01005876.2</t>
-  </si>
-  <si>
-    <t>01005878.2</t>
-  </si>
-  <si>
-    <t>01005839.3</t>
-  </si>
-  <si>
     <t>01005934.1</t>
   </si>
   <si>
-    <t>QUALIMMED - COM. ATAC. DE MED. E MAT. HOSPITALAR</t>
-  </si>
-  <si>
-    <t>01005765.5</t>
+    <t>01005822.3</t>
+  </si>
+  <si>
+    <t>01005881.2</t>
+  </si>
+  <si>
+    <t>01005878.3</t>
+  </si>
+  <si>
+    <t>01005951.1</t>
+  </si>
+  <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
+  </si>
+  <si>
+    <t>01005955.1</t>
+  </si>
+  <si>
+    <t>01005876.3</t>
+  </si>
+  <si>
+    <t>01005934.2</t>
   </si>
   <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01005940.1</t>
-  </si>
-  <si>
-    <t>01005820.3</t>
-  </si>
-  <si>
-    <t>01005822.3</t>
-  </si>
-  <si>
-    <t>01005881.2</t>
-  </si>
-  <si>
-    <t>01005878.3</t>
-  </si>
-  <si>
-    <t>KELLEN</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
-  </si>
-  <si>
-    <t>01005955.1</t>
-  </si>
-  <si>
-    <t>01005951.1</t>
-  </si>
-  <si>
-    <t>01005876.3</t>
-  </si>
-  <si>
-    <t>01005968.1</t>
-  </si>
-  <si>
-    <t>01005934.2</t>
-  </si>
-  <si>
-    <t>01005820.4</t>
-  </si>
-  <si>
     <t>01005940.2</t>
   </si>
   <si>
@@ -453,34 +443,46 @@
     <t>01005979.1</t>
   </si>
   <si>
-    <t>01005863.4</t>
-  </si>
-  <si>
-    <t>01005913.3</t>
-  </si>
-  <si>
-    <t>FARMAGUEDES COMERCIO DE PROD FARMAC. MED E HOSP LT</t>
-  </si>
-  <si>
-    <t>01005950.2</t>
+    <t>01005876.4</t>
+  </si>
+  <si>
+    <t>01005955.2</t>
+  </si>
+  <si>
+    <t>01005951.2</t>
   </si>
   <si>
     <t>01005822.4</t>
   </si>
   <si>
-    <t>01005955.2</t>
-  </si>
-  <si>
-    <t>01005951.2</t>
-  </si>
-  <si>
-    <t>01005876.4</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA PARNAIBA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006002.1</t>
+    <t>01005923.3</t>
+  </si>
+  <si>
+    <t>01005968.2</t>
+  </si>
+  <si>
+    <t>01005881.3</t>
+  </si>
+  <si>
+    <t>01005934.3</t>
+  </si>
+  <si>
+    <t>01005940.3</t>
+  </si>
+  <si>
+    <t>L G PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01005988.2</t>
+  </si>
+  <si>
+    <t>01006025.1</t>
+  </si>
+  <si>
+    <t>01005979.2</t>
+  </si>
+  <si>
+    <t>01005983.2</t>
   </si>
 </sst>
 </file>
@@ -500,13 +502,13 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -556,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -571,6 +573,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -907,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -915,12 +920,13 @@
     <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="3.7109375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="12.140625" style="1"/>
+    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -942,16 +948,19 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4">
         <v>45326</v>
@@ -959,22 +968,25 @@
       <c r="E2" s="5">
         <v>9391.7800000000007</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
+      <c r="F2" s="6">
+        <v>806</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4">
         <v>45346</v>
@@ -982,22 +994,25 @@
       <c r="E3" s="5">
         <v>5418</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>10</v>
+      <c r="F3" s="6">
+        <v>786</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4">
         <v>45350</v>
@@ -1005,22 +1020,25 @@
       <c r="E4" s="5">
         <v>1264.8699999999999</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>16</v>
+      <c r="F4" s="6">
+        <v>782</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4">
         <v>45356</v>
@@ -1028,22 +1046,25 @@
       <c r="E5" s="5">
         <v>5418</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>10</v>
+      <c r="F5" s="6">
+        <v>776</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4">
         <v>45362</v>
@@ -1051,22 +1072,25 @@
       <c r="E6" s="5">
         <v>384</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
+      <c r="F6" s="6">
+        <v>770</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4">
         <v>45364</v>
@@ -1074,22 +1098,25 @@
       <c r="E7" s="5">
         <v>816</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
+      <c r="F7" s="6">
+        <v>768</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4">
         <v>45378</v>
@@ -1097,22 +1124,25 @@
       <c r="E8" s="5">
         <v>816</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>16</v>
+      <c r="F8" s="6">
+        <v>754</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4">
         <v>45463</v>
@@ -1120,22 +1150,25 @@
       <c r="E9" s="5">
         <v>1674.52</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>10</v>
+      <c r="F9" s="6">
+        <v>669</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" s="4">
         <v>45493</v>
@@ -1143,22 +1176,25 @@
       <c r="E10" s="5">
         <v>873.6</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>10</v>
+      <c r="F10" s="6">
+        <v>639</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="4">
         <v>45523</v>
@@ -1166,22 +1202,25 @@
       <c r="E11" s="5">
         <v>873.6</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>10</v>
+      <c r="F11" s="6">
+        <v>609</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4">
         <v>45600</v>
@@ -1189,22 +1228,25 @@
       <c r="E12" s="5">
         <v>2000</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="6">
+        <v>532</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4">
         <v>45607</v>
@@ -1212,22 +1254,25 @@
       <c r="E13" s="5">
         <v>3204.34</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>10</v>
+      <c r="F13" s="6">
+        <v>525</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="4">
         <v>45608</v>
@@ -1235,22 +1280,25 @@
       <c r="E14" s="5">
         <v>4439.8999999999996</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="6">
+        <v>524</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="4">
         <v>45614</v>
@@ -1258,22 +1306,25 @@
       <c r="E15" s="5">
         <v>2000</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>10</v>
+      <c r="F15" s="6">
+        <v>518</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="4">
         <v>45615</v>
@@ -1281,22 +1332,25 @@
       <c r="E16" s="5">
         <v>1216.8599999999999</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>10</v>
+      <c r="F16" s="6">
+        <v>517</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="4">
         <v>45617</v>
@@ -1304,22 +1358,25 @@
       <c r="E17" s="5">
         <v>1843.87</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>10</v>
+      <c r="F17" s="6">
+        <v>515</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" s="4">
         <v>45622</v>
@@ -1327,22 +1384,25 @@
       <c r="E18" s="5">
         <v>1216.8599999999999</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>10</v>
+      <c r="F18" s="6">
+        <v>510</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="4">
         <v>45622</v>
@@ -1350,22 +1410,25 @@
       <c r="E19" s="5">
         <v>4439.8999999999996</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>10</v>
+      <c r="F19" s="6">
+        <v>510</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D20" s="4">
         <v>45624</v>
@@ -1373,22 +1436,25 @@
       <c r="E20" s="5">
         <v>1843.88</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>10</v>
+      <c r="F20" s="6">
+        <v>508</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" s="4">
         <v>45688</v>
@@ -1396,22 +1462,25 @@
       <c r="E21" s="5">
         <v>1118.4000000000001</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>10</v>
+      <c r="F21" s="6">
+        <v>444</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D22" s="4">
         <v>45695</v>
@@ -1419,22 +1488,25 @@
       <c r="E22" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="6">
+        <v>437</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23" s="4">
         <v>45699</v>
@@ -1442,22 +1514,25 @@
       <c r="E23" s="5">
         <v>2330</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>10</v>
+      <c r="F23" s="6">
+        <v>433</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24" s="4">
         <v>45702</v>
@@ -1465,22 +1540,25 @@
       <c r="E24" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>10</v>
+      <c r="F24" s="6">
+        <v>430</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25" s="4">
         <v>45705</v>
@@ -1488,22 +1566,25 @@
       <c r="E25" s="5">
         <v>2541</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>16</v>
+      <c r="F25" s="6">
+        <v>427</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D26" s="4">
         <v>45709</v>
@@ -1511,22 +1592,25 @@
       <c r="E26" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>10</v>
+      <c r="F26" s="6">
+        <v>423</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" s="4">
         <v>45712</v>
@@ -1534,22 +1618,25 @@
       <c r="E27" s="5">
         <v>2541</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>16</v>
+      <c r="F27" s="6">
+        <v>420</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D28" s="4">
         <v>45726</v>
@@ -1557,22 +1644,25 @@
       <c r="E28" s="5">
         <v>2541</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>16</v>
+      <c r="F28" s="6">
+        <v>406</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D29" s="4">
         <v>45727</v>
@@ -1580,22 +1670,25 @@
       <c r="E29" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>10</v>
+      <c r="F29" s="6">
+        <v>405</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30" s="4">
         <v>45734</v>
@@ -1603,22 +1696,25 @@
       <c r="E30" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>10</v>
+      <c r="F30" s="6">
+        <v>398</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D31" s="4">
         <v>45734</v>
@@ -1626,22 +1722,25 @@
       <c r="E31" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>10</v>
+      <c r="F31" s="6">
+        <v>398</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D32" s="4">
         <v>45740</v>
@@ -1649,22 +1748,25 @@
       <c r="E32" s="5">
         <v>2541</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>16</v>
+      <c r="F32" s="6">
+        <v>392</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33" s="4">
         <v>45741</v>
@@ -1672,22 +1774,25 @@
       <c r="E33" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>10</v>
+      <c r="F33" s="6">
+        <v>391</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D34" s="4">
         <v>45741</v>
@@ -1695,22 +1800,25 @@
       <c r="E34" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>10</v>
+      <c r="F34" s="6">
+        <v>391</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D35" s="4">
         <v>45748</v>
@@ -1718,22 +1826,25 @@
       <c r="E35" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>10</v>
+      <c r="F35" s="6">
+        <v>384</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D36" s="4">
         <v>45748</v>
@@ -1741,22 +1852,25 @@
       <c r="E36" s="5">
         <v>7562.76</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>10</v>
+      <c r="F36" s="6">
+        <v>384</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D37" s="4">
         <v>45755</v>
@@ -1764,22 +1878,25 @@
       <c r="E37" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>10</v>
+      <c r="F37" s="6">
+        <v>377</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D38" s="4">
         <v>45761</v>
@@ -1787,22 +1904,25 @@
       <c r="E38" s="5">
         <v>6169.53</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>10</v>
+      <c r="F38" s="6">
+        <v>371</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D39" s="4">
         <v>45768</v>
@@ -1810,22 +1930,25 @@
       <c r="E39" s="5">
         <v>3850</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>10</v>
+      <c r="F39" s="6">
+        <v>364</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D40" s="4">
         <v>45775</v>
@@ -1833,22 +1956,25 @@
       <c r="E40" s="5">
         <v>3850</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>10</v>
+      <c r="F40" s="6">
+        <v>357</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D41" s="4">
         <v>45775</v>
@@ -1856,22 +1982,25 @@
       <c r="E41" s="5">
         <v>6089.41</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>10</v>
+      <c r="F41" s="6">
+        <v>357</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D42" s="4">
         <v>45782</v>
@@ -1879,22 +2008,25 @@
       <c r="E42" s="5">
         <v>3800</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>10</v>
+      <c r="F42" s="6">
+        <v>350</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D43" s="4">
         <v>45789</v>
@@ -1902,22 +2034,25 @@
       <c r="E43" s="5">
         <v>3800</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>10</v>
+      <c r="F43" s="6">
+        <v>343</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D44" s="4">
         <v>45789</v>
@@ -1925,22 +2060,25 @@
       <c r="E44" s="5">
         <v>1143.54</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>16</v>
+      <c r="F44" s="6">
+        <v>343</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D45" s="4">
         <v>45796</v>
@@ -1948,22 +2086,25 @@
       <c r="E45" s="5">
         <v>2287.06</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>16</v>
+      <c r="F45" s="6">
+        <v>336</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D46" s="4">
         <v>45896</v>
@@ -1971,22 +2112,25 @@
       <c r="E46" s="5">
         <v>4572.62</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>16</v>
+      <c r="F46" s="6">
+        <v>236</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D47" s="4">
         <v>45910</v>
@@ -1994,22 +2138,25 @@
       <c r="E47" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>16</v>
+      <c r="F47" s="6">
+        <v>222</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D48" s="4">
         <v>45924</v>
@@ -2017,22 +2164,25 @@
       <c r="E48" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>16</v>
+      <c r="F48" s="6">
+        <v>208</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D49" s="4">
         <v>45947</v>
@@ -2040,22 +2190,25 @@
       <c r="E49" s="5">
         <v>3867.34</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>16</v>
+      <c r="F49" s="6">
+        <v>185</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D50" s="4">
         <v>45954</v>
@@ -2063,22 +2216,25 @@
       <c r="E50" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>16</v>
+      <c r="F50" s="6">
+        <v>178</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D51" s="4">
         <v>45961</v>
@@ -2086,22 +2242,25 @@
       <c r="E51" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>16</v>
+      <c r="F51" s="6">
+        <v>171</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D52" s="4">
         <v>45968</v>
@@ -2109,22 +2268,25 @@
       <c r="E52" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>16</v>
+      <c r="F52" s="6">
+        <v>164</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D53" s="4">
         <v>45980</v>
@@ -2132,22 +2294,25 @@
       <c r="E53" s="5">
         <v>4480</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>16</v>
+      <c r="F53" s="6">
+        <v>152</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D54" s="4">
         <v>45980</v>
@@ -2155,20 +2320,23 @@
       <c r="E54" s="5">
         <v>48213.84</v>
       </c>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F54" s="6">
+        <v>152</v>
+      </c>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D55" s="4">
         <v>45987</v>
@@ -2176,20 +2344,23 @@
       <c r="E55" s="5">
         <v>33844.160000000003</v>
       </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F55" s="6">
+        <v>145</v>
+      </c>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D56" s="4">
         <v>45989</v>
@@ -2197,20 +2368,23 @@
       <c r="E56" s="5">
         <v>3220</v>
       </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F56" s="6">
+        <v>143</v>
+      </c>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D57" s="4">
         <v>45994</v>
@@ -2218,20 +2392,23 @@
       <c r="E57" s="5">
         <v>38740.53</v>
       </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F57" s="6">
+        <v>138</v>
+      </c>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D58" s="4">
         <v>46090</v>
@@ -2239,763 +2416,865 @@
       <c r="E58" s="5">
         <v>806.34</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>16</v>
+      <c r="F58" s="6">
+        <v>42</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H58" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="4">
+        <v>46097</v>
+      </c>
+      <c r="E59" s="5">
+        <v>503.28</v>
+      </c>
+      <c r="F59" s="6">
+        <v>35</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="4">
-        <v>46092</v>
-      </c>
-      <c r="E59" s="5">
-        <v>2089.5700000000002</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G59" s="3" t="s">
+      <c r="B60" s="3" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>99</v>
       </c>
       <c r="D60" s="4">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="E60" s="5">
+        <v>7584.01</v>
+      </c>
+      <c r="F60" s="6">
+        <v>33</v>
+      </c>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D61" s="4">
+        <v>46104</v>
+      </c>
+      <c r="E61" s="5">
         <v>503.28</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D61" s="4">
-        <v>46099</v>
-      </c>
-      <c r="E61" s="5">
-        <v>2089.56</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>16</v>
+      <c r="F61" s="6">
+        <v>28</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D62" s="4">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="E62" s="5">
-        <v>7584.01</v>
-      </c>
-      <c r="F62" s="3"/>
+        <v>1812.31</v>
+      </c>
+      <c r="F62" s="6">
+        <v>27</v>
+      </c>
       <c r="G62" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D63" s="4">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="E63" s="5">
-        <v>503.28</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>16</v>
+        <v>4434.51</v>
+      </c>
+      <c r="F63" s="6">
+        <v>27</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H63" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D64" s="4">
         <v>46105</v>
       </c>
       <c r="E64" s="5">
-        <v>1812.31</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>16</v>
+        <v>5466.66</v>
+      </c>
+      <c r="F64" s="6">
+        <v>27</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D65" s="4">
+        <v>46106</v>
+      </c>
+      <c r="E65" s="5">
+        <v>4646.53</v>
+      </c>
+      <c r="F65" s="6">
+        <v>26</v>
+      </c>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" s="4">
+        <v>46106</v>
+      </c>
+      <c r="E66" s="5">
+        <v>9832.7000000000007</v>
+      </c>
+      <c r="F66" s="6">
+        <v>26</v>
+      </c>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="4">
+        <v>46108</v>
+      </c>
+      <c r="E67" s="5">
+        <v>1470</v>
+      </c>
+      <c r="F67" s="6">
+        <v>24</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46111</v>
+      </c>
+      <c r="E68" s="5">
+        <v>5826.6</v>
+      </c>
+      <c r="F68" s="6">
+        <v>21</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D69" s="4">
+        <v>46112</v>
+      </c>
+      <c r="E69" s="5">
+        <v>4434.51</v>
+      </c>
+      <c r="F69" s="6">
+        <v>20</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D65" s="4">
-        <v>46105</v>
-      </c>
-      <c r="E65" s="5">
-        <v>4434.51</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D66" s="4">
-        <v>46105</v>
-      </c>
-      <c r="E66" s="5">
-        <v>5466.66</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D67" s="4">
-        <v>46106</v>
-      </c>
-      <c r="E67" s="5">
-        <v>4646.53</v>
-      </c>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D68" s="4">
-        <v>46106</v>
-      </c>
-      <c r="E68" s="5">
-        <v>9832.7000000000007</v>
-      </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D69" s="4">
-        <v>46108</v>
-      </c>
-      <c r="E69" s="5">
-        <v>1470</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D70" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="E70" s="5">
-        <v>5826.6</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>16</v>
+        <v>1452.13</v>
+      </c>
+      <c r="F70" s="6">
+        <v>20</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>118</v>
       </c>
       <c r="D71" s="4">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="E71" s="5">
-        <v>4434.51</v>
-      </c>
-      <c r="F71" s="3" t="s">
+        <v>4646.54</v>
+      </c>
+      <c r="F71" s="6">
+        <v>19</v>
+      </c>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E72" s="5">
+        <v>3013.43</v>
+      </c>
+      <c r="F72" s="6">
+        <v>18</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73" s="4">
+        <v>46116</v>
+      </c>
+      <c r="E73" s="5">
+        <v>9832.7000000000007</v>
+      </c>
+      <c r="F73" s="6">
         <v>16</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D72" s="4">
-        <v>46112</v>
-      </c>
-      <c r="E72" s="5">
-        <v>1452.13</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D73" s="4">
-        <v>46113</v>
-      </c>
-      <c r="E73" s="5">
-        <v>4646.54</v>
-      </c>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G73" s="3"/>
+      <c r="H73" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D74" s="4">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="E74" s="5">
-        <v>3013.43</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>10</v>
+        <v>1470</v>
+      </c>
+      <c r="F74" s="6">
+        <v>14</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>123</v>
       </c>
       <c r="D75" s="4">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="E75" s="5">
-        <v>12150</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>1452.14</v>
+      </c>
+      <c r="F75" s="6">
+        <v>13</v>
+      </c>
       <c r="G75" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H75" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D76" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E76" s="5">
+        <v>1265.78</v>
+      </c>
+      <c r="F76" s="6">
         <v>13</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C76" s="3" t="s">
+      <c r="G76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D76" s="4">
-        <v>46115</v>
-      </c>
-      <c r="E76" s="5">
+      <c r="B77" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D77" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E77" s="5">
+        <v>6319.14</v>
+      </c>
+      <c r="F77" s="6">
+        <v>13</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D78" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E78" s="5">
+        <v>4434.51</v>
+      </c>
+      <c r="F78" s="6">
+        <v>13</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D79" s="4">
+        <v>46121</v>
+      </c>
+      <c r="E79" s="5">
+        <v>3013.43</v>
+      </c>
+      <c r="F79" s="6">
+        <v>11</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D80" s="4">
+        <v>46122</v>
+      </c>
+      <c r="E80" s="5">
         <v>2570.4</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F80" s="6">
         <v>10</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C77" s="3" t="s">
+      <c r="G80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="D77" s="4">
-        <v>46116</v>
-      </c>
-      <c r="E77" s="5">
-        <v>5826.6</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D78" s="4">
-        <v>46116</v>
-      </c>
-      <c r="E78" s="5">
-        <v>9832.7000000000007</v>
-      </c>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D79" s="4">
-        <v>46118</v>
-      </c>
-      <c r="E79" s="5">
-        <v>1470</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D80" s="4">
-        <v>46119</v>
-      </c>
-      <c r="E80" s="5">
-        <v>1452.14</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>132</v>
       </c>
       <c r="D81" s="4">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="E81" s="5">
-        <v>6319.14</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>16</v>
+        <v>10282.5</v>
+      </c>
+      <c r="F81" s="6">
+        <v>10</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D82" s="4">
+        <v>46122</v>
+      </c>
+      <c r="E82" s="5">
+        <v>3316.11</v>
+      </c>
+      <c r="F82" s="6">
+        <v>10</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D82" s="4">
-        <v>46119</v>
-      </c>
-      <c r="E82" s="5">
-        <v>1265.78</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D83" s="4">
-        <v>46119</v>
+        <v>46126</v>
       </c>
       <c r="E83" s="5">
         <v>4434.51</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>16</v>
+      <c r="F83" s="6">
+        <v>6</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D84" s="4">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="E84" s="5">
+        <v>3150</v>
+      </c>
+      <c r="F84" s="6">
+        <v>6</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D85" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E85" s="5">
+        <v>1265.78</v>
+      </c>
+      <c r="F85" s="6">
+        <v>6</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D86" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E86" s="5">
+        <v>9832.7000000000007</v>
+      </c>
+      <c r="F86" s="6">
+        <v>6</v>
+      </c>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D87" s="4">
+        <v>46127</v>
+      </c>
+      <c r="E87" s="5">
+        <v>1854</v>
+      </c>
+      <c r="F87" s="6">
+        <v>5</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D88" s="4">
+        <v>46127</v>
+      </c>
+      <c r="E88" s="5">
         <v>1150.8</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D85" s="4">
-        <v>46121</v>
-      </c>
-      <c r="E85" s="5">
-        <v>3013.43</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D86" s="4">
-        <v>46121</v>
-      </c>
-      <c r="E86" s="5">
-        <v>5826.6</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D87" s="4">
-        <v>46122</v>
-      </c>
-      <c r="E87" s="5">
-        <v>2570.4</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D88" s="4">
-        <v>46122</v>
-      </c>
-      <c r="E88" s="5">
-        <v>10282.5</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>16</v>
+      <c r="F88" s="6">
+        <v>5</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D89" s="4">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="E89" s="5">
-        <v>3316.11</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>10</v>
+        <v>1470</v>
+      </c>
+      <c r="F89" s="6">
+        <v>4</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>142</v>
       </c>
       <c r="D90" s="4">
-        <v>46125</v>
+        <v>46128</v>
       </c>
       <c r="E90" s="5">
-        <v>863.1</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>16</v>
+        <v>3013.43</v>
+      </c>
+      <c r="F90" s="6">
+        <v>4</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D91" s="4">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="E91" s="5">
-        <v>863.1</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>16</v>
+        <v>2570.4</v>
+      </c>
+      <c r="F91" s="6">
+        <v>3</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>144</v>
@@ -3004,129 +3283,97 @@
         <v>145</v>
       </c>
       <c r="D92" s="4">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="E92" s="5">
-        <v>707.78</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>10</v>
+        <v>4422</v>
+      </c>
+      <c r="F92" s="6">
+        <v>3</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D93" s="4">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="E93" s="5">
-        <v>9832.7000000000007</v>
-      </c>
-      <c r="F93" s="3"/>
+        <v>5112</v>
+      </c>
+      <c r="F93" s="6">
+        <v>3</v>
+      </c>
       <c r="G93" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>147</v>
       </c>
       <c r="D94" s="4">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="E94" s="5">
-        <v>3150</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>16</v>
+        <v>1890</v>
+      </c>
+      <c r="F94" s="6">
+        <v>3</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>148</v>
       </c>
       <c r="D95" s="4">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="E95" s="5">
-        <v>1265.78</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>10</v>
+        <v>5125.68</v>
+      </c>
+      <c r="F95" s="6">
+        <v>3</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H95" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D96" s="4">
-        <v>46126</v>
-      </c>
-      <c r="E96" s="5">
-        <v>4434.51</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D97" s="4">
-        <v>46126</v>
-      </c>
-      <c r="E97" s="5">
-        <v>2100</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,26 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEABD749-DD46-4010-93BE-1326886C3F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4363B0-1466-46F8-BB29-49CAE4A584F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -36,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="157">
   <si>
     <t>Funcionário</t>
   </si>
@@ -365,9 +354,6 @@
     <t>01005683.3</t>
   </si>
   <si>
-    <t>01005839.2</t>
-  </si>
-  <si>
     <t>JMC COMERCIAL LTDA</t>
   </si>
   <si>
@@ -413,6 +399,9 @@
     <t>01005951.1</t>
   </si>
   <si>
+    <t>01005876.3</t>
+  </si>
+  <si>
     <t>KELLEN</t>
   </si>
   <si>
@@ -422,42 +411,27 @@
     <t>01005955.1</t>
   </si>
   <si>
-    <t>01005876.3</t>
-  </si>
-  <si>
     <t>01005934.2</t>
   </si>
   <si>
+    <t>01005983.1</t>
+  </si>
+  <si>
+    <t>01005955.2</t>
+  </si>
+  <si>
+    <t>01005822.4</t>
+  </si>
+  <si>
+    <t>01005876.4</t>
+  </si>
+  <si>
+    <t>01005951.2</t>
+  </si>
+  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01005940.2</t>
-  </si>
-  <si>
-    <t>01005983.1</t>
-  </si>
-  <si>
-    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
-  </si>
-  <si>
-    <t>01005979.1</t>
-  </si>
-  <si>
-    <t>01005876.4</t>
-  </si>
-  <si>
-    <t>01005955.2</t>
-  </si>
-  <si>
-    <t>01005951.2</t>
-  </si>
-  <si>
-    <t>01005822.4</t>
-  </si>
-  <si>
-    <t>01005923.3</t>
-  </si>
-  <si>
     <t>01005968.2</t>
   </si>
   <si>
@@ -470,19 +444,58 @@
     <t>01005940.3</t>
   </si>
   <si>
+    <t>01005983.2</t>
+  </si>
+  <si>
+    <t>NOVA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006034.1</t>
+  </si>
+  <si>
+    <t>01005913.4</t>
+  </si>
+  <si>
     <t>L G PRODUTOS HOSPITALARES LTDA</t>
   </si>
   <si>
-    <t>01005988.2</t>
-  </si>
-  <si>
-    <t>01006025.1</t>
-  </si>
-  <si>
-    <t>01005979.2</t>
-  </si>
-  <si>
-    <t>01005983.2</t>
+    <t>01005855.5</t>
+  </si>
+  <si>
+    <t>01005907.4</t>
+  </si>
+  <si>
+    <t>01006040.1</t>
+  </si>
+  <si>
+    <t>ATHUS HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01005994.1</t>
+  </si>
+  <si>
+    <t>01005955.3</t>
+  </si>
+  <si>
+    <t>01005920.4</t>
+  </si>
+  <si>
+    <t>01005951.3</t>
+  </si>
+  <si>
+    <t>01005968.3</t>
+  </si>
+  <si>
+    <t>01005892.5</t>
+  </si>
+  <si>
+    <t>01005934.4</t>
+  </si>
+  <si>
+    <t>MONTALVAO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01006044.1</t>
   </si>
 </sst>
 </file>
@@ -502,13 +515,13 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -912,7 +925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -969,7 +982,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
@@ -995,7 +1008,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -1021,7 +1034,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -1047,7 +1060,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -1073,7 +1086,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1099,7 +1112,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
@@ -1125,7 +1138,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
@@ -1151,7 +1164,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -1177,7 +1190,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>11</v>
@@ -1203,7 +1216,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -1229,7 +1242,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>11</v>
@@ -1255,7 +1268,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -1281,7 +1294,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
@@ -1307,7 +1320,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -1333,7 +1346,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>11</v>
@@ -1359,7 +1372,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -1385,7 +1398,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>11</v>
@@ -1411,7 +1424,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -1437,7 +1450,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>11</v>
@@ -1463,7 +1476,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -1489,7 +1502,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
@@ -1515,7 +1528,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -1541,7 +1554,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>11</v>
@@ -1567,7 +1580,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>17</v>
@@ -1593,7 +1606,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>11</v>
@@ -1619,7 +1632,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
@@ -1645,7 +1658,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -1671,7 +1684,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -1697,7 +1710,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>11</v>
@@ -1723,7 +1736,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -1749,7 +1762,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>17</v>
@@ -1775,7 +1788,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -1801,7 +1814,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
@@ -1827,7 +1840,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -1853,7 +1866,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>11</v>
@@ -1879,7 +1892,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -1905,7 +1918,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>11</v>
@@ -1931,7 +1944,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -1957,7 +1970,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>11</v>
@@ -1983,7 +1996,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -2009,7 +2022,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -2035,7 +2048,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -2061,7 +2074,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -2087,7 +2100,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -2113,7 +2126,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -2139,7 +2152,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -2165,7 +2178,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -2191,7 +2204,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -2217,7 +2230,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -2243,7 +2256,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -2269,7 +2282,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -2295,7 +2308,7 @@
         <v>4480</v>
       </c>
       <c r="F53" s="6">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>17</v>
@@ -2321,7 +2334,7 @@
         <v>48213.84</v>
       </c>
       <c r="F54" s="6">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
@@ -2345,7 +2358,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2369,7 +2382,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2393,7 +2406,7 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2417,7 +2430,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -2443,7 +2456,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -2469,7 +2482,7 @@
         <v>7584.01</v>
       </c>
       <c r="F60" s="6">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3" t="s">
@@ -2493,7 +2506,7 @@
         <v>503.28</v>
       </c>
       <c r="F61" s="6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>17</v>
@@ -2519,7 +2532,7 @@
         <v>1812.31</v>
       </c>
       <c r="F62" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>17</v>
@@ -2545,7 +2558,7 @@
         <v>4434.51</v>
       </c>
       <c r="F63" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>17</v>
@@ -2571,7 +2584,7 @@
         <v>5466.66</v>
       </c>
       <c r="F64" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>11</v>
@@ -2582,26 +2595,26 @@
     </row>
     <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D65" s="4">
         <v>46106</v>
       </c>
       <c r="E65" s="5">
-        <v>4646.53</v>
+        <v>9832.7000000000007</v>
       </c>
       <c r="F65" s="6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2609,83 +2622,85 @@
         <v>8</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D66" s="4">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="E66" s="5">
-        <v>9832.7000000000007</v>
+        <v>1470</v>
       </c>
       <c r="F66" s="6">
-        <v>26</v>
-      </c>
-      <c r="G66" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H66" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D67" s="4">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="E67" s="5">
-        <v>1470</v>
+        <v>5826.6</v>
       </c>
       <c r="F67" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>115</v>
       </c>
       <c r="D68" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="E68" s="5">
-        <v>5826.6</v>
+        <v>4434.51</v>
       </c>
       <c r="F68" s="6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>116</v>
@@ -2694,42 +2709,40 @@
         <v>46112</v>
       </c>
       <c r="E69" s="5">
-        <v>4434.51</v>
+        <v>1452.13</v>
       </c>
       <c r="F69" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D70" s="4">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="E70" s="5">
-        <v>1452.13</v>
+        <v>4646.54</v>
       </c>
       <c r="F70" s="6">
-        <v>20</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2737,49 +2750,49 @@
         <v>97</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D71" s="4">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="E71" s="5">
-        <v>4646.54</v>
+        <v>3013.43</v>
       </c>
       <c r="F71" s="6">
-        <v>19</v>
-      </c>
-      <c r="G71" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H71" s="3" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D72" s="4">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="E72" s="5">
-        <v>3013.43</v>
+        <v>9832.7000000000007</v>
       </c>
       <c r="F72" s="6">
-        <v>18</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2787,57 +2800,59 @@
         <v>8</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D73" s="4">
-        <v>46116</v>
+        <v>46118</v>
       </c>
       <c r="E73" s="5">
-        <v>9832.7000000000007</v>
+        <v>1470</v>
       </c>
       <c r="F73" s="6">
-        <v>16</v>
-      </c>
-      <c r="G73" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H73" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>122</v>
       </c>
       <c r="D74" s="4">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="E74" s="5">
-        <v>1470</v>
+        <v>1452.14</v>
       </c>
       <c r="F74" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>123</v>
@@ -2846,16 +2861,16 @@
         <v>46119</v>
       </c>
       <c r="E75" s="5">
-        <v>1452.14</v>
+        <v>1265.78</v>
       </c>
       <c r="F75" s="6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2872,13 +2887,13 @@
         <v>46119</v>
       </c>
       <c r="E76" s="5">
-        <v>1265.78</v>
+        <v>4434.51</v>
       </c>
       <c r="F76" s="6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>106</v>
@@ -2901,7 +2916,7 @@
         <v>6319.14</v>
       </c>
       <c r="F77" s="6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>17</v>
@@ -2915,103 +2930,101 @@
         <v>97</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D78" s="4">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="E78" s="5">
-        <v>4434.51</v>
+        <v>3013.43</v>
       </c>
       <c r="F78" s="6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D79" s="4">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="E79" s="5">
-        <v>3013.43</v>
+        <v>10282.5</v>
       </c>
       <c r="F79" s="6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="D80" s="4">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="E80" s="5">
-        <v>2570.4</v>
+        <v>3150</v>
       </c>
       <c r="F80" s="6">
         <v>10</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D81" s="4">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="E81" s="5">
-        <v>10282.5</v>
+        <v>9832.7000000000007</v>
       </c>
       <c r="F81" s="6">
         <v>10</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3019,22 +3032,22 @@
         <v>97</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D82" s="4">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="E82" s="5">
-        <v>3316.11</v>
+        <v>4434.51</v>
       </c>
       <c r="F82" s="6">
         <v>10</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>106</v>
@@ -3048,19 +3061,19 @@
         <v>104</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D83" s="4">
         <v>46126</v>
       </c>
       <c r="E83" s="5">
-        <v>4434.51</v>
+        <v>1265.78</v>
       </c>
       <c r="F83" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>106</v>
@@ -3068,78 +3081,80 @@
     </row>
     <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D84" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E84" s="5">
-        <v>3150</v>
+        <v>1150.8</v>
       </c>
       <c r="F84" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D85" s="4">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="E85" s="5">
-        <v>1265.78</v>
+        <v>1470</v>
       </c>
       <c r="F85" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D86" s="4">
+        <v>46128</v>
+      </c>
+      <c r="E86" s="5">
+        <v>3013.43</v>
+      </c>
+      <c r="F86" s="6">
         <v>8</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D86" s="4">
-        <v>46126</v>
-      </c>
-      <c r="E86" s="5">
-        <v>9832.7000000000007</v>
-      </c>
-      <c r="F86" s="6">
-        <v>6</v>
-      </c>
-      <c r="G86" s="3"/>
+      <c r="G86" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H86" s="3" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3147,22 +3162,22 @@
         <v>14</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D87" s="4">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="E87" s="5">
-        <v>1854</v>
+        <v>2570.4</v>
       </c>
       <c r="F87" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>45</v>
@@ -3170,28 +3185,28 @@
     </row>
     <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D88" s="4">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="E88" s="5">
-        <v>1150.8</v>
+        <v>5125.68</v>
       </c>
       <c r="F88" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3199,19 +3214,19 @@
         <v>8</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D89" s="4">
-        <v>46128</v>
+        <v>46131</v>
       </c>
       <c r="E89" s="5">
-        <v>1470</v>
+        <v>21334.44</v>
       </c>
       <c r="F89" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>11</v>
@@ -3222,48 +3237,48 @@
     </row>
     <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>142</v>
       </c>
       <c r="D90" s="4">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="E90" s="5">
-        <v>3013.43</v>
+        <v>863.1</v>
       </c>
       <c r="F90" s="6">
         <v>4</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D91" s="4">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="E91" s="5">
-        <v>2570.4</v>
+        <v>3499.88</v>
       </c>
       <c r="F91" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>11</v>
@@ -3277,22 +3292,22 @@
         <v>28</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>145</v>
       </c>
       <c r="D92" s="4">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="E92" s="5">
-        <v>4422</v>
+        <v>6129.6</v>
       </c>
       <c r="F92" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>45</v>
@@ -3300,22 +3315,22 @@
     </row>
     <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D93" s="4">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="E93" s="5">
-        <v>5112</v>
+        <v>863.1</v>
       </c>
       <c r="F93" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>11</v>
@@ -3329,25 +3344,23 @@
         <v>97</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D94" s="4">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="E94" s="5">
-        <v>1890</v>
+        <v>1763.27</v>
       </c>
       <c r="F94" s="6">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G94" s="3"/>
       <c r="H94" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3358,13 +3371,13 @@
         <v>126</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D95" s="4">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="E95" s="5">
-        <v>5125.68</v>
+        <v>3150</v>
       </c>
       <c r="F95" s="6">
         <v>3</v>
@@ -3374,6 +3387,162 @@
       </c>
       <c r="H95" s="3" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D96" s="4">
+        <v>46133</v>
+      </c>
+      <c r="E96" s="5">
+        <v>3084.48</v>
+      </c>
+      <c r="F96" s="6">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D97" s="4">
+        <v>46133</v>
+      </c>
+      <c r="E97" s="5">
+        <v>1265.78</v>
+      </c>
+      <c r="F97" s="6">
+        <v>3</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D98" s="4">
+        <v>46134</v>
+      </c>
+      <c r="E98" s="5">
+        <v>1150.8</v>
+      </c>
+      <c r="F98" s="6">
+        <v>2</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D99" s="4">
+        <v>46135</v>
+      </c>
+      <c r="E99" s="5">
+        <v>2142</v>
+      </c>
+      <c r="F99" s="6">
+        <v>1</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D100" s="4">
+        <v>46135</v>
+      </c>
+      <c r="E100" s="5">
+        <v>3013.43</v>
+      </c>
+      <c r="F100" s="6">
+        <v>1</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D101" s="4">
+        <v>46135</v>
+      </c>
+      <c r="E101" s="5">
+        <v>12361.94</v>
+      </c>
+      <c r="F101" s="6">
+        <v>1</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4363B0-1466-46F8-BB29-49CAE4A584F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1E8AD6-F67D-4013-9FB8-05A45E589FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="155">
   <si>
     <t>Funcionário</t>
   </si>
@@ -318,69 +318,66 @@
     <t>01005781.2</t>
   </si>
   <si>
+    <t>01005781.3</t>
+  </si>
+  <si>
+    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01005878.1</t>
+  </si>
+  <si>
     <t>MARCOS DUTRA</t>
   </si>
   <si>
+    <t>R7 DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005876.1</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01005683.3</t>
+  </si>
+  <si>
+    <t>JMC COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01005822.2</t>
+  </si>
+  <si>
+    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
+  </si>
+  <si>
+    <t>01005881.1</t>
+  </si>
+  <si>
+    <t>DISTRIMEDICA COM PROD MED E ODONT LTDA</t>
+  </si>
+  <si>
+    <t>01005820.2</t>
+  </si>
+  <si>
+    <t>01005878.2</t>
+  </si>
+  <si>
+    <t>01005876.2</t>
+  </si>
+  <si>
     <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
   </si>
   <si>
-    <t>01005839.1</t>
+    <t>01005839.3</t>
   </si>
   <si>
     <t>PI</t>
   </si>
   <si>
-    <t>01005781.3</t>
-  </si>
-  <si>
-    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
-  </si>
-  <si>
-    <t>01005878.1</t>
-  </si>
-  <si>
-    <t>R7 DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005876.1</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01005683.3</t>
-  </si>
-  <si>
-    <t>JMC COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01005822.2</t>
-  </si>
-  <si>
-    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
-  </si>
-  <si>
-    <t>01005881.1</t>
-  </si>
-  <si>
-    <t>DISTRIMEDICA COM PROD MED E ODONT LTDA</t>
-  </si>
-  <si>
-    <t>01005820.2</t>
-  </si>
-  <si>
-    <t>01005876.2</t>
-  </si>
-  <si>
-    <t>01005878.2</t>
-  </si>
-  <si>
-    <t>01005839.3</t>
-  </si>
-  <si>
     <t>VITAL DISTRIBUIDORA LTDA</t>
   </si>
   <si>
@@ -399,36 +396,36 @@
     <t>01005951.1</t>
   </si>
   <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
+  </si>
+  <si>
+    <t>01005955.1</t>
+  </si>
+  <si>
     <t>01005876.3</t>
   </si>
   <si>
-    <t>KELLEN</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
-  </si>
-  <si>
-    <t>01005955.1</t>
-  </si>
-  <si>
     <t>01005934.2</t>
   </si>
   <si>
     <t>01005983.1</t>
   </si>
   <si>
+    <t>01005876.4</t>
+  </si>
+  <si>
     <t>01005955.2</t>
   </si>
   <si>
+    <t>01005951.2</t>
+  </si>
+  <si>
     <t>01005822.4</t>
   </si>
   <si>
-    <t>01005876.4</t>
-  </si>
-  <si>
-    <t>01005951.2</t>
-  </si>
-  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
@@ -456,46 +453,43 @@
     <t>01005913.4</t>
   </si>
   <si>
+    <t>01006040.1</t>
+  </si>
+  <si>
+    <t>01005951.3</t>
+  </si>
+  <si>
+    <t>01005955.3</t>
+  </si>
+  <si>
+    <t>01005968.3</t>
+  </si>
+  <si>
+    <t>01005934.4</t>
+  </si>
+  <si>
+    <t>MONTALVAO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01006044.1</t>
+  </si>
+  <si>
+    <t>01005983.3</t>
+  </si>
+  <si>
+    <t>DICOREL DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006061.1</t>
+  </si>
+  <si>
     <t>L G PRODUTOS HOSPITALARES LTDA</t>
   </si>
   <si>
-    <t>01005855.5</t>
-  </si>
-  <si>
-    <t>01005907.4</t>
-  </si>
-  <si>
-    <t>01006040.1</t>
-  </si>
-  <si>
-    <t>ATHUS HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01005994.1</t>
-  </si>
-  <si>
-    <t>01005955.3</t>
-  </si>
-  <si>
-    <t>01005920.4</t>
-  </si>
-  <si>
-    <t>01005951.3</t>
-  </si>
-  <si>
-    <t>01005968.3</t>
-  </si>
-  <si>
-    <t>01005892.5</t>
-  </si>
-  <si>
-    <t>01005934.4</t>
-  </si>
-  <si>
-    <t>MONTALVAO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01006044.1</t>
+    <t>01005988.3</t>
+  </si>
+  <si>
+    <t>01006025.2</t>
   </si>
 </sst>
 </file>
@@ -925,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -982,7 +976,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
@@ -1008,7 +1002,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -1034,7 +1028,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -1060,7 +1054,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -1086,7 +1080,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1112,7 +1106,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
@@ -1138,7 +1132,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
@@ -1164,7 +1158,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -1190,7 +1184,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>11</v>
@@ -1216,7 +1210,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -1242,7 +1236,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>11</v>
@@ -1268,7 +1262,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -1294,7 +1288,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
@@ -1320,7 +1314,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -1346,7 +1340,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>11</v>
@@ -1372,7 +1366,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -1398,7 +1392,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>11</v>
@@ -1424,7 +1418,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -1450,7 +1444,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>11</v>
@@ -1476,7 +1470,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -1502,7 +1496,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
@@ -1528,7 +1522,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -1554,7 +1548,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>11</v>
@@ -1580,7 +1574,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>17</v>
@@ -1606,7 +1600,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>11</v>
@@ -1632,7 +1626,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
@@ -1658,7 +1652,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -1684,7 +1678,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -1710,7 +1704,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>11</v>
@@ -1736,7 +1730,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -1762,7 +1756,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>17</v>
@@ -1788,7 +1782,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -1814,7 +1808,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
@@ -1840,7 +1834,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -1866,7 +1860,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>11</v>
@@ -1892,7 +1886,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -1918,7 +1912,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>11</v>
@@ -1944,7 +1938,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -1970,7 +1964,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>11</v>
@@ -1996,7 +1990,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -2022,7 +2016,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -2048,7 +2042,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -2074,7 +2068,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -2100,7 +2094,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -2126,7 +2120,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -2152,7 +2146,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -2178,7 +2172,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -2204,7 +2198,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -2230,7 +2224,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -2256,7 +2250,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -2282,7 +2276,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -2308,7 +2302,7 @@
         <v>4480</v>
       </c>
       <c r="F53" s="6">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>17</v>
@@ -2334,7 +2328,7 @@
         <v>48213.84</v>
       </c>
       <c r="F54" s="6">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
@@ -2358,7 +2352,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2382,7 +2376,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2406,7 +2400,7 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2430,7 +2424,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -2456,7 +2450,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -2467,83 +2461,85 @@
     </row>
     <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D60" s="4">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="E60" s="5">
-        <v>7584.01</v>
+        <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>37</v>
-      </c>
-      <c r="G60" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H60" s="3" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D61" s="4">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="E61" s="5">
-        <v>503.28</v>
+        <v>1812.31</v>
       </c>
       <c r="F61" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D62" s="4">
         <v>46105</v>
       </c>
       <c r="E62" s="5">
-        <v>1812.31</v>
+        <v>4434.51</v>
       </c>
       <c r="F62" s="6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>104</v>
@@ -2555,16 +2551,16 @@
         <v>46105</v>
       </c>
       <c r="E63" s="5">
-        <v>4434.51</v>
+        <v>5466.66</v>
       </c>
       <c r="F63" s="6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2572,23 +2568,21 @@
         <v>8</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="D64" s="4">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="E64" s="5">
-        <v>5466.66</v>
+        <v>9832.7000000000007</v>
       </c>
       <c r="F64" s="6">
-        <v>31</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
         <v>25</v>
       </c>
@@ -2598,86 +2592,88 @@
         <v>8</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="D65" s="4">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="E65" s="5">
-        <v>9832.7000000000007</v>
+        <v>1470</v>
       </c>
       <c r="F65" s="6">
-        <v>30</v>
-      </c>
-      <c r="G65" s="3"/>
+        <v>31</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H65" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="D66" s="4">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="E66" s="5">
-        <v>1470</v>
+        <v>5826.6</v>
       </c>
       <c r="F66" s="6">
         <v>28</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D67" s="4">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="E67" s="5">
-        <v>5826.6</v>
+        <v>1452.13</v>
       </c>
       <c r="F67" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D68" s="4">
         <v>46112</v>
@@ -2686,89 +2682,87 @@
         <v>4434.51</v>
       </c>
       <c r="F68" s="6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D69" s="4">
+        <v>46113</v>
+      </c>
+      <c r="E69" s="5">
+        <v>4646.54</v>
+      </c>
+      <c r="F69" s="6">
+        <v>26</v>
+      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="D69" s="4">
-        <v>46112</v>
-      </c>
-      <c r="E69" s="5">
-        <v>1452.13</v>
-      </c>
-      <c r="F69" s="6">
-        <v>24</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D70" s="4">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="E70" s="5">
-        <v>4646.54</v>
+        <v>3013.43</v>
       </c>
       <c r="F70" s="6">
-        <v>23</v>
-      </c>
-      <c r="G70" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H70" s="3" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>119</v>
       </c>
       <c r="D71" s="4">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="E71" s="5">
-        <v>3013.43</v>
+        <v>9832.7000000000007</v>
       </c>
       <c r="F71" s="6">
-        <v>22</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2776,57 +2770,59 @@
         <v>8</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D72" s="4">
-        <v>46116</v>
+        <v>46118</v>
       </c>
       <c r="E72" s="5">
-        <v>9832.7000000000007</v>
+        <v>1470</v>
       </c>
       <c r="F72" s="6">
-        <v>20</v>
-      </c>
-      <c r="G72" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H72" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D73" s="4">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="E73" s="5">
-        <v>1470</v>
+        <v>1452.14</v>
       </c>
       <c r="F73" s="6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>122</v>
@@ -2835,53 +2831,53 @@
         <v>46119</v>
       </c>
       <c r="E74" s="5">
-        <v>1452.14</v>
+        <v>1265.78</v>
       </c>
       <c r="F74" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D75" s="4">
         <v>46119</v>
       </c>
       <c r="E75" s="5">
-        <v>1265.78</v>
+        <v>6319.14</v>
       </c>
       <c r="F75" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D76" s="4">
         <v>46119</v>
@@ -2890,99 +2886,99 @@
         <v>4434.51</v>
       </c>
       <c r="F76" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>127</v>
       </c>
       <c r="D77" s="4">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="E77" s="5">
-        <v>6319.14</v>
+        <v>3013.43</v>
       </c>
       <c r="F77" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D78" s="4">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="E78" s="5">
-        <v>3013.43</v>
+        <v>10282.5</v>
       </c>
       <c r="F78" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D79" s="4">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="E79" s="5">
-        <v>10282.5</v>
+        <v>4434.51</v>
       </c>
       <c r="F79" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>130</v>
@@ -2994,21 +2990,21 @@
         <v>3150</v>
       </c>
       <c r="F80" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>131</v>
@@ -3017,22 +3013,24 @@
         <v>46126</v>
       </c>
       <c r="E81" s="5">
-        <v>9832.7000000000007</v>
+        <v>1265.78</v>
       </c>
       <c r="F81" s="6">
-        <v>10</v>
-      </c>
-      <c r="G81" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H81" s="3" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>132</v>
@@ -3041,76 +3039,74 @@
         <v>46126</v>
       </c>
       <c r="E82" s="5">
-        <v>4434.51</v>
+        <v>9832.7000000000007</v>
       </c>
       <c r="F82" s="6">
-        <v>10</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G82" s="3"/>
       <c r="H82" s="3" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D83" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E83" s="5">
-        <v>1265.78</v>
+        <v>1150.8</v>
       </c>
       <c r="F83" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>135</v>
       </c>
       <c r="D84" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="E84" s="5">
-        <v>1150.8</v>
+        <v>1470</v>
       </c>
       <c r="F84" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>136</v>
@@ -3119,50 +3115,50 @@
         <v>46128</v>
       </c>
       <c r="E85" s="5">
-        <v>1470</v>
+        <v>3013.43</v>
       </c>
       <c r="F85" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D86" s="4">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="E86" s="5">
-        <v>3013.43</v>
+        <v>2570.4</v>
       </c>
       <c r="F86" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>138</v>
@@ -3171,68 +3167,68 @@
         <v>46129</v>
       </c>
       <c r="E87" s="5">
-        <v>2570.4</v>
+        <v>5125.68</v>
       </c>
       <c r="F87" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D88" s="4">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="E88" s="5">
-        <v>5125.68</v>
+        <v>21334.44</v>
       </c>
       <c r="F88" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D89" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="E89" s="5">
-        <v>21334.44</v>
+        <v>863.1</v>
       </c>
       <c r="F89" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3240,7 +3236,7 @@
         <v>14</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>142</v>
@@ -3252,10 +3248,10 @@
         <v>863.1</v>
       </c>
       <c r="F90" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>45</v>
@@ -3263,54 +3259,54 @@
     </row>
     <row r="91" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="D91" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="E91" s="5">
-        <v>3499.88</v>
+        <v>1265.78</v>
       </c>
       <c r="F91" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D92" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="E92" s="5">
-        <v>6129.6</v>
+        <v>3150</v>
       </c>
       <c r="F92" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3318,19 +3314,19 @@
         <v>14</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D93" s="4">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="E93" s="5">
-        <v>863.1</v>
+        <v>1150.8</v>
       </c>
       <c r="F93" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>11</v>
@@ -3341,69 +3337,71 @@
     </row>
     <row r="94" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D94" s="4">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="E94" s="5">
-        <v>1763.27</v>
+        <v>3013.43</v>
       </c>
       <c r="F94" s="6">
         <v>4</v>
       </c>
-      <c r="G94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H94" s="3" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D95" s="4">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="E95" s="5">
-        <v>3150</v>
+        <v>12361.94</v>
       </c>
       <c r="F95" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D96" s="4">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="E96" s="5">
-        <v>3084.48</v>
+        <v>5125.68</v>
       </c>
       <c r="F96" s="6">
         <v>3</v>
@@ -3412,24 +3410,24 @@
         <v>17</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>151</v>
       </c>
       <c r="D97" s="4">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="E97" s="5">
-        <v>1265.78</v>
+        <v>4539</v>
       </c>
       <c r="F97" s="6">
         <v>3</v>
@@ -3438,30 +3436,30 @@
         <v>11</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D98" s="4">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="E98" s="5">
-        <v>1150.8</v>
+        <v>4422</v>
       </c>
       <c r="F98" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>45</v>
@@ -3472,77 +3470,25 @@
         <v>28</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D99" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="E99" s="5">
-        <v>2142</v>
+        <v>5112</v>
       </c>
       <c r="F99" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D100" s="4">
-        <v>46135</v>
-      </c>
-      <c r="E100" s="5">
-        <v>3013.43</v>
-      </c>
-      <c r="F100" s="6">
-        <v>1</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D101" s="4">
-        <v>46135</v>
-      </c>
-      <c r="E101" s="5">
-        <v>12361.94</v>
-      </c>
-      <c r="F101" s="6">
-        <v>1</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1E8AD6-F67D-4013-9FB8-05A45E589FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE12C2D5-9AC1-4DCA-85BA-FB503483CAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateCount="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="156">
   <si>
     <t>Funcionário</t>
   </si>
@@ -288,18 +288,18 @@
     <t>01004900.4</t>
   </si>
   <si>
+    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
+  </si>
+  <si>
+    <t>01005217.1BPBP</t>
+  </si>
+  <si>
     <t>BR MEDICAMENTOS LTDA</t>
   </si>
   <si>
     <t>01005075.3</t>
   </si>
   <si>
-    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
-  </si>
-  <si>
-    <t>01005217.1BPBP</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
@@ -321,175 +321,178 @@
     <t>01005781.3</t>
   </si>
   <si>
+    <t>MARCOS DUTRA</t>
+  </si>
+  <si>
+    <t>R7 DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005876.1</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01005683.3</t>
+  </si>
+  <si>
+    <t>JMC COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01005822.2</t>
+  </si>
+  <si>
+    <t>01005822.3</t>
+  </si>
+  <si>
+    <t>01005876.3</t>
+  </si>
+  <si>
     <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
   </si>
   <si>
-    <t>01005878.1</t>
-  </si>
-  <si>
-    <t>MARCOS DUTRA</t>
-  </si>
-  <si>
-    <t>R7 DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005876.1</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01005683.3</t>
-  </si>
-  <si>
-    <t>JMC COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01005822.2</t>
+    <t>01005878.3</t>
+  </si>
+  <si>
+    <t>01005876.4</t>
+  </si>
+  <si>
+    <t>01005951.2</t>
+  </si>
+  <si>
+    <t>01005822.4</t>
+  </si>
+  <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
+  </si>
+  <si>
+    <t>01005955.2</t>
+  </si>
+  <si>
+    <t>VITAL DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01005934.3</t>
+  </si>
+  <si>
+    <t>PI</t>
   </si>
   <si>
     <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
   </si>
   <si>
-    <t>01005881.1</t>
-  </si>
-  <si>
-    <t>DISTRIMEDICA COM PROD MED E ODONT LTDA</t>
-  </si>
-  <si>
-    <t>01005820.2</t>
-  </si>
-  <si>
-    <t>01005878.2</t>
-  </si>
-  <si>
-    <t>01005876.2</t>
-  </si>
-  <si>
-    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005839.3</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>VITAL DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01005934.1</t>
-  </si>
-  <si>
-    <t>01005822.3</t>
-  </si>
-  <si>
-    <t>01005881.2</t>
-  </si>
-  <si>
-    <t>01005878.3</t>
-  </si>
-  <si>
-    <t>01005951.1</t>
-  </si>
-  <si>
-    <t>KELLEN</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
-  </si>
-  <si>
-    <t>01005955.1</t>
-  </si>
-  <si>
-    <t>01005876.3</t>
-  </si>
-  <si>
-    <t>01005934.2</t>
-  </si>
-  <si>
-    <t>01005983.1</t>
-  </si>
-  <si>
-    <t>01005876.4</t>
-  </si>
-  <si>
-    <t>01005955.2</t>
-  </si>
-  <si>
-    <t>01005951.2</t>
-  </si>
-  <si>
-    <t>01005822.4</t>
+    <t>01005881.3</t>
+  </si>
+  <si>
+    <t>01005983.2</t>
+  </si>
+  <si>
+    <t>NOVA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006034.1</t>
+  </si>
+  <si>
+    <t>01005955.3</t>
+  </si>
+  <si>
+    <t>01005951.3</t>
+  </si>
+  <si>
+    <t>01005934.4</t>
+  </si>
+  <si>
+    <t>MONTALVAO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01006044.1</t>
+  </si>
+  <si>
+    <t>01005983.3</t>
+  </si>
+  <si>
+    <t>LEANDRA LUIZA SILVA</t>
+  </si>
+  <si>
+    <t>METTA FARMA DISTRIBUICAO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006048.1</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>01005881.4</t>
   </si>
   <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01005968.2</t>
-  </si>
-  <si>
-    <t>01005881.3</t>
-  </si>
-  <si>
-    <t>01005934.3</t>
-  </si>
-  <si>
-    <t>01005940.3</t>
-  </si>
-  <si>
-    <t>01005983.2</t>
-  </si>
-  <si>
-    <t>NOVA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006034.1</t>
-  </si>
-  <si>
-    <t>01005913.4</t>
-  </si>
-  <si>
-    <t>01006040.1</t>
-  </si>
-  <si>
-    <t>01005951.3</t>
-  </si>
-  <si>
-    <t>01005955.3</t>
-  </si>
-  <si>
-    <t>01005968.3</t>
-  </si>
-  <si>
-    <t>01005934.4</t>
-  </si>
-  <si>
-    <t>MONTALVAO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01006044.1</t>
-  </si>
-  <si>
-    <t>01005983.3</t>
-  </si>
-  <si>
-    <t>DICOREL DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006061.1</t>
-  </si>
-  <si>
-    <t>L G PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01005988.3</t>
-  </si>
-  <si>
-    <t>01006025.2</t>
+    <t>01006040.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01006060.1</t>
+  </si>
+  <si>
+    <t>01005951.4</t>
+  </si>
+  <si>
+    <t>01005955.4</t>
+  </si>
+  <si>
+    <t>01006077.1</t>
+  </si>
+  <si>
+    <t>C DE CARVALHO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01005935.5</t>
+  </si>
+  <si>
+    <t>01005983.4</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA PARNAIBA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006002.1</t>
+  </si>
+  <si>
+    <t>01006044.2</t>
+  </si>
+  <si>
+    <t>01006017.2</t>
+  </si>
+  <si>
+    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
+  </si>
+  <si>
+    <t>01005979.1</t>
+  </si>
+  <si>
+    <t>01006040.3</t>
+  </si>
+  <si>
+    <t>01006097.1</t>
+  </si>
+  <si>
+    <t>01006034.2</t>
+  </si>
+  <si>
+    <t>01006060.2</t>
+  </si>
+  <si>
+    <t>01006077.2</t>
   </si>
 </sst>
 </file>
@@ -919,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -976,7 +979,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
@@ -1002,7 +1005,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -1028,7 +1031,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -1054,7 +1057,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -1080,7 +1083,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1106,7 +1109,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
@@ -1132,7 +1135,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
@@ -1158,7 +1161,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -1184,7 +1187,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>11</v>
@@ -1210,7 +1213,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -1236,7 +1239,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>11</v>
@@ -1262,7 +1265,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -1288,7 +1291,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
@@ -1314,7 +1317,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -1340,7 +1343,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>11</v>
@@ -1366,7 +1369,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -1392,7 +1395,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>11</v>
@@ -1418,7 +1421,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -1444,7 +1447,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>11</v>
@@ -1470,7 +1473,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -1496,7 +1499,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
@@ -1522,7 +1525,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -1548,7 +1551,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>11</v>
@@ -1574,7 +1577,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>17</v>
@@ -1600,7 +1603,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>11</v>
@@ -1626,7 +1629,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
@@ -1652,7 +1655,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -1678,7 +1681,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -1704,7 +1707,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>11</v>
@@ -1730,7 +1733,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -1756,7 +1759,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>17</v>
@@ -1782,7 +1785,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -1808,7 +1811,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
@@ -1834,7 +1837,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -1860,7 +1863,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>11</v>
@@ -1886,7 +1889,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -1912,7 +1915,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>11</v>
@@ -1938,7 +1941,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -1964,7 +1967,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>11</v>
@@ -1990,7 +1993,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -2016,7 +2019,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -2042,7 +2045,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -2068,7 +2071,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -2094,7 +2097,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -2120,7 +2123,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -2146,7 +2149,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -2172,7 +2175,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -2198,7 +2201,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -2224,7 +2227,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -2250,7 +2253,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -2276,7 +2279,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -2287,7 +2290,7 @@
     </row>
     <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>87</v>
@@ -2299,21 +2302,19 @@
         <v>45980</v>
       </c>
       <c r="E53" s="5">
-        <v>4480</v>
+        <v>48213.84</v>
       </c>
       <c r="F53" s="6">
-        <v>159</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>89</v>
@@ -2325,14 +2326,16 @@
         <v>45980</v>
       </c>
       <c r="E54" s="5">
-        <v>48213.84</v>
+        <v>4480</v>
       </c>
       <c r="F54" s="6">
-        <v>159</v>
-      </c>
-      <c r="G54" s="3"/>
+        <v>168</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H54" s="3" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2340,7 +2343,7 @@
         <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>91</v>
@@ -2352,7 +2355,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2364,7 +2367,7 @@
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>92</v>
@@ -2376,7 +2379,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2388,7 +2391,7 @@
         <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>93</v>
@@ -2400,7 +2403,7 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2424,7 +2427,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -2450,7 +2453,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -2476,7 +2479,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>17</v>
@@ -2487,54 +2490,54 @@
     </row>
     <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D61" s="4">
         <v>46105</v>
       </c>
       <c r="E61" s="5">
-        <v>1812.31</v>
+        <v>4434.51</v>
       </c>
       <c r="F61" s="6">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D62" s="4">
         <v>46105</v>
       </c>
       <c r="E62" s="5">
-        <v>4434.51</v>
+        <v>5466.66</v>
       </c>
       <c r="F62" s="6">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2548,17 +2551,15 @@
         <v>105</v>
       </c>
       <c r="D63" s="4">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="E63" s="5">
-        <v>5466.66</v>
+        <v>9832.7000000000007</v>
       </c>
       <c r="F63" s="6">
-        <v>34</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
         <v>25</v>
       </c>
@@ -2568,19 +2569,19 @@
         <v>8</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="D64" s="4">
-        <v>46106</v>
+        <v>46116</v>
       </c>
       <c r="E64" s="5">
         <v>9832.7000000000007</v>
       </c>
       <c r="F64" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
@@ -2589,180 +2590,182 @@
     </row>
     <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D65" s="4">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="E65" s="5">
-        <v>1470</v>
+        <v>4434.51</v>
       </c>
       <c r="F65" s="6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D66" s="4">
-        <v>46111</v>
+        <v>46119</v>
       </c>
       <c r="E66" s="5">
-        <v>5826.6</v>
+        <v>1452.14</v>
       </c>
       <c r="F66" s="6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D67" s="4">
-        <v>46112</v>
+        <v>46126</v>
       </c>
       <c r="E67" s="5">
-        <v>1452.13</v>
+        <v>4434.51</v>
       </c>
       <c r="F67" s="6">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E68" s="5">
+        <v>1265.78</v>
+      </c>
+      <c r="F68" s="6">
+        <v>22</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D68" s="4">
-        <v>46112</v>
-      </c>
-      <c r="E68" s="5">
-        <v>4434.51</v>
-      </c>
-      <c r="F68" s="6">
-        <v>27</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D69" s="4">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="E69" s="5">
-        <v>4646.54</v>
+        <v>9832.7000000000007</v>
       </c>
       <c r="F69" s="6">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D70" s="4">
-        <v>46114</v>
+        <v>46126</v>
       </c>
       <c r="E70" s="5">
-        <v>3013.43</v>
+        <v>3150</v>
       </c>
       <c r="F70" s="6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D71" s="4">
-        <v>46116</v>
+        <v>46128</v>
       </c>
       <c r="E71" s="5">
-        <v>9832.7000000000007</v>
+        <v>3013.43</v>
       </c>
       <c r="F71" s="6">
-        <v>23</v>
-      </c>
-      <c r="G71" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H71" s="3" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2770,19 +2773,19 @@
         <v>8</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D72" s="4">
-        <v>46118</v>
+        <v>46128</v>
       </c>
       <c r="E72" s="5">
         <v>1470</v>
       </c>
       <c r="F72" s="6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>11</v>
@@ -2793,338 +2796,338 @@
     </row>
     <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D73" s="4">
-        <v>46119</v>
+        <v>46129</v>
       </c>
       <c r="E73" s="5">
-        <v>1452.14</v>
+        <v>5125.68</v>
       </c>
       <c r="F73" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D74" s="4">
-        <v>46119</v>
+        <v>46131</v>
       </c>
       <c r="E74" s="5">
-        <v>1265.78</v>
+        <v>21334.44</v>
       </c>
       <c r="F74" s="6">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="D75" s="4">
-        <v>46119</v>
+        <v>46133</v>
       </c>
       <c r="E75" s="5">
-        <v>6319.14</v>
+        <v>3150</v>
       </c>
       <c r="F75" s="6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D76" s="4">
+        <v>46133</v>
+      </c>
+      <c r="E76" s="5">
+        <v>1265.78</v>
+      </c>
+      <c r="F76" s="6">
+        <v>15</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D76" s="4">
-        <v>46119</v>
-      </c>
-      <c r="E76" s="5">
-        <v>4434.51</v>
-      </c>
-      <c r="F76" s="6">
-        <v>20</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D77" s="4">
-        <v>46121</v>
+        <v>46135</v>
       </c>
       <c r="E77" s="5">
         <v>3013.43</v>
       </c>
       <c r="F77" s="6">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D78" s="4">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="E78" s="5">
-        <v>10282.5</v>
+        <v>12361.94</v>
       </c>
       <c r="F78" s="6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D79" s="4">
-        <v>46126</v>
+        <v>46136</v>
       </c>
       <c r="E79" s="5">
-        <v>4434.51</v>
+        <v>5125.68</v>
       </c>
       <c r="F79" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D80" s="4">
-        <v>46126</v>
+        <v>46138</v>
       </c>
       <c r="E80" s="5">
-        <v>3150</v>
+        <v>4494.08</v>
       </c>
       <c r="F80" s="6">
-        <v>13</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G80" s="3"/>
       <c r="H80" s="3" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D81" s="4">
-        <v>46126</v>
+        <v>46138</v>
       </c>
       <c r="E81" s="5">
-        <v>1265.78</v>
+        <v>1470</v>
       </c>
       <c r="F81" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D82" s="4">
-        <v>46126</v>
+        <v>46139</v>
       </c>
       <c r="E82" s="5">
-        <v>9832.7000000000007</v>
+        <v>863.1</v>
       </c>
       <c r="F82" s="6">
-        <v>13</v>
-      </c>
-      <c r="G82" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H82" s="3" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D83" s="4">
-        <v>46127</v>
+        <v>46139</v>
       </c>
       <c r="E83" s="5">
-        <v>1150.8</v>
+        <v>7889.44</v>
       </c>
       <c r="F83" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D84" s="4">
+        <v>46140</v>
+      </c>
+      <c r="E84" s="5">
+        <v>1265.78</v>
+      </c>
+      <c r="F84" s="6">
         <v>8</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D84" s="4">
-        <v>46128</v>
-      </c>
-      <c r="E84" s="5">
-        <v>1470</v>
-      </c>
-      <c r="F84" s="6">
-        <v>11</v>
-      </c>
       <c r="G84" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D85" s="4">
-        <v>46128</v>
+        <v>46140</v>
       </c>
       <c r="E85" s="5">
-        <v>3013.43</v>
+        <v>3150</v>
       </c>
       <c r="F85" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3132,22 +3135,22 @@
         <v>14</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D86" s="4">
-        <v>46129</v>
+        <v>46140</v>
       </c>
       <c r="E86" s="5">
-        <v>2570.4</v>
+        <v>3672</v>
       </c>
       <c r="F86" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>45</v>
@@ -3155,158 +3158,158 @@
     </row>
     <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D87" s="4">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="E87" s="5">
-        <v>5125.68</v>
+        <v>3284.64</v>
       </c>
       <c r="F87" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D88" s="4">
-        <v>46131</v>
+        <v>46143</v>
       </c>
       <c r="E88" s="5">
-        <v>21334.44</v>
+        <v>5125.68</v>
       </c>
       <c r="F88" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D89" s="4">
-        <v>46132</v>
+        <v>46144</v>
       </c>
       <c r="E89" s="5">
-        <v>863.1</v>
+        <v>2100</v>
       </c>
       <c r="F89" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D90" s="4">
-        <v>46132</v>
+        <v>46145</v>
       </c>
       <c r="E90" s="5">
-        <v>863.1</v>
+        <v>7020</v>
       </c>
       <c r="F90" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D91" s="4">
-        <v>46133</v>
+        <v>46145</v>
       </c>
       <c r="E91" s="5">
-        <v>1265.78</v>
+        <v>15028</v>
       </c>
       <c r="F91" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D92" s="4">
-        <v>46133</v>
+        <v>46145</v>
       </c>
       <c r="E92" s="5">
-        <v>3150</v>
+        <v>3316.11</v>
       </c>
       <c r="F92" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3314,19 +3317,19 @@
         <v>14</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D93" s="4">
-        <v>46134</v>
+        <v>46146</v>
       </c>
       <c r="E93" s="5">
-        <v>1150.8</v>
+        <v>863.1</v>
       </c>
       <c r="F93" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>11</v>
@@ -3337,28 +3340,28 @@
     </row>
     <row r="94" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D94" s="4">
-        <v>46135</v>
+        <v>46146</v>
       </c>
       <c r="E94" s="5">
-        <v>3013.43</v>
+        <v>1109.7</v>
       </c>
       <c r="F94" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3366,128 +3369,76 @@
         <v>8</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D95" s="4">
-        <v>46135</v>
+        <v>46146</v>
       </c>
       <c r="E95" s="5">
-        <v>12361.94</v>
+        <v>12096</v>
       </c>
       <c r="F95" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D96" s="4">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="E96" s="5">
-        <v>5125.68</v>
+        <v>4375</v>
       </c>
       <c r="F96" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D97" s="4">
-        <v>46136</v>
+        <v>46147</v>
       </c>
       <c r="E97" s="5">
-        <v>4539</v>
+        <v>3672</v>
       </c>
       <c r="F97" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D98" s="4">
-        <v>46136</v>
-      </c>
-      <c r="E98" s="5">
-        <v>4422</v>
-      </c>
-      <c r="F98" s="6">
-        <v>3</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D99" s="4">
-        <v>46136</v>
-      </c>
-      <c r="E99" s="5">
-        <v>5112</v>
-      </c>
-      <c r="F99" s="6">
-        <v>3</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H99" s="3" t="s">
         <v>45</v>
       </c>
     </row>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE12C2D5-9AC1-4DCA-85BA-FB503483CAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0786B0DB-161C-467A-9127-CB1B14DB8C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateCount="1"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="146">
   <si>
     <t>Funcionário</t>
   </si>
@@ -288,16 +288,16 @@
     <t>01004900.4</t>
   </si>
   <si>
+    <t>BR MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005075.3</t>
+  </si>
+  <si>
     <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
   </si>
   <si>
-    <t>01005217.1BPBP</t>
-  </si>
-  <si>
-    <t>BR MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005075.3</t>
+    <t>01005217.1BPBPBP</t>
   </si>
   <si>
     <t>01005217.2BP</t>
@@ -339,33 +339,15 @@
     <t>01005683.3</t>
   </si>
   <si>
-    <t>JMC COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01005822.2</t>
-  </si>
-  <si>
-    <t>01005822.3</t>
-  </si>
-  <si>
     <t>01005876.3</t>
   </si>
   <si>
-    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
-  </si>
-  <si>
-    <t>01005878.3</t>
-  </si>
-  <si>
     <t>01005876.4</t>
   </si>
   <si>
     <t>01005951.2</t>
   </si>
   <si>
-    <t>01005822.4</t>
-  </si>
-  <si>
     <t>KELLEN</t>
   </si>
   <si>
@@ -408,15 +390,12 @@
     <t>01005934.4</t>
   </si>
   <si>
-    <t>MONTALVAO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01006044.1</t>
-  </si>
-  <si>
     <t>01005983.3</t>
   </si>
   <si>
+    <t>01005881.4</t>
+  </si>
+  <si>
     <t>LEANDRA LUIZA SILVA</t>
   </si>
   <si>
@@ -429,55 +408,46 @@
     <t>AM</t>
   </si>
   <si>
-    <t>01005881.4</t>
-  </si>
-  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
     <t>01006040.2</t>
   </si>
   <si>
+    <t>01006077.1</t>
+  </si>
+  <si>
+    <t>01005955.4</t>
+  </si>
+  <si>
+    <t>01005951.4</t>
+  </si>
+  <si>
+    <t>C DE CARVALHO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01005935.5</t>
+  </si>
+  <si>
+    <t>01005983.4</t>
+  </si>
+  <si>
+    <t>01006017.2</t>
+  </si>
+  <si>
+    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
+  </si>
+  <si>
+    <t>01005979.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
   </si>
   <si>
-    <t>01006060.1</t>
-  </si>
-  <si>
-    <t>01005951.4</t>
-  </si>
-  <si>
-    <t>01005955.4</t>
-  </si>
-  <si>
-    <t>01006077.1</t>
-  </si>
-  <si>
-    <t>C DE CARVALHO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01005935.5</t>
-  </si>
-  <si>
-    <t>01005983.4</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA PARNAIBA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006002.1</t>
-  </si>
-  <si>
-    <t>01006044.2</t>
-  </si>
-  <si>
-    <t>01006017.2</t>
-  </si>
-  <si>
-    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
-  </si>
-  <si>
-    <t>01005979.1</t>
+    <t>01006060.2</t>
+  </si>
+  <si>
+    <t>01006034.2</t>
   </si>
   <si>
     <t>01006040.3</t>
@@ -486,13 +456,13 @@
     <t>01006097.1</t>
   </si>
   <si>
-    <t>01006034.2</t>
-  </si>
-  <si>
-    <t>01006060.2</t>
-  </si>
-  <si>
     <t>01006077.2</t>
+  </si>
+  <si>
+    <t>MP COMERCIO DE PRODUTOS HOSPITALARES E ALIMENTICIO</t>
+  </si>
+  <si>
+    <t>01006100.1</t>
   </si>
 </sst>
 </file>
@@ -922,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -979,7 +949,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
@@ -1005,7 +975,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -1031,7 +1001,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -1057,7 +1027,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -1083,7 +1053,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1109,7 +1079,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
@@ -1135,7 +1105,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
@@ -1161,7 +1131,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -1187,7 +1157,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>11</v>
@@ -1213,7 +1183,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -1239,7 +1209,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>11</v>
@@ -1265,7 +1235,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -1291,7 +1261,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
@@ -1317,7 +1287,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -1343,7 +1313,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>11</v>
@@ -1369,7 +1339,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -1395,7 +1365,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>11</v>
@@ -1421,7 +1391,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -1447,7 +1417,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>11</v>
@@ -1473,7 +1443,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -1499,7 +1469,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
@@ -1525,7 +1495,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -1551,7 +1521,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>11</v>
@@ -1577,7 +1547,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>17</v>
@@ -1603,7 +1573,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>11</v>
@@ -1629,7 +1599,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
@@ -1655,7 +1625,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -1681,7 +1651,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -1707,7 +1677,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>11</v>
@@ -1733,7 +1703,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -1759,7 +1729,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>17</v>
@@ -1785,7 +1755,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -1811,7 +1781,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
@@ -1837,7 +1807,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -1863,7 +1833,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>11</v>
@@ -1889,7 +1859,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -1915,7 +1885,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>11</v>
@@ -1941,7 +1911,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -1967,7 +1937,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>11</v>
@@ -1993,7 +1963,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -2019,7 +1989,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -2045,7 +2015,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -2071,7 +2041,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -2097,7 +2067,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -2123,7 +2093,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -2149,7 +2119,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -2175,7 +2145,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -2201,7 +2171,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -2227,7 +2197,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -2253,7 +2223,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -2279,7 +2249,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -2290,7 +2260,7 @@
     </row>
     <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>87</v>
@@ -2302,19 +2272,21 @@
         <v>45980</v>
       </c>
       <c r="E53" s="5">
-        <v>48213.84</v>
+        <v>4480</v>
       </c>
       <c r="F53" s="6">
-        <v>168</v>
-      </c>
-      <c r="G53" s="3"/>
+        <v>169</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H53" s="3" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>89</v>
@@ -2326,16 +2298,14 @@
         <v>45980</v>
       </c>
       <c r="E54" s="5">
-        <v>4480</v>
+        <v>38840.89</v>
       </c>
       <c r="F54" s="6">
-        <v>168</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2343,7 +2313,7 @@
         <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>91</v>
@@ -2355,7 +2325,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2367,7 +2337,7 @@
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>92</v>
@@ -2379,7 +2349,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2391,7 +2361,7 @@
         <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>93</v>
@@ -2403,7 +2373,7 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2427,7 +2397,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -2453,7 +2423,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -2479,7 +2449,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>17</v>
@@ -2505,7 +2475,7 @@
         <v>4434.51</v>
       </c>
       <c r="F61" s="6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>17</v>
@@ -2531,7 +2501,7 @@
         <v>5466.66</v>
       </c>
       <c r="F62" s="6">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>11</v>
@@ -2542,50 +2512,54 @@
     </row>
     <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="D63" s="4">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="E63" s="5">
-        <v>9832.7000000000007</v>
+        <v>4434.51</v>
       </c>
       <c r="F63" s="6">
-        <v>42</v>
-      </c>
-      <c r="G63" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H63" s="3" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D64" s="4">
-        <v>46116</v>
+        <v>46126</v>
       </c>
       <c r="E64" s="5">
-        <v>9832.7000000000007</v>
+        <v>4434.51</v>
       </c>
       <c r="F64" s="6">
-        <v>32</v>
-      </c>
-      <c r="G64" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H64" s="3" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2596,19 +2570,19 @@
         <v>99</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D65" s="4">
-        <v>46119</v>
+        <v>46126</v>
       </c>
       <c r="E65" s="5">
-        <v>4434.51</v>
+        <v>1265.78</v>
       </c>
       <c r="F65" s="6">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>101</v>
@@ -2616,7 +2590,7 @@
     </row>
     <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>28</v>
+        <v>107</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>108</v>
@@ -2625,19 +2599,19 @@
         <v>109</v>
       </c>
       <c r="D66" s="4">
-        <v>46119</v>
+        <v>46126</v>
       </c>
       <c r="E66" s="5">
-        <v>1452.14</v>
+        <v>3150</v>
       </c>
       <c r="F66" s="6">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2645,329 +2619,329 @@
         <v>98</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D67" s="4">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="E67" s="5">
-        <v>4434.51</v>
+        <v>3013.43</v>
       </c>
       <c r="F67" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D68" s="4">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="E68" s="5">
-        <v>1265.78</v>
+        <v>1470</v>
       </c>
       <c r="F68" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D69" s="4">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="E69" s="5">
-        <v>9832.7000000000007</v>
+        <v>5125.68</v>
       </c>
       <c r="F69" s="6">
-        <v>22</v>
-      </c>
-      <c r="G69" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H69" s="3" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D70" s="4">
-        <v>46126</v>
+        <v>46131</v>
       </c>
       <c r="E70" s="5">
-        <v>3150</v>
+        <v>21334.44</v>
       </c>
       <c r="F70" s="6">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D71" s="4">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="E71" s="5">
-        <v>3013.43</v>
+        <v>3150</v>
       </c>
       <c r="F71" s="6">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="D72" s="4">
-        <v>46128</v>
+        <v>46133</v>
       </c>
       <c r="E72" s="5">
-        <v>1470</v>
+        <v>1265.78</v>
       </c>
       <c r="F72" s="6">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D73" s="4">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="E73" s="5">
-        <v>5125.68</v>
+        <v>3013.43</v>
       </c>
       <c r="F73" s="6">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D74" s="4">
-        <v>46131</v>
+        <v>46136</v>
       </c>
       <c r="E74" s="5">
-        <v>21334.44</v>
+        <v>5125.68</v>
       </c>
       <c r="F74" s="6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="C75" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D75" s="4">
-        <v>46133</v>
+        <v>46138</v>
       </c>
       <c r="E75" s="5">
-        <v>3150</v>
+        <v>1470</v>
       </c>
       <c r="F75" s="6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D76" s="4">
-        <v>46133</v>
+        <v>46138</v>
       </c>
       <c r="E76" s="5">
-        <v>1265.78</v>
+        <v>4494.08</v>
       </c>
       <c r="F76" s="6">
-        <v>15</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D77" s="4">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="E77" s="5">
-        <v>3013.43</v>
+        <v>863.1</v>
       </c>
       <c r="F77" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>127</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D78" s="4">
-        <v>46135</v>
+        <v>46140</v>
       </c>
       <c r="E78" s="5">
-        <v>12361.94</v>
+        <v>3672</v>
       </c>
       <c r="F78" s="6">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D79" s="4">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="E79" s="5">
-        <v>5125.68</v>
+        <v>3150</v>
       </c>
       <c r="F79" s="6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>17</v>
@@ -2978,104 +2952,106 @@
     </row>
     <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="D80" s="4">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="E80" s="5">
-        <v>4494.08</v>
+        <v>1265.78</v>
       </c>
       <c r="F80" s="6">
-        <v>10</v>
-      </c>
-      <c r="G80" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H80" s="3" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D81" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="E81" s="5">
-        <v>1470</v>
+        <v>3284.64</v>
       </c>
       <c r="F81" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D82" s="4">
-        <v>46139</v>
+        <v>46143</v>
       </c>
       <c r="E82" s="5">
-        <v>863.1</v>
+        <v>5125.68</v>
       </c>
       <c r="F82" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D83" s="4">
-        <v>46139</v>
+        <v>46145</v>
       </c>
       <c r="E83" s="5">
-        <v>7889.44</v>
+        <v>15028</v>
       </c>
       <c r="F83" s="6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3083,19 +3059,19 @@
         <v>98</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D84" s="4">
-        <v>46140</v>
+        <v>46145</v>
       </c>
       <c r="E84" s="5">
-        <v>1265.78</v>
+        <v>3316.11</v>
       </c>
       <c r="F84" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>11</v>
@@ -3106,340 +3082,158 @@
     </row>
     <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D85" s="4">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="E85" s="5">
-        <v>3150</v>
+        <v>4375</v>
       </c>
       <c r="F85" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D86" s="4">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="E86" s="5">
-        <v>3672</v>
+        <v>12096</v>
       </c>
       <c r="F86" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D87" s="4">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="E87" s="5">
-        <v>3284.64</v>
+        <v>863.1</v>
       </c>
       <c r="F87" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D88" s="4">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="E88" s="5">
-        <v>5125.68</v>
+        <v>1109.7</v>
       </c>
       <c r="F88" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D89" s="4">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="E89" s="5">
-        <v>2100</v>
+        <v>3672</v>
       </c>
       <c r="F89" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D90" s="4">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="E90" s="5">
-        <v>7020</v>
+        <v>9982.9</v>
       </c>
       <c r="F90" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D91" s="4">
-        <v>46145</v>
-      </c>
-      <c r="E91" s="5">
-        <v>15028</v>
-      </c>
-      <c r="F91" s="6">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D92" s="4">
-        <v>46145</v>
-      </c>
-      <c r="E92" s="5">
-        <v>3316.11</v>
-      </c>
-      <c r="F92" s="6">
-        <v>3</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D93" s="4">
-        <v>46146</v>
-      </c>
-      <c r="E93" s="5">
-        <v>863.1</v>
-      </c>
-      <c r="F93" s="6">
-        <v>2</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D94" s="4">
-        <v>46146</v>
-      </c>
-      <c r="E94" s="5">
-        <v>1109.7</v>
-      </c>
-      <c r="F94" s="6">
-        <v>2</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D95" s="4">
-        <v>46146</v>
-      </c>
-      <c r="E95" s="5">
-        <v>12096</v>
-      </c>
-      <c r="F95" s="6">
-        <v>2</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D96" s="4">
-        <v>46146</v>
-      </c>
-      <c r="E96" s="5">
-        <v>4375</v>
-      </c>
-      <c r="F96" s="6">
-        <v>2</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D97" s="4">
-        <v>46147</v>
-      </c>
-      <c r="E97" s="5">
-        <v>3672</v>
-      </c>
-      <c r="F97" s="6">
-        <v>1</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0786B0DB-161C-467A-9127-CB1B14DB8C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBDFAF6-4551-4DD9-A951-987FF8F7C991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'XLS_Grid_LANCAMENTO A RECEBER'!$A$1:$H$90</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="148">
   <si>
     <t>Funcionário</t>
   </si>
@@ -348,30 +351,27 @@
     <t>01005951.2</t>
   </si>
   <si>
+    <t>VITAL DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01005934.3</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
+  </si>
+  <si>
+    <t>01005881.3</t>
+  </si>
+  <si>
     <t>KELLEN</t>
   </si>
   <si>
     <t>DISTRIBUIDORA BELLFARMA LTDA</t>
   </si>
   <si>
-    <t>01005955.2</t>
-  </si>
-  <si>
-    <t>VITAL DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01005934.3</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
-  </si>
-  <si>
-    <t>01005881.3</t>
-  </si>
-  <si>
     <t>01005983.2</t>
   </si>
   <si>
@@ -381,12 +381,12 @@
     <t>01006034.1</t>
   </si>
   <si>
+    <t>01005951.3</t>
+  </si>
+  <si>
     <t>01005955.3</t>
   </si>
   <si>
-    <t>01005951.3</t>
-  </si>
-  <si>
     <t>01005934.4</t>
   </si>
   <si>
@@ -411,9 +411,6 @@
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006040.2</t>
-  </si>
-  <si>
     <t>01006077.1</t>
   </si>
   <si>
@@ -432,27 +429,21 @@
     <t>01005983.4</t>
   </si>
   <si>
-    <t>01006017.2</t>
-  </si>
-  <si>
     <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
   </si>
   <si>
     <t>01005979.1</t>
   </si>
   <si>
+    <t>01006034.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
   </si>
   <si>
     <t>01006060.2</t>
   </si>
   <si>
-    <t>01006034.2</t>
-  </si>
-  <si>
-    <t>01006040.3</t>
-  </si>
-  <si>
     <t>01006097.1</t>
   </si>
   <si>
@@ -463,6 +454,24 @@
   </si>
   <si>
     <t>01006100.1</t>
+  </si>
+  <si>
+    <t>01006109.1</t>
+  </si>
+  <si>
+    <t>RR COMERCIO DE PRODUTOS FARMACEUTICOS E HOSPITALAR</t>
+  </si>
+  <si>
+    <t>01006112.1</t>
+  </si>
+  <si>
+    <t>L G PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01005988.5</t>
+  </si>
+  <si>
+    <t>01006025.4</t>
   </si>
 </sst>
 </file>
@@ -949,7 +958,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
@@ -975,7 +984,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -1001,7 +1010,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -1027,7 +1036,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -1053,7 +1062,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1079,7 +1088,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
@@ -1105,7 +1114,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
@@ -1131,7 +1140,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -1157,7 +1166,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>11</v>
@@ -1183,7 +1192,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -1209,7 +1218,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>11</v>
@@ -1235,7 +1244,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -1261,7 +1270,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
@@ -1287,7 +1296,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -1313,7 +1322,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>11</v>
@@ -1339,7 +1348,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -1365,7 +1374,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>11</v>
@@ -1391,7 +1400,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -1417,7 +1426,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>11</v>
@@ -1443,7 +1452,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -1469,7 +1478,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
@@ -1495,7 +1504,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -1521,7 +1530,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>11</v>
@@ -1547,7 +1556,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>17</v>
@@ -1573,7 +1582,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>11</v>
@@ -1599,7 +1608,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
@@ -1625,7 +1634,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -1651,7 +1660,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -1677,7 +1686,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>11</v>
@@ -1703,7 +1712,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -1729,7 +1738,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>17</v>
@@ -1755,7 +1764,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -1781,7 +1790,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
@@ -1807,7 +1816,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -1833,7 +1842,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>11</v>
@@ -1859,7 +1868,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -1885,7 +1894,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>11</v>
@@ -1911,7 +1920,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -1937,7 +1946,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>11</v>
@@ -1963,7 +1972,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -1989,7 +1998,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -2015,7 +2024,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -2041,7 +2050,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -2067,7 +2076,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -2093,7 +2102,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -2119,7 +2128,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -2145,7 +2154,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -2171,7 +2180,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -2197,7 +2206,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -2223,7 +2232,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -2249,7 +2258,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -2275,7 +2284,7 @@
         <v>4480</v>
       </c>
       <c r="F53" s="6">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>17</v>
@@ -2301,7 +2310,7 @@
         <v>38840.89</v>
       </c>
       <c r="F54" s="6">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
@@ -2325,7 +2334,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2349,7 +2358,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2373,7 +2382,7 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2397,7 +2406,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -2423,7 +2432,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -2449,7 +2458,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>17</v>
@@ -2475,7 +2484,7 @@
         <v>4434.51</v>
       </c>
       <c r="F61" s="6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>17</v>
@@ -2501,7 +2510,7 @@
         <v>5466.66</v>
       </c>
       <c r="F62" s="6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>11</v>
@@ -2527,7 +2536,7 @@
         <v>4434.51</v>
       </c>
       <c r="F63" s="6">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>17</v>
@@ -2553,7 +2562,7 @@
         <v>4434.51</v>
       </c>
       <c r="F64" s="6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>17</v>
@@ -2579,7 +2588,7 @@
         <v>1265.78</v>
       </c>
       <c r="F65" s="6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>11</v>
@@ -2590,33 +2599,33 @@
     </row>
     <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="D66" s="4">
+        <v>46128</v>
+      </c>
+      <c r="E66" s="5">
+        <v>3013.43</v>
+      </c>
+      <c r="F66" s="6">
+        <v>25</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="D66" s="4">
-        <v>46126</v>
-      </c>
-      <c r="E66" s="5">
-        <v>3150</v>
-      </c>
-      <c r="F66" s="6">
-        <v>23</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>110</v>
@@ -2628,21 +2637,21 @@
         <v>46128</v>
       </c>
       <c r="E67" s="5">
-        <v>3013.43</v>
+        <v>1470</v>
       </c>
       <c r="F67" s="6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>113</v>
@@ -2651,79 +2660,79 @@
         <v>114</v>
       </c>
       <c r="D68" s="4">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="E68" s="5">
-        <v>1470</v>
+        <v>5125.68</v>
       </c>
       <c r="F68" s="6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D69" s="4">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="E69" s="5">
-        <v>5125.68</v>
+        <v>21334.44</v>
       </c>
       <c r="F69" s="6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D70" s="4">
-        <v>46131</v>
+        <v>46133</v>
       </c>
       <c r="E70" s="5">
-        <v>21334.44</v>
+        <v>1265.78</v>
       </c>
       <c r="F70" s="6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>118</v>
@@ -2735,7 +2744,7 @@
         <v>3150</v>
       </c>
       <c r="F71" s="6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>17</v>
@@ -2749,161 +2758,161 @@
         <v>98</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>119</v>
       </c>
       <c r="D72" s="4">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="E72" s="5">
-        <v>1265.78</v>
+        <v>3013.43</v>
       </c>
       <c r="F72" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D73" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="E73" s="5">
-        <v>3013.43</v>
+        <v>5125.68</v>
       </c>
       <c r="F73" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D74" s="4">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="E74" s="5">
-        <v>5125.68</v>
+        <v>1470</v>
       </c>
       <c r="F74" s="6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D75" s="4">
         <v>46138</v>
       </c>
       <c r="E75" s="5">
-        <v>1470</v>
+        <v>4494.08</v>
       </c>
       <c r="F75" s="6">
-        <v>11</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G75" s="3"/>
       <c r="H75" s="3" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>123</v>
+        <v>14</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D76" s="4">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="E76" s="5">
-        <v>4494.08</v>
+        <v>3672</v>
       </c>
       <c r="F76" s="6">
-        <v>11</v>
-      </c>
-      <c r="G76" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H76" s="3" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D77" s="4">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="E77" s="5">
-        <v>863.1</v>
+        <v>3150</v>
       </c>
       <c r="F77" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>129</v>
@@ -2912,65 +2921,65 @@
         <v>46140</v>
       </c>
       <c r="E78" s="5">
-        <v>3672</v>
+        <v>1265.78</v>
       </c>
       <c r="F78" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D79" s="4">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="E79" s="5">
-        <v>3150</v>
+        <v>3284.64</v>
       </c>
       <c r="F79" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D80" s="4">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="E80" s="5">
-        <v>1265.78</v>
+        <v>5125.68</v>
       </c>
       <c r="F80" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>101</v>
@@ -2981,227 +2990,227 @@
         <v>98</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D81" s="4">
-        <v>46142</v>
+        <v>46145</v>
       </c>
       <c r="E81" s="5">
-        <v>3284.64</v>
+        <v>3316.11</v>
       </c>
       <c r="F81" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D82" s="4">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="E82" s="5">
-        <v>5125.68</v>
+        <v>12096</v>
       </c>
       <c r="F82" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D83" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="E83" s="5">
-        <v>15028</v>
+        <v>4375</v>
       </c>
       <c r="F83" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D84" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="E84" s="5">
-        <v>3316.11</v>
+        <v>1109.7</v>
       </c>
       <c r="F84" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>139</v>
       </c>
       <c r="D85" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="E85" s="5">
-        <v>4375</v>
+        <v>3672</v>
       </c>
       <c r="F85" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D86" s="4">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="E86" s="5">
-        <v>12096</v>
+        <v>9982.9</v>
       </c>
       <c r="F86" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D87" s="4">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="E87" s="5">
-        <v>863.1</v>
+        <v>3118.8</v>
       </c>
       <c r="F87" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D88" s="4">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="E88" s="5">
-        <v>1109.7</v>
+        <v>7966.96</v>
       </c>
       <c r="F88" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D89" s="4">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="E89" s="5">
-        <v>3672</v>
+        <v>4422</v>
       </c>
       <c r="F89" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>17</v>
@@ -3212,31 +3221,32 @@
     </row>
     <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D90" s="4">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="E90" s="5">
-        <v>9982.9</v>
+        <v>5112</v>
       </c>
       <c r="F90" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H90" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,34 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBDFAF6-4551-4DD9-A951-987FF8F7C991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'XLS_Grid_LANCAMENTO A RECEBER'!$A$1:$H$90</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr refMode="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>Funcionário</t>
   </si>
@@ -324,6 +309,12 @@
     <t>01005781.3</t>
   </si>
   <si>
+    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01005683.3</t>
+  </si>
+  <si>
     <t>MARCOS DUTRA</t>
   </si>
   <si>
@@ -336,171 +327,124 @@
     <t>MA</t>
   </si>
   <si>
-    <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01005683.3</t>
-  </si>
-  <si>
     <t>01005876.3</t>
   </si>
   <si>
     <t>01005876.4</t>
   </si>
   <si>
-    <t>01005951.2</t>
+    <t>01005951.3</t>
+  </si>
+  <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
+  </si>
+  <si>
+    <t>01005955.3</t>
   </si>
   <si>
     <t>VITAL DISTRIBUIDORA LTDA</t>
   </si>
   <si>
-    <t>01005934.3</t>
+    <t>01005934.4</t>
   </si>
   <si>
     <t>PI</t>
   </si>
   <si>
+    <t>01005983.3</t>
+  </si>
+  <si>
     <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
   </si>
   <si>
-    <t>01005881.3</t>
-  </si>
-  <si>
-    <t>KELLEN</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
-  </si>
-  <si>
-    <t>01005983.2</t>
-  </si>
-  <si>
-    <t>NOVA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006034.1</t>
-  </si>
-  <si>
-    <t>01005951.3</t>
-  </si>
-  <si>
-    <t>01005955.3</t>
-  </si>
-  <si>
-    <t>01005934.4</t>
-  </si>
-  <si>
-    <t>01005983.3</t>
-  </si>
-  <si>
     <t>01005881.4</t>
   </si>
   <si>
-    <t>LEANDRA LUIZA SILVA</t>
-  </si>
-  <si>
-    <t>METTA FARMA DISTRIBUICAO DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006048.1</t>
-  </si>
-  <si>
-    <t>AM</t>
+    <t>01005955.4</t>
+  </si>
+  <si>
+    <t>01005951.4</t>
+  </si>
+  <si>
+    <t>01005983.4</t>
+  </si>
+  <si>
+    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
+  </si>
+  <si>
+    <t>01005979.1</t>
+  </si>
+  <si>
+    <t>01005979.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01006060.3</t>
   </si>
   <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006077.1</t>
-  </si>
-  <si>
-    <t>01005955.4</t>
-  </si>
-  <si>
-    <t>01005951.4</t>
-  </si>
-  <si>
-    <t>C DE CARVALHO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01005935.5</t>
-  </si>
-  <si>
-    <t>01005983.4</t>
-  </si>
-  <si>
-    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
-  </si>
-  <si>
-    <t>01005979.1</t>
-  </si>
-  <si>
-    <t>01006034.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
-  </si>
-  <si>
-    <t>01006060.2</t>
-  </si>
-  <si>
-    <t>01006097.1</t>
-  </si>
-  <si>
-    <t>01006077.2</t>
-  </si>
-  <si>
-    <t>MP COMERCIO DE PRODUTOS HOSPITALARES E ALIMENTICIO</t>
-  </si>
-  <si>
-    <t>01006100.1</t>
-  </si>
-  <si>
-    <t>01006109.1</t>
-  </si>
-  <si>
-    <t>RR COMERCIO DE PRODUTOS FARMACEUTICOS E HOSPITALAR</t>
-  </si>
-  <si>
-    <t>01006112.1</t>
-  </si>
-  <si>
-    <t>L G PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01005988.5</t>
-  </si>
-  <si>
-    <t>01006025.4</t>
+    <t>01006149.1</t>
+  </si>
+  <si>
+    <t>01006040.4</t>
+  </si>
+  <si>
+    <t>01006097.2</t>
+  </si>
+  <si>
+    <t>01006077.3</t>
+  </si>
+  <si>
+    <t>01006159.1</t>
+  </si>
+  <si>
+    <t>MONTALVAO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01006044.3</t>
+  </si>
+  <si>
+    <t>01006089.3</t>
+  </si>
+  <si>
+    <t>01006135.2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
+    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -519,8 +463,14 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -543,379 +493,117 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA0A0A0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA0A0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+  <cellXfs count="11">
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H90"/>
-  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
+  <dimension ref="A1:H84"/>
+  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.140625" style="1"/>
+    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
+    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
+    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
+    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
+    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
+    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
+    <col max="7" min="7" style="1" width="26.28515625" customWidth="true"/>
+    <col max="8" min="8" style="1" width="3.7109375" customWidth="true"/>
+    <col max="16384" min="9" style="1" width="12.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -941,7 +629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -951,14 +639,14 @@
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="4" t="n">
         <v>45326</v>
       </c>
-      <c r="E2" s="5">
-        <v>9391.7800000000007</v>
-      </c>
-      <c r="F2" s="6">
-        <v>827</v>
+      <c r="E2" s="5" t="n">
+        <v>9391.78</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>831</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
@@ -967,7 +655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -977,14 +665,14 @@
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="4" t="n">
         <v>45346</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="F3" s="6">
-        <v>807</v>
+      <c r="F3" s="6" t="n">
+        <v>811</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -993,7 +681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1003,14 +691,14 @@
       <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="4" t="n">
         <v>45350</v>
       </c>
-      <c r="E4" s="5">
-        <v>1264.8699999999999</v>
-      </c>
-      <c r="F4" s="6">
-        <v>803</v>
+      <c r="E4" s="5" t="n">
+        <v>1264.87</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>807</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -1019,7 +707,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1029,14 +717,14 @@
       <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="4" t="n">
         <v>45356</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="F5" s="6">
-        <v>797</v>
+      <c r="F5" s="6" t="n">
+        <v>801</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -1045,7 +733,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -1055,14 +743,14 @@
       <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="4" t="n">
         <v>45362</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="5" t="n">
         <v>384</v>
       </c>
-      <c r="F6" s="6">
-        <v>791</v>
+      <c r="F6" s="6" t="n">
+        <v>795</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -1071,7 +759,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -1081,14 +769,14 @@
       <c r="C7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="n">
         <v>45364</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="F7" s="6">
-        <v>789</v>
+      <c r="F7" s="6" t="n">
+        <v>793</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
@@ -1097,7 +785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -1107,14 +795,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="4" t="n">
         <v>45378</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="F8" s="6">
-        <v>775</v>
+      <c r="F8" s="6" t="n">
+        <v>779</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
@@ -1123,7 +811,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1133,14 +821,14 @@
       <c r="C9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="4" t="n">
         <v>45463</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5" t="n">
         <v>1674.52</v>
       </c>
-      <c r="F9" s="6">
-        <v>690</v>
+      <c r="F9" s="6" t="n">
+        <v>694</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -1149,7 +837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -1159,14 +847,14 @@
       <c r="C10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="4" t="n">
         <v>45493</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="F10" s="6">
-        <v>660</v>
+      <c r="F10" s="6" t="n">
+        <v>664</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>11</v>
@@ -1175,7 +863,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1185,14 +873,14 @@
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="4" t="n">
         <v>45523</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="F11" s="6">
-        <v>630</v>
+      <c r="F11" s="6" t="n">
+        <v>634</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -1201,7 +889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -1211,14 +899,14 @@
       <c r="C12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="4" t="n">
         <v>45600</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="F12" s="6">
-        <v>553</v>
+      <c r="F12" s="6" t="n">
+        <v>557</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>11</v>
@@ -1227,7 +915,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
@@ -1237,14 +925,14 @@
       <c r="C13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="4" t="n">
         <v>45607</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="5" t="n">
         <v>3204.34</v>
       </c>
-      <c r="F13" s="6">
-        <v>546</v>
+      <c r="F13" s="6" t="n">
+        <v>550</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -1253,7 +941,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
@@ -1263,14 +951,14 @@
       <c r="C14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="4" t="n">
         <v>45608</v>
       </c>
-      <c r="E14" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="F14" s="6">
-        <v>545</v>
+      <c r="E14" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>549</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
@@ -1279,7 +967,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -1289,14 +977,14 @@
       <c r="C15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="4" t="n">
         <v>45614</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="F15" s="6">
-        <v>539</v>
+      <c r="F15" s="6" t="n">
+        <v>543</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -1305,7 +993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
@@ -1315,14 +1003,14 @@
       <c r="C16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="4" t="n">
         <v>45615</v>
       </c>
-      <c r="E16" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="F16" s="6">
-        <v>538</v>
+      <c r="E16" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>542</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>11</v>
@@ -1331,7 +1019,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
@@ -1341,14 +1029,14 @@
       <c r="C17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="4" t="n">
         <v>45617</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="5" t="n">
         <v>1843.87</v>
       </c>
-      <c r="F17" s="6">
-        <v>536</v>
+      <c r="F17" s="6" t="n">
+        <v>540</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -1357,7 +1045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A18" s="3" t="s">
         <v>28</v>
       </c>
@@ -1367,14 +1055,14 @@
       <c r="C18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E18" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="F18" s="6">
-        <v>531</v>
+      <c r="E18" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>535</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>11</v>
@@ -1383,7 +1071,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -1393,14 +1081,14 @@
       <c r="C19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E19" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="F19" s="6">
-        <v>531</v>
+      <c r="E19" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>535</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -1409,7 +1097,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A20" s="3" t="s">
         <v>28</v>
       </c>
@@ -1419,14 +1107,14 @@
       <c r="C20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="4" t="n">
         <v>45624</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="5" t="n">
         <v>1843.88</v>
       </c>
-      <c r="F20" s="6">
-        <v>529</v>
+      <c r="F20" s="6" t="n">
+        <v>533</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>11</v>
@@ -1435,7 +1123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
@@ -1445,14 +1133,14 @@
       <c r="C21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="4" t="n">
         <v>45688</v>
       </c>
-      <c r="E21" s="5">
-        <v>1118.4000000000001</v>
-      </c>
-      <c r="F21" s="6">
-        <v>465</v>
+      <c r="E21" s="5" t="n">
+        <v>1118.4</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>469</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -1461,7 +1149,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A22" s="3" t="s">
         <v>28</v>
       </c>
@@ -1471,14 +1159,14 @@
       <c r="C22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="4" t="n">
         <v>45695</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="F22" s="6">
-        <v>458</v>
+      <c r="F22" s="6" t="n">
+        <v>462</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
@@ -1487,7 +1175,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
@@ -1497,14 +1185,14 @@
       <c r="C23" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="4" t="n">
         <v>45699</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="5" t="n">
         <v>2330</v>
       </c>
-      <c r="F23" s="6">
-        <v>454</v>
+      <c r="F23" s="6" t="n">
+        <v>458</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -1513,7 +1201,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A24" s="3" t="s">
         <v>28</v>
       </c>
@@ -1523,14 +1211,14 @@
       <c r="C24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="4" t="n">
         <v>45702</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="F24" s="6">
-        <v>451</v>
+      <c r="F24" s="6" t="n">
+        <v>455</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>11</v>
@@ -1539,7 +1227,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
@@ -1549,14 +1237,14 @@
       <c r="C25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="4" t="n">
         <v>45705</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F25" s="6">
-        <v>448</v>
+      <c r="F25" s="6" t="n">
+        <v>452</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>17</v>
@@ -1565,7 +1253,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -1575,14 +1263,14 @@
       <c r="C26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="4" t="n">
         <v>45709</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="F26" s="6">
-        <v>444</v>
+      <c r="F26" s="6" t="n">
+        <v>448</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>11</v>
@@ -1591,7 +1279,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A27" s="3" t="s">
         <v>28</v>
       </c>
@@ -1601,14 +1289,14 @@
       <c r="C27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="4" t="n">
         <v>45712</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F27" s="6">
-        <v>441</v>
+      <c r="F27" s="6" t="n">
+        <v>445</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
@@ -1617,7 +1305,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
@@ -1627,14 +1315,14 @@
       <c r="C28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="4" t="n">
         <v>45726</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F28" s="6">
-        <v>427</v>
+      <c r="F28" s="6" t="n">
+        <v>431</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -1643,7 +1331,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
@@ -1653,14 +1341,14 @@
       <c r="C29" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="4" t="n">
         <v>45727</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="F29" s="6">
-        <v>426</v>
+      <c r="F29" s="6" t="n">
+        <v>430</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -1669,7 +1357,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
@@ -1679,14 +1367,14 @@
       <c r="C30" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="4" t="n">
         <v>45734</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="F30" s="6">
-        <v>419</v>
+      <c r="F30" s="6" t="n">
+        <v>423</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>11</v>
@@ -1695,7 +1383,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
@@ -1705,14 +1393,14 @@
       <c r="C31" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="4" t="n">
         <v>45734</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F31" s="6">
-        <v>419</v>
+      <c r="F31" s="6" t="n">
+        <v>423</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -1721,7 +1409,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A32" s="3" t="s">
         <v>28</v>
       </c>
@@ -1731,14 +1419,14 @@
       <c r="C32" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="4" t="n">
         <v>45740</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F32" s="6">
-        <v>413</v>
+      <c r="F32" s="6" t="n">
+        <v>417</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>17</v>
@@ -1747,7 +1435,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A33" s="3" t="s">
         <v>28</v>
       </c>
@@ -1757,14 +1445,14 @@
       <c r="C33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="F33" s="6">
-        <v>412</v>
+      <c r="F33" s="6" t="n">
+        <v>416</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -1773,7 +1461,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A34" s="3" t="s">
         <v>32</v>
       </c>
@@ -1783,14 +1471,14 @@
       <c r="C34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F34" s="6">
-        <v>412</v>
+      <c r="F34" s="6" t="n">
+        <v>416</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
@@ -1799,7 +1487,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
@@ -1809,14 +1497,14 @@
       <c r="C35" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F35" s="6">
-        <v>405</v>
+      <c r="F35" s="6" t="n">
+        <v>409</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -1825,7 +1513,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A36" s="3" t="s">
         <v>28</v>
       </c>
@@ -1835,14 +1523,14 @@
       <c r="C36" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="5" t="n">
         <v>7562.76</v>
       </c>
-      <c r="F36" s="6">
-        <v>405</v>
+      <c r="F36" s="6" t="n">
+        <v>409</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>11</v>
@@ -1851,7 +1539,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A37" s="3" t="s">
         <v>32</v>
       </c>
@@ -1861,14 +1549,14 @@
       <c r="C37" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="4" t="n">
         <v>45755</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F37" s="6">
-        <v>398</v>
+      <c r="F37" s="6" t="n">
+        <v>402</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -1877,7 +1565,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A38" s="3" t="s">
         <v>32</v>
       </c>
@@ -1887,14 +1575,14 @@
       <c r="C38" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="4" t="n">
         <v>45761</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="5" t="n">
         <v>6169.53</v>
       </c>
-      <c r="F38" s="6">
-        <v>392</v>
+      <c r="F38" s="6" t="n">
+        <v>396</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>11</v>
@@ -1903,7 +1591,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A39" s="3" t="s">
         <v>32</v>
       </c>
@@ -1913,14 +1601,14 @@
       <c r="C39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="4" t="n">
         <v>45768</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="F39" s="6">
-        <v>385</v>
+      <c r="F39" s="6" t="n">
+        <v>389</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -1929,7 +1617,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A40" s="3" t="s">
         <v>32</v>
       </c>
@@ -1939,14 +1627,14 @@
       <c r="C40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="F40" s="6">
-        <v>378</v>
+      <c r="F40" s="6" t="n">
+        <v>382</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>11</v>
@@ -1955,7 +1643,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
@@ -1965,14 +1653,14 @@
       <c r="C41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="5" t="n">
         <v>6089.41</v>
       </c>
-      <c r="F41" s="6">
-        <v>378</v>
+      <c r="F41" s="6" t="n">
+        <v>382</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -1981,7 +1669,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A42" s="3" t="s">
         <v>32</v>
       </c>
@@ -1991,14 +1679,14 @@
       <c r="C42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="F42" s="6">
-        <v>371</v>
+      <c r="F42" s="6" t="n">
+        <v>375</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -2007,7 +1695,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A43" s="3" t="s">
         <v>32</v>
       </c>
@@ -2017,14 +1705,14 @@
       <c r="C43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="F43" s="6">
-        <v>364</v>
+      <c r="F43" s="6" t="n">
+        <v>368</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -2033,7 +1721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A44" s="3" t="s">
         <v>72</v>
       </c>
@@ -2043,14 +1731,14 @@
       <c r="C44" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="5" t="n">
         <v>1143.54</v>
       </c>
-      <c r="F44" s="6">
-        <v>364</v>
+      <c r="F44" s="6" t="n">
+        <v>368</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -2059,7 +1747,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A45" s="3" t="s">
         <v>72</v>
       </c>
@@ -2069,14 +1757,14 @@
       <c r="C45" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="4" t="n">
         <v>45796</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="5" t="n">
         <v>2287.06</v>
       </c>
-      <c r="F45" s="6">
-        <v>357</v>
+      <c r="F45" s="6" t="n">
+        <v>361</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -2085,7 +1773,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A46" s="3" t="s">
         <v>28</v>
       </c>
@@ -2095,14 +1783,14 @@
       <c r="C46" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="4" t="n">
         <v>45896</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="5" t="n">
         <v>4572.62</v>
       </c>
-      <c r="F46" s="6">
-        <v>257</v>
+      <c r="F46" s="6" t="n">
+        <v>261</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -2111,7 +1799,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A47" s="3" t="s">
         <v>28</v>
       </c>
@@ -2121,14 +1809,14 @@
       <c r="C47" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="4" t="n">
         <v>45910</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="F47" s="6">
-        <v>243</v>
+      <c r="F47" s="6" t="n">
+        <v>247</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -2137,7 +1825,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A48" s="3" t="s">
         <v>28</v>
       </c>
@@ -2147,14 +1835,14 @@
       <c r="C48" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="4" t="n">
         <v>45924</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="F48" s="6">
-        <v>229</v>
+      <c r="F48" s="6" t="n">
+        <v>233</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -2163,7 +1851,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A49" s="3" t="s">
         <v>81</v>
       </c>
@@ -2173,14 +1861,14 @@
       <c r="C49" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="4" t="n">
         <v>45947</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="5" t="n">
         <v>3867.34</v>
       </c>
-      <c r="F49" s="6">
-        <v>206</v>
+      <c r="F49" s="6" t="n">
+        <v>210</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -2189,7 +1877,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A50" s="3" t="s">
         <v>81</v>
       </c>
@@ -2199,14 +1887,14 @@
       <c r="C50" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="4" t="n">
         <v>45954</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="F50" s="6">
-        <v>199</v>
+      <c r="F50" s="6" t="n">
+        <v>203</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -2215,7 +1903,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A51" s="3" t="s">
         <v>81</v>
       </c>
@@ -2225,14 +1913,14 @@
       <c r="C51" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="4" t="n">
         <v>45961</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="F51" s="6">
-        <v>192</v>
+      <c r="F51" s="6" t="n">
+        <v>196</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -2241,7 +1929,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A52" s="3" t="s">
         <v>81</v>
       </c>
@@ -2251,14 +1939,14 @@
       <c r="C52" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="4" t="n">
         <v>45968</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="F52" s="6">
-        <v>185</v>
+      <c r="F52" s="6" t="n">
+        <v>189</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -2267,7 +1955,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A53" s="3" t="s">
         <v>72</v>
       </c>
@@ -2277,14 +1965,14 @@
       <c r="C53" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="4" t="n">
         <v>45980</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="5" t="n">
         <v>4480</v>
       </c>
-      <c r="F53" s="6">
-        <v>173</v>
+      <c r="F53" s="6" t="n">
+        <v>177</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>17</v>
@@ -2293,7 +1981,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A54" s="3" t="s">
         <v>81</v>
       </c>
@@ -2303,21 +1991,21 @@
       <c r="C54" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="4" t="n">
         <v>45980</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="5" t="n">
         <v>38840.89</v>
       </c>
-      <c r="F54" s="6">
-        <v>173</v>
+      <c r="F54" s="6" t="n">
+        <v>177</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A55" s="3" t="s">
         <v>81</v>
       </c>
@@ -2327,21 +2015,21 @@
       <c r="C55" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="4" t="n">
         <v>45987</v>
       </c>
-      <c r="E55" s="5">
-        <v>33844.160000000003</v>
-      </c>
-      <c r="F55" s="6">
-        <v>166</v>
+      <c r="E55" s="5" t="n">
+        <v>33844.16</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>170</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A56" s="3" t="s">
         <v>72</v>
       </c>
@@ -2351,21 +2039,21 @@
       <c r="C56" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="4" t="n">
         <v>45989</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="5" t="n">
         <v>3220</v>
       </c>
-      <c r="F56" s="6">
-        <v>164</v>
+      <c r="F56" s="6" t="n">
+        <v>168</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A57" s="3" t="s">
         <v>81</v>
       </c>
@@ -2375,21 +2063,21 @@
       <c r="C57" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="4" t="n">
         <v>45994</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="5" t="n">
         <v>38740.53</v>
       </c>
-      <c r="F57" s="6">
-        <v>159</v>
+      <c r="F57" s="6" t="n">
+        <v>163</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A58" s="3" t="s">
         <v>14</v>
       </c>
@@ -2399,14 +2087,14 @@
       <c r="C58" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="4" t="n">
         <v>46090</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="5" t="n">
         <v>806.34</v>
       </c>
-      <c r="F58" s="6">
-        <v>63</v>
+      <c r="F58" s="6" t="n">
+        <v>67</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -2415,7 +2103,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A59" s="3" t="s">
         <v>14</v>
       </c>
@@ -2425,14 +2113,14 @@
       <c r="C59" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="4" t="n">
         <v>46097</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="F59" s="6">
-        <v>56</v>
+      <c r="F59" s="6" t="n">
+        <v>60</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -2441,7 +2129,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A60" s="3" t="s">
         <v>14</v>
       </c>
@@ -2451,14 +2139,14 @@
       <c r="C60" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="4" t="n">
         <v>46104</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="F60" s="6">
-        <v>49</v>
+      <c r="F60" s="6" t="n">
+        <v>53</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>17</v>
@@ -2467,165 +2155,165 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>5466.66</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A62" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="4">
+      <c r="B62" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D62" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E62" s="5" t="n">
         <v>4434.51</v>
       </c>
-      <c r="F61" s="6">
-        <v>48</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H61" s="3" t="s">
+      <c r="F62" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A63" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D62" s="4">
-        <v>46105</v>
-      </c>
-      <c r="E62" s="5">
-        <v>5466.66</v>
-      </c>
-      <c r="F62" s="6">
-        <v>48</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="4" t="n">
         <v>46119</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="5" t="n">
         <v>4434.51</v>
       </c>
-      <c r="F63" s="6">
-        <v>34</v>
+      <c r="F63" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H63" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A64" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="4" t="n">
         <v>46126</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E64" s="5" t="n">
         <v>4434.51</v>
       </c>
-      <c r="F64" s="6">
-        <v>27</v>
+      <c r="F64" s="6" t="n">
+        <v>31</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H64" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A65" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D65" s="4">
-        <v>46126</v>
-      </c>
-      <c r="E65" s="5">
+      <c r="D65" s="4" t="n">
+        <v>46133</v>
+      </c>
+      <c r="E65" s="5" t="n">
         <v>1265.78</v>
       </c>
-      <c r="F65" s="6">
-        <v>27</v>
+      <c r="F65" s="6" t="n">
+        <v>24</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A66" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D66" s="4">
-        <v>46128</v>
-      </c>
-      <c r="E66" s="5">
-        <v>3013.43</v>
-      </c>
-      <c r="F66" s="6">
-        <v>25</v>
+        <v>109</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>46133</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>24</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A67" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>110</v>
@@ -2633,66 +2321,66 @@
       <c r="C67" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="4">
-        <v>46128</v>
-      </c>
-      <c r="E67" s="5">
-        <v>1470</v>
-      </c>
-      <c r="F67" s="6">
-        <v>25</v>
+      <c r="D67" s="4" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>3013.43</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>22</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A68" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" s="4">
-        <v>46129</v>
-      </c>
-      <c r="E68" s="5">
+      <c r="D68" s="4" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E68" s="5" t="n">
         <v>5125.68</v>
       </c>
-      <c r="F68" s="6">
-        <v>24</v>
+      <c r="F68" s="6" t="n">
+        <v>21</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A69" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D69" s="4">
-        <v>46131</v>
-      </c>
-      <c r="E69" s="5">
-        <v>21334.44</v>
-      </c>
-      <c r="F69" s="6">
-        <v>22</v>
+      <c r="D69" s="4" t="n">
+        <v>46138</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>19</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>11</v>
@@ -2701,552 +2389,383 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A70" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>46140</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>3150</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A71" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D70" s="4">
-        <v>46133</v>
-      </c>
-      <c r="E70" s="5">
+      <c r="D71" s="4" t="n">
+        <v>46140</v>
+      </c>
+      <c r="E71" s="5" t="n">
         <v>1265.78</v>
       </c>
-      <c r="F70" s="6">
-        <v>20</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C71" s="3" t="s">
+      <c r="F71" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A72" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D71" s="4">
-        <v>46133</v>
-      </c>
-      <c r="E71" s="5">
-        <v>3150</v>
-      </c>
-      <c r="F71" s="6">
-        <v>20</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>5125.68</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A73" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="D72" s="4">
-        <v>46135</v>
-      </c>
-      <c r="E72" s="5">
-        <v>3013.43</v>
-      </c>
-      <c r="F72" s="6">
-        <v>18</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D73" s="4">
-        <v>46136</v>
-      </c>
-      <c r="E73" s="5">
-        <v>5125.68</v>
-      </c>
-      <c r="F73" s="6">
-        <v>17</v>
+      <c r="D73" s="4" t="n">
+        <v>46145</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>3316.11</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>12</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A74" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="4">
-        <v>46138</v>
-      </c>
-      <c r="E74" s="5">
-        <v>1470</v>
-      </c>
-      <c r="F74" s="6">
-        <v>15</v>
+      <c r="D74" s="4" t="n">
+        <v>46152</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A75" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D75" s="4">
-        <v>46138</v>
-      </c>
-      <c r="E75" s="5">
-        <v>4494.08</v>
-      </c>
-      <c r="F75" s="6">
-        <v>15</v>
-      </c>
-      <c r="G75" s="3"/>
+      <c r="D75" s="4" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>4375</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H75" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A76" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D76" s="4">
-        <v>46140</v>
-      </c>
-      <c r="E76" s="5">
-        <v>3672</v>
-      </c>
-      <c r="F76" s="6">
-        <v>13</v>
+        <v>125</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>127.63</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A77" s="3" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>863.1</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1109.7</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D77" s="4">
-        <v>46140</v>
-      </c>
-      <c r="E77" s="5">
-        <v>3150</v>
-      </c>
-      <c r="F77" s="6">
-        <v>13</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C78" s="3" t="s">
+      <c r="D79" s="4" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>3672</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A80" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D78" s="4">
-        <v>46140</v>
-      </c>
-      <c r="E78" s="5">
-        <v>1265.78</v>
-      </c>
-      <c r="F78" s="6">
-        <v>13</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B79" s="3" t="s">
+      <c r="D80" s="4" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>1021.07</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D79" s="4">
-        <v>46142</v>
-      </c>
-      <c r="E79" s="5">
-        <v>3284.64</v>
-      </c>
-      <c r="F79" s="6">
-        <v>11</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C80" s="3" t="s">
+      <c r="D81" s="4" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>7020</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A82" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D80" s="4">
-        <v>46143</v>
-      </c>
-      <c r="E80" s="5">
-        <v>5125.68</v>
-      </c>
-      <c r="F80" s="6">
-        <v>10</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B81" s="3" t="s">
+      <c r="D82" s="4" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>127.64</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D81" s="4">
-        <v>46145</v>
-      </c>
-      <c r="E81" s="5">
-        <v>3316.11</v>
-      </c>
-      <c r="F81" s="6">
-        <v>8</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D82" s="4">
-        <v>46146</v>
-      </c>
-      <c r="E82" s="5">
-        <v>12096</v>
-      </c>
-      <c r="F82" s="6">
-        <v>7</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D83" s="4">
-        <v>46146</v>
-      </c>
-      <c r="E83" s="5">
-        <v>4375</v>
-      </c>
-      <c r="F83" s="6">
-        <v>7</v>
+      <c r="D83" s="4" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>127.63</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D84" s="4">
-        <v>46146</v>
-      </c>
-      <c r="E84" s="5">
-        <v>1109.7</v>
-      </c>
-      <c r="F84" s="6">
-        <v>7</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H84" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D85" s="4">
-        <v>46147</v>
-      </c>
-      <c r="E85" s="5">
-        <v>3672</v>
-      </c>
-      <c r="F85" s="6">
-        <v>6</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D86" s="4">
-        <v>46148</v>
-      </c>
-      <c r="E86" s="5">
-        <v>9982.9</v>
-      </c>
-      <c r="F86" s="6">
-        <v>5</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D87" s="4">
-        <v>46149</v>
-      </c>
-      <c r="E87" s="5">
-        <v>3118.8</v>
-      </c>
-      <c r="F87" s="6">
-        <v>4</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D88" s="4">
-        <v>46149</v>
-      </c>
-      <c r="E88" s="5">
-        <v>7966.96</v>
-      </c>
-      <c r="F88" s="6">
-        <v>4</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D89" s="4">
-        <v>46150</v>
-      </c>
-      <c r="E89" s="5">
-        <v>4422</v>
-      </c>
-      <c r="F89" s="6">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D90" s="4">
-        <v>46150</v>
-      </c>
-      <c r="E90" s="5">
-        <v>5112</v>
-      </c>
-      <c r="F90" s="6">
-        <v>3</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>45</v>
-      </c>
+    <row r="84" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A84" s="7"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="9" t="n">
+        <v>347623.97</v>
+      </c>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H90" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="default" cellComments="none"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -276,18 +276,18 @@
     <t>01004900.4</t>
   </si>
   <si>
+    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
+  </si>
+  <si>
+    <t>01005217.1BPBPBP</t>
+  </si>
+  <si>
     <t>BR MEDICAMENTOS LTDA</t>
   </si>
   <si>
     <t>01005075.3</t>
   </si>
   <si>
-    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
-  </si>
-  <si>
-    <t>01005217.1BPBPBP</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
@@ -354,9 +354,6 @@
     <t>PI</t>
   </si>
   <si>
-    <t>01005983.3</t>
-  </si>
-  <si>
     <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
   </si>
   <si>
@@ -372,15 +369,6 @@
     <t>01005983.4</t>
   </si>
   <si>
-    <t>3M DISTRIBUIDORA DE MEDICAMENTOS E INSUMOS HOSPITA</t>
-  </si>
-  <si>
-    <t>01005979.1</t>
-  </si>
-  <si>
-    <t>01005979.2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
   </si>
   <si>
@@ -415,6 +403,18 @@
   </si>
   <si>
     <t>01006135.2</t>
+  </si>
+  <si>
+    <t>AMAZONIA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006141.2</t>
+  </si>
+  <si>
+    <t>ASPEN SERVICE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01005993.4</t>
   </si>
 </sst>
 </file>
@@ -589,7 +589,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
@@ -646,7 +646,7 @@
         <v>9391.78</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
@@ -672,7 +672,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -698,7 +698,7 @@
         <v>1264.87</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -724,7 +724,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -750,7 +750,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -776,7 +776,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
@@ -802,7 +802,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
@@ -828,7 +828,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -854,7 +854,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>11</v>
@@ -880,7 +880,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -906,7 +906,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>11</v>
@@ -932,7 +932,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -958,7 +958,7 @@
         <v>4439.9</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
@@ -984,7 +984,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -1010,7 +1010,7 @@
         <v>1216.86</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>11</v>
@@ -1036,7 +1036,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -1062,7 +1062,7 @@
         <v>1216.86</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>11</v>
@@ -1088,7 +1088,7 @@
         <v>4439.9</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -1114,7 +1114,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>11</v>
@@ -1140,7 +1140,7 @@
         <v>1118.4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -1166,7 +1166,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
@@ -1192,7 +1192,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -1218,7 +1218,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>11</v>
@@ -1244,7 +1244,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>17</v>
@@ -1270,7 +1270,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>11</v>
@@ -1296,7 +1296,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
@@ -1322,7 +1322,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -1348,7 +1348,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -1374,7 +1374,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>11</v>
@@ -1400,7 +1400,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -1426,7 +1426,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>17</v>
@@ -1452,7 +1452,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -1478,7 +1478,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
@@ -1504,7 +1504,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -1530,7 +1530,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>11</v>
@@ -1556,7 +1556,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -1582,7 +1582,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>11</v>
@@ -1608,7 +1608,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -1634,7 +1634,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>11</v>
@@ -1660,7 +1660,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -1686,7 +1686,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -1712,7 +1712,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -1738,7 +1738,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -1764,7 +1764,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -1790,7 +1790,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -1816,7 +1816,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -1842,7 +1842,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -1868,7 +1868,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -1894,7 +1894,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -1920,7 +1920,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -1946,7 +1946,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -1957,7 +1957,7 @@
     </row>
     <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A53" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>87</v>
@@ -1969,21 +1969,19 @@
         <v>45980</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>4480</v>
+        <v>38840.89</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>177</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A54" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>89</v>
@@ -1995,14 +1993,16 @@
         <v>45980</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>38840.89</v>
+        <v>4480</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>177</v>
-      </c>
-      <c r="G54" s="3"/>
+        <v>180</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H54" s="3" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
@@ -2010,7 +2010,7 @@
         <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>91</v>
@@ -2022,7 +2022,7 @@
         <v>33844.16</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2034,7 +2034,7 @@
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>92</v>
@@ -2046,7 +2046,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2058,7 +2058,7 @@
         <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>93</v>
@@ -2070,7 +2070,7 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2094,7 +2094,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -2120,7 +2120,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -2146,7 +2146,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>17</v>
@@ -2172,7 +2172,7 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>11</v>
@@ -2198,7 +2198,7 @@
         <v>4434.51</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>17</v>
@@ -2224,7 +2224,7 @@
         <v>4434.51</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>17</v>
@@ -2250,7 +2250,7 @@
         <v>4434.51</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>17</v>
@@ -2276,7 +2276,7 @@
         <v>1265.78</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>11</v>
@@ -2302,7 +2302,7 @@
         <v>3150</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>17</v>
@@ -2328,7 +2328,7 @@
         <v>3013.43</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>11</v>
@@ -2339,62 +2339,62 @@
     </row>
     <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A68" s="3" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>5125.68</v>
+        <v>1470</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A69" s="3" t="s">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>115</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>1470</v>
+        <v>3150</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A70" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>116</v>
@@ -2403,13 +2403,13 @@
         <v>46140</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>3150</v>
+        <v>1265.78</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>103</v>
@@ -2417,25 +2417,25 @@
     </row>
     <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A71" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1265.78</v>
+        <v>5125.68</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>103</v>
@@ -2443,88 +2443,88 @@
     </row>
     <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A72" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>5125.68</v>
+        <v>4375</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A73" s="3" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>46145</v>
+        <v>46153</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>3316.11</v>
+        <v>127.63</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A74" s="3" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1890</v>
+        <v>863.1</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A75" s="3" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>123</v>
@@ -2533,16 +2533,16 @@
         <v>46153</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>4375</v>
+        <v>1109.7</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
@@ -2550,22 +2550,22 @@
         <v>14</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="D76" s="4" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>127.63</v>
+        <v>3672</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>45</v>
@@ -2576,19 +2576,19 @@
         <v>14</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>863.1</v>
+        <v>1021.07</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>11</v>
@@ -2599,28 +2599,28 @@
     </row>
     <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A78" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>127</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1109.7</v>
+        <v>7020</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
@@ -2628,22 +2628,22 @@
         <v>14</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>128</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>3672</v>
+        <v>127.64</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>45</v>
@@ -2654,19 +2654,19 @@
         <v>14</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1021.07</v>
+        <v>127.63</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>11</v>
@@ -2677,7 +2677,7 @@
     </row>
     <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A81" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>130</v>
@@ -2686,84 +2686,58 @@
         <v>131</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>7020</v>
+        <v>2033.33</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A82" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>127.64</v>
+        <v>10947</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A83" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>46156</v>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>127.63</v>
-      </c>
-      <c r="F83" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="84" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A84" s="7"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="9" t="n">
-        <v>347623.97</v>
-      </c>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="10"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A83" s="7"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="9" t="n">
+        <v>350272.51</v>
+      </c>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="10"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0791818F-8287-4EC1-A34D-0AECBCE78D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="134">
   <si>
     <t>Funcionário</t>
   </si>
@@ -420,31 +432,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -463,14 +474,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -493,117 +498,379 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
-  <dimension ref="A1:H83"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H82"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
-    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
-    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
-    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
-    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="26.28515625" customWidth="true"/>
-    <col max="8" min="8" style="1" width="3.7109375" customWidth="true"/>
-    <col max="16384" min="9" style="1" width="12.140625"/>
+    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -629,7 +896,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -639,13 +906,13 @@
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>45326</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>9391.78</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="5">
+        <v>9391.7800000000007</v>
+      </c>
+      <c r="F2" s="6">
         <v>834</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -655,7 +922,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -665,13 +932,13 @@
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>45346</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5">
         <v>5418</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="6">
         <v>814</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -681,7 +948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -691,13 +958,13 @@
       <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>45350</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1264.87</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="E4" s="5">
+        <v>1264.8699999999999</v>
+      </c>
+      <c r="F4" s="6">
         <v>810</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -707,7 +974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -717,13 +984,13 @@
       <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>45356</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5">
         <v>5418</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="6">
         <v>804</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -733,7 +1000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -743,13 +1010,13 @@
       <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>45362</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5">
         <v>384</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="6">
         <v>798</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -759,7 +1026,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -769,13 +1036,13 @@
       <c r="C7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>45364</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5">
         <v>816</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="6">
         <v>796</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -785,7 +1052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -795,13 +1062,13 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>45378</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5">
         <v>816</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="6">
         <v>782</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -811,7 +1078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -821,13 +1088,13 @@
       <c r="C9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>45463</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5">
         <v>1674.52</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="6">
         <v>697</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -837,7 +1104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -847,13 +1114,13 @@
       <c r="C10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>45493</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5">
         <v>873.6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="6">
         <v>667</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -863,7 +1130,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -873,13 +1140,13 @@
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>45523</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5">
         <v>873.6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="6">
         <v>637</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -889,7 +1156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -899,13 +1166,13 @@
       <c r="C12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>45600</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5">
         <v>2000</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="6">
         <v>560</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -915,7 +1182,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
@@ -925,13 +1192,13 @@
       <c r="C13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>45607</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5">
         <v>3204.34</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="6">
         <v>553</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -941,7 +1208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
@@ -951,13 +1218,13 @@
       <c r="C14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>45608</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F14" s="6">
         <v>552</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -967,7 +1234,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -977,13 +1244,13 @@
       <c r="C15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>45614</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="5">
         <v>2000</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="6">
         <v>546</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -993,7 +1260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
@@ -1003,13 +1270,13 @@
       <c r="C16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>45615</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F16" s="6">
         <v>545</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -1019,7 +1286,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
@@ -1029,13 +1296,13 @@
       <c r="C17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>45617</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="5">
         <v>1843.87</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="6">
         <v>543</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -1045,7 +1312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>28</v>
       </c>
@@ -1055,13 +1322,13 @@
       <c r="C18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>45622</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F18" s="6" t="n">
+      <c r="E18" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F18" s="6">
         <v>538</v>
       </c>
       <c r="G18" s="3" t="s">
@@ -1071,7 +1338,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -1081,13 +1348,13 @@
       <c r="C19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>45622</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F19" s="6" t="n">
+      <c r="E19" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F19" s="6">
         <v>538</v>
       </c>
       <c r="G19" s="3" t="s">
@@ -1097,7 +1364,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>28</v>
       </c>
@@ -1107,13 +1374,13 @@
       <c r="C20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>45624</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="5">
         <v>1843.88</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="6">
         <v>536</v>
       </c>
       <c r="G20" s="3" t="s">
@@ -1123,7 +1390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
@@ -1133,13 +1400,13 @@
       <c r="C21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>45688</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>1118.4</v>
-      </c>
-      <c r="F21" s="6" t="n">
+      <c r="E21" s="5">
+        <v>1118.4000000000001</v>
+      </c>
+      <c r="F21" s="6">
         <v>472</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -1149,7 +1416,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>28</v>
       </c>
@@ -1159,13 +1426,13 @@
       <c r="C22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>45695</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="6">
         <v>465</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -1175,7 +1442,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
@@ -1185,13 +1452,13 @@
       <c r="C23" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>45699</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="5">
         <v>2330</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="6">
         <v>461</v>
       </c>
       <c r="G23" s="3" t="s">
@@ -1201,7 +1468,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>28</v>
       </c>
@@ -1211,13 +1478,13 @@
       <c r="C24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>45702</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="6">
         <v>458</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -1227,7 +1494,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
@@ -1237,13 +1504,13 @@
       <c r="C25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>45705</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="5">
         <v>2541</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="6">
         <v>455</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -1253,7 +1520,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -1263,13 +1530,13 @@
       <c r="C26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>45709</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="6">
         <v>451</v>
       </c>
       <c r="G26" s="3" t="s">
@@ -1279,7 +1546,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>28</v>
       </c>
@@ -1289,13 +1556,13 @@
       <c r="C27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>45712</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="5">
         <v>2541</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="6">
         <v>448</v>
       </c>
       <c r="G27" s="3" t="s">
@@ -1305,7 +1572,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
@@ -1315,13 +1582,13 @@
       <c r="C28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>45726</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="5">
         <v>2541</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="6">
         <v>434</v>
       </c>
       <c r="G28" s="3" t="s">
@@ -1331,7 +1598,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
@@ -1341,13 +1608,13 @@
       <c r="C29" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4">
         <v>45727</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="6">
         <v>433</v>
       </c>
       <c r="G29" s="3" t="s">
@@ -1357,7 +1624,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
@@ -1367,13 +1634,13 @@
       <c r="C30" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>45734</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="6">
         <v>426</v>
       </c>
       <c r="G30" s="3" t="s">
@@ -1383,7 +1650,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
@@ -1393,13 +1660,13 @@
       <c r="C31" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>45734</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="6">
         <v>426</v>
       </c>
       <c r="G31" s="3" t="s">
@@ -1409,7 +1676,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>28</v>
       </c>
@@ -1419,13 +1686,13 @@
       <c r="C32" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>45740</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="5">
         <v>2541</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="6">
         <v>420</v>
       </c>
       <c r="G32" s="3" t="s">
@@ -1435,7 +1702,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>28</v>
       </c>
@@ -1445,13 +1712,13 @@
       <c r="C33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>45741</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="6">
         <v>419</v>
       </c>
       <c r="G33" s="3" t="s">
@@ -1461,7 +1728,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>32</v>
       </c>
@@ -1471,13 +1738,13 @@
       <c r="C34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>45741</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="6">
         <v>419</v>
       </c>
       <c r="G34" s="3" t="s">
@@ -1487,7 +1754,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
@@ -1497,13 +1764,13 @@
       <c r="C35" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4">
         <v>45748</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="6">
         <v>412</v>
       </c>
       <c r="G35" s="3" t="s">
@@ -1513,7 +1780,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>28</v>
       </c>
@@ -1523,13 +1790,13 @@
       <c r="C36" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4">
         <v>45748</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="5">
         <v>7562.76</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="6">
         <v>412</v>
       </c>
       <c r="G36" s="3" t="s">
@@ -1539,7 +1806,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>32</v>
       </c>
@@ -1549,13 +1816,13 @@
       <c r="C37" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4">
         <v>45755</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="6">
         <v>405</v>
       </c>
       <c r="G37" s="3" t="s">
@@ -1565,7 +1832,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>32</v>
       </c>
@@ -1575,13 +1842,13 @@
       <c r="C38" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="4">
         <v>45761</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="5">
         <v>6169.53</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="6">
         <v>399</v>
       </c>
       <c r="G38" s="3" t="s">
@@ -1591,7 +1858,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>32</v>
       </c>
@@ -1601,13 +1868,13 @@
       <c r="C39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="4">
         <v>45768</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="5">
         <v>3850</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="6">
         <v>392</v>
       </c>
       <c r="G39" s="3" t="s">
@@ -1617,7 +1884,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>32</v>
       </c>
@@ -1627,13 +1894,13 @@
       <c r="C40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="4">
         <v>45775</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="5">
         <v>3850</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="6">
         <v>385</v>
       </c>
       <c r="G40" s="3" t="s">
@@ -1643,7 +1910,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
@@ -1653,13 +1920,13 @@
       <c r="C41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="4">
         <v>45775</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="5">
         <v>6089.41</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="6">
         <v>385</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -1669,7 +1936,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>32</v>
       </c>
@@ -1679,13 +1946,13 @@
       <c r="C42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="4">
         <v>45782</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="5">
         <v>3800</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="6">
         <v>378</v>
       </c>
       <c r="G42" s="3" t="s">
@@ -1695,7 +1962,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>32</v>
       </c>
@@ -1705,13 +1972,13 @@
       <c r="C43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="4">
         <v>45789</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="5">
         <v>3800</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="6">
         <v>371</v>
       </c>
       <c r="G43" s="3" t="s">
@@ -1721,7 +1988,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>72</v>
       </c>
@@ -1731,13 +1998,13 @@
       <c r="C44" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="4">
         <v>45789</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="5">
         <v>1143.54</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="6">
         <v>371</v>
       </c>
       <c r="G44" s="3" t="s">
@@ -1747,7 +2014,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>72</v>
       </c>
@@ -1757,13 +2024,13 @@
       <c r="C45" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="4">
         <v>45796</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="5">
         <v>2287.06</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="6">
         <v>364</v>
       </c>
       <c r="G45" s="3" t="s">
@@ -1773,7 +2040,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>28</v>
       </c>
@@ -1783,13 +2050,13 @@
       <c r="C46" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="4">
         <v>45896</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="5">
         <v>4572.62</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="6">
         <v>264</v>
       </c>
       <c r="G46" s="3" t="s">
@@ -1799,7 +2066,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>28</v>
       </c>
@@ -1809,13 +2076,13 @@
       <c r="C47" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="4">
         <v>45910</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="6">
         <v>250</v>
       </c>
       <c r="G47" s="3" t="s">
@@ -1825,7 +2092,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>28</v>
       </c>
@@ -1835,13 +2102,13 @@
       <c r="C48" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="4">
         <v>45924</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="6">
         <v>236</v>
       </c>
       <c r="G48" s="3" t="s">
@@ -1851,7 +2118,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="49" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>81</v>
       </c>
@@ -1861,13 +2128,13 @@
       <c r="C49" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="4">
         <v>45947</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="5">
         <v>3867.34</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="6">
         <v>213</v>
       </c>
       <c r="G49" s="3" t="s">
@@ -1877,7 +2144,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>81</v>
       </c>
@@ -1887,13 +2154,13 @@
       <c r="C50" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="4">
         <v>45954</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="6">
         <v>206</v>
       </c>
       <c r="G50" s="3" t="s">
@@ -1903,7 +2170,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="51" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>81</v>
       </c>
@@ -1913,13 +2180,13 @@
       <c r="C51" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="4">
         <v>45961</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F51" s="6">
         <v>199</v>
       </c>
       <c r="G51" s="3" t="s">
@@ -1929,7 +2196,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>81</v>
       </c>
@@ -1939,13 +2206,13 @@
       <c r="C52" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="4">
         <v>45968</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F52" s="6">
         <v>192</v>
       </c>
       <c r="G52" s="3" t="s">
@@ -1955,7 +2222,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>81</v>
       </c>
@@ -1965,13 +2232,13 @@
       <c r="C53" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="4">
         <v>45980</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E53" s="5">
         <v>38840.89</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F53" s="6">
         <v>180</v>
       </c>
       <c r="G53" s="3"/>
@@ -1979,7 +2246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>72</v>
       </c>
@@ -1989,13 +2256,13 @@
       <c r="C54" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="4">
         <v>45980</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E54" s="5">
         <v>4480</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F54" s="6">
         <v>180</v>
       </c>
       <c r="G54" s="3" t="s">
@@ -2005,7 +2272,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>81</v>
       </c>
@@ -2015,13 +2282,13 @@
       <c r="C55" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="4">
         <v>45987</v>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>33844.16</v>
-      </c>
-      <c r="F55" s="6" t="n">
+      <c r="E55" s="5">
+        <v>33844.160000000003</v>
+      </c>
+      <c r="F55" s="6">
         <v>173</v>
       </c>
       <c r="G55" s="3"/>
@@ -2029,7 +2296,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="56" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>72</v>
       </c>
@@ -2039,13 +2306,13 @@
       <c r="C56" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="4">
         <v>45989</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="5">
         <v>3220</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F56" s="6">
         <v>171</v>
       </c>
       <c r="G56" s="3"/>
@@ -2053,7 +2320,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>81</v>
       </c>
@@ -2063,13 +2330,13 @@
       <c r="C57" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="4">
         <v>45994</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="5">
         <v>38740.53</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="6">
         <v>166</v>
       </c>
       <c r="G57" s="3"/>
@@ -2077,7 +2344,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="58" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>14</v>
       </c>
@@ -2087,13 +2354,13 @@
       <c r="C58" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="4">
         <v>46090</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="5">
         <v>806.34</v>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F58" s="6">
         <v>70</v>
       </c>
       <c r="G58" s="3" t="s">
@@ -2103,7 +2370,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="59" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>14</v>
       </c>
@@ -2113,13 +2380,13 @@
       <c r="C59" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="4">
         <v>46097</v>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E59" s="5">
         <v>503.28</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F59" s="6">
         <v>63</v>
       </c>
       <c r="G59" s="3" t="s">
@@ -2129,7 +2396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>14</v>
       </c>
@@ -2139,13 +2406,13 @@
       <c r="C60" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="4">
         <v>46104</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="5">
         <v>503.28</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F60" s="6">
         <v>56</v>
       </c>
       <c r="G60" s="3" t="s">
@@ -2155,7 +2422,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2165,13 +2432,13 @@
       <c r="C61" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="4">
         <v>46105</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="5">
         <v>5466.66</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F61" s="6">
         <v>55</v>
       </c>
       <c r="G61" s="3" t="s">
@@ -2181,7 +2448,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>100</v>
       </c>
@@ -2191,13 +2458,13 @@
       <c r="C62" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="4">
         <v>46105</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E62" s="5">
         <v>4434.51</v>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F62" s="6">
         <v>55</v>
       </c>
       <c r="G62" s="3" t="s">
@@ -2207,7 +2474,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>100</v>
       </c>
@@ -2217,13 +2484,13 @@
       <c r="C63" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="4">
         <v>46119</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="5">
         <v>4434.51</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="6">
         <v>41</v>
       </c>
       <c r="G63" s="3" t="s">
@@ -2233,7 +2500,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>100</v>
       </c>
@@ -2243,13 +2510,13 @@
       <c r="C64" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="4">
         <v>46126</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="5">
         <v>4434.51</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="6">
         <v>34</v>
       </c>
       <c r="G64" s="3" t="s">
@@ -2259,7 +2526,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>100</v>
       </c>
@@ -2269,13 +2536,13 @@
       <c r="C65" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="4">
         <v>46133</v>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E65" s="5">
         <v>1265.78</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="6">
         <v>27</v>
       </c>
       <c r="G65" s="3" t="s">
@@ -2285,7 +2552,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>107</v>
       </c>
@@ -2295,13 +2562,13 @@
       <c r="C66" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="4">
         <v>46133</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="5">
         <v>3150</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="F66" s="6">
         <v>27</v>
       </c>
       <c r="G66" s="3" t="s">
@@ -2311,7 +2578,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>100</v>
       </c>
@@ -2321,13 +2588,13 @@
       <c r="C67" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="4">
         <v>46135</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="5">
         <v>3013.43</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" s="6">
         <v>25</v>
       </c>
       <c r="G67" s="3" t="s">
@@ -2337,7 +2604,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>8</v>
       </c>
@@ -2347,13 +2614,13 @@
       <c r="C68" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="4">
         <v>46138</v>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E68" s="5">
         <v>1470</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" s="6">
         <v>22</v>
       </c>
       <c r="G68" s="3" t="s">
@@ -2363,7 +2630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>107</v>
       </c>
@@ -2373,13 +2640,13 @@
       <c r="C69" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="4">
         <v>46140</v>
       </c>
-      <c r="E69" s="5" t="n">
+      <c r="E69" s="5">
         <v>3150</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F69" s="6">
         <v>20</v>
       </c>
       <c r="G69" s="3" t="s">
@@ -2389,7 +2656,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>100</v>
       </c>
@@ -2399,13 +2666,13 @@
       <c r="C70" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="4">
         <v>46140</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="5">
         <v>1265.78</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="F70" s="6">
         <v>20</v>
       </c>
       <c r="G70" s="3" t="s">
@@ -2415,7 +2682,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>107</v>
       </c>
@@ -2425,13 +2692,13 @@
       <c r="C71" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="4">
         <v>46143</v>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E71" s="5">
         <v>5125.68</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="F71" s="6">
         <v>17</v>
       </c>
       <c r="G71" s="3" t="s">
@@ -2441,7 +2708,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>81</v>
       </c>
@@ -2451,13 +2718,13 @@
       <c r="C72" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="4">
         <v>46153</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E72" s="5">
         <v>4375</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="6">
         <v>7</v>
       </c>
       <c r="G72" s="3" t="s">
@@ -2467,7 +2734,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>14</v>
       </c>
@@ -2477,13 +2744,13 @@
       <c r="C73" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="4">
         <v>46153</v>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="5">
         <v>127.63</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" s="6">
         <v>7</v>
       </c>
       <c r="G73" s="3" t="s">
@@ -2493,7 +2760,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>14</v>
       </c>
@@ -2503,13 +2770,13 @@
       <c r="C74" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="4">
         <v>46153</v>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E74" s="5">
         <v>863.1</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="6">
         <v>7</v>
       </c>
       <c r="G74" s="3" t="s">
@@ -2519,7 +2786,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>14</v>
       </c>
@@ -2529,13 +2796,13 @@
       <c r="C75" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="4">
         <v>46153</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E75" s="5">
         <v>1109.7</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="F75" s="6">
         <v>7</v>
       </c>
       <c r="G75" s="3" t="s">
@@ -2545,7 +2812,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>14</v>
       </c>
@@ -2555,13 +2822,13 @@
       <c r="C76" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="4">
         <v>46154</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="5">
         <v>3672</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="6">
         <v>6</v>
       </c>
       <c r="G76" s="3" t="s">
@@ -2571,7 +2838,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>14</v>
       </c>
@@ -2581,13 +2848,13 @@
       <c r="C77" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="4">
         <v>46154</v>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="E77" s="5">
         <v>1021.07</v>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="F77" s="6">
         <v>6</v>
       </c>
       <c r="G77" s="3" t="s">
@@ -2597,7 +2864,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>8</v>
       </c>
@@ -2607,13 +2874,13 @@
       <c r="C78" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="4">
         <v>46155</v>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E78" s="5">
         <v>7020</v>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="F78" s="6">
         <v>5</v>
       </c>
       <c r="G78" s="3" t="s">
@@ -2623,7 +2890,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>14</v>
       </c>
@@ -2633,13 +2900,13 @@
       <c r="C79" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="4">
         <v>46156</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E79" s="5">
         <v>127.64</v>
       </c>
-      <c r="F79" s="6" t="n">
+      <c r="F79" s="6">
         <v>4</v>
       </c>
       <c r="G79" s="3" t="s">
@@ -2649,7 +2916,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>14</v>
       </c>
@@ -2659,13 +2926,13 @@
       <c r="C80" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="4">
         <v>46156</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="E80" s="5">
         <v>127.63</v>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="F80" s="6">
         <v>4</v>
       </c>
       <c r="G80" s="3" t="s">
@@ -2675,7 +2942,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>100</v>
       </c>
@@ -2685,13 +2952,13 @@
       <c r="C81" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" s="4">
         <v>46157</v>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E81" s="5">
         <v>2033.33</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="F81" s="6">
         <v>3</v>
       </c>
       <c r="G81" s="3" t="s">
@@ -2701,7 +2968,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>8</v>
       </c>
@@ -2711,13 +2978,13 @@
       <c r="C82" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="4">
         <v>46157</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E82" s="5">
         <v>10947</v>
       </c>
-      <c r="F82" s="6" t="n">
+      <c r="F82" s="6">
         <v>3</v>
       </c>
       <c r="G82" s="3" t="s">
@@ -2727,19 +2994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A83" s="7"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="9" t="n">
-        <v>350272.51</v>
-      </c>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="10"/>
-    </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>Funcionário</t>
   </si>
@@ -39,12 +39,6 @@
     <t>UF</t>
   </si>
   <si>
-    <t>Cod.Barras - Boleto</t>
-  </si>
-  <si>
-    <t>Cod.Pag-Banco</t>
-  </si>
-  <si>
     <t>DANILO</t>
   </si>
   <si>
@@ -60,15 +54,9 @@
     <t>AL</t>
   </si>
   <si>
-    <t>34192961600009391781090001019578120992717000</t>
-  </si>
-  <si>
     <t>01001504.3</t>
   </si>
   <si>
-    <t>34194963600005418001090001019738120992717000</t>
-  </si>
-  <si>
     <t>MARCELO LOPES</t>
   </si>
   <si>
@@ -84,33 +72,18 @@
     <t>PE</t>
   </si>
   <si>
-    <t>00191964000001264870000003473568000002622117</t>
-  </si>
-  <si>
     <t>01001504.4</t>
   </si>
   <si>
-    <t>34194964600005418001090001019818120992717000</t>
-  </si>
-  <si>
     <t>01001548.3</t>
   </si>
   <si>
-    <t>00193965200000384000000003473568000002617517</t>
-  </si>
-  <si>
     <t>01001617.2</t>
   </si>
   <si>
-    <t>00191965400000816000000003473568000002622217</t>
-  </si>
-  <si>
     <t>01001617.3</t>
   </si>
   <si>
-    <t>00192966800000816000000003473568000002622317</t>
-  </si>
-  <si>
     <t>VEC HOSPITALAR LTDA ME</t>
   </si>
   <si>
@@ -120,21 +93,12 @@
     <t>SE</t>
   </si>
   <si>
-    <t>34192975300001674521090001106858120992717000</t>
-  </si>
-  <si>
     <t>01002233.3</t>
   </si>
   <si>
-    <t>34192978300000873601090001107018120992717000</t>
-  </si>
-  <si>
     <t>01002233.5</t>
   </si>
   <si>
-    <t>34191981300000873601090001107278120992717000</t>
-  </si>
-  <si>
     <t>MARIO JR</t>
   </si>
   <si>
@@ -144,15 +108,9 @@
     <t>01003029.2</t>
   </si>
   <si>
-    <t>34195989000002000001090001238528120992717000</t>
-  </si>
-  <si>
     <t>01003029.1</t>
   </si>
   <si>
-    <t>34197987600003204341090001238458120992717000</t>
-  </si>
-  <si>
     <t>MOISES</t>
   </si>
   <si>
@@ -165,45 +123,24 @@
     <t>BA</t>
   </si>
   <si>
-    <t>34196989800004439901090001240908120992717000</t>
-  </si>
-  <si>
     <t>01003029.3</t>
   </si>
   <si>
-    <t>34195990400002000001090001238608120992717000</t>
-  </si>
-  <si>
     <t>01002938.2</t>
   </si>
   <si>
-    <t>34194986400001216861090001218808120992717000</t>
-  </si>
-  <si>
     <t>01002951.2</t>
   </si>
   <si>
-    <t>34193985900001843871090001228138120992717000</t>
-  </si>
-  <si>
     <t>01002938.3</t>
   </si>
   <si>
-    <t>34192987800001216861090001218988120992717000</t>
-  </si>
-  <si>
     <t>01002991.4</t>
   </si>
   <si>
-    <t>34197991200004439901090001241088120992717000</t>
-  </si>
-  <si>
     <t>01002951.3</t>
   </si>
   <si>
-    <t>34194986600001843881090001228218120992717000</t>
-  </si>
-  <si>
     <t>SERGIO ROBERTO</t>
   </si>
   <si>
@@ -216,9 +153,6 @@
     <t>PB</t>
   </si>
   <si>
-    <t>34191997800001118401090001280758120992717000</t>
-  </si>
-  <si>
     <t xml:space="preserve">RN COMERCIO DE MEDICAMENTOS E MATERIAL HOSPITALAR </t>
   </si>
   <si>
@@ -228,141 +162,75 @@
     <t>RN</t>
   </si>
   <si>
-    <t>34194998500003296801090001307668120992717000</t>
-  </si>
-  <si>
     <t>01003409.6</t>
   </si>
   <si>
-    <t>34199998900002330001090001290998120992717000</t>
-  </si>
-  <si>
     <t>01003464.5</t>
   </si>
   <si>
-    <t>34198999200003296801090001307748120992717000</t>
-  </si>
-  <si>
     <t>01003504.1</t>
   </si>
   <si>
-    <t>00191999500002541000000003473568000002851217</t>
-  </si>
-  <si>
     <t>01003464.6</t>
   </si>
   <si>
-    <t>34191999900003296801090001307828120992717000</t>
-  </si>
-  <si>
     <t>01003504.2</t>
   </si>
   <si>
-    <t>00195100200002541000000003473568000002851317</t>
-  </si>
-  <si>
     <t>01003504.4</t>
   </si>
   <si>
-    <t>00194101600002541000000003473568000002851517</t>
-  </si>
-  <si>
     <t>01003589.1</t>
   </si>
   <si>
-    <t>34197101700007562781090001319968120992717000</t>
-  </si>
-  <si>
     <t>01003589.2</t>
   </si>
   <si>
-    <t>34198102400007562781090001320028120992717000</t>
-  </si>
-  <si>
     <t>MED-K COMERCIO LTDA</t>
   </si>
   <si>
     <t>01003592.2</t>
   </si>
   <si>
-    <t>34194102400001154561090001320448120992717000</t>
-  </si>
-  <si>
     <t>01003504.6</t>
   </si>
   <si>
-    <t>00193103000002541000000003473568000002851717</t>
-  </si>
-  <si>
     <t>01003589.3</t>
   </si>
   <si>
-    <t>34191103100007562781090001320108120992717000</t>
-  </si>
-  <si>
     <t>01003592.3</t>
   </si>
   <si>
-    <t>34194103100001154561090001320518120992717000</t>
-  </si>
-  <si>
     <t>01003592.4</t>
   </si>
   <si>
-    <t>34194103800001154561090001320698120992717000</t>
-  </si>
-  <si>
     <t>01003589.4</t>
   </si>
   <si>
-    <t>34197103800007562761090001320288120992717000</t>
-  </si>
-  <si>
     <t>01003592.5</t>
   </si>
   <si>
-    <t>34198104500001154561090001320778120992717000</t>
-  </si>
-  <si>
     <t>ICARE MED LTDA</t>
   </si>
   <si>
     <t>01003747.1</t>
   </si>
   <si>
-    <t>34194105100006169531090001342898120992717000</t>
-  </si>
-  <si>
     <t>01003747.2</t>
   </si>
   <si>
-    <t>34198105800003850001090001342978120992717000</t>
-  </si>
-  <si>
     <t>01003747.3</t>
   </si>
   <si>
-    <t>34196106500003850001090001343058120992717000</t>
-  </si>
-  <si>
     <t>01003828.1</t>
   </si>
   <si>
-    <t>34191106500006089411090001356748120992717000</t>
-  </si>
-  <si>
     <t>01003828.2</t>
   </si>
   <si>
-    <t>34196107200003800001090001356828120992717000</t>
-  </si>
-  <si>
     <t>01003828.3</t>
   </si>
   <si>
-    <t>34191107900003800001090001356908120992717000</t>
-  </si>
-  <si>
     <t>MALCA</t>
   </si>
   <si>
@@ -375,36 +243,21 @@
     <t>CE</t>
   </si>
   <si>
-    <t>00196107900002287070000003473568000002883717</t>
-  </si>
-  <si>
     <t>01003847.3</t>
   </si>
   <si>
-    <t>00193108600002287060000003473568000002883817</t>
-  </si>
-  <si>
     <t>ISA COMERCIO VAREJISTA DE PRODUTOS HOSPITALARES LT</t>
   </si>
   <si>
     <t>01004522.1</t>
   </si>
   <si>
-    <t>00191118600004572620000003473568000002940517</t>
-  </si>
-  <si>
     <t>01004522.2</t>
   </si>
   <si>
-    <t>00191120000003663840000003473568000002940617</t>
-  </si>
-  <si>
     <t>01004522.3</t>
   </si>
   <si>
-    <t>00193121400003663840000003473568000002940717</t>
-  </si>
-  <si>
     <t>JOSEMAR</t>
   </si>
   <si>
@@ -414,25 +267,19 @@
     <t>01004900.1</t>
   </si>
   <si>
-    <t>00192123700003867340000003473568000002964017</t>
-  </si>
-  <si>
     <t>01004900.2</t>
   </si>
   <si>
-    <t>00192124400002144590000003473568000002964117</t>
-  </si>
-  <si>
     <t>01004900.3</t>
   </si>
   <si>
-    <t>00197125100002144590000003473568000002964217</t>
-  </si>
-  <si>
     <t>01004900.4</t>
   </si>
   <si>
-    <t>00191125800002144590000003473568000002964317</t>
+    <t>BR MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005075.3</t>
   </si>
   <si>
     <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
@@ -441,15 +288,6 @@
     <t>01005217.1BPBPBP</t>
   </si>
   <si>
-    <t>BR MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005075.3</t>
-  </si>
-  <si>
-    <t>00195127000004480000000003473568000002981317</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
@@ -465,205 +303,106 @@
     <t>01005781.1</t>
   </si>
   <si>
-    <t>00194138000000806340000003473568000003029417</t>
-  </si>
-  <si>
     <t>01005781.2</t>
   </si>
   <si>
-    <t>00194138700000503280000003473568000003029517</t>
-  </si>
-  <si>
     <t>01005781.3</t>
   </si>
   <si>
-    <t>00199139400000503280000003473568000003029617</t>
-  </si>
-  <si>
     <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
   </si>
   <si>
     <t>01005683.3</t>
   </si>
   <si>
-    <t>34199139500005466661090002533378120992717000</t>
+    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
+  </si>
+  <si>
+    <t>01005881.4</t>
+  </si>
+  <si>
+    <t>MONTALVAO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01006044.3</t>
+  </si>
+  <si>
+    <t>LEANDRA LUIZA SILVA</t>
+  </si>
+  <si>
+    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006179.1</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01006097.3</t>
+  </si>
+  <si>
+    <t>01006149.2</t>
+  </si>
+  <si>
+    <t>01006159.2</t>
+  </si>
+  <si>
+    <t>01006135.3</t>
+  </si>
+  <si>
+    <t>PBMED DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01006432.1</t>
+  </si>
+  <si>
+    <t>CRALAB SAUDE ATACADO LTDA</t>
+  </si>
+  <si>
+    <t>01006225.1</t>
+  </si>
+  <si>
+    <t>01006044.4</t>
+  </si>
+  <si>
+    <t>01006149.3</t>
+  </si>
+  <si>
+    <t>01006097.4</t>
+  </si>
+  <si>
+    <t>01006159.3</t>
   </si>
   <si>
     <t>MARCOS DUTRA</t>
   </si>
   <si>
-    <t>R7 DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005876.1</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>00191139500004434510000003473568000003040017</t>
-  </si>
-  <si>
-    <t>01005876.3</t>
-  </si>
-  <si>
-    <t>00198140900004434510000003473568000003040217</t>
-  </si>
-  <si>
-    <t>01005876.4</t>
-  </si>
-  <si>
-    <t>00192141600004434510000003473568000003040317</t>
-  </si>
-  <si>
-    <t>01005951.3</t>
-  </si>
-  <si>
-    <t>34191142300001265781090002549058120992717000</t>
-  </si>
-  <si>
-    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
-  </si>
-  <si>
-    <t>01005881.4</t>
-  </si>
-  <si>
-    <t>34195142800001470001090002540618120992717000</t>
-  </si>
-  <si>
-    <t>01005951.4</t>
-  </si>
-  <si>
-    <t>34194143000001265781090002549138120992717000</t>
-  </si>
-  <si>
-    <t>KELLEN</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA BELLFARMA LTDA</t>
-  </si>
-  <si>
-    <t>01005983.4</t>
-  </si>
-  <si>
-    <t>00197143300005125680000003473568000003055317</t>
-  </si>
-  <si>
-    <t>MONTALVAO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01006044.3</t>
-  </si>
-  <si>
-    <t>34199144500007020001090002558458120992717000</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01006089.3</t>
-  </si>
-  <si>
-    <t>34191144600000127641090002565958120992717000</t>
-  </si>
-  <si>
-    <t>01006135.2</t>
-  </si>
-  <si>
-    <t>34199144600000127631090002567288120992717000</t>
-  </si>
-  <si>
-    <t>LEANDRA LUIZA SILVA</t>
-  </si>
-  <si>
-    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
-  </si>
-  <si>
-    <t>01006179.1</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>00192144900006248230000003473568000003075617</t>
-  </si>
-  <si>
-    <t>01006097.3</t>
-  </si>
-  <si>
-    <t>34191145000001109701090002566608120992717000</t>
-  </si>
-  <si>
-    <t>01006149.2</t>
-  </si>
-  <si>
-    <t>34191145000000127631090002568508120992717000</t>
+    <t>3A DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006248.1</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006237.1</t>
+  </si>
+  <si>
+    <t>01006276.1</t>
   </si>
   <si>
     <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
   </si>
   <si>
-    <t>01006060.4</t>
-  </si>
-  <si>
-    <t>34198145000004375001090002562648120992717000</t>
-  </si>
-  <si>
-    <t>NOVA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006017.3</t>
-  </si>
-  <si>
-    <t>00191145000015028000000003473568000003058117</t>
-  </si>
-  <si>
-    <t>01006034.3</t>
-  </si>
-  <si>
-    <t>34197145100012096001090002555148120992717000</t>
-  </si>
-  <si>
-    <t>01006159.2</t>
-  </si>
-  <si>
-    <t>34197145100001021071090002568848120992717000</t>
-  </si>
-  <si>
-    <t>01006204.1</t>
-  </si>
-  <si>
-    <t>01006205.1</t>
-  </si>
-  <si>
-    <t>00198145200007395940000003473568000003078117</t>
-  </si>
-  <si>
-    <t>01006215.1</t>
-  </si>
-  <si>
-    <t>00191145200008305760000003473568000003086217</t>
-  </si>
-  <si>
-    <t>CRALAB SAUDE ATACADO LTDA</t>
-  </si>
-  <si>
-    <t>01006225.1</t>
-  </si>
-  <si>
-    <t>00193145300002100000000003473568000003079117</t>
-  </si>
-  <si>
-    <t>01006135.3</t>
-  </si>
-  <si>
-    <t>34191145300000127641090002567368120992717000</t>
-  </si>
-  <si>
-    <t>PBMED DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01006432.1</t>
+    <t>01006259.1</t>
   </si>
 </sst>
 </file>
@@ -838,7 +577,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
@@ -849,9 +588,7 @@
     <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
     <col max="7" min="7" style="1" width="26.28515625" customWidth="true"/>
     <col max="8" min="8" style="1" width="3.7109375" customWidth="true"/>
-    <col max="9" min="9" style="1" width="60.5703125" customWidth="true"/>
-    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
-    <col max="16384" min="11" style="1" width="12.140625"/>
+    <col max="16384" min="9" style="1" width="12.140625"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
@@ -879,22 +616,16 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>45326</v>
@@ -903,28 +634,24 @@
         <v>9391.78</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="3"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>45346</v>
@@ -933,28 +660,24 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="3"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>45350</v>
@@ -963,28 +686,24 @@
         <v>1264.87</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>45356</v>
@@ -993,28 +712,24 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="3"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>45362</v>
@@ -1023,28 +738,24 @@
         <v>384</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>45364</v>
@@ -1053,28 +764,24 @@
         <v>816</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>45378</v>
@@ -1083,28 +790,24 @@
         <v>816</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A9" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>45463</v>
@@ -1113,28 +816,24 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="3"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A10" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>45493</v>
@@ -1143,28 +842,24 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="3"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A11" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>45523</v>
@@ -1173,28 +868,24 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" s="3"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>45600</v>
@@ -1203,28 +894,24 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>45607</v>
@@ -1233,28 +920,24 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>45608</v>
@@ -1263,28 +946,24 @@
         <v>4439.9</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J14" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A15" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>45614</v>
@@ -1293,28 +972,24 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A16" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>45615</v>
@@ -1323,28 +998,24 @@
         <v>1216.86</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J16" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A17" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>45617</v>
@@ -1353,28 +1024,24 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J17" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>45622</v>
@@ -1383,28 +1050,24 @@
         <v>1216.86</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J18" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A19" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>45622</v>
@@ -1413,28 +1076,24 @@
         <v>4439.9</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>45624</v>
@@ -1443,28 +1102,24 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A21" s="3" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>45688</v>
@@ -1473,28 +1128,24 @@
         <v>1118.4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>45695</v>
@@ -1503,28 +1154,24 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J22" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>45699</v>
@@ -1533,28 +1180,24 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>45702</v>
@@ -1563,28 +1206,24 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J24" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>45705</v>
@@ -1593,28 +1232,24 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J25" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A26" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>45709</v>
@@ -1623,28 +1258,24 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J26" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A27" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>45712</v>
@@ -1653,28 +1284,24 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J27" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>45726</v>
@@ -1683,28 +1310,24 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J28" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A29" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>45727</v>
@@ -1713,28 +1336,24 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J29" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A30" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>45734</v>
@@ -1743,28 +1362,24 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J30" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A31" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>45734</v>
@@ -1773,28 +1388,24 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J31" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A32" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>45740</v>
@@ -1803,28 +1414,24 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J32" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A33" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>45741</v>
@@ -1833,28 +1440,24 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J33" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A34" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>45741</v>
@@ -1863,28 +1466,24 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A35" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>45748</v>
@@ -1893,28 +1492,24 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J35" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>45748</v>
@@ -1923,28 +1518,24 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J36" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A37" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>45755</v>
@@ -1953,28 +1544,24 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J37" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A38" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>45761</v>
@@ -1983,28 +1570,24 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J38" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A39" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>45768</v>
@@ -2013,28 +1596,24 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="J39" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A40" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>45775</v>
@@ -2043,28 +1622,24 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J40" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A41" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>45775</v>
@@ -2073,28 +1648,24 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J41" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A42" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>45782</v>
@@ -2103,28 +1674,24 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J42" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A43" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>45789</v>
@@ -2133,28 +1700,24 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J43" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A44" s="3" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="D44" s="4" t="n">
         <v>45789</v>
@@ -2163,28 +1726,24 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J44" s="3"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A45" s="3" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>45796</v>
@@ -2193,28 +1752,24 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J45" s="3"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>45896</v>
@@ -2223,28 +1778,24 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J46" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A47" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>45910</v>
@@ -2253,28 +1804,24 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J47" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A48" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>45924</v>
@@ -2283,28 +1830,24 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J48" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A49" s="3" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>45947</v>
@@ -2313,28 +1856,24 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J49" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A50" s="3" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="D50" s="4" t="n">
         <v>45954</v>
@@ -2343,28 +1882,24 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="J50" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A51" s="3" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>45961</v>
@@ -2373,28 +1908,24 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J51" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A52" s="3" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>45968</v>
@@ -2403,84 +1934,74 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J52" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A53" s="3" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="D53" s="4" t="n">
         <v>45980</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>38840.89</v>
+        <v>4480</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>184</v>
-      </c>
-      <c r="G53" s="3"/>
+        <v>190</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H53" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A54" s="3" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>45980</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>4480</v>
+        <v>38840.89</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>184</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J54" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A55" s="3" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>45987</v>
@@ -2489,24 +2010,22 @@
         <v>33844.16</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A56" s="3" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>45989</v>
@@ -2515,24 +2034,22 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A57" s="3" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>45994</v>
@@ -2541,24 +2058,22 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A58" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>46090</v>
@@ -2567,28 +2082,24 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="J58" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A59" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>46097</v>
@@ -2597,28 +2108,24 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J59" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A60" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>46104</v>
@@ -2627,28 +2134,24 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J60" s="3"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A61" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>46105</v>
@@ -2657,714 +2160,464 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J61" s="3"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A62" s="3" t="s">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>46105</v>
+        <v>46138</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>4434.51</v>
+        <v>1470</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J62" s="3"/>
+        <v>12</v>
+      </c>
     </row>
     <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A63" s="3" t="s">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>46119</v>
+        <v>46155</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>4434.51</v>
+        <v>7020</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J63" s="3"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A64" s="3" t="s">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>165</v>
+        <v>106</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>46126</v>
+        <v>46159</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>4434.51</v>
+        <v>6248.23</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J64" s="3"/>
+        <v>107</v>
+      </c>
     </row>
     <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A65" s="3" t="s">
-        <v>158</v>
+        <v>14</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>46133</v>
+        <v>46160</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1265.78</v>
+        <v>1109.7</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J65" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A66" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>46160</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>127.63</v>
+      </c>
+      <c r="F66" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>46138</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>1470</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>26</v>
-      </c>
       <c r="G66" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J66" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A67" s="3" t="s">
-        <v>158</v>
+        <v>14</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>46140</v>
+        <v>46161</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1265.78</v>
+        <v>1021.07</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="J67" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A68" s="3" t="s">
-        <v>174</v>
+        <v>14</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>46143</v>
+        <v>46163</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>5125.68</v>
+        <v>127.64</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J68" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A69" s="3" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>7020</v>
+        <v>8483.9</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J69" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A70" s="3" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>127.64</v>
+        <v>2100</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J70" s="3"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A71" s="3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>181</v>
+        <v>102</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>184</v>
+        <v>117</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>46156</v>
+        <v>46165</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>127.63</v>
+        <v>7020</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J71" s="3"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A72" s="3" t="s">
-        <v>186</v>
+        <v>14</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>188</v>
+        <v>118</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>46159</v>
+        <v>46167</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>6248.23</v>
+        <v>127.64</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="J72" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A73" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>1109.7</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J73" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A74" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>127.63</v>
+        <v>1021.06</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J74" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A75" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>4375</v>
+        <v>345.45</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J75" s="3"/>
+        <v>124</v>
+      </c>
     </row>
     <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A76" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>199</v>
+        <v>126</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>15028</v>
+        <v>17468.55</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J76" s="3"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A77" s="3" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>12096</v>
+        <v>838.8</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J77" s="3"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A78" s="3" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1021.07</v>
+        <v>3951.33</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J78" s="3"/>
-    </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A79" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>46162</v>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>27719.25</v>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-    </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A80" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>46162</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>7395.94</v>
-      </c>
-      <c r="F80" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J80" s="3"/>
-    </row>
-    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A81" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>46162</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>8305.76</v>
-      </c>
-      <c r="F81" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="J81" s="3"/>
-    </row>
-    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A82" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J82" s="3"/>
-    </row>
-    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A83" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>127.64</v>
-      </c>
-      <c r="F83" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J83" s="3"/>
-    </row>
-    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A84" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>46163</v>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>8483.9</v>
-      </c>
-      <c r="F84" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
-    </row>
-    <row r="85" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A85" s="7"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="9" t="n">
-        <v>410948.37</v>
-      </c>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
-      <c r="J85" s="10"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A79" s="7"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="9" t="n">
+        <v>346694.91</v>
+      </c>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="10"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t>Funcionário</t>
   </si>
@@ -276,18 +276,18 @@
     <t>01004900.4</t>
   </si>
   <si>
+    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
+  </si>
+  <si>
+    <t>01005217.1BPBPBP</t>
+  </si>
+  <si>
     <t>BR MEDICAMENTOS LTDA</t>
   </si>
   <si>
     <t>01005075.3</t>
   </si>
   <si>
-    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
-  </si>
-  <si>
-    <t>01005217.1BPBPBP</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
@@ -315,12 +315,6 @@
     <t>01005683.3</t>
   </si>
   <si>
-    <t>D E A FARMA DISTRIBUIDORA DE PRODUTOS FARMACEUTICO</t>
-  </si>
-  <si>
-    <t>01005881.4</t>
-  </si>
-  <si>
     <t>MONTALVAO COMERCIAL LTDA</t>
   </si>
   <si>
@@ -339,63 +333,27 @@
     <t>AM</t>
   </si>
   <si>
+    <t>CRALAB SAUDE ATACADO LTDA</t>
+  </si>
+  <si>
+    <t>01006225.1</t>
+  </si>
+  <si>
+    <t>01006044.4</t>
+  </si>
+  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006097.3</t>
-  </si>
-  <si>
-    <t>01006149.2</t>
-  </si>
-  <si>
-    <t>01006159.2</t>
-  </si>
-  <si>
-    <t>01006135.3</t>
-  </si>
-  <si>
-    <t>PBMED DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01006432.1</t>
-  </si>
-  <si>
-    <t>CRALAB SAUDE ATACADO LTDA</t>
-  </si>
-  <si>
-    <t>01006225.1</t>
-  </si>
-  <si>
-    <t>01006044.4</t>
+    <t>01006097.4</t>
   </si>
   <si>
     <t>01006149.3</t>
   </si>
   <si>
-    <t>01006097.4</t>
-  </si>
-  <si>
     <t>01006159.3</t>
   </si>
   <si>
-    <t>MARCOS DUTRA</t>
-  </si>
-  <si>
-    <t>3A DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006248.1</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>01006237.1</t>
-  </si>
-  <si>
     <t>01006276.1</t>
   </si>
   <si>
@@ -403,6 +361,27 @@
   </si>
   <si>
     <t>01006259.1</t>
+  </si>
+  <si>
+    <t>01006225.2</t>
+  </si>
+  <si>
+    <t>01006255.1</t>
+  </si>
+  <si>
+    <t>EMERSON</t>
+  </si>
+  <si>
+    <t>EXPRESS DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>280526</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
+    <t>01006233.2</t>
   </si>
 </sst>
 </file>
@@ -577,7 +556,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
@@ -634,7 +613,7 @@
         <v>9391.78</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
@@ -660,7 +639,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -686,7 +665,7 @@
         <v>1264.87</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -712,7 +691,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -738,7 +717,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -764,7 +743,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
@@ -790,7 +769,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
@@ -816,7 +795,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -842,7 +821,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>11</v>
@@ -868,7 +847,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -894,7 +873,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>11</v>
@@ -920,7 +899,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -946,7 +925,7 @@
         <v>4439.9</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
@@ -972,7 +951,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -998,7 +977,7 @@
         <v>1216.86</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>11</v>
@@ -1024,7 +1003,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -1050,7 +1029,7 @@
         <v>1216.86</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>11</v>
@@ -1076,7 +1055,7 @@
         <v>4439.9</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -1102,7 +1081,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>11</v>
@@ -1128,7 +1107,7 @@
         <v>1118.4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -1154,7 +1133,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
@@ -1180,7 +1159,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -1206,7 +1185,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>11</v>
@@ -1232,7 +1211,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>17</v>
@@ -1258,7 +1237,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>11</v>
@@ -1284,7 +1263,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
@@ -1310,7 +1289,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -1336,7 +1315,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -1362,7 +1341,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>11</v>
@@ -1388,7 +1367,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -1414,7 +1393,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>17</v>
@@ -1440,7 +1419,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -1466,7 +1445,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
@@ -1492,7 +1471,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -1518,7 +1497,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>11</v>
@@ -1544,7 +1523,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -1570,7 +1549,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>11</v>
@@ -1596,7 +1575,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -1622,7 +1601,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>11</v>
@@ -1648,7 +1627,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -1674,7 +1653,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -1700,7 +1679,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -1726,7 +1705,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -1752,7 +1731,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -1778,7 +1757,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -1804,7 +1783,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -1830,7 +1809,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -1856,7 +1835,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -1882,7 +1861,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -1908,7 +1887,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -1934,7 +1913,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -1945,7 +1924,7 @@
     </row>
     <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A53" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>87</v>
@@ -1957,21 +1936,19 @@
         <v>45980</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>4480</v>
+        <v>38840.89</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>190</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A54" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>89</v>
@@ -1983,14 +1960,16 @@
         <v>45980</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>38840.89</v>
+        <v>4480</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>190</v>
-      </c>
-      <c r="G54" s="3"/>
+        <v>194</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H54" s="3" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
@@ -1998,7 +1977,7 @@
         <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>91</v>
@@ -2010,7 +1989,7 @@
         <v>33844.16</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2022,7 +2001,7 @@
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>92</v>
@@ -2034,7 +2013,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2046,7 +2025,7 @@
         <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>93</v>
@@ -2058,7 +2037,7 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2082,7 +2061,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -2108,7 +2087,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -2134,7 +2113,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>17</v>
@@ -2160,7 +2139,7 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>11</v>
@@ -2180,62 +2159,62 @@
         <v>101</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>46138</v>
+        <v>46155</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1470</v>
+        <v>7020</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A63" s="3" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>46155</v>
+        <v>46159</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>7020</v>
+        <v>6248.23</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A64" s="3" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>46159</v>
+        <v>46163</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>6248.23</v>
+        <v>2100</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>11</v>
@@ -2244,33 +2223,33 @@
         <v>17</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A65" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="D65" s="4" t="n">
-        <v>46160</v>
+        <v>46165</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1109.7</v>
+        <v>7020</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
@@ -2278,19 +2257,19 @@
         <v>14</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>110</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>127.63</v>
+        <v>1109.7</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>11</v>
@@ -2304,19 +2283,19 @@
         <v>14</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1021.07</v>
+        <v>127.64</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>11</v>
@@ -2330,19 +2309,19 @@
         <v>14</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>112</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>127.64</v>
+        <v>1021.06</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>11</v>
@@ -2353,78 +2332,80 @@
     </row>
     <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A69" s="3" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="D69" s="4" t="n">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>8483.9</v>
+        <v>838.8</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G69" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="H69" s="3" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A70" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="D70" s="4" t="n">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2100</v>
+        <v>3951.33</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A71" s="3" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>46165</v>
+        <v>46170</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>7020</v>
+        <v>2100</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
@@ -2432,48 +2413,46 @@
         <v>14</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>127.64</v>
+        <v>2570.4</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A73" s="3" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1109.7</v>
+        <v>10</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>45</v>
@@ -2481,143 +2460,41 @@
     </row>
     <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A74" s="3" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1021.06</v>
+        <v>2077.2</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A75" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>46168</v>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>345.45</v>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A76" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>17468.55</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A77" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>838.8</v>
-      </c>
-      <c r="F77" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A78" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>3951.33</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H78" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="79" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A79" s="7"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="9" t="n">
-        <v>346694.91</v>
-      </c>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="10"/>
+    <row r="75" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A75" s="7"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="9" t="n">
+        <v>323298.57</v>
+      </c>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="10"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6441F9A5-6191-4B4A-A3D8-5775219B1350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="147">
   <si>
     <t>Funcionário</t>
   </si>
@@ -276,18 +288,18 @@
     <t>01004900.4</t>
   </si>
   <si>
+    <t>BR MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01005075.3</t>
+  </si>
+  <si>
     <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
   </si>
   <si>
     <t>01005217.1BPBPBP</t>
   </si>
   <si>
-    <t>BR MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01005075.3</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
@@ -342,76 +354,147 @@
     <t>01006044.4</t>
   </si>
   <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01006259.1</t>
+  </si>
+  <si>
+    <t>01006225.2</t>
+  </si>
+  <si>
+    <t>EMERSON</t>
+  </si>
+  <si>
+    <t>EXPRESS DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>280526</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006097.4</t>
-  </si>
-  <si>
-    <t>01006149.3</t>
-  </si>
-  <si>
-    <t>01006159.3</t>
-  </si>
-  <si>
-    <t>01006276.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
-  </si>
-  <si>
-    <t>01006259.1</t>
-  </si>
-  <si>
-    <t>01006225.2</t>
-  </si>
-  <si>
     <t>01006255.1</t>
   </si>
   <si>
-    <t>EMERSON</t>
-  </si>
-  <si>
-    <t>EXPRESS DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>280526</t>
-  </si>
-  <si>
-    <t>BRADESCO</t>
-  </si>
-  <si>
     <t>01006233.2</t>
+  </si>
+  <si>
+    <t>ORTHOMED COMERCIO DE PROD. HOSP. E ORTHOP. LTDA</t>
+  </si>
+  <si>
+    <t>01006314.1</t>
+  </si>
+  <si>
+    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01006305.1</t>
+  </si>
+  <si>
+    <t>NOVA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006017.4</t>
+  </si>
+  <si>
+    <t>01006034.4</t>
+  </si>
+  <si>
+    <t>01006259.2</t>
+  </si>
+  <si>
+    <t>01006215.3</t>
+  </si>
+  <si>
+    <t>MEDZ DISTRIBUIDORA HOSPITALAR E MEDICA LTDA</t>
+  </si>
+  <si>
+    <t>01006341.1</t>
+  </si>
+  <si>
+    <t>MARCOS DUTRA</t>
+  </si>
+  <si>
+    <t>DICOREL DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006336.1</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>01006225.3</t>
+  </si>
+  <si>
+    <t>01006204.2</t>
+  </si>
+  <si>
+    <t>01006205.2</t>
+  </si>
+  <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>RICCO FARMA DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01006195.2</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>01006255.2</t>
+  </si>
+  <si>
+    <t>MEDLOG LTDA</t>
+  </si>
+  <si>
+    <t>01006203.1</t>
+  </si>
+  <si>
+    <t>01006233.3</t>
+  </si>
+  <si>
+    <t>VWL DIST. DE MED. E MAT. MEDICO-HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01006092.4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -430,14 +513,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -460,117 +537,379 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
-  <dimension ref="A1:H75"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
-    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
-    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
-    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
-    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="26.28515625" customWidth="true"/>
-    <col max="8" min="8" style="1" width="3.7109375" customWidth="true"/>
-    <col max="16384" min="9" style="1" width="12.140625"/>
+    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -596,7 +935,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -606,14 +945,14 @@
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>45326</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>9391.78</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>848</v>
+      <c r="E2" s="5">
+        <v>9391.7800000000007</v>
+      </c>
+      <c r="F2" s="6">
+        <v>855</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>11</v>
@@ -622,7 +961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -632,14 +971,14 @@
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>45346</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5">
         <v>5418</v>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>828</v>
+      <c r="F3" s="6">
+        <v>835</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -648,7 +987,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -658,14 +997,14 @@
       <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>45350</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1264.87</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>824</v>
+      <c r="E4" s="5">
+        <v>1264.8699999999999</v>
+      </c>
+      <c r="F4" s="6">
+        <v>831</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
@@ -674,7 +1013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -684,14 +1023,14 @@
       <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>45356</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5">
         <v>5418</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>818</v>
+      <c r="F5" s="6">
+        <v>825</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -700,7 +1039,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -710,14 +1049,14 @@
       <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>45362</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5">
         <v>384</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>812</v>
+      <c r="F6" s="6">
+        <v>819</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
@@ -726,7 +1065,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -736,14 +1075,14 @@
       <c r="C7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>45364</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5">
         <v>816</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>810</v>
+      <c r="F7" s="6">
+        <v>817</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>17</v>
@@ -752,7 +1091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -762,14 +1101,14 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>45378</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5">
         <v>816</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>796</v>
+      <c r="F8" s="6">
+        <v>803</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>17</v>
@@ -778,7 +1117,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -788,14 +1127,14 @@
       <c r="C9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>45463</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5">
         <v>1674.52</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>711</v>
+      <c r="F9" s="6">
+        <v>718</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -804,7 +1143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -814,14 +1153,14 @@
       <c r="C10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>45493</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5">
         <v>873.6</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>681</v>
+      <c r="F10" s="6">
+        <v>688</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>11</v>
@@ -830,7 +1169,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -840,14 +1179,14 @@
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>45523</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5">
         <v>873.6</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>651</v>
+      <c r="F11" s="6">
+        <v>658</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -856,7 +1195,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -866,14 +1205,14 @@
       <c r="C12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>45600</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5">
         <v>2000</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>574</v>
+      <c r="F12" s="6">
+        <v>581</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>11</v>
@@ -882,7 +1221,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>28</v>
       </c>
@@ -892,14 +1231,14 @@
       <c r="C13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>45607</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5">
         <v>3204.34</v>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>567</v>
+      <c r="F13" s="6">
+        <v>574</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -908,7 +1247,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
@@ -918,14 +1257,14 @@
       <c r="C14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>45608</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>566</v>
+      <c r="E14" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F14" s="6">
+        <v>573</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>11</v>
@@ -934,7 +1273,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -944,14 +1283,14 @@
       <c r="C15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>45614</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="5">
         <v>2000</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>560</v>
+      <c r="F15" s="6">
+        <v>567</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -960,7 +1299,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
@@ -970,14 +1309,14 @@
       <c r="C16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>45615</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>559</v>
+      <c r="E16" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F16" s="6">
+        <v>566</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>11</v>
@@ -986,7 +1325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
@@ -996,14 +1335,14 @@
       <c r="C17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>45617</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="5">
         <v>1843.87</v>
       </c>
-      <c r="F17" s="6" t="n">
-        <v>557</v>
+      <c r="F17" s="6">
+        <v>564</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -1012,7 +1351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>28</v>
       </c>
@@ -1022,14 +1361,14 @@
       <c r="C18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>45622</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>552</v>
+      <c r="E18" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F18" s="6">
+        <v>559</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>11</v>
@@ -1038,7 +1377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -1048,14 +1387,14 @@
       <c r="C19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>45622</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>552</v>
+      <c r="E19" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F19" s="6">
+        <v>559</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -1064,7 +1403,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>28</v>
       </c>
@@ -1074,14 +1413,14 @@
       <c r="C20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>45624</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="5">
         <v>1843.88</v>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>550</v>
+      <c r="F20" s="6">
+        <v>557</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>11</v>
@@ -1090,7 +1429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
@@ -1100,14 +1439,14 @@
       <c r="C21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>45688</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>1118.4</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>486</v>
+      <c r="E21" s="5">
+        <v>1118.4000000000001</v>
+      </c>
+      <c r="F21" s="6">
+        <v>493</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -1116,7 +1455,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>28</v>
       </c>
@@ -1126,14 +1465,14 @@
       <c r="C22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>45695</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>479</v>
+      <c r="F22" s="6">
+        <v>486</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>11</v>
@@ -1142,7 +1481,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
@@ -1152,14 +1491,14 @@
       <c r="C23" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>45699</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="5">
         <v>2330</v>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>475</v>
+      <c r="F23" s="6">
+        <v>482</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -1168,7 +1507,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>28</v>
       </c>
@@ -1178,14 +1517,14 @@
       <c r="C24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>45702</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>472</v>
+      <c r="F24" s="6">
+        <v>479</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>11</v>
@@ -1194,7 +1533,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>28</v>
       </c>
@@ -1204,14 +1543,14 @@
       <c r="C25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>45705</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="5">
         <v>2541</v>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>469</v>
+      <c r="F25" s="6">
+        <v>476</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>17</v>
@@ -1220,7 +1559,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
@@ -1230,14 +1569,14 @@
       <c r="C26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>45709</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>465</v>
+      <c r="F26" s="6">
+        <v>472</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>11</v>
@@ -1246,7 +1585,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>28</v>
       </c>
@@ -1256,14 +1595,14 @@
       <c r="C27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>45712</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="5">
         <v>2541</v>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>462</v>
+      <c r="F27" s="6">
+        <v>469</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>17</v>
@@ -1272,7 +1611,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
@@ -1282,14 +1621,14 @@
       <c r="C28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>45726</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="5">
         <v>2541</v>
       </c>
-      <c r="F28" s="6" t="n">
-        <v>448</v>
+      <c r="F28" s="6">
+        <v>455</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -1298,7 +1637,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
@@ -1308,14 +1647,14 @@
       <c r="C29" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4">
         <v>45727</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F29" s="6" t="n">
-        <v>447</v>
+      <c r="F29" s="6">
+        <v>454</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -1324,7 +1663,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
@@ -1334,14 +1673,14 @@
       <c r="C30" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>45734</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F30" s="6" t="n">
-        <v>440</v>
+      <c r="F30" s="6">
+        <v>447</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>11</v>
@@ -1350,7 +1689,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>32</v>
       </c>
@@ -1360,14 +1699,14 @@
       <c r="C31" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>45734</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F31" s="6" t="n">
-        <v>440</v>
+      <c r="F31" s="6">
+        <v>447</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -1376,7 +1715,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>28</v>
       </c>
@@ -1386,14 +1725,14 @@
       <c r="C32" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>45740</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="5">
         <v>2541</v>
       </c>
-      <c r="F32" s="6" t="n">
-        <v>434</v>
+      <c r="F32" s="6">
+        <v>441</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>17</v>
@@ -1402,7 +1741,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>28</v>
       </c>
@@ -1412,14 +1751,14 @@
       <c r="C33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>45741</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F33" s="6" t="n">
-        <v>433</v>
+      <c r="F33" s="6">
+        <v>440</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -1428,7 +1767,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>32</v>
       </c>
@@ -1438,14 +1777,14 @@
       <c r="C34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>45741</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F34" s="6" t="n">
-        <v>433</v>
+      <c r="F34" s="6">
+        <v>440</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>11</v>
@@ -1454,7 +1793,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
@@ -1464,14 +1803,14 @@
       <c r="C35" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4">
         <v>45748</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F35" s="6" t="n">
-        <v>426</v>
+      <c r="F35" s="6">
+        <v>433</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -1480,7 +1819,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>28</v>
       </c>
@@ -1490,14 +1829,14 @@
       <c r="C36" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4">
         <v>45748</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="5">
         <v>7562.76</v>
       </c>
-      <c r="F36" s="6" t="n">
-        <v>426</v>
+      <c r="F36" s="6">
+        <v>433</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>11</v>
@@ -1506,7 +1845,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>32</v>
       </c>
@@ -1516,14 +1855,14 @@
       <c r="C37" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4">
         <v>45755</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F37" s="6" t="n">
-        <v>419</v>
+      <c r="F37" s="6">
+        <v>426</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -1532,7 +1871,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>32</v>
       </c>
@@ -1542,14 +1881,14 @@
       <c r="C38" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="4">
         <v>45761</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="5">
         <v>6169.53</v>
       </c>
-      <c r="F38" s="6" t="n">
-        <v>413</v>
+      <c r="F38" s="6">
+        <v>420</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>11</v>
@@ -1558,7 +1897,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>32</v>
       </c>
@@ -1568,14 +1907,14 @@
       <c r="C39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="4">
         <v>45768</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="5">
         <v>3850</v>
       </c>
-      <c r="F39" s="6" t="n">
-        <v>406</v>
+      <c r="F39" s="6">
+        <v>413</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -1584,7 +1923,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>32</v>
       </c>
@@ -1594,14 +1933,14 @@
       <c r="C40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="4">
         <v>45775</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="5">
         <v>3850</v>
       </c>
-      <c r="F40" s="6" t="n">
-        <v>399</v>
+      <c r="F40" s="6">
+        <v>406</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>11</v>
@@ -1610,7 +1949,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>32</v>
       </c>
@@ -1620,14 +1959,14 @@
       <c r="C41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="4">
         <v>45775</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="5">
         <v>6089.41</v>
       </c>
-      <c r="F41" s="6" t="n">
-        <v>399</v>
+      <c r="F41" s="6">
+        <v>406</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -1636,7 +1975,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>32</v>
       </c>
@@ -1646,14 +1985,14 @@
       <c r="C42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="4">
         <v>45782</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="5">
         <v>3800</v>
       </c>
-      <c r="F42" s="6" t="n">
-        <v>392</v>
+      <c r="F42" s="6">
+        <v>399</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>11</v>
@@ -1662,7 +2001,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>32</v>
       </c>
@@ -1672,14 +2011,14 @@
       <c r="C43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="4">
         <v>45789</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="5">
         <v>3800</v>
       </c>
-      <c r="F43" s="6" t="n">
-        <v>385</v>
+      <c r="F43" s="6">
+        <v>392</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -1688,7 +2027,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>72</v>
       </c>
@@ -1698,14 +2037,14 @@
       <c r="C44" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="4">
         <v>45789</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="5">
         <v>1143.54</v>
       </c>
-      <c r="F44" s="6" t="n">
-        <v>385</v>
+      <c r="F44" s="6">
+        <v>392</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>17</v>
@@ -1714,7 +2053,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>72</v>
       </c>
@@ -1724,14 +2063,14 @@
       <c r="C45" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="4">
         <v>45796</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="5">
         <v>2287.06</v>
       </c>
-      <c r="F45" s="6" t="n">
-        <v>378</v>
+      <c r="F45" s="6">
+        <v>385</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -1740,7 +2079,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>28</v>
       </c>
@@ -1750,14 +2089,14 @@
       <c r="C46" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="4">
         <v>45896</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="5">
         <v>4572.62</v>
       </c>
-      <c r="F46" s="6" t="n">
-        <v>278</v>
+      <c r="F46" s="6">
+        <v>285</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>17</v>
@@ -1766,7 +2105,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>28</v>
       </c>
@@ -1776,14 +2115,14 @@
       <c r="C47" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="4">
         <v>45910</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F47" s="6" t="n">
-        <v>264</v>
+      <c r="F47" s="6">
+        <v>271</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>17</v>
@@ -1792,7 +2131,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>28</v>
       </c>
@@ -1802,14 +2141,14 @@
       <c r="C48" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="4">
         <v>45924</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F48" s="6" t="n">
-        <v>250</v>
+      <c r="F48" s="6">
+        <v>257</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
@@ -1818,7 +2157,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="49" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>81</v>
       </c>
@@ -1828,14 +2167,14 @@
       <c r="C49" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="4">
         <v>45947</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="5">
         <v>3867.34</v>
       </c>
-      <c r="F49" s="6" t="n">
-        <v>227</v>
+      <c r="F49" s="6">
+        <v>234</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>17</v>
@@ -1844,7 +2183,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>81</v>
       </c>
@@ -1854,14 +2193,14 @@
       <c r="C50" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="4">
         <v>45954</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F50" s="6" t="n">
-        <v>220</v>
+      <c r="F50" s="6">
+        <v>227</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>17</v>
@@ -1870,7 +2209,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="51" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>81</v>
       </c>
@@ -1880,14 +2219,14 @@
       <c r="C51" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="4">
         <v>45961</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F51" s="6" t="n">
-        <v>213</v>
+      <c r="F51" s="6">
+        <v>220</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>17</v>
@@ -1896,7 +2235,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>81</v>
       </c>
@@ -1906,14 +2245,14 @@
       <c r="C52" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="4">
         <v>45968</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F52" s="6" t="n">
-        <v>206</v>
+      <c r="F52" s="6">
+        <v>213</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
@@ -1922,9 +2261,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>87</v>
@@ -1932,23 +2271,25 @@
       <c r="C53" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="4">
         <v>45980</v>
       </c>
-      <c r="E53" s="5" t="n">
-        <v>38840.89</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>194</v>
-      </c>
-      <c r="G53" s="3"/>
+      <c r="E53" s="5">
+        <v>4480</v>
+      </c>
+      <c r="F53" s="6">
+        <v>201</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H53" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>89</v>
@@ -1956,95 +2297,93 @@
       <c r="C54" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="4">
         <v>45980</v>
       </c>
-      <c r="E54" s="5" t="n">
-        <v>4480</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>194</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="E54" s="5">
+        <v>38840.89</v>
+      </c>
+      <c r="F54" s="6">
+        <v>201</v>
+      </c>
+      <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="4">
         <v>45987</v>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>33844.16</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>187</v>
+      <c r="E55" s="5">
+        <v>33844.160000000003</v>
+      </c>
+      <c r="F55" s="6">
+        <v>194</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="56" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="4">
         <v>45989</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="5">
         <v>3220</v>
       </c>
-      <c r="F56" s="6" t="n">
-        <v>185</v>
+      <c r="F56" s="6">
+        <v>192</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="4">
         <v>45994</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="5">
         <v>38740.53</v>
       </c>
-      <c r="F57" s="6" t="n">
-        <v>180</v>
+      <c r="F57" s="6">
+        <v>187</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="58" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>14</v>
       </c>
@@ -2054,14 +2393,14 @@
       <c r="C58" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="4">
         <v>46090</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="5">
         <v>806.34</v>
       </c>
-      <c r="F58" s="6" t="n">
-        <v>84</v>
+      <c r="F58" s="6">
+        <v>91</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>17</v>
@@ -2070,7 +2409,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="59" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>14</v>
       </c>
@@ -2080,14 +2419,14 @@
       <c r="C59" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="4">
         <v>46097</v>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E59" s="5">
         <v>503.28</v>
       </c>
-      <c r="F59" s="6" t="n">
-        <v>77</v>
+      <c r="F59" s="6">
+        <v>84</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>17</v>
@@ -2096,7 +2435,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>14</v>
       </c>
@@ -2106,14 +2445,14 @@
       <c r="C60" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="4">
         <v>46104</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="5">
         <v>503.28</v>
       </c>
-      <c r="F60" s="6" t="n">
-        <v>70</v>
+      <c r="F60" s="6">
+        <v>77</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>17</v>
@@ -2122,7 +2461,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
@@ -2132,14 +2471,14 @@
       <c r="C61" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="4">
         <v>46105</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="5">
         <v>5466.66</v>
       </c>
-      <c r="F61" s="6" t="n">
-        <v>69</v>
+      <c r="F61" s="6">
+        <v>76</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>11</v>
@@ -2148,7 +2487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>8</v>
       </c>
@@ -2158,14 +2497,14 @@
       <c r="C62" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="4">
         <v>46155</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E62" s="5">
         <v>7020</v>
       </c>
-      <c r="F62" s="6" t="n">
-        <v>19</v>
+      <c r="F62" s="6">
+        <v>26</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>11</v>
@@ -2174,7 +2513,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>102</v>
       </c>
@@ -2184,14 +2523,14 @@
       <c r="C63" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="4">
         <v>46159</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="5">
         <v>6248.23</v>
       </c>
-      <c r="F63" s="6" t="n">
-        <v>15</v>
+      <c r="F63" s="6">
+        <v>22</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>17</v>
@@ -2200,7 +2539,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>72</v>
       </c>
@@ -2210,14 +2549,14 @@
       <c r="C64" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="4">
         <v>46163</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="5">
         <v>2100</v>
       </c>
-      <c r="F64" s="6" t="n">
-        <v>11</v>
+      <c r="F64" s="6">
+        <v>18</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>17</v>
@@ -2226,7 +2565,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>8</v>
       </c>
@@ -2236,14 +2575,14 @@
       <c r="C65" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="4">
         <v>46165</v>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E65" s="5">
         <v>7020</v>
       </c>
-      <c r="F65" s="6" t="n">
-        <v>9</v>
+      <c r="F65" s="6">
+        <v>16</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>11</v>
@@ -2252,9 +2591,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>109</v>
@@ -2262,118 +2601,116 @@
       <c r="C66" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D66" s="4" t="n">
-        <v>46167</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>1109.7</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>7</v>
+      <c r="D66" s="4">
+        <v>46169</v>
+      </c>
+      <c r="E66" s="5">
+        <v>3951.33</v>
+      </c>
+      <c r="F66" s="6">
+        <v>12</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D67" s="4" t="n">
-        <v>46167</v>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>127.64</v>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>7</v>
+      <c r="D67" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E67" s="5">
+        <v>2100</v>
+      </c>
+      <c r="F67" s="6">
+        <v>11</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>46168</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>1021.06</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>6</v>
+        <v>114</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E68" s="5">
+        <v>10</v>
+      </c>
+      <c r="F68" s="6">
+        <v>11</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>838.8</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D69" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2570.4</v>
+      </c>
+      <c r="F69" s="6">
+        <v>11</v>
+      </c>
+      <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>3951.33</v>
-      </c>
-      <c r="F70" s="6" t="n">
-        <v>5</v>
+        <v>118</v>
+      </c>
+      <c r="D70" s="4">
+        <v>46171</v>
+      </c>
+      <c r="E70" s="5">
+        <v>2077.1999999999998</v>
+      </c>
+      <c r="F70" s="6">
+        <v>10</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>17</v>
@@ -2382,121 +2719,409 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>46170</v>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D71" s="4">
+        <v>46172</v>
+      </c>
+      <c r="E71" s="5">
+        <v>5106.55</v>
+      </c>
+      <c r="F71" s="6">
+        <v>9</v>
+      </c>
+      <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>46170</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>2570.4</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>4</v>
+        <v>122</v>
+      </c>
+      <c r="D72" s="4">
+        <v>46174</v>
+      </c>
+      <c r="E72" s="5">
+        <v>1034.3800000000001</v>
+      </c>
+      <c r="F72" s="6">
+        <v>7</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>46170</v>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F73" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="D73" s="4">
+        <v>46175</v>
+      </c>
+      <c r="E73" s="5">
+        <v>15028</v>
+      </c>
+      <c r="F73" s="6">
+        <v>6</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D74" s="4">
+        <v>46176</v>
+      </c>
+      <c r="E74" s="5">
+        <v>12096</v>
+      </c>
+      <c r="F74" s="6">
+        <v>5</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D75" s="4">
+        <v>46176</v>
+      </c>
+      <c r="E75" s="5">
+        <v>1971.6</v>
+      </c>
+      <c r="F75" s="6">
+        <v>5</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D76" s="4">
+        <v>46176</v>
+      </c>
+      <c r="E76" s="5">
+        <v>5183.09</v>
+      </c>
+      <c r="F76" s="6">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D77" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E77" s="5">
+        <v>2127.2399999999998</v>
+      </c>
+      <c r="F77" s="6">
         <v>4</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="H73" s="3" t="s">
+      <c r="G77" s="3"/>
+      <c r="H77" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E78" s="5">
+        <v>7768.64</v>
+      </c>
+      <c r="F78" s="6">
+        <v>4</v>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D79" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E79" s="5">
+        <v>2100</v>
+      </c>
+      <c r="F79" s="6">
+        <v>4</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D80" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E80" s="5">
+        <v>15716</v>
+      </c>
+      <c r="F80" s="6">
+        <v>4</v>
+      </c>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D81" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E81" s="5">
+        <v>4193.28</v>
+      </c>
+      <c r="F81" s="6">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D82" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E82" s="5">
+        <v>27757.97</v>
+      </c>
+      <c r="F82" s="6">
+        <v>4</v>
+      </c>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D83" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E83" s="5">
+        <v>2570.4</v>
+      </c>
+      <c r="F83" s="6">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A74" s="3" t="s">
+    <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E84" s="5">
+        <v>9092.44</v>
+      </c>
+      <c r="F84" s="6">
+        <v>4</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>2077.2</v>
-      </c>
-      <c r="F74" s="6" t="n">
+      <c r="B85" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D85" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E85" s="5">
+        <v>2077.1999999999998</v>
+      </c>
+      <c r="F85" s="6">
         <v>3</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H74" s="3" t="s">
+      <c r="G85" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H85" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="75" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A75" s="7"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="9" t="n">
-        <v>323298.57</v>
-      </c>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="10"/>
+    <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D86" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E86" s="5">
+        <v>2625</v>
+      </c>
+      <c r="F86" s="6">
+        <v>3</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6441F9A5-6191-4B4A-A3D8-5775219B1350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4191E296-1BBC-4306-A144-3375FFEBD7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="211">
   <si>
     <t>Funcionário</t>
   </si>
@@ -51,6 +51,12 @@
     <t>UF</t>
   </si>
   <si>
+    <t>Cod.Barras - Boleto</t>
+  </si>
+  <si>
+    <t>Cod.Pag-Banco</t>
+  </si>
+  <si>
     <t>DANILO</t>
   </si>
   <si>
@@ -66,9 +72,15 @@
     <t>AL</t>
   </si>
   <si>
+    <t>34192961600009391781090001019578120992717000</t>
+  </si>
+  <si>
     <t>01001504.3</t>
   </si>
   <si>
+    <t>34194963600005418001090001019738120992717000</t>
+  </si>
+  <si>
     <t>MARCELO LOPES</t>
   </si>
   <si>
@@ -84,18 +96,33 @@
     <t>PE</t>
   </si>
   <si>
+    <t>00191964000001264870000003473568000002622117</t>
+  </si>
+  <si>
     <t>01001504.4</t>
   </si>
   <si>
+    <t>34194964600005418001090001019818120992717000</t>
+  </si>
+  <si>
     <t>01001548.3</t>
   </si>
   <si>
+    <t>00193965200000384000000003473568000002617517</t>
+  </si>
+  <si>
     <t>01001617.2</t>
   </si>
   <si>
+    <t>00191965400000816000000003473568000002622217</t>
+  </si>
+  <si>
     <t>01001617.3</t>
   </si>
   <si>
+    <t>00192966800000816000000003473568000002622317</t>
+  </si>
+  <si>
     <t>VEC HOSPITALAR LTDA ME</t>
   </si>
   <si>
@@ -105,12 +132,21 @@
     <t>SE</t>
   </si>
   <si>
+    <t>34192975300001674521090001106858120992717000</t>
+  </si>
+  <si>
     <t>01002233.3</t>
   </si>
   <si>
+    <t>34192978300000873601090001107018120992717000</t>
+  </si>
+  <si>
     <t>01002233.5</t>
   </si>
   <si>
+    <t>34191981300000873601090001107278120992717000</t>
+  </si>
+  <si>
     <t>MARIO JR</t>
   </si>
   <si>
@@ -120,9 +156,15 @@
     <t>01003029.2</t>
   </si>
   <si>
+    <t>34195989000002000001090001238528120992717000</t>
+  </si>
+  <si>
     <t>01003029.1</t>
   </si>
   <si>
+    <t>34197987600003204341090001238458120992717000</t>
+  </si>
+  <si>
     <t>MOISES</t>
   </si>
   <si>
@@ -135,24 +177,45 @@
     <t>BA</t>
   </si>
   <si>
+    <t>34196989800004439901090001240908120992717000</t>
+  </si>
+  <si>
     <t>01003029.3</t>
   </si>
   <si>
+    <t>34195990400002000001090001238608120992717000</t>
+  </si>
+  <si>
     <t>01002938.2</t>
   </si>
   <si>
+    <t>34194986400001216861090001218808120992717000</t>
+  </si>
+  <si>
     <t>01002951.2</t>
   </si>
   <si>
+    <t>34193985900001843871090001228138120992717000</t>
+  </si>
+  <si>
     <t>01002938.3</t>
   </si>
   <si>
+    <t>34192987800001216861090001218988120992717000</t>
+  </si>
+  <si>
     <t>01002991.4</t>
   </si>
   <si>
+    <t>34197991200004439901090001241088120992717000</t>
+  </si>
+  <si>
     <t>01002951.3</t>
   </si>
   <si>
+    <t>34194986600001843881090001228218120992717000</t>
+  </si>
+  <si>
     <t>SERGIO ROBERTO</t>
   </si>
   <si>
@@ -165,6 +228,9 @@
     <t>PB</t>
   </si>
   <si>
+    <t>34191997800001118401090001280758120992717000</t>
+  </si>
+  <si>
     <t xml:space="preserve">RN COMERCIO DE MEDICAMENTOS E MATERIAL HOSPITALAR </t>
   </si>
   <si>
@@ -174,75 +240,141 @@
     <t>RN</t>
   </si>
   <si>
+    <t>34194998500003296801090001307668120992717000</t>
+  </si>
+  <si>
     <t>01003409.6</t>
   </si>
   <si>
+    <t>34199998900002330001090001290998120992717000</t>
+  </si>
+  <si>
     <t>01003464.5</t>
   </si>
   <si>
+    <t>34198999200003296801090001307748120992717000</t>
+  </si>
+  <si>
     <t>01003504.1</t>
   </si>
   <si>
+    <t>00191999500002541000000003473568000002851217</t>
+  </si>
+  <si>
     <t>01003464.6</t>
   </si>
   <si>
+    <t>34191999900003296801090001307828120992717000</t>
+  </si>
+  <si>
     <t>01003504.2</t>
   </si>
   <si>
+    <t>00195100200002541000000003473568000002851317</t>
+  </si>
+  <si>
     <t>01003504.4</t>
   </si>
   <si>
+    <t>00194101600002541000000003473568000002851517</t>
+  </si>
+  <si>
     <t>01003589.1</t>
   </si>
   <si>
+    <t>34197101700007562781090001319968120992717000</t>
+  </si>
+  <si>
     <t>01003589.2</t>
   </si>
   <si>
+    <t>34198102400007562781090001320028120992717000</t>
+  </si>
+  <si>
     <t>MED-K COMERCIO LTDA</t>
   </si>
   <si>
     <t>01003592.2</t>
   </si>
   <si>
+    <t>34194102400001154561090001320448120992717000</t>
+  </si>
+  <si>
     <t>01003504.6</t>
   </si>
   <si>
+    <t>00193103000002541000000003473568000002851717</t>
+  </si>
+  <si>
     <t>01003589.3</t>
   </si>
   <si>
+    <t>34191103100007562781090001320108120992717000</t>
+  </si>
+  <si>
     <t>01003592.3</t>
   </si>
   <si>
+    <t>34194103100001154561090001320518120992717000</t>
+  </si>
+  <si>
     <t>01003592.4</t>
   </si>
   <si>
+    <t>34194103800001154561090001320698120992717000</t>
+  </si>
+  <si>
     <t>01003589.4</t>
   </si>
   <si>
+    <t>34197103800007562761090001320288120992717000</t>
+  </si>
+  <si>
     <t>01003592.5</t>
   </si>
   <si>
+    <t>34198104500001154561090001320778120992717000</t>
+  </si>
+  <si>
     <t>ICARE MED LTDA</t>
   </si>
   <si>
     <t>01003747.1</t>
   </si>
   <si>
+    <t>34194105100006169531090001342898120992717000</t>
+  </si>
+  <si>
     <t>01003747.2</t>
   </si>
   <si>
+    <t>34198105800003850001090001342978120992717000</t>
+  </si>
+  <si>
     <t>01003747.3</t>
   </si>
   <si>
+    <t>34196106500003850001090001343058120992717000</t>
+  </si>
+  <si>
     <t>01003828.1</t>
   </si>
   <si>
+    <t>34191106500006089411090001356748120992717000</t>
+  </si>
+  <si>
     <t>01003828.2</t>
   </si>
   <si>
+    <t>34196107200003800001090001356828120992717000</t>
+  </si>
+  <si>
     <t>01003828.3</t>
   </si>
   <si>
+    <t>34191107900003800001090001356908120992717000</t>
+  </si>
+  <si>
     <t>MALCA</t>
   </si>
   <si>
@@ -255,21 +387,36 @@
     <t>CE</t>
   </si>
   <si>
+    <t>00196107900002287070000003473568000002883717</t>
+  </si>
+  <si>
     <t>01003847.3</t>
   </si>
   <si>
+    <t>00193108600002287060000003473568000002883817</t>
+  </si>
+  <si>
     <t>ISA COMERCIO VAREJISTA DE PRODUTOS HOSPITALARES LT</t>
   </si>
   <si>
     <t>01004522.1</t>
   </si>
   <si>
+    <t>00191118600004572620000003473568000002940517</t>
+  </si>
+  <si>
     <t>01004522.2</t>
   </si>
   <si>
+    <t>00191120000003663840000003473568000002940617</t>
+  </si>
+  <si>
     <t>01004522.3</t>
   </si>
   <si>
+    <t>00193121400003663840000003473568000002940717</t>
+  </si>
+  <si>
     <t>JOSEMAR</t>
   </si>
   <si>
@@ -279,21 +426,36 @@
     <t>01004900.1</t>
   </si>
   <si>
+    <t>00192123700003867340000003473568000002964017</t>
+  </si>
+  <si>
     <t>01004900.2</t>
   </si>
   <si>
+    <t>00192124400002144590000003473568000002964117</t>
+  </si>
+  <si>
     <t>01004900.3</t>
   </si>
   <si>
+    <t>00197125100002144590000003473568000002964217</t>
+  </si>
+  <si>
     <t>01004900.4</t>
   </si>
   <si>
+    <t>00191125800002144590000003473568000002964317</t>
+  </si>
+  <si>
     <t>BR MEDICAMENTOS LTDA</t>
   </si>
   <si>
     <t>01005075.3</t>
   </si>
   <si>
+    <t>00195127000004480000000003473568000002981317</t>
+  </si>
+  <si>
     <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
   </si>
   <si>
@@ -315,157 +477,187 @@
     <t>01005781.1</t>
   </si>
   <si>
+    <t>00194138000000806340000003473568000003029417</t>
+  </si>
+  <si>
     <t>01005781.2</t>
   </si>
   <si>
+    <t>00194138700000503280000003473568000003029517</t>
+  </si>
+  <si>
     <t>01005781.3</t>
   </si>
   <si>
+    <t>00199139400000503280000003473568000003029617</t>
+  </si>
+  <si>
     <t>MAIS SAUDE COMERCIO DE PRODUTOS HOSPITALARES LTDA</t>
   </si>
   <si>
     <t>01005683.3</t>
   </si>
   <si>
+    <t>34199139500005466661090002533378120992717000</t>
+  </si>
+  <si>
+    <t>LEANDRA LUIZA SILVA</t>
+  </si>
+  <si>
+    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006179.1</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>00192144900006248230000003473568000003075617</t>
+  </si>
+  <si>
+    <t>CRALAB SAUDE ATACADO LTDA</t>
+  </si>
+  <si>
+    <t>01006225.1</t>
+  </si>
+  <si>
+    <t>00193145300002100000000003473568000003079117</t>
+  </si>
+  <si>
     <t>MONTALVAO COMERCIAL LTDA</t>
   </si>
   <si>
-    <t>01006044.3</t>
-  </si>
-  <si>
-    <t>LEANDRA LUIZA SILVA</t>
-  </si>
-  <si>
-    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
-  </si>
-  <si>
-    <t>01006179.1</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>CRALAB SAUDE ATACADO LTDA</t>
-  </si>
-  <si>
-    <t>01006225.1</t>
-  </si>
-  <si>
     <t>01006044.4</t>
   </si>
   <si>
+    <t>34195145500007020001090002558528120992717000</t>
+  </si>
+  <si>
+    <t>01006225.2</t>
+  </si>
+  <si>
+    <t>00198146000002100000000003473568000003079217</t>
+  </si>
+  <si>
+    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01006305.1</t>
+  </si>
+  <si>
+    <t>NOVA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006017.4</t>
+  </si>
+  <si>
+    <t>00191146500015028000000003473568000003058217</t>
+  </si>
+  <si>
+    <t>01006034.4</t>
+  </si>
+  <si>
+    <t>34194146600012096001090002555228120992717000</t>
+  </si>
+  <si>
     <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
   </si>
   <si>
-    <t>01006259.1</t>
-  </si>
-  <si>
-    <t>01006225.2</t>
-  </si>
-  <si>
-    <t>EMERSON</t>
-  </si>
-  <si>
-    <t>EXPRESS DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>280526</t>
-  </si>
-  <si>
-    <t>BRADESCO</t>
+    <t>01006259.2</t>
+  </si>
+  <si>
+    <t>00193146600001971600000003473568000003085817</t>
+  </si>
+  <si>
+    <t>01006215.3</t>
+  </si>
+  <si>
+    <t>00198146600005183090000003473568000003086417</t>
+  </si>
+  <si>
+    <t>01006225.3</t>
+  </si>
+  <si>
+    <t>00192146700002100000000003473568000003079317</t>
+  </si>
+  <si>
+    <t>01006204.2</t>
+  </si>
+  <si>
+    <t>01006205.2</t>
+  </si>
+  <si>
+    <t>00194146700004193280000003473568000003078217</t>
   </si>
   <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006255.1</t>
-  </si>
-  <si>
-    <t>01006233.2</t>
+    <t>01006255.2</t>
+  </si>
+  <si>
+    <t>01006233.3</t>
+  </si>
+  <si>
+    <t>00196146800002077200000003473568000003083117</t>
+  </si>
+  <si>
+    <t>VWL DIST. DE MED. E MAT. MEDICO-HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01006092.4</t>
+  </si>
+  <si>
+    <t>00192146800002625000000003473568000003064817</t>
+  </si>
+  <si>
+    <t>01006207.2</t>
+  </si>
+  <si>
+    <t>S&amp;J DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01006105.4</t>
+  </si>
+  <si>
+    <t>00195146900001800000000003473568000003066317</t>
+  </si>
+  <si>
+    <t>CAMEDIC COMERCIAL E SERVIÇOS DE PROD MED HOSP EIRE</t>
+  </si>
+  <si>
+    <t>01006350.1</t>
+  </si>
+  <si>
+    <t>34193147100001565051090002579738120992717000</t>
+  </si>
+  <si>
+    <t>01006305.2</t>
+  </si>
+  <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>RICCO FARMA DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>01006166.3</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>L G PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01006307.2</t>
   </si>
   <si>
     <t>ORTHOMED COMERCIO DE PROD. HOSP. E ORTHOP. LTDA</t>
   </si>
   <si>
-    <t>01006314.1</t>
-  </si>
-  <si>
-    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
-  </si>
-  <si>
-    <t>01006305.1</t>
-  </si>
-  <si>
-    <t>NOVA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006017.4</t>
-  </si>
-  <si>
-    <t>01006034.4</t>
-  </si>
-  <si>
-    <t>01006259.2</t>
-  </si>
-  <si>
-    <t>01006215.3</t>
-  </si>
-  <si>
-    <t>MEDZ DISTRIBUIDORA HOSPITALAR E MEDICA LTDA</t>
-  </si>
-  <si>
-    <t>01006341.1</t>
-  </si>
-  <si>
-    <t>MARCOS DUTRA</t>
-  </si>
-  <si>
-    <t>DICOREL DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006336.1</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>01006225.3</t>
-  </si>
-  <si>
-    <t>01006204.2</t>
-  </si>
-  <si>
-    <t>01006205.2</t>
-  </si>
-  <si>
-    <t>KELLEN</t>
-  </si>
-  <si>
-    <t>RICCO FARMA DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01006195.2</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>01006255.2</t>
-  </si>
-  <si>
-    <t>MEDLOG LTDA</t>
-  </si>
-  <si>
-    <t>01006203.1</t>
-  </si>
-  <si>
-    <t>01006233.3</t>
-  </si>
-  <si>
-    <t>VWL DIST. DE MED. E MAT. MEDICO-HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01006092.4</t>
+    <t>01006314.2</t>
   </si>
 </sst>
 </file>
@@ -895,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -906,10 +1098,12 @@
     <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
     <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.140625" style="1"/>
+    <col min="9" max="9" width="60.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -934,16 +1128,22 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4">
         <v>45326</v>
@@ -952,24 +1152,28 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" s="4">
         <v>45346</v>
@@ -978,24 +1182,28 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4">
         <v>45350</v>
@@ -1004,24 +1212,28 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4">
         <v>45356</v>
@@ -1030,24 +1242,28 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4">
         <v>45362</v>
@@ -1056,24 +1272,28 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B7" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4">
         <v>45364</v>
@@ -1082,24 +1302,28 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4">
         <v>45378</v>
@@ -1108,24 +1332,28 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D9" s="4">
         <v>45463</v>
@@ -1134,24 +1362,28 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D10" s="4">
         <v>45493</v>
@@ -1160,24 +1392,28 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D11" s="4">
         <v>45523</v>
@@ -1186,24 +1422,28 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D12" s="4">
         <v>45600</v>
@@ -1212,24 +1452,28 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D13" s="4">
         <v>45607</v>
@@ -1238,24 +1482,28 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D14" s="4">
         <v>45608</v>
@@ -1264,24 +1512,28 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D15" s="4">
         <v>45614</v>
@@ -1290,24 +1542,28 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D16" s="4">
         <v>45615</v>
@@ -1316,24 +1572,28 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D17" s="4">
         <v>45617</v>
@@ -1342,24 +1602,28 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D18" s="4">
         <v>45622</v>
@@ -1368,24 +1632,28 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D19" s="4">
         <v>45622</v>
@@ -1394,24 +1662,28 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D20" s="4">
         <v>45624</v>
@@ -1420,24 +1692,28 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D21" s="4">
         <v>45688</v>
@@ -1446,24 +1722,28 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="D22" s="4">
         <v>45695</v>
@@ -1472,24 +1752,28 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D23" s="4">
         <v>45699</v>
@@ -1498,24 +1782,28 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D24" s="4">
         <v>45702</v>
@@ -1524,24 +1812,28 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D25" s="4">
         <v>45705</v>
@@ -1550,24 +1842,28 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D26" s="4">
         <v>45709</v>
@@ -1576,24 +1872,28 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="D27" s="4">
         <v>45712</v>
@@ -1602,24 +1902,28 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="D28" s="4">
         <v>45726</v>
@@ -1628,24 +1932,28 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="D29" s="4">
         <v>45727</v>
@@ -1654,24 +1962,28 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D30" s="4">
         <v>45734</v>
@@ -1680,24 +1992,28 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D31" s="4">
         <v>45734</v>
@@ -1706,24 +2022,28 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="D32" s="4">
         <v>45740</v>
@@ -1732,24 +2052,28 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="D33" s="4">
         <v>45741</v>
@@ -1758,24 +2082,28 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="D34" s="4">
         <v>45741</v>
@@ -1784,24 +2112,28 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="D35" s="4">
         <v>45748</v>
@@ -1810,24 +2142,28 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="D36" s="4">
         <v>45748</v>
@@ -1836,24 +2172,28 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D37" s="4">
         <v>45755</v>
@@ -1862,24 +2202,28 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D38" s="4">
         <v>45761</v>
@@ -1888,24 +2232,28 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="D39" s="4">
         <v>45768</v>
@@ -1914,24 +2262,28 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D40" s="4">
         <v>45775</v>
@@ -1940,24 +2292,28 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="D41" s="4">
         <v>45775</v>
@@ -1966,24 +2322,28 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D42" s="4">
         <v>45782</v>
@@ -1992,24 +2352,28 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="D43" s="4">
         <v>45789</v>
@@ -2018,24 +2382,28 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D44" s="4">
         <v>45789</v>
@@ -2044,24 +2412,28 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="D45" s="4">
         <v>45796</v>
@@ -2070,24 +2442,28 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="D46" s="4">
         <v>45896</v>
@@ -2096,24 +2472,28 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="D47" s="4">
         <v>45910</v>
@@ -2122,24 +2502,28 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="D48" s="4">
         <v>45924</v>
@@ -2148,24 +2532,28 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="D49" s="4">
         <v>45947</v>
@@ -2174,24 +2562,28 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="D50" s="4">
         <v>45954</v>
@@ -2200,24 +2592,28 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="D51" s="4">
         <v>45961</v>
@@ -2226,24 +2622,28 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J51" s="3"/>
+    </row>
+    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="D52" s="4">
         <v>45968</v>
@@ -2252,24 +2652,28 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J52" s="3"/>
+    </row>
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="D53" s="4">
         <v>45980</v>
@@ -2278,24 +2682,28 @@
         <v>4480</v>
       </c>
       <c r="F53" s="6">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="D54" s="4">
         <v>45980</v>
@@ -2304,22 +2712,24 @@
         <v>38840.89</v>
       </c>
       <c r="F54" s="6">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="D55" s="4">
         <v>45987</v>
@@ -2328,22 +2738,24 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="D56" s="4">
         <v>45989</v>
@@ -2352,22 +2764,24 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="D57" s="4">
         <v>45994</v>
@@ -2376,22 +2790,24 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="D58" s="4">
         <v>46090</v>
@@ -2400,24 +2816,28 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J58" s="3"/>
+    </row>
+    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B59" s="3" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="D59" s="4">
         <v>46097</v>
@@ -2426,24 +2846,28 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="B60" s="3" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="D60" s="4">
         <v>46104</v>
@@ -2452,24 +2876,28 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="D61" s="4">
         <v>46105</v>
@@ -2478,648 +2906,646 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="D62" s="4">
-        <v>46155</v>
+        <v>46159</v>
       </c>
       <c r="E62" s="5">
+        <v>6248.23</v>
+      </c>
+      <c r="F62" s="6">
+        <v>24</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D63" s="4">
+        <v>46163</v>
+      </c>
+      <c r="E63" s="5">
+        <v>2100</v>
+      </c>
+      <c r="F63" s="6">
+        <v>20</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J63" s="3"/>
+    </row>
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D64" s="4">
+        <v>46165</v>
+      </c>
+      <c r="E64" s="5">
         <v>7020</v>
-      </c>
-      <c r="F62" s="6">
-        <v>26</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D63" s="4">
-        <v>46159</v>
-      </c>
-      <c r="E63" s="5">
-        <v>6248.23</v>
-      </c>
-      <c r="F63" s="6">
-        <v>22</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D64" s="4">
-        <v>46163</v>
-      </c>
-      <c r="E64" s="5">
-        <v>2100</v>
       </c>
       <c r="F64" s="6">
         <v>18</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J64" s="3"/>
+    </row>
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D65" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E65" s="5">
+        <v>2100</v>
+      </c>
+      <c r="F65" s="6">
+        <v>13</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J65" s="3"/>
+    </row>
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D66" s="4">
+        <v>46174</v>
+      </c>
+      <c r="E66" s="5">
+        <v>1034.3800000000001</v>
+      </c>
+      <c r="F66" s="6">
+        <v>9</v>
+      </c>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+    </row>
+    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D67" s="4">
+        <v>46175</v>
+      </c>
+      <c r="E67" s="5">
+        <v>15028</v>
+      </c>
+      <c r="F67" s="6">
         <v>8</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" s="4">
-        <v>46165</v>
-      </c>
-      <c r="E65" s="5">
-        <v>7020</v>
-      </c>
-      <c r="F65" s="6">
-        <v>16</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D66" s="4">
-        <v>46169</v>
-      </c>
-      <c r="E66" s="5">
-        <v>3951.33</v>
-      </c>
-      <c r="F66" s="6">
-        <v>12</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D67" s="4">
-        <v>46170</v>
-      </c>
-      <c r="E67" s="5">
+      <c r="G67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J67" s="3"/>
+    </row>
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46176</v>
+      </c>
+      <c r="E68" s="5">
+        <v>12096</v>
+      </c>
+      <c r="F68" s="6">
+        <v>7</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J68" s="3"/>
+    </row>
+    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D69" s="4">
+        <v>46176</v>
+      </c>
+      <c r="E69" s="5">
+        <v>1971.6</v>
+      </c>
+      <c r="F69" s="6">
+        <v>7</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J69" s="3"/>
+    </row>
+    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D70" s="4">
+        <v>46176</v>
+      </c>
+      <c r="E70" s="5">
+        <v>5183.09</v>
+      </c>
+      <c r="F70" s="6">
+        <v>7</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J70" s="3"/>
+    </row>
+    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D71" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E71" s="5">
         <v>2100</v>
       </c>
-      <c r="F67" s="6">
-        <v>11</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" s="4">
-        <v>46170</v>
-      </c>
-      <c r="E68" s="5">
+      <c r="F71" s="6">
+        <v>6</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J71" s="3"/>
+    </row>
+    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="6">
-        <v>11</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D69" s="4">
-        <v>46170</v>
-      </c>
-      <c r="E69" s="5">
-        <v>2570.4</v>
-      </c>
-      <c r="F69" s="6">
-        <v>11</v>
-      </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D70" s="4">
-        <v>46171</v>
-      </c>
-      <c r="E70" s="5">
-        <v>2077.1999999999998</v>
-      </c>
-      <c r="F70" s="6">
-        <v>10</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D71" s="4">
-        <v>46172</v>
-      </c>
-      <c r="E71" s="5">
-        <v>5106.55</v>
-      </c>
-      <c r="F71" s="6">
-        <v>9</v>
-      </c>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="B72" s="3" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="D72" s="4">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="E72" s="5">
-        <v>1034.3800000000001</v>
+        <v>15716</v>
       </c>
       <c r="F72" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+    </row>
+    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="D73" s="4">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="E73" s="5">
-        <v>15028</v>
+        <v>4193.28</v>
       </c>
       <c r="F73" s="6">
         <v>6</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J73" s="3"/>
+    </row>
+    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="D74" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E74" s="5">
-        <v>12096</v>
+        <v>2570.4</v>
       </c>
       <c r="F74" s="6">
-        <v>5</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+    </row>
+    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="D75" s="4">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E75" s="5">
-        <v>1971.6</v>
+        <v>2077.1999999999998</v>
       </c>
       <c r="F75" s="6">
         <v>5</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J75" s="3"/>
+    </row>
+    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>127</v>
+        <v>193</v>
       </c>
       <c r="D76" s="4">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E76" s="5">
-        <v>5183.09</v>
+        <v>2625</v>
       </c>
       <c r="F76" s="6">
         <v>5</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J76" s="3"/>
+    </row>
+    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="D77" s="4">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="E77" s="5">
-        <v>2127.2399999999998</v>
+        <v>3667.76</v>
       </c>
       <c r="F77" s="6">
         <v>4</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="D78" s="4">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="E78" s="5">
-        <v>7768.64</v>
+        <v>1800</v>
       </c>
       <c r="F78" s="6">
         <v>4</v>
       </c>
-      <c r="G78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H78" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J78" s="3"/>
+    </row>
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>106</v>
+        <v>199</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="D79" s="4">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="E79" s="5">
-        <v>2100</v>
+        <v>1565.05</v>
       </c>
       <c r="F79" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J79" s="3"/>
+    </row>
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="D80" s="4">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="E80" s="5">
-        <v>15716</v>
+        <v>828.8</v>
       </c>
       <c r="F80" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+    </row>
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>136</v>
+        <v>205</v>
       </c>
       <c r="D81" s="4">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="E81" s="5">
-        <v>4193.28</v>
+        <v>6933.34</v>
       </c>
       <c r="F81" s="6">
-        <v>4</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="D82" s="4">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="E82" s="5">
-        <v>27757.97</v>
+        <v>3337.78</v>
       </c>
       <c r="F82" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+    </row>
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="D83" s="4">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="E83" s="5">
-        <v>2570.4</v>
+        <v>2832.42</v>
       </c>
       <c r="F83" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D84" s="4">
-        <v>46177</v>
-      </c>
-      <c r="E84" s="5">
-        <v>9092.44</v>
-      </c>
-      <c r="F84" s="6">
-        <v>4</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D85" s="4">
-        <v>46178</v>
-      </c>
-      <c r="E85" s="5">
-        <v>2077.1999999999998</v>
-      </c>
-      <c r="F85" s="6">
-        <v>3</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D86" s="4">
-        <v>46178</v>
-      </c>
-      <c r="E86" s="5">
-        <v>2625</v>
-      </c>
-      <c r="F86" s="6">
-        <v>3</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,31 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4191E296-1BBC-4306-A144-3375FFEBD7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr refMode="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
     <t>Funcionário</t>
   </si>
@@ -447,6 +435,12 @@
     <t>00191125800002144590000003473568000002964317</t>
   </si>
   <si>
+    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
+  </si>
+  <si>
+    <t>01005217.1BPBPBP</t>
+  </si>
+  <si>
     <t>BR MEDICAMENTOS LTDA</t>
   </si>
   <si>
@@ -456,12 +450,6 @@
     <t>00195127000004480000000003473568000002981317</t>
   </si>
   <si>
-    <t>PHARMACEUTICA DISTRIBUIDORA DE MAT. E MED. HOSPITA</t>
-  </si>
-  <si>
-    <t>01005217.1BPBPBP</t>
-  </si>
-  <si>
     <t>01005217.2BP</t>
   </si>
   <si>
@@ -525,21 +513,6 @@
     <t>00193145300002100000000003473568000003079117</t>
   </si>
   <si>
-    <t>MONTALVAO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01006044.4</t>
-  </si>
-  <si>
-    <t>34195145500007020001090002558528120992717000</t>
-  </si>
-  <si>
-    <t>01006225.2</t>
-  </si>
-  <si>
-    <t>00198146000002100000000003473568000003079217</t>
-  </si>
-  <si>
     <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
   </si>
   <si>
@@ -576,12 +549,6 @@
     <t>00198146600005183090000003473568000003086417</t>
   </si>
   <si>
-    <t>01006225.3</t>
-  </si>
-  <si>
-    <t>00192146700002100000000003473568000003079317</t>
-  </si>
-  <si>
     <t>01006204.2</t>
   </si>
   <si>
@@ -591,102 +558,91 @@
     <t>00194146700004193280000003473568000003078217</t>
   </si>
   <si>
+    <t>01006233.3</t>
+  </si>
+  <si>
+    <t>00196146800002077200000003473568000003083117</t>
+  </si>
+  <si>
+    <t>VWL DIST. DE MED. E MAT. MEDICO-HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01006092.4</t>
+  </si>
+  <si>
+    <t>00192146800002625000000003473568000003064817</t>
+  </si>
+  <si>
+    <t>01006207.2</t>
+  </si>
+  <si>
+    <t>01006305.2</t>
+  </si>
+  <si>
+    <t>METTA FARMA DISTRIBUICAO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006048.4</t>
+  </si>
+  <si>
+    <t>01006259.3</t>
+  </si>
+  <si>
+    <t>00198147300001971600000003473568000003085917</t>
+  </si>
+  <si>
+    <t>MARCOS DUTRA</t>
+  </si>
+  <si>
+    <t>DICOREL DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006336.2</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006255.2</t>
-  </si>
-  <si>
-    <t>01006233.3</t>
-  </si>
-  <si>
-    <t>00196146800002077200000003473568000003083117</t>
-  </si>
-  <si>
-    <t>VWL DIST. DE MED. E MAT. MEDICO-HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01006092.4</t>
-  </si>
-  <si>
-    <t>00192146800002625000000003473568000003064817</t>
-  </si>
-  <si>
-    <t>01006207.2</t>
-  </si>
-  <si>
-    <t>S&amp;J DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01006105.4</t>
-  </si>
-  <si>
-    <t>00195146900001800000000003473568000003066317</t>
-  </si>
-  <si>
-    <t>CAMEDIC COMERCIAL E SERVIÇOS DE PROD MED HOSP EIRE</t>
-  </si>
-  <si>
-    <t>01006350.1</t>
-  </si>
-  <si>
-    <t>34193147100001565051090002579738120992717000</t>
-  </si>
-  <si>
-    <t>01006305.2</t>
-  </si>
-  <si>
-    <t>KELLEN</t>
-  </si>
-  <si>
-    <t>RICCO FARMA DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>01006166.3</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>L G PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01006307.2</t>
-  </si>
-  <si>
-    <t>ORTHOMED COMERCIO DE PROD. HOSP. E ORTHOP. LTDA</t>
-  </si>
-  <si>
-    <t>01006314.2</t>
+    <t>01006255.3</t>
+  </si>
+  <si>
+    <t>01006233.4</t>
+  </si>
+  <si>
+    <t>00191147500002077200000003473568000003083217</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
+    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -705,8 +661,14 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -729,381 +691,119 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA0A0A0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA0A0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+  <cellXfs count="11">
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J83"/>
-  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
+  <dimension ref="A1:J80"/>
+  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="60.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.140625" style="1"/>
+    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
+    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
+    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
+    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
+    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
+    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
+    <col max="7" min="7" style="1" width="26.28515625" customWidth="true"/>
+    <col max="8" min="8" style="1" width="3.7109375" customWidth="true"/>
+    <col max="9" min="9" style="1" width="60.5703125" customWidth="true"/>
+    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
+    <col max="16384" min="11" style="1" width="12.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1135,7 +835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1145,14 +845,14 @@
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="4" t="n">
         <v>45326</v>
       </c>
-      <c r="E2" s="5">
-        <v>9391.7800000000007</v>
-      </c>
-      <c r="F2" s="6">
-        <v>857</v>
+      <c r="E2" s="5" t="n">
+        <v>9391.78</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>862</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1165,7 +865,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -1175,14 +875,14 @@
       <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="4" t="n">
         <v>45346</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="F3" s="6">
-        <v>837</v>
+      <c r="F3" s="6" t="n">
+        <v>842</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
@@ -1195,7 +895,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -1205,14 +905,14 @@
       <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="4" t="n">
         <v>45350</v>
       </c>
-      <c r="E4" s="5">
-        <v>1264.8699999999999</v>
-      </c>
-      <c r="F4" s="6">
-        <v>833</v>
+      <c r="E4" s="5" t="n">
+        <v>1264.87</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>838</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
@@ -1225,7 +925,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1235,14 +935,14 @@
       <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="4" t="n">
         <v>45356</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="F5" s="6">
-        <v>827</v>
+      <c r="F5" s="6" t="n">
+        <v>832</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
@@ -1255,7 +955,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -1265,14 +965,14 @@
       <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="4" t="n">
         <v>45362</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="5" t="n">
         <v>384</v>
       </c>
-      <c r="F6" s="6">
-        <v>821</v>
+      <c r="F6" s="6" t="n">
+        <v>826</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
@@ -1285,7 +985,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1295,14 +995,14 @@
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="n">
         <v>45364</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="F7" s="6">
-        <v>819</v>
+      <c r="F7" s="6" t="n">
+        <v>824</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
@@ -1315,7 +1015,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1325,14 +1025,14 @@
       <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="4" t="n">
         <v>45378</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="F8" s="6">
-        <v>805</v>
+      <c r="F8" s="6" t="n">
+        <v>810</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>21</v>
@@ -1345,7 +1045,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -1355,14 +1055,14 @@
       <c r="C9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="4" t="n">
         <v>45463</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5" t="n">
         <v>1674.52</v>
       </c>
-      <c r="F9" s="6">
-        <v>720</v>
+      <c r="F9" s="6" t="n">
+        <v>725</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
@@ -1375,7 +1075,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -1385,14 +1085,14 @@
       <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="4" t="n">
         <v>45493</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="F10" s="6">
-        <v>690</v>
+      <c r="F10" s="6" t="n">
+        <v>695</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
@@ -1405,7 +1105,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1415,14 +1115,14 @@
       <c r="C11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="4" t="n">
         <v>45523</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="F11" s="6">
-        <v>660</v>
+      <c r="F11" s="6" t="n">
+        <v>665</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>13</v>
@@ -1435,7 +1135,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -1445,14 +1145,14 @@
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="4" t="n">
         <v>45600</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="F12" s="6">
-        <v>583</v>
+      <c r="F12" s="6" t="n">
+        <v>588</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>13</v>
@@ -1465,7 +1165,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A13" s="3" t="s">
         <v>40</v>
       </c>
@@ -1475,14 +1175,14 @@
       <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="4" t="n">
         <v>45607</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="5" t="n">
         <v>3204.34</v>
       </c>
-      <c r="F13" s="6">
-        <v>576</v>
+      <c r="F13" s="6" t="n">
+        <v>581</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>13</v>
@@ -1495,7 +1195,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1505,14 +1205,14 @@
       <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="4" t="n">
         <v>45608</v>
       </c>
-      <c r="E14" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="F14" s="6">
-        <v>575</v>
+      <c r="E14" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>580</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>13</v>
@@ -1525,7 +1225,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -1535,14 +1235,14 @@
       <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="4" t="n">
         <v>45614</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="F15" s="6">
-        <v>569</v>
+      <c r="F15" s="6" t="n">
+        <v>574</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>13</v>
@@ -1555,7 +1255,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
@@ -1565,14 +1265,14 @@
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="4" t="n">
         <v>45615</v>
       </c>
-      <c r="E16" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="F16" s="6">
-        <v>568</v>
+      <c r="E16" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>573</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
@@ -1585,7 +1285,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -1595,14 +1295,14 @@
       <c r="C17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="4" t="n">
         <v>45617</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="5" t="n">
         <v>1843.87</v>
       </c>
-      <c r="F17" s="6">
-        <v>566</v>
+      <c r="F17" s="6" t="n">
+        <v>571</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>13</v>
@@ -1615,7 +1315,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
@@ -1625,14 +1325,14 @@
       <c r="C18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E18" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="F18" s="6">
-        <v>561</v>
+      <c r="E18" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>566</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
@@ -1645,7 +1345,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A19" s="3" t="s">
         <v>46</v>
       </c>
@@ -1655,14 +1355,14 @@
       <c r="C19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E19" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="F19" s="6">
-        <v>561</v>
+      <c r="E19" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>566</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>13</v>
@@ -1675,7 +1375,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
@@ -1685,14 +1385,14 @@
       <c r="C20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="4" t="n">
         <v>45624</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="5" t="n">
         <v>1843.88</v>
       </c>
-      <c r="F20" s="6">
-        <v>559</v>
+      <c r="F20" s="6" t="n">
+        <v>564</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>13</v>
@@ -1705,7 +1405,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A21" s="3" t="s">
         <v>63</v>
       </c>
@@ -1715,14 +1415,14 @@
       <c r="C21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="4" t="n">
         <v>45688</v>
       </c>
-      <c r="E21" s="5">
-        <v>1118.4000000000001</v>
-      </c>
-      <c r="F21" s="6">
-        <v>495</v>
+      <c r="E21" s="5" t="n">
+        <v>1118.4</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>500</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>13</v>
@@ -1735,7 +1435,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -1745,14 +1445,14 @@
       <c r="C22" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="4" t="n">
         <v>45695</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="F22" s="6">
-        <v>488</v>
+      <c r="F22" s="6" t="n">
+        <v>493</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>13</v>
@@ -1765,7 +1465,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -1775,14 +1475,14 @@
       <c r="C23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="4" t="n">
         <v>45699</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="5" t="n">
         <v>2330</v>
       </c>
-      <c r="F23" s="6">
-        <v>484</v>
+      <c r="F23" s="6" t="n">
+        <v>489</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>13</v>
@@ -1795,7 +1495,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -1805,14 +1505,14 @@
       <c r="C24" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="4" t="n">
         <v>45702</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="F24" s="6">
-        <v>481</v>
+      <c r="F24" s="6" t="n">
+        <v>486</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>13</v>
@@ -1825,7 +1525,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
@@ -1835,14 +1535,14 @@
       <c r="C25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="4" t="n">
         <v>45705</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F25" s="6">
-        <v>478</v>
+      <c r="F25" s="6" t="n">
+        <v>483</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>21</v>
@@ -1855,7 +1555,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
@@ -1865,14 +1565,14 @@
       <c r="C26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="4" t="n">
         <v>45709</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="F26" s="6">
-        <v>474</v>
+      <c r="F26" s="6" t="n">
+        <v>479</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>13</v>
@@ -1885,7 +1585,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A27" s="3" t="s">
         <v>40</v>
       </c>
@@ -1895,14 +1595,14 @@
       <c r="C27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="4" t="n">
         <v>45712</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F27" s="6">
-        <v>471</v>
+      <c r="F27" s="6" t="n">
+        <v>476</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>21</v>
@@ -1915,7 +1615,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
@@ -1925,14 +1625,14 @@
       <c r="C28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="4" t="n">
         <v>45726</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F28" s="6">
-        <v>457</v>
+      <c r="F28" s="6" t="n">
+        <v>462</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>21</v>
@@ -1945,7 +1645,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
@@ -1955,14 +1655,14 @@
       <c r="C29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="4" t="n">
         <v>45727</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="F29" s="6">
-        <v>456</v>
+      <c r="F29" s="6" t="n">
+        <v>461</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>13</v>
@@ -1975,7 +1675,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
@@ -1985,14 +1685,14 @@
       <c r="C30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="4" t="n">
         <v>45734</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="F30" s="6">
-        <v>449</v>
+      <c r="F30" s="6" t="n">
+        <v>454</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>13</v>
@@ -2005,7 +1705,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A31" s="3" t="s">
         <v>46</v>
       </c>
@@ -2015,14 +1715,14 @@
       <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="4" t="n">
         <v>45734</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F31" s="6">
-        <v>449</v>
+      <c r="F31" s="6" t="n">
+        <v>454</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>13</v>
@@ -2035,7 +1735,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -2045,14 +1745,14 @@
       <c r="C32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="4" t="n">
         <v>45740</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F32" s="6">
-        <v>443</v>
+      <c r="F32" s="6" t="n">
+        <v>448</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>21</v>
@@ -2065,7 +1765,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -2075,14 +1775,14 @@
       <c r="C33" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="F33" s="6">
-        <v>442</v>
+      <c r="F33" s="6" t="n">
+        <v>447</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>13</v>
@@ -2095,7 +1795,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A34" s="3" t="s">
         <v>46</v>
       </c>
@@ -2105,14 +1805,14 @@
       <c r="C34" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F34" s="6">
-        <v>442</v>
+      <c r="F34" s="6" t="n">
+        <v>447</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>13</v>
@@ -2125,7 +1825,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A35" s="3" t="s">
         <v>46</v>
       </c>
@@ -2135,14 +1835,14 @@
       <c r="C35" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F35" s="6">
-        <v>435</v>
+      <c r="F35" s="6" t="n">
+        <v>440</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>13</v>
@@ -2155,7 +1855,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A36" s="3" t="s">
         <v>40</v>
       </c>
@@ -2165,14 +1865,14 @@
       <c r="C36" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="5" t="n">
         <v>7562.76</v>
       </c>
-      <c r="F36" s="6">
-        <v>435</v>
+      <c r="F36" s="6" t="n">
+        <v>440</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>13</v>
@@ -2185,7 +1885,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
@@ -2195,14 +1895,14 @@
       <c r="C37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="4" t="n">
         <v>45755</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F37" s="6">
-        <v>428</v>
+      <c r="F37" s="6" t="n">
+        <v>433</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>13</v>
@@ -2215,7 +1915,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A38" s="3" t="s">
         <v>46</v>
       </c>
@@ -2225,14 +1925,14 @@
       <c r="C38" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="4" t="n">
         <v>45761</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="5" t="n">
         <v>6169.53</v>
       </c>
-      <c r="F38" s="6">
-        <v>422</v>
+      <c r="F38" s="6" t="n">
+        <v>427</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>13</v>
@@ -2245,7 +1945,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A39" s="3" t="s">
         <v>46</v>
       </c>
@@ -2255,14 +1955,14 @@
       <c r="C39" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="4" t="n">
         <v>45768</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="F39" s="6">
-        <v>415</v>
+      <c r="F39" s="6" t="n">
+        <v>420</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>13</v>
@@ -2275,7 +1975,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A40" s="3" t="s">
         <v>46</v>
       </c>
@@ -2285,14 +1985,14 @@
       <c r="C40" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="F40" s="6">
-        <v>408</v>
+      <c r="F40" s="6" t="n">
+        <v>413</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>13</v>
@@ -2305,7 +2005,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A41" s="3" t="s">
         <v>46</v>
       </c>
@@ -2315,14 +2015,14 @@
       <c r="C41" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="5" t="n">
         <v>6089.41</v>
       </c>
-      <c r="F41" s="6">
-        <v>408</v>
+      <c r="F41" s="6" t="n">
+        <v>413</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>13</v>
@@ -2335,7 +2035,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A42" s="3" t="s">
         <v>46</v>
       </c>
@@ -2345,14 +2045,14 @@
       <c r="C42" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="F42" s="6">
-        <v>401</v>
+      <c r="F42" s="6" t="n">
+        <v>406</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>13</v>
@@ -2365,7 +2065,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A43" s="3" t="s">
         <v>46</v>
       </c>
@@ -2375,14 +2075,14 @@
       <c r="C43" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="F43" s="6">
-        <v>394</v>
+      <c r="F43" s="6" t="n">
+        <v>399</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>13</v>
@@ -2395,7 +2095,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A44" s="3" t="s">
         <v>116</v>
       </c>
@@ -2405,14 +2105,14 @@
       <c r="C44" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="5" t="n">
         <v>1143.54</v>
       </c>
-      <c r="F44" s="6">
-        <v>394</v>
+      <c r="F44" s="6" t="n">
+        <v>399</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>21</v>
@@ -2425,7 +2125,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A45" s="3" t="s">
         <v>116</v>
       </c>
@@ -2435,14 +2135,14 @@
       <c r="C45" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="4" t="n">
         <v>45796</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="5" t="n">
         <v>2287.06</v>
       </c>
-      <c r="F45" s="6">
-        <v>387</v>
+      <c r="F45" s="6" t="n">
+        <v>392</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>21</v>
@@ -2455,7 +2155,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
@@ -2465,14 +2165,14 @@
       <c r="C46" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="4" t="n">
         <v>45896</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="5" t="n">
         <v>4572.62</v>
       </c>
-      <c r="F46" s="6">
-        <v>287</v>
+      <c r="F46" s="6" t="n">
+        <v>292</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>21</v>
@@ -2485,7 +2185,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
@@ -2495,14 +2195,14 @@
       <c r="C47" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="4" t="n">
         <v>45910</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="F47" s="6">
-        <v>273</v>
+      <c r="F47" s="6" t="n">
+        <v>278</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>21</v>
@@ -2515,7 +2215,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A48" s="3" t="s">
         <v>40</v>
       </c>
@@ -2525,14 +2225,14 @@
       <c r="C48" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="4" t="n">
         <v>45924</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="F48" s="6">
-        <v>259</v>
+      <c r="F48" s="6" t="n">
+        <v>264</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>21</v>
@@ -2545,7 +2245,7 @@
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A49" s="3" t="s">
         <v>130</v>
       </c>
@@ -2555,14 +2255,14 @@
       <c r="C49" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="4" t="n">
         <v>45947</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="5" t="n">
         <v>3867.34</v>
       </c>
-      <c r="F49" s="6">
-        <v>236</v>
+      <c r="F49" s="6" t="n">
+        <v>241</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>21</v>
@@ -2575,7 +2275,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
@@ -2585,14 +2285,14 @@
       <c r="C50" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="4" t="n">
         <v>45954</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="F50" s="6">
-        <v>229</v>
+      <c r="F50" s="6" t="n">
+        <v>234</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>21</v>
@@ -2605,7 +2305,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A51" s="3" t="s">
         <v>130</v>
       </c>
@@ -2615,14 +2315,14 @@
       <c r="C51" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="4" t="n">
         <v>45961</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="F51" s="6">
-        <v>222</v>
+      <c r="F51" s="6" t="n">
+        <v>227</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>21</v>
@@ -2635,7 +2335,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A52" s="3" t="s">
         <v>130</v>
       </c>
@@ -2645,14 +2345,14 @@
       <c r="C52" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="4" t="n">
         <v>45968</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="F52" s="6">
-        <v>215</v>
+      <c r="F52" s="6" t="n">
+        <v>220</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>21</v>
@@ -2665,9 +2365,9 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A53" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>140</v>
@@ -2675,70 +2375,70 @@
       <c r="C53" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="4" t="n">
         <v>45980</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="5" t="n">
+        <v>38840.89</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A54" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>45980</v>
+      </c>
+      <c r="E54" s="5" t="n">
         <v>4480</v>
       </c>
-      <c r="F53" s="6">
-        <v>203</v>
-      </c>
-      <c r="G53" s="3" t="s">
+      <c r="F54" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I53" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J53" s="3"/>
-    </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="I54" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D54" s="4">
-        <v>45980</v>
-      </c>
-      <c r="E54" s="5">
-        <v>38840.89</v>
-      </c>
-      <c r="F54" s="6">
-        <v>203</v>
-      </c>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I54" s="3"/>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A55" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="4" t="n">
         <v>45987</v>
       </c>
-      <c r="E55" s="5">
-        <v>33844.160000000003</v>
-      </c>
-      <c r="F55" s="6">
-        <v>196</v>
+      <c r="E55" s="5" t="n">
+        <v>33844.16</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>201</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2747,24 +2447,24 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A56" s="3" t="s">
         <v>116</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="4" t="n">
         <v>45989</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="5" t="n">
         <v>3220</v>
       </c>
-      <c r="F56" s="6">
-        <v>194</v>
+      <c r="F56" s="6" t="n">
+        <v>199</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2773,24 +2473,24 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A57" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="4" t="n">
         <v>45994</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="5" t="n">
         <v>38740.53</v>
       </c>
-      <c r="F57" s="6">
-        <v>189</v>
+      <c r="F57" s="6" t="n">
+        <v>194</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2799,7 +2499,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2809,14 +2509,14 @@
       <c r="C58" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="4" t="n">
         <v>46090</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="5" t="n">
         <v>806.34</v>
       </c>
-      <c r="F58" s="6">
-        <v>93</v>
+      <c r="F58" s="6" t="n">
+        <v>98</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>21</v>
@@ -2829,7 +2529,7 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A59" s="3" t="s">
         <v>18</v>
       </c>
@@ -2839,14 +2539,14 @@
       <c r="C59" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="4" t="n">
         <v>46097</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="F59" s="6">
-        <v>86</v>
+      <c r="F59" s="6" t="n">
+        <v>91</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>21</v>
@@ -2859,7 +2559,7 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A60" s="3" t="s">
         <v>18</v>
       </c>
@@ -2869,14 +2569,14 @@
       <c r="C60" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="4" t="n">
         <v>46104</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="F60" s="6">
-        <v>79</v>
+      <c r="F60" s="6" t="n">
+        <v>84</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>21</v>
@@ -2889,7 +2589,7 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A61" s="3" t="s">
         <v>10</v>
       </c>
@@ -2899,14 +2599,14 @@
       <c r="C61" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="5" t="n">
         <v>5466.66</v>
       </c>
-      <c r="F61" s="6">
-        <v>78</v>
+      <c r="F61" s="6" t="n">
+        <v>83</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>13</v>
@@ -2919,7 +2619,7 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A62" s="3" t="s">
         <v>158</v>
       </c>
@@ -2929,14 +2629,14 @@
       <c r="C62" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="4" t="n">
         <v>46159</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="5" t="n">
         <v>6248.23</v>
       </c>
-      <c r="F62" s="6">
-        <v>24</v>
+      <c r="F62" s="6" t="n">
+        <v>29</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>21</v>
@@ -2949,7 +2649,7 @@
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A63" s="3" t="s">
         <v>116</v>
       </c>
@@ -2959,14 +2659,14 @@
       <c r="C63" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="5" t="n">
         <v>2100</v>
       </c>
-      <c r="F63" s="6">
-        <v>20</v>
+      <c r="F63" s="6" t="n">
+        <v>25</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>21</v>
@@ -2979,9 +2679,9 @@
       </c>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A64" s="3" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>166</v>
@@ -2989,85 +2689,85 @@
       <c r="C64" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D64" s="4">
-        <v>46165</v>
-      </c>
-      <c r="E64" s="5">
-        <v>7020</v>
-      </c>
-      <c r="F64" s="6">
-        <v>18</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="D64" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>1034.38</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I64" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+    </row>
+    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A65" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="J64" s="3"/>
-    </row>
-    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D65" s="4">
-        <v>46170</v>
-      </c>
-      <c r="E65" s="5">
-        <v>2100</v>
-      </c>
-      <c r="F65" s="6">
+      <c r="D65" s="4" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>15028</v>
+      </c>
+      <c r="F65" s="6" t="n">
         <v>13</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>170</v>
       </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A66" s="3" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="D66" s="4" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>12096</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D66" s="4">
-        <v>46174</v>
-      </c>
-      <c r="E66" s="5">
-        <v>1034.3800000000001</v>
-      </c>
-      <c r="F66" s="6">
-        <v>9</v>
-      </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I66" s="3"/>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A67" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>173</v>
@@ -3075,220 +2775,216 @@
       <c r="C67" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D67" s="4">
-        <v>46175</v>
-      </c>
-      <c r="E67" s="5">
-        <v>15028</v>
-      </c>
-      <c r="F67" s="6">
-        <v>8</v>
+      <c r="D67" s="4" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>1971.6</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>12</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>175</v>
       </c>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A68" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="4" t="n">
         <v>46176</v>
       </c>
-      <c r="E68" s="5">
-        <v>12096</v>
-      </c>
-      <c r="F68" s="6">
-        <v>7</v>
+      <c r="E68" s="5" t="n">
+        <v>5183.09</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>12</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>177</v>
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A69" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="4" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>15716</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+    </row>
+    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A70" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D69" s="4">
-        <v>46176</v>
-      </c>
-      <c r="E69" s="5">
-        <v>1971.6</v>
-      </c>
-      <c r="F69" s="6">
-        <v>7</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J69" s="3"/>
-    </row>
-    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D70" s="4">
-        <v>46176</v>
-      </c>
-      <c r="E70" s="5">
-        <v>5183.09</v>
-      </c>
-      <c r="F70" s="6">
-        <v>7</v>
+      <c r="D70" s="4" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>4193.28</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A71" s="3" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D71" s="4">
-        <v>46177</v>
-      </c>
-      <c r="E71" s="5">
-        <v>2100</v>
-      </c>
-      <c r="F71" s="6">
-        <v>6</v>
+        <v>181</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>46178</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>2077.2</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>46178</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>2625</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D72" s="4">
-        <v>46177</v>
-      </c>
-      <c r="E72" s="5">
-        <v>15716</v>
-      </c>
-      <c r="F72" s="6">
-        <v>6</v>
-      </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I72" s="3"/>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A73" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D73" s="4">
-        <v>46177</v>
-      </c>
-      <c r="E73" s="5">
-        <v>4193.28</v>
-      </c>
-      <c r="F73" s="6">
-        <v>6</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="D73" s="4" t="n">
+        <v>46179</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>3667.76</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G73" s="3"/>
       <c r="H73" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+    </row>
+    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A74" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J73" s="3"/>
-    </row>
-    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D74" s="4">
-        <v>46177</v>
-      </c>
-      <c r="E74" s="5">
-        <v>2570.4</v>
-      </c>
-      <c r="F74" s="6">
-        <v>6</v>
+      <c r="D74" s="4" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>828.8</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
@@ -3297,95 +2993,91 @@
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A75" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>4494.06</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+    </row>
+    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A76" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C75" s="3" t="s">
+      <c r="B76" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D75" s="4">
-        <v>46178</v>
-      </c>
-      <c r="E75" s="5">
-        <v>2077.1999999999998</v>
-      </c>
-      <c r="F75" s="6">
-        <v>5</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J75" s="3"/>
-    </row>
-    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D76" s="4">
-        <v>46178</v>
-      </c>
-      <c r="E76" s="5">
-        <v>2625</v>
-      </c>
-      <c r="F76" s="6">
+      <c r="D76" s="4" t="n">
+        <v>46183</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>1971.6</v>
+      </c>
+      <c r="F76" s="6" t="n">
         <v>5</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I76" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J76" s="3"/>
+    </row>
+    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A77" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J76" s="3"/>
-    </row>
-    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D77" s="4">
-        <v>46179</v>
-      </c>
-      <c r="E77" s="5">
-        <v>3667.76</v>
-      </c>
-      <c r="F77" s="6">
+      <c r="D77" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>7768.64</v>
+      </c>
+      <c r="F77" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A78" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>196</v>
@@ -3393,161 +3085,67 @@
       <c r="C78" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D78" s="4">
-        <v>46179</v>
-      </c>
-      <c r="E78" s="5">
-        <v>1800</v>
-      </c>
-      <c r="F78" s="6">
+      <c r="D78" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>2570.4</v>
+      </c>
+      <c r="F78" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="3"/>
+      <c r="H78" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+    </row>
+    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A79" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>2077.2</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H78" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J78" s="3"/>
-    </row>
-    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B79" s="3" t="s">
+      <c r="H79" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I79" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D79" s="4">
-        <v>46181</v>
-      </c>
-      <c r="E79" s="5">
-        <v>1565.05</v>
-      </c>
-      <c r="F79" s="6">
-        <v>2</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D80" s="4">
-        <v>46181</v>
-      </c>
-      <c r="E80" s="5">
-        <v>828.8</v>
-      </c>
-      <c r="F80" s="6">
-        <v>2</v>
-      </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3"/>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D81" s="4">
-        <v>46182</v>
-      </c>
-      <c r="E81" s="5">
-        <v>6933.34</v>
-      </c>
-      <c r="F81" s="6">
-        <v>1</v>
-      </c>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="I81" s="3"/>
-      <c r="J81" s="3"/>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D82" s="4">
-        <v>46182</v>
-      </c>
-      <c r="E82" s="5">
-        <v>3337.78</v>
-      </c>
-      <c r="F82" s="6">
-        <v>1</v>
-      </c>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3"/>
-    </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D83" s="4">
-        <v>46182</v>
-      </c>
-      <c r="E83" s="5">
-        <v>2832.42</v>
-      </c>
-      <c r="F83" s="6">
-        <v>1</v>
-      </c>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I83" s="3"/>
-      <c r="J83" s="3"/>
+    <row r="80" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A80" s="7"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="9" t="n">
+        <v>378755.45</v>
+      </c>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="10"/>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="default" cellComments="none"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
   <si>
     <t>Funcionário</t>
   </si>
@@ -489,108 +489,90 @@
     <t>34199139500005466661090002533378120992717000</t>
   </si>
   <si>
+    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01006305.1</t>
+  </si>
+  <si>
+    <t>NOVA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006017.4</t>
+  </si>
+  <si>
+    <t>00191146500015028000000003473568000003058217</t>
+  </si>
+  <si>
+    <t>01006034.4</t>
+  </si>
+  <si>
+    <t>34194146600012096001090002555228120992717000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01006259.2</t>
+  </si>
+  <si>
+    <t>00193146600001971600000003473568000003085817</t>
+  </si>
+  <si>
+    <t>01006215.3</t>
+  </si>
+  <si>
+    <t>00198146600005183090000003473568000003086417</t>
+  </si>
+  <si>
+    <t>01006204.2</t>
+  </si>
+  <si>
+    <t>01006205.2</t>
+  </si>
+  <si>
+    <t>00194146700004193280000003473568000003078217</t>
+  </si>
+  <si>
+    <t>01006233.3</t>
+  </si>
+  <si>
+    <t>00196146800002077200000003473568000003083117</t>
+  </si>
+  <si>
+    <t>VWL DIST. DE MED. E MAT. MEDICO-HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01006092.4</t>
+  </si>
+  <si>
+    <t>00192146800002625000000003473568000003064817</t>
+  </si>
+  <si>
+    <t>01006207.2</t>
+  </si>
+  <si>
+    <t>01006305.2</t>
+  </si>
+  <si>
+    <t>01006259.3</t>
+  </si>
+  <si>
+    <t>00198147300001971600000003473568000003085917</t>
+  </si>
+  <si>
     <t>LEANDRA LUIZA SILVA</t>
   </si>
   <si>
-    <t>JM COMERCIO DE PRODUTOS FARMACEUTICOS LTDA</t>
-  </si>
-  <si>
-    <t>01006179.1</t>
+    <t>METTA FARMA DISTRIBUICAO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006048.4</t>
   </si>
   <si>
     <t>AM</t>
   </si>
   <si>
-    <t>00192144900006248230000003473568000003075617</t>
-  </si>
-  <si>
-    <t>CRALAB SAUDE ATACADO LTDA</t>
-  </si>
-  <si>
-    <t>01006225.1</t>
-  </si>
-  <si>
-    <t>00193145300002100000000003473568000003079117</t>
-  </si>
-  <si>
-    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
-  </si>
-  <si>
-    <t>01006305.1</t>
-  </si>
-  <si>
-    <t>NOVA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006017.4</t>
-  </si>
-  <si>
-    <t>00191146500015028000000003473568000003058217</t>
-  </si>
-  <si>
-    <t>01006034.4</t>
-  </si>
-  <si>
-    <t>34194146600012096001090002555228120992717000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
-  </si>
-  <si>
-    <t>01006259.2</t>
-  </si>
-  <si>
-    <t>00193146600001971600000003473568000003085817</t>
-  </si>
-  <si>
-    <t>01006215.3</t>
-  </si>
-  <si>
-    <t>00198146600005183090000003473568000003086417</t>
-  </si>
-  <si>
-    <t>01006204.2</t>
-  </si>
-  <si>
-    <t>01006205.2</t>
-  </si>
-  <si>
-    <t>00194146700004193280000003473568000003078217</t>
-  </si>
-  <si>
-    <t>01006233.3</t>
-  </si>
-  <si>
-    <t>00196146800002077200000003473568000003083117</t>
-  </si>
-  <si>
-    <t>VWL DIST. DE MED. E MAT. MEDICO-HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01006092.4</t>
-  </si>
-  <si>
-    <t>00192146800002625000000003473568000003064817</t>
-  </si>
-  <si>
-    <t>01006207.2</t>
-  </si>
-  <si>
-    <t>01006305.2</t>
-  </si>
-  <si>
-    <t>METTA FARMA DISTRIBUICAO DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006048.4</t>
-  </si>
-  <si>
-    <t>01006259.3</t>
-  </si>
-  <si>
-    <t>00198147300001971600000003473568000003085917</t>
-  </si>
-  <si>
     <t>MARCOS DUTRA</t>
   </si>
   <si>
@@ -613,6 +595,87 @@
   </si>
   <si>
     <t>00191147500002077200000003473568000003083217</t>
+  </si>
+  <si>
+    <t>01006305.3</t>
+  </si>
+  <si>
+    <t>L G PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>01006430.1</t>
+  </si>
+  <si>
+    <t>00194147900001928590000003473568000003094917</t>
+  </si>
+  <si>
+    <t>01006307.3</t>
+  </si>
+  <si>
+    <t>01006391.2</t>
+  </si>
+  <si>
+    <t>00198148000001551280000003473568000003093117</t>
+  </si>
+  <si>
+    <t>VENDEDOR</t>
+  </si>
+  <si>
+    <t>EXPRESS DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>10062026</t>
+  </si>
+  <si>
+    <t>DAYCOVAL</t>
+  </si>
+  <si>
+    <t>70791148000000010000001121205064100845801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDALAB COMERCIO DE ARTIGOS LABORAT E HOSP LTDA - </t>
+  </si>
+  <si>
+    <t>01006429.1</t>
+  </si>
+  <si>
+    <t>00198148000001219440000003473568000003095917</t>
+  </si>
+  <si>
+    <t>01006440.1</t>
+  </si>
+  <si>
+    <t>34192148000001409181090002586178120992717000</t>
+  </si>
+  <si>
+    <t>FARMAGUEDES COMERCIO DE PROD FARMAC. MED E HOSP LT</t>
+  </si>
+  <si>
+    <t>01006446.1</t>
+  </si>
+  <si>
+    <t>34194148000001467581090002586668120992717000</t>
+  </si>
+  <si>
+    <t>01006259.4</t>
+  </si>
+  <si>
+    <t>00194148000001971600000003473568000003086017</t>
+  </si>
+  <si>
+    <t>JMC COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01006395.1</t>
+  </si>
+  <si>
+    <t>FELM - COMERCIO DE MEDICAMENTOS E MATERIAIS HOSPIT</t>
+  </si>
+  <si>
+    <t>01006389.2</t>
+  </si>
+  <si>
+    <t>34191148000001562601090002581128120992717000</t>
   </si>
 </sst>
 </file>
@@ -787,7 +850,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
@@ -852,7 +915,7 @@
         <v>9391.78</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -882,7 +945,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
@@ -912,7 +975,7 @@
         <v>1264.87</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
@@ -942,7 +1005,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
@@ -972,7 +1035,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
@@ -1002,7 +1065,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
@@ -1032,7 +1095,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>21</v>
@@ -1062,7 +1125,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
@@ -1092,7 +1155,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
@@ -1122,7 +1185,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>13</v>
@@ -1152,7 +1215,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>13</v>
@@ -1182,7 +1245,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>13</v>
@@ -1212,7 +1275,7 @@
         <v>4439.9</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>13</v>
@@ -1242,7 +1305,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>13</v>
@@ -1272,7 +1335,7 @@
         <v>1216.86</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
@@ -1302,7 +1365,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>13</v>
@@ -1332,7 +1395,7 @@
         <v>1216.86</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
@@ -1362,7 +1425,7 @@
         <v>4439.9</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>13</v>
@@ -1392,7 +1455,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>13</v>
@@ -1422,7 +1485,7 @@
         <v>1118.4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>13</v>
@@ -1452,7 +1515,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>13</v>
@@ -1482,7 +1545,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>13</v>
@@ -1512,7 +1575,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>13</v>
@@ -1542,7 +1605,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>21</v>
@@ -1572,7 +1635,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>13</v>
@@ -1602,7 +1665,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>21</v>
@@ -1632,7 +1695,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>21</v>
@@ -1662,7 +1725,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>13</v>
@@ -1692,7 +1755,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>13</v>
@@ -1722,7 +1785,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>13</v>
@@ -1752,7 +1815,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>21</v>
@@ -1782,7 +1845,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>13</v>
@@ -1812,7 +1875,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>13</v>
@@ -1842,7 +1905,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>13</v>
@@ -1872,7 +1935,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>13</v>
@@ -1902,7 +1965,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>13</v>
@@ -1932,7 +1995,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>13</v>
@@ -1962,7 +2025,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>13</v>
@@ -1992,7 +2055,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>13</v>
@@ -2022,7 +2085,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>13</v>
@@ -2052,7 +2115,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>13</v>
@@ -2082,7 +2145,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>13</v>
@@ -2112,7 +2175,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>21</v>
@@ -2142,7 +2205,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>21</v>
@@ -2172,7 +2235,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>21</v>
@@ -2202,7 +2265,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>21</v>
@@ -2232,7 +2295,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>21</v>
@@ -2262,7 +2325,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>21</v>
@@ -2292,7 +2355,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>21</v>
@@ -2322,7 +2385,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>21</v>
@@ -2352,7 +2415,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>21</v>
@@ -2382,7 +2445,7 @@
         <v>38840.89</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
@@ -2408,7 +2471,7 @@
         <v>4480</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>21</v>
@@ -2438,7 +2501,7 @@
         <v>33844.16</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2464,7 +2527,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2490,7 +2553,7 @@
         <v>38740.53</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2516,7 +2579,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>21</v>
@@ -2546,7 +2609,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>21</v>
@@ -2576,7 +2639,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>21</v>
@@ -2606,7 +2669,7 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>13</v>
@@ -2621,234 +2684,234 @@
     </row>
     <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="D62" s="4" t="n">
-        <v>46159</v>
+        <v>46174</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>6248.23</v>
+        <v>1034.38</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>162</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="I62" s="3"/>
       <c r="J62" s="3"/>
     </row>
     <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A63" s="3" t="s">
-        <v>116</v>
+        <v>10</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>46163</v>
+        <v>46175</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2100</v>
+        <v>15028</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J63" s="3"/>
     </row>
     <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A64" s="3" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1034.38</v>
+        <v>12096</v>
       </c>
       <c r="F64" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I64" s="3"/>
+      <c r="I64" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="J64" s="3"/>
     </row>
     <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A65" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>15028</v>
+        <v>1971.6</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J65" s="3"/>
     </row>
     <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A66" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>46176</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>12096</v>
+        <v>5183.09</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J66" s="3"/>
     </row>
     <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A67" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1971.6</v>
+        <v>15716</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>175</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I67" s="3"/>
       <c r="J67" s="3"/>
     </row>
     <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A68" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>5183.09</v>
+        <v>4193.28</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J68" s="3"/>
     </row>
     <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A69" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>15716</v>
+        <v>2077.2</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G69" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H69" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I69" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>174</v>
+      </c>
       <c r="J69" s="3"/>
     </row>
     <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
@@ -2856,243 +2919,239 @@
         <v>10</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>4193.28</v>
+        <v>2625</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J70" s="3"/>
     </row>
     <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A71" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>2077.2</v>
+        <v>3667.76</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I71" s="3"/>
       <c r="J71" s="3"/>
     </row>
     <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A72" s="3" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2625</v>
+        <v>828.8</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>185</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="I72" s="3"/>
       <c r="J72" s="3"/>
     </row>
     <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A73" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>3667.76</v>
+        <v>1971.6</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G73" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H73" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I73" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="J73" s="3"/>
     </row>
     <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A74" s="3" t="s">
-        <v>40</v>
+        <v>182</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>828.8</v>
+        <v>4494.06</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
     </row>
     <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A75" s="3" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="D75" s="4" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>4494.06</v>
+        <v>7768.64</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
     </row>
     <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A76" s="3" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1971.6</v>
+        <v>2570.4</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>191</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="I76" s="3"/>
       <c r="J76" s="3"/>
     </row>
     <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A77" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="D77" s="4" t="n">
+        <v>46185</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>2077.2</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>7768.64</v>
-      </c>
-      <c r="F77" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="I77" s="3"/>
       <c r="J77" s="3"/>
     </row>
     <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A78" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>2570.4</v>
+        <v>828.8</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3" t="s">
@@ -3103,47 +3162,309 @@
     </row>
     <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A79" s="3" t="s">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2077.2</v>
+        <v>1928.59</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H79" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J79" s="3"/>
+    </row>
+    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A80" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>3337.78</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+    </row>
+    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A81" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1551.28</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J81" s="3"/>
+    </row>
+    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A82" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J82" s="3"/>
+    </row>
+    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A83" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>1219.44</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J83" s="3"/>
+    </row>
+    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A84" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>1409.18</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J84" s="3"/>
+    </row>
+    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A85" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>1467.58</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="J85" s="3"/>
+    </row>
+    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A86" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>1971.6</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I79" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="J79" s="3"/>
-    </row>
-    <row r="80" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A80" s="7"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="9" t="n">
-        <v>378755.45</v>
-      </c>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="10"/>
+      <c r="I86" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="J86" s="3"/>
+    </row>
+    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A87" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>21985.58</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+    </row>
+    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A88" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>1562.6</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J88" s="3"/>
+    </row>
+    <row r="89" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A89" s="7"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="9" t="n">
+        <v>407679.65</v>
+      </c>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="10"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0967F40-9292-44FB-B17A-46CB886C1CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="221">
   <si>
     <t>Funcionário</t>
   </si>
@@ -681,31 +693,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,14 +735,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -754,119 +759,381 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
-  <dimension ref="A1:J89"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J88"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
-    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
-    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
-    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
-    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="26.28515625" customWidth="true"/>
-    <col max="8" min="8" style="1" width="3.7109375" customWidth="true"/>
-    <col max="9" min="9" style="1" width="60.5703125" customWidth="true"/>
-    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
-    <col max="16384" min="11" style="1" width="12.140625"/>
+    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="60.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -898,7 +1165,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -908,13 +1175,13 @@
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>45326</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>9391.78</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="5">
+        <v>9391.7800000000007</v>
+      </c>
+      <c r="F2" s="6">
         <v>865</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -928,7 +1195,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -938,13 +1205,13 @@
       <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>45346</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5">
         <v>5418</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="6">
         <v>845</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -958,7 +1225,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -968,13 +1235,13 @@
       <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>45350</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1264.87</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="E4" s="5">
+        <v>1264.8699999999999</v>
+      </c>
+      <c r="F4" s="6">
         <v>841</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -988,7 +1255,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -998,13 +1265,13 @@
       <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>45356</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5">
         <v>5418</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="6">
         <v>835</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -1018,7 +1285,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -1028,13 +1295,13 @@
       <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>45362</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5">
         <v>384</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="6">
         <v>829</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1048,7 +1315,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1058,13 +1325,13 @@
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>45364</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5">
         <v>816</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="6">
         <v>827</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1078,7 +1345,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1088,13 +1355,13 @@
       <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>45378</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5">
         <v>816</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="6">
         <v>813</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1108,7 +1375,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -1118,13 +1385,13 @@
       <c r="C9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>45463</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5">
         <v>1674.52</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="6">
         <v>728</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1138,7 +1405,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -1148,13 +1415,13 @@
       <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>45493</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5">
         <v>873.6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="6">
         <v>698</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -1168,7 +1435,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1178,13 +1445,13 @@
       <c r="C11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>45523</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5">
         <v>873.6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="6">
         <v>668</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -1198,7 +1465,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -1208,13 +1475,13 @@
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>45600</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5">
         <v>2000</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="6">
         <v>591</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1228,7 +1495,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>40</v>
       </c>
@@ -1238,13 +1505,13 @@
       <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>45607</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5">
         <v>3204.34</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="6">
         <v>584</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -1258,7 +1525,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1268,13 +1535,13 @@
       <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>45608</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F14" s="6">
         <v>583</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1288,7 +1555,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -1298,13 +1565,13 @@
       <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>45614</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="5">
         <v>2000</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="6">
         <v>577</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -1318,7 +1585,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
@@ -1328,13 +1595,13 @@
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>45615</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F16" s="6">
         <v>576</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -1348,7 +1615,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -1358,13 +1625,13 @@
       <c r="C17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>45617</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="5">
         <v>1843.87</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="6">
         <v>574</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -1378,7 +1645,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
@@ -1388,13 +1655,13 @@
       <c r="C18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>45622</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F18" s="6" t="n">
+      <c r="E18" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F18" s="6">
         <v>569</v>
       </c>
       <c r="G18" s="3" t="s">
@@ -1408,7 +1675,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>46</v>
       </c>
@@ -1418,13 +1685,13 @@
       <c r="C19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>45622</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F19" s="6" t="n">
+      <c r="E19" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F19" s="6">
         <v>569</v>
       </c>
       <c r="G19" s="3" t="s">
@@ -1438,7 +1705,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
@@ -1448,13 +1715,13 @@
       <c r="C20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>45624</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="5">
         <v>1843.88</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="6">
         <v>567</v>
       </c>
       <c r="G20" s="3" t="s">
@@ -1468,7 +1735,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>63</v>
       </c>
@@ -1478,13 +1745,13 @@
       <c r="C21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>45688</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>1118.4</v>
-      </c>
-      <c r="F21" s="6" t="n">
+      <c r="E21" s="5">
+        <v>1118.4000000000001</v>
+      </c>
+      <c r="F21" s="6">
         <v>503</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -1498,7 +1765,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -1508,13 +1775,13 @@
       <c r="C22" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>45695</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="6">
         <v>496</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -1528,7 +1795,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -1538,13 +1805,13 @@
       <c r="C23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>45699</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="5">
         <v>2330</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="6">
         <v>492</v>
       </c>
       <c r="G23" s="3" t="s">
@@ -1558,7 +1825,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -1568,13 +1835,13 @@
       <c r="C24" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>45702</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="6">
         <v>489</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -1588,7 +1855,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
@@ -1598,13 +1865,13 @@
       <c r="C25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>45705</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="5">
         <v>2541</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="6">
         <v>486</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -1618,7 +1885,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
@@ -1628,13 +1895,13 @@
       <c r="C26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>45709</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="6">
         <v>482</v>
       </c>
       <c r="G26" s="3" t="s">
@@ -1648,7 +1915,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>40</v>
       </c>
@@ -1658,13 +1925,13 @@
       <c r="C27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>45712</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="5">
         <v>2541</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="6">
         <v>479</v>
       </c>
       <c r="G27" s="3" t="s">
@@ -1678,7 +1945,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
@@ -1688,13 +1955,13 @@
       <c r="C28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>45726</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="5">
         <v>2541</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="6">
         <v>465</v>
       </c>
       <c r="G28" s="3" t="s">
@@ -1708,7 +1975,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
@@ -1718,13 +1985,13 @@
       <c r="C29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4">
         <v>45727</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="6">
         <v>464</v>
       </c>
       <c r="G29" s="3" t="s">
@@ -1738,7 +2005,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
@@ -1748,13 +2015,13 @@
       <c r="C30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>45734</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="6">
         <v>457</v>
       </c>
       <c r="G30" s="3" t="s">
@@ -1768,7 +2035,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>46</v>
       </c>
@@ -1778,13 +2045,13 @@
       <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>45734</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="6">
         <v>457</v>
       </c>
       <c r="G31" s="3" t="s">
@@ -1798,7 +2065,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -1808,13 +2075,13 @@
       <c r="C32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>45740</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="5">
         <v>2541</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="6">
         <v>451</v>
       </c>
       <c r="G32" s="3" t="s">
@@ -1828,7 +2095,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -1838,13 +2105,13 @@
       <c r="C33" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>45741</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="6">
         <v>450</v>
       </c>
       <c r="G33" s="3" t="s">
@@ -1858,7 +2125,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>46</v>
       </c>
@@ -1868,13 +2135,13 @@
       <c r="C34" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>45741</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="6">
         <v>450</v>
       </c>
       <c r="G34" s="3" t="s">
@@ -1888,7 +2155,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>46</v>
       </c>
@@ -1898,13 +2165,13 @@
       <c r="C35" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4">
         <v>45748</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="6">
         <v>443</v>
       </c>
       <c r="G35" s="3" t="s">
@@ -1918,7 +2185,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>40</v>
       </c>
@@ -1928,13 +2195,13 @@
       <c r="C36" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4">
         <v>45748</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="5">
         <v>7562.76</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="6">
         <v>443</v>
       </c>
       <c r="G36" s="3" t="s">
@@ -1948,7 +2215,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
@@ -1958,13 +2225,13 @@
       <c r="C37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4">
         <v>45755</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="6">
         <v>436</v>
       </c>
       <c r="G37" s="3" t="s">
@@ -1978,7 +2245,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>46</v>
       </c>
@@ -1988,13 +2255,13 @@
       <c r="C38" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="4">
         <v>45761</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="5">
         <v>6169.53</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="6">
         <v>430</v>
       </c>
       <c r="G38" s="3" t="s">
@@ -2008,7 +2275,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>46</v>
       </c>
@@ -2018,13 +2285,13 @@
       <c r="C39" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="4">
         <v>45768</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="5">
         <v>3850</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="6">
         <v>423</v>
       </c>
       <c r="G39" s="3" t="s">
@@ -2038,7 +2305,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>46</v>
       </c>
@@ -2048,13 +2315,13 @@
       <c r="C40" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="4">
         <v>45775</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="5">
         <v>3850</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="6">
         <v>416</v>
       </c>
       <c r="G40" s="3" t="s">
@@ -2068,7 +2335,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>46</v>
       </c>
@@ -2078,13 +2345,13 @@
       <c r="C41" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="4">
         <v>45775</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="5">
         <v>6089.41</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="6">
         <v>416</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -2098,7 +2365,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>46</v>
       </c>
@@ -2108,13 +2375,13 @@
       <c r="C42" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="4">
         <v>45782</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="5">
         <v>3800</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="6">
         <v>409</v>
       </c>
       <c r="G42" s="3" t="s">
@@ -2128,7 +2395,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>46</v>
       </c>
@@ -2138,13 +2405,13 @@
       <c r="C43" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="4">
         <v>45789</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="5">
         <v>3800</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="6">
         <v>402</v>
       </c>
       <c r="G43" s="3" t="s">
@@ -2158,7 +2425,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>116</v>
       </c>
@@ -2168,13 +2435,13 @@
       <c r="C44" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="4">
         <v>45789</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="5">
         <v>1143.54</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="6">
         <v>402</v>
       </c>
       <c r="G44" s="3" t="s">
@@ -2188,7 +2455,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>116</v>
       </c>
@@ -2198,13 +2465,13 @@
       <c r="C45" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="4">
         <v>45796</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="5">
         <v>2287.06</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="6">
         <v>395</v>
       </c>
       <c r="G45" s="3" t="s">
@@ -2218,7 +2485,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
@@ -2228,13 +2495,13 @@
       <c r="C46" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="4">
         <v>45896</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="5">
         <v>4572.62</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="6">
         <v>295</v>
       </c>
       <c r="G46" s="3" t="s">
@@ -2248,7 +2515,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
@@ -2258,13 +2525,13 @@
       <c r="C47" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="4">
         <v>45910</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="6">
         <v>281</v>
       </c>
       <c r="G47" s="3" t="s">
@@ -2278,7 +2545,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>40</v>
       </c>
@@ -2288,13 +2555,13 @@
       <c r="C48" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="4">
         <v>45924</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="6">
         <v>267</v>
       </c>
       <c r="G48" s="3" t="s">
@@ -2308,7 +2575,7 @@
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>130</v>
       </c>
@@ -2318,13 +2585,13 @@
       <c r="C49" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="4">
         <v>45947</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="5">
         <v>3867.34</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="6">
         <v>244</v>
       </c>
       <c r="G49" s="3" t="s">
@@ -2338,7 +2605,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
@@ -2348,13 +2615,13 @@
       <c r="C50" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="4">
         <v>45954</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="6">
         <v>237</v>
       </c>
       <c r="G50" s="3" t="s">
@@ -2368,7 +2635,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>130</v>
       </c>
@@ -2378,13 +2645,13 @@
       <c r="C51" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="4">
         <v>45961</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F51" s="6">
         <v>230</v>
       </c>
       <c r="G51" s="3" t="s">
@@ -2398,7 +2665,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>130</v>
       </c>
@@ -2408,13 +2675,13 @@
       <c r="C52" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="4">
         <v>45968</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F52" s="6">
         <v>223</v>
       </c>
       <c r="G52" s="3" t="s">
@@ -2428,7 +2695,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>130</v>
       </c>
@@ -2438,13 +2705,13 @@
       <c r="C53" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="4">
         <v>45980</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E53" s="5">
         <v>38840.89</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F53" s="6">
         <v>211</v>
       </c>
       <c r="G53" s="3"/>
@@ -2454,7 +2721,7 @@
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>116</v>
       </c>
@@ -2464,13 +2731,13 @@
       <c r="C54" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="4">
         <v>45980</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E54" s="5">
         <v>4480</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F54" s="6">
         <v>211</v>
       </c>
       <c r="G54" s="3" t="s">
@@ -2484,7 +2751,7 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>130</v>
       </c>
@@ -2494,13 +2761,13 @@
       <c r="C55" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="4">
         <v>45987</v>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>33844.16</v>
-      </c>
-      <c r="F55" s="6" t="n">
+      <c r="E55" s="5">
+        <v>33844.160000000003</v>
+      </c>
+      <c r="F55" s="6">
         <v>204</v>
       </c>
       <c r="G55" s="3"/>
@@ -2510,7 +2777,7 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>116</v>
       </c>
@@ -2520,13 +2787,13 @@
       <c r="C56" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="4">
         <v>45989</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="5">
         <v>3220</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F56" s="6">
         <v>202</v>
       </c>
       <c r="G56" s="3"/>
@@ -2536,7 +2803,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>130</v>
       </c>
@@ -2546,13 +2813,13 @@
       <c r="C57" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="4">
         <v>45994</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="5">
         <v>38740.53</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="6">
         <v>197</v>
       </c>
       <c r="G57" s="3"/>
@@ -2562,7 +2829,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2572,13 +2839,13 @@
       <c r="C58" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="4">
         <v>46090</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="5">
         <v>806.34</v>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F58" s="6">
         <v>101</v>
       </c>
       <c r="G58" s="3" t="s">
@@ -2592,7 +2859,7 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>18</v>
       </c>
@@ -2602,13 +2869,13 @@
       <c r="C59" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="4">
         <v>46097</v>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E59" s="5">
         <v>503.28</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F59" s="6">
         <v>94</v>
       </c>
       <c r="G59" s="3" t="s">
@@ -2622,7 +2889,7 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>18</v>
       </c>
@@ -2632,13 +2899,13 @@
       <c r="C60" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="4">
         <v>46104</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="5">
         <v>503.28</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F60" s="6">
         <v>87</v>
       </c>
       <c r="G60" s="3" t="s">
@@ -2652,7 +2919,7 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>10</v>
       </c>
@@ -2662,13 +2929,13 @@
       <c r="C61" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="4">
         <v>46105</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="5">
         <v>5466.66</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F61" s="6">
         <v>86</v>
       </c>
       <c r="G61" s="3" t="s">
@@ -2682,7 +2949,7 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>40</v>
       </c>
@@ -2692,13 +2959,13 @@
       <c r="C62" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="4">
         <v>46174</v>
       </c>
-      <c r="E62" s="5" t="n">
-        <v>1034.38</v>
-      </c>
-      <c r="F62" s="6" t="n">
+      <c r="E62" s="5">
+        <v>1034.3800000000001</v>
+      </c>
+      <c r="F62" s="6">
         <v>17</v>
       </c>
       <c r="G62" s="3"/>
@@ -2708,7 +2975,7 @@
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>10</v>
       </c>
@@ -2718,13 +2985,13 @@
       <c r="C63" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="4">
         <v>46175</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="5">
         <v>15028</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="6">
         <v>16</v>
       </c>
       <c r="G63" s="3" t="s">
@@ -2738,7 +3005,7 @@
       </c>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>10</v>
       </c>
@@ -2748,13 +3015,13 @@
       <c r="C64" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="4">
         <v>46176</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="5">
         <v>12096</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="6">
         <v>15</v>
       </c>
       <c r="G64" s="3" t="s">
@@ -2768,7 +3035,7 @@
       </c>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>130</v>
       </c>
@@ -2778,13 +3045,13 @@
       <c r="C65" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="4">
         <v>46176</v>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E65" s="5">
         <v>1971.6</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="6">
         <v>15</v>
       </c>
       <c r="G65" s="3" t="s">
@@ -2798,7 +3065,7 @@
       </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>130</v>
       </c>
@@ -2808,13 +3075,13 @@
       <c r="C66" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="4">
         <v>46176</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="5">
         <v>5183.09</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="F66" s="6">
         <v>15</v>
       </c>
       <c r="G66" s="3" t="s">
@@ -2828,7 +3095,7 @@
       </c>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>10</v>
       </c>
@@ -2838,13 +3105,13 @@
       <c r="C67" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="4">
         <v>46177</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="5">
         <v>15716</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" s="6">
         <v>14</v>
       </c>
       <c r="G67" s="3"/>
@@ -2854,7 +3121,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>10</v>
       </c>
@@ -2864,13 +3131,13 @@
       <c r="C68" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="4">
         <v>46177</v>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E68" s="5">
         <v>4193.28</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" s="6">
         <v>14</v>
       </c>
       <c r="G68" s="3" t="s">
@@ -2884,7 +3151,7 @@
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>130</v>
       </c>
@@ -2894,13 +3161,13 @@
       <c r="C69" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="4">
         <v>46178</v>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>2077.2</v>
-      </c>
-      <c r="F69" s="6" t="n">
+      <c r="E69" s="5">
+        <v>2077.1999999999998</v>
+      </c>
+      <c r="F69" s="6">
         <v>13</v>
       </c>
       <c r="G69" s="3" t="s">
@@ -2914,7 +3181,7 @@
       </c>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>10</v>
       </c>
@@ -2924,13 +3191,13 @@
       <c r="C70" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="4">
         <v>46178</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="5">
         <v>2625</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="F70" s="6">
         <v>13</v>
       </c>
       <c r="G70" s="3" t="s">
@@ -2944,7 +3211,7 @@
       </c>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>10</v>
       </c>
@@ -2954,13 +3221,13 @@
       <c r="C71" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="4">
         <v>46179</v>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E71" s="5">
         <v>3667.76</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="F71" s="6">
         <v>12</v>
       </c>
       <c r="G71" s="3"/>
@@ -2970,7 +3237,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>40</v>
       </c>
@@ -2980,13 +3247,13 @@
       <c r="C72" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="4">
         <v>46181</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E72" s="5">
         <v>828.8</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="6">
         <v>10</v>
       </c>
       <c r="G72" s="3"/>
@@ -2996,7 +3263,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>130</v>
       </c>
@@ -3006,13 +3273,13 @@
       <c r="C73" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="4">
         <v>46183</v>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="5">
         <v>1971.6</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" s="6">
         <v>8</v>
       </c>
       <c r="G73" s="3" t="s">
@@ -3026,7 +3293,7 @@
       </c>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>182</v>
       </c>
@@ -3036,13 +3303,13 @@
       <c r="C74" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="4">
         <v>46183</v>
       </c>
-      <c r="E74" s="5" t="n">
-        <v>4494.06</v>
-      </c>
-      <c r="F74" s="6" t="n">
+      <c r="E74" s="5">
+        <v>4494.0600000000004</v>
+      </c>
+      <c r="F74" s="6">
         <v>8</v>
       </c>
       <c r="G74" s="3"/>
@@ -3052,7 +3319,7 @@
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>186</v>
       </c>
@@ -3062,13 +3329,13 @@
       <c r="C75" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="4">
         <v>46184</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E75" s="5">
         <v>7768.64</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="F75" s="6">
         <v>7</v>
       </c>
       <c r="G75" s="3"/>
@@ -3078,7 +3345,7 @@
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>18</v>
       </c>
@@ -3088,13 +3355,13 @@
       <c r="C76" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="4">
         <v>46184</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="5">
         <v>2570.4</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="6">
         <v>7</v>
       </c>
       <c r="G76" s="3"/>
@@ -3104,7 +3371,7 @@
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>130</v>
       </c>
@@ -3114,13 +3381,13 @@
       <c r="C77" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="4">
         <v>46185</v>
       </c>
-      <c r="E77" s="5" t="n">
-        <v>2077.2</v>
-      </c>
-      <c r="F77" s="6" t="n">
+      <c r="E77" s="5">
+        <v>2077.1999999999998</v>
+      </c>
+      <c r="F77" s="6">
         <v>6</v>
       </c>
       <c r="G77" s="3" t="s">
@@ -3134,7 +3401,7 @@
       </c>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>40</v>
       </c>
@@ -3144,13 +3411,13 @@
       <c r="C78" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="4">
         <v>46188</v>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E78" s="5">
         <v>828.8</v>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="F78" s="6">
         <v>3</v>
       </c>
       <c r="G78" s="3"/>
@@ -3160,7 +3427,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
     </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>40</v>
       </c>
@@ -3170,13 +3437,13 @@
       <c r="C79" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="4">
         <v>46189</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E79" s="5">
         <v>1928.59</v>
       </c>
-      <c r="F79" s="6" t="n">
+      <c r="F79" s="6">
         <v>2</v>
       </c>
       <c r="G79" s="3" t="s">
@@ -3190,7 +3457,7 @@
       </c>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>40</v>
       </c>
@@ -3200,13 +3467,13 @@
       <c r="C80" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="4">
         <v>46189</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="E80" s="5">
         <v>3337.78</v>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="F80" s="6">
         <v>2</v>
       </c>
       <c r="G80" s="3"/>
@@ -3216,7 +3483,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>40</v>
       </c>
@@ -3226,13 +3493,13 @@
       <c r="C81" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" s="4">
         <v>46190</v>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E81" s="5">
         <v>1551.28</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="F81" s="6">
         <v>1</v>
       </c>
       <c r="G81" s="3" t="s">
@@ -3246,7 +3513,7 @@
       </c>
       <c r="J81" s="3"/>
     </row>
-    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>201</v>
       </c>
@@ -3256,13 +3523,13 @@
       <c r="C82" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="4">
         <v>46190</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E82" s="5">
         <v>10</v>
       </c>
-      <c r="F82" s="6" t="n">
+      <c r="F82" s="6">
         <v>1</v>
       </c>
       <c r="G82" s="3" t="s">
@@ -3276,7 +3543,7 @@
       </c>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>63</v>
       </c>
@@ -3286,13 +3553,13 @@
       <c r="C83" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="D83" s="4">
         <v>46190</v>
       </c>
-      <c r="E83" s="5" t="n">
+      <c r="E83" s="5">
         <v>1219.44</v>
       </c>
-      <c r="F83" s="6" t="n">
+      <c r="F83" s="6">
         <v>1</v>
       </c>
       <c r="G83" s="3" t="s">
@@ -3306,7 +3573,7 @@
       </c>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>40</v>
       </c>
@@ -3316,13 +3583,13 @@
       <c r="C84" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="D84" s="4">
         <v>46190</v>
       </c>
-      <c r="E84" s="5" t="n">
+      <c r="E84" s="5">
         <v>1409.18</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" s="6">
         <v>1</v>
       </c>
       <c r="G84" s="3" t="s">
@@ -3336,7 +3603,7 @@
       </c>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>40</v>
       </c>
@@ -3346,13 +3613,13 @@
       <c r="C85" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" s="4">
         <v>46190</v>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E85" s="5">
         <v>1467.58</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F85" s="6">
         <v>1</v>
       </c>
       <c r="G85" s="3" t="s">
@@ -3366,7 +3633,7 @@
       </c>
       <c r="J85" s="3"/>
     </row>
-    <row r="86" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>130</v>
       </c>
@@ -3376,13 +3643,13 @@
       <c r="C86" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="D86" s="4">
         <v>46190</v>
       </c>
-      <c r="E86" s="5" t="n">
+      <c r="E86" s="5">
         <v>1971.6</v>
       </c>
-      <c r="F86" s="6" t="n">
+      <c r="F86" s="6">
         <v>1</v>
       </c>
       <c r="G86" s="3" t="s">
@@ -3396,7 +3663,7 @@
       </c>
       <c r="J86" s="3"/>
     </row>
-    <row r="87" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>10</v>
       </c>
@@ -3406,13 +3673,13 @@
       <c r="C87" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="D87" s="4">
         <v>46190</v>
       </c>
-      <c r="E87" s="5" t="n">
+      <c r="E87" s="5">
         <v>21985.58</v>
       </c>
-      <c r="F87" s="6" t="n">
+      <c r="F87" s="6">
         <v>1</v>
       </c>
       <c r="G87" s="3"/>
@@ -3422,7 +3689,7 @@
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
     </row>
-    <row r="88" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="88" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>18</v>
       </c>
@@ -3432,13 +3699,13 @@
       <c r="C88" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="4">
         <v>46190</v>
       </c>
-      <c r="E88" s="5" t="n">
+      <c r="E88" s="5">
         <v>1562.6</v>
       </c>
-      <c r="F88" s="6" t="n">
+      <c r="F88" s="6">
         <v>1</v>
       </c>
       <c r="G88" s="3" t="s">
@@ -3452,21 +3719,7 @@
       </c>
       <c r="J88" s="3"/>
     </row>
-    <row r="89" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A89" s="7"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="9" t="n">
-        <v>407679.65</v>
-      </c>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8"/>
-      <c r="J89" s="10"/>
-    </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0967F40-9292-44FB-B17A-46CB886C1CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B8215F-DC0C-4D55-B9B4-C6A7AAC8E956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="217">
   <si>
     <t>Funcionário</t>
   </si>
@@ -468,7 +468,7 @@
     <t>01005144.3</t>
   </si>
   <si>
-    <t>01005217.3BP</t>
+    <t>01005217.3BPBP</t>
   </si>
   <si>
     <t>DENTAL SORRISO LTDA</t>
@@ -546,12 +546,6 @@
     <t>00194146700004193280000003473568000003078217</t>
   </si>
   <si>
-    <t>01006233.3</t>
-  </si>
-  <si>
-    <t>00196146800002077200000003473568000003083117</t>
-  </si>
-  <si>
     <t>VWL DIST. DE MED. E MAT. MEDICO-HOSPITALARES LTDA</t>
   </si>
   <si>
@@ -567,127 +561,121 @@
     <t>01006305.2</t>
   </si>
   <si>
-    <t>01006259.3</t>
-  </si>
-  <si>
-    <t>00198147300001971600000003473568000003085917</t>
-  </si>
-  <si>
-    <t>LEANDRA LUIZA SILVA</t>
-  </si>
-  <si>
-    <t>METTA FARMA DISTRIBUICAO DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006048.4</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>MARCOS DUTRA</t>
-  </si>
-  <si>
-    <t>DICOREL DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006336.2</t>
-  </si>
-  <si>
-    <t>PI</t>
+    <t>01006305.3</t>
+  </si>
+  <si>
+    <t>JMC COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01006395.1</t>
+  </si>
+  <si>
+    <t>01006205.3</t>
+  </si>
+  <si>
+    <t>00192148200004193280000003473568000003078317</t>
+  </si>
+  <si>
+    <t>01006204.3</t>
+  </si>
+  <si>
+    <t>01006508.1</t>
+  </si>
+  <si>
+    <t>KELLEN</t>
+  </si>
+  <si>
+    <t>NM DISTRIBUIDORA E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006226.3</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>00191148400002800000000003473568000003079017</t>
+  </si>
+  <si>
+    <t>CAMEDIC COMERCIAL E SERVIÇOS DE PROD MED HOSP EIRE</t>
+  </si>
+  <si>
+    <t>01006350.2</t>
+  </si>
+  <si>
+    <t>34195148500001254011090002579818120992717000</t>
   </si>
   <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006255.3</t>
-  </si>
-  <si>
-    <t>01006233.4</t>
-  </si>
-  <si>
-    <t>00191147500002077200000003473568000003083217</t>
-  </si>
-  <si>
-    <t>01006305.3</t>
+    <t>01006515.1</t>
+  </si>
+  <si>
+    <t>34193148800001416241090002593268120992717000</t>
   </si>
   <si>
     <t>L G PRODUTOS HOSPITALARES LTDA</t>
   </si>
   <si>
-    <t>01006430.1</t>
-  </si>
-  <si>
-    <t>00194147900001928590000003473568000003094917</t>
-  </si>
-  <si>
-    <t>01006307.3</t>
-  </si>
-  <si>
-    <t>01006391.2</t>
-  </si>
-  <si>
-    <t>00198148000001551280000003473568000003093117</t>
-  </si>
-  <si>
-    <t>VENDEDOR</t>
-  </si>
-  <si>
-    <t>EXPRESS DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>10062026</t>
-  </si>
-  <si>
-    <t>DAYCOVAL</t>
-  </si>
-  <si>
-    <t>70791148000000010000001121205064100845801086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIDALAB COMERCIO DE ARTIGOS LABORAT E HOSP LTDA - </t>
-  </si>
-  <si>
-    <t>01006429.1</t>
-  </si>
-  <si>
-    <t>00198148000001219440000003473568000003095917</t>
-  </si>
-  <si>
-    <t>01006440.1</t>
-  </si>
-  <si>
-    <t>34192148000001409181090002586178120992717000</t>
-  </si>
-  <si>
-    <t>FARMAGUEDES COMERCIO DE PROD FARMAC. MED E HOSP LT</t>
-  </si>
-  <si>
-    <t>01006446.1</t>
-  </si>
-  <si>
-    <t>34194148000001467581090002586668120992717000</t>
-  </si>
-  <si>
-    <t>01006259.4</t>
-  </si>
-  <si>
-    <t>00194148000001971600000003473568000003086017</t>
-  </si>
-  <si>
-    <t>JMC COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01006395.1</t>
-  </si>
-  <si>
-    <t>FELM - COMERCIO DE MEDICAMENTOS E MATERIAIS HOSPIT</t>
-  </si>
-  <si>
-    <t>01006389.2</t>
-  </si>
-  <si>
-    <t>34191148000001562601090002581128120992717000</t>
+    <t>01006470.2</t>
+  </si>
+  <si>
+    <t>01006508.2</t>
+  </si>
+  <si>
+    <t>ASPEN SERVICE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01006387.2</t>
+  </si>
+  <si>
+    <t>01006395.2</t>
+  </si>
+  <si>
+    <t>PROMED DIST. DE MEDIC E PROD. PARA SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>01006538.1</t>
+  </si>
+  <si>
+    <t>00191149100002068000000003473568000003104717</t>
+  </si>
+  <si>
+    <t>L G MED DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006520.1</t>
+  </si>
+  <si>
+    <t>01006536.1</t>
+  </si>
+  <si>
+    <t>00195149100007447560000003473568000003104017</t>
+  </si>
+  <si>
+    <t>01006357.4</t>
+  </si>
+  <si>
+    <t>00195149200003921600000003473568000003090817</t>
+  </si>
+  <si>
+    <t>ESTRELA COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01006263.2</t>
+  </si>
+  <si>
+    <t>00194149200005796930000003473568000003087617</t>
+  </si>
+  <si>
+    <t>VIAMED LTDA</t>
+  </si>
+  <si>
+    <t>01006359.4</t>
+  </si>
+  <si>
+    <t>34199149200001797941090002579578120992717000</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -1182,7 +1170,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1212,7 +1200,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
@@ -1242,7 +1230,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
@@ -1272,7 +1260,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
@@ -1302,7 +1290,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
@@ -1332,7 +1320,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
@@ -1362,7 +1350,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>21</v>
@@ -1392,7 +1380,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
@@ -1422,7 +1410,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
@@ -1452,7 +1440,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>13</v>
@@ -1482,7 +1470,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>13</v>
@@ -1512,7 +1500,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>13</v>
@@ -1542,7 +1530,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>13</v>
@@ -1572,7 +1560,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>13</v>
@@ -1602,7 +1590,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
@@ -1632,7 +1620,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>13</v>
@@ -1662,7 +1650,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
@@ -1692,7 +1680,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>13</v>
@@ -1722,7 +1710,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>13</v>
@@ -1752,7 +1740,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>13</v>
@@ -1782,7 +1770,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>13</v>
@@ -1812,7 +1800,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>13</v>
@@ -1842,7 +1830,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>13</v>
@@ -1872,7 +1860,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>21</v>
@@ -1902,7 +1890,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>13</v>
@@ -1932,7 +1920,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>21</v>
@@ -1962,7 +1950,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>21</v>
@@ -1992,7 +1980,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>13</v>
@@ -2022,7 +2010,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>13</v>
@@ -2052,7 +2040,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>13</v>
@@ -2082,7 +2070,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>21</v>
@@ -2112,7 +2100,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>13</v>
@@ -2142,7 +2130,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>13</v>
@@ -2172,7 +2160,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>13</v>
@@ -2202,7 +2190,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>13</v>
@@ -2232,7 +2220,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>13</v>
@@ -2262,7 +2250,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>13</v>
@@ -2292,7 +2280,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>13</v>
@@ -2322,7 +2310,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>13</v>
@@ -2352,7 +2340,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>13</v>
@@ -2382,7 +2370,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>13</v>
@@ -2412,7 +2400,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>13</v>
@@ -2442,7 +2430,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>21</v>
@@ -2472,7 +2460,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>21</v>
@@ -2502,7 +2490,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>21</v>
@@ -2532,7 +2520,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>21</v>
@@ -2562,7 +2550,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>21</v>
@@ -2592,7 +2580,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>21</v>
@@ -2622,7 +2610,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>21</v>
@@ -2652,7 +2640,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>21</v>
@@ -2682,7 +2670,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>21</v>
@@ -2712,7 +2700,7 @@
         <v>38840.89</v>
       </c>
       <c r="F53" s="6">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
@@ -2738,7 +2726,7 @@
         <v>4480</v>
       </c>
       <c r="F54" s="6">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>21</v>
@@ -2768,7 +2756,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2794,7 +2782,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2817,10 +2805,10 @@
         <v>45994</v>
       </c>
       <c r="E57" s="5">
-        <v>38740.53</v>
+        <v>27216.799999999999</v>
       </c>
       <c r="F57" s="6">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2846,7 +2834,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>21</v>
@@ -2876,7 +2864,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>21</v>
@@ -2906,7 +2894,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>21</v>
@@ -2936,7 +2924,7 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>13</v>
@@ -2966,7 +2954,7 @@
         <v>1034.3800000000001</v>
       </c>
       <c r="F62" s="6">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
@@ -2992,7 +2980,7 @@
         <v>15028</v>
       </c>
       <c r="F63" s="6">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>21</v>
@@ -3022,7 +3010,7 @@
         <v>12096</v>
       </c>
       <c r="F64" s="6">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>13</v>
@@ -3052,7 +3040,7 @@
         <v>1971.6</v>
       </c>
       <c r="F65" s="6">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>21</v>
@@ -3082,7 +3070,7 @@
         <v>5183.09</v>
       </c>
       <c r="F66" s="6">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>21</v>
@@ -3112,7 +3100,7 @@
         <v>15716</v>
       </c>
       <c r="F67" s="6">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
@@ -3138,7 +3126,7 @@
         <v>4193.28</v>
       </c>
       <c r="F68" s="6">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>21</v>
@@ -3153,31 +3141,31 @@
     </row>
     <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D69" s="4">
         <v>46178</v>
       </c>
       <c r="E69" s="5">
-        <v>2077.1999999999998</v>
+        <v>2625</v>
       </c>
       <c r="F69" s="6">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J69" s="3"/>
     </row>
@@ -3186,53 +3174,49 @@
         <v>10</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>176</v>
       </c>
       <c r="D70" s="4">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="E70" s="5">
-        <v>2625</v>
+        <v>3667.76</v>
       </c>
       <c r="F70" s="6">
-        <v>13</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I70" s="3" t="s">
-        <v>177</v>
-      </c>
+      <c r="I70" s="3"/>
       <c r="J70" s="3"/>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D71" s="4">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="E71" s="5">
-        <v>3667.76</v>
+        <v>828.8</v>
       </c>
       <c r="F71" s="6">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
@@ -3245,16 +3229,16 @@
         <v>158</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D72" s="4">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E72" s="5">
         <v>828.8</v>
       </c>
       <c r="F72" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
@@ -3265,195 +3249,199 @@
     </row>
     <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>180</v>
       </c>
       <c r="D73" s="4">
-        <v>46183</v>
+        <v>46190</v>
       </c>
       <c r="E73" s="5">
-        <v>1971.6</v>
+        <v>21985.58</v>
       </c>
       <c r="F73" s="6">
-        <v>8</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G73" s="3"/>
       <c r="H73" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>181</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I73" s="3"/>
       <c r="J73" s="3"/>
     </row>
     <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D74" s="4">
+        <v>46192</v>
+      </c>
+      <c r="E74" s="5">
+        <v>4193.28</v>
+      </c>
+      <c r="F74" s="6">
+        <v>11</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D74" s="4">
-        <v>46183</v>
-      </c>
-      <c r="E74" s="5">
-        <v>4494.0600000000004</v>
-      </c>
-      <c r="F74" s="6">
-        <v>8</v>
-      </c>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="I74" s="3"/>
       <c r="J74" s="3"/>
     </row>
     <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>186</v>
+        <v>10</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D75" s="4">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="E75" s="5">
-        <v>7768.64</v>
+        <v>15716</v>
       </c>
       <c r="F75" s="6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="3" t="s">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
     </row>
     <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D76" s="4">
-        <v>46184</v>
+        <v>46192</v>
       </c>
       <c r="E76" s="5">
-        <v>2570.4</v>
+        <v>7494.53</v>
       </c>
       <c r="F76" s="6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
     </row>
     <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D77" s="4">
-        <v>46185</v>
+        <v>46194</v>
       </c>
       <c r="E77" s="5">
-        <v>2077.1999999999998</v>
+        <v>2800</v>
       </c>
       <c r="F77" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J77" s="3"/>
     </row>
     <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D78" s="4">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E78" s="5">
-        <v>828.8</v>
+        <v>1254.01</v>
       </c>
       <c r="F78" s="6">
-        <v>3</v>
-      </c>
-      <c r="G78" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H78" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I78" s="3"/>
+      <c r="I78" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="J78" s="3"/>
     </row>
     <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D79" s="4">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="E79" s="5">
-        <v>1928.59</v>
+        <v>1416.24</v>
       </c>
       <c r="F79" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>66</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J79" s="3"/>
     </row>
@@ -3462,19 +3450,19 @@
         <v>40</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D80" s="4">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="E80" s="5">
-        <v>3337.78</v>
+        <v>4989.6000000000004</v>
       </c>
       <c r="F80" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3" t="s">
@@ -3485,239 +3473,257 @@
     </row>
     <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D81" s="4">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="E81" s="5">
-        <v>1551.28</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="F81" s="6">
-        <v>1</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>200</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I81" s="3"/>
       <c r="J81" s="3"/>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>201</v>
+        <v>10</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D82" s="4">
-        <v>46190</v>
+        <v>46200</v>
       </c>
       <c r="E82" s="5">
-        <v>10</v>
+        <v>13138.76</v>
       </c>
       <c r="F82" s="6">
-        <v>1</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>204</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G82" s="3"/>
       <c r="H82" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>205</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I82" s="3"/>
       <c r="J82" s="3"/>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D83" s="4">
-        <v>46190</v>
+        <v>46200</v>
       </c>
       <c r="E83" s="5">
-        <v>1219.44</v>
+        <v>12485</v>
       </c>
       <c r="F83" s="6">
-        <v>1</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G83" s="3"/>
       <c r="H83" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>208</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I83" s="3"/>
       <c r="J83" s="3"/>
     </row>
     <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D84" s="4">
-        <v>46190</v>
+        <v>46201</v>
       </c>
       <c r="E84" s="5">
-        <v>1409.18</v>
+        <v>2068</v>
       </c>
       <c r="F84" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="J84" s="3"/>
     </row>
     <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D85" s="4">
-        <v>46190</v>
+        <v>46201</v>
       </c>
       <c r="E85" s="5">
-        <v>1467.58</v>
+        <v>49153.88</v>
       </c>
       <c r="F85" s="6">
-        <v>1</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G85" s="3"/>
       <c r="H85" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>213</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="I85" s="3"/>
       <c r="J85" s="3"/>
     </row>
     <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D86" s="4">
-        <v>46190</v>
+        <v>46201</v>
       </c>
       <c r="E86" s="5">
-        <v>1971.6</v>
+        <v>7447.56</v>
       </c>
       <c r="F86" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="J86" s="3"/>
     </row>
     <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>10</v>
+        <v>185</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D87" s="4">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="E87" s="5">
-        <v>21985.58</v>
+        <v>3921.6</v>
       </c>
       <c r="F87" s="6">
         <v>1</v>
       </c>
-      <c r="G87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H87" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I87" s="3"/>
+        <v>188</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="J87" s="3"/>
     </row>
     <row r="88" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D88" s="4">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="E88" s="5">
-        <v>1562.6</v>
+        <v>5796.93</v>
       </c>
       <c r="F88" s="6">
         <v>1</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="J88" s="3"/>
+    </row>
+    <row r="89" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D89" s="4">
+        <v>46202</v>
+      </c>
+      <c r="E89" s="5">
+        <v>1797.94</v>
+      </c>
+      <c r="F89" s="6">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J89" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B8215F-DC0C-4D55-B9B4-C6A7AAC8E956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEB365F-7537-4D57-B1A3-F35D0F0675B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="217">
   <si>
     <t>Funcionário</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Cod.Pag-Banco</t>
   </si>
   <si>
-    <t>DANILO</t>
+    <t>DANILO - AL/SE/BA</t>
   </si>
   <si>
     <t>RB DISTRIBUIDORA DE PRODUTOS HOSPITALARES LTDA</t>
@@ -147,7 +147,7 @@
     <t>34191981300000873601090001107278120992717000</t>
   </si>
   <si>
-    <t>MARIO JR</t>
+    <t>MARIO JR - PE/PB/RN</t>
   </si>
   <si>
     <t>GLOBAL MEDIC LTDA</t>
@@ -216,7 +216,7 @@
     <t>34194986600001843881090001228218120992717000</t>
   </si>
   <si>
-    <t>SERGIO ROBERTO</t>
+    <t>SERGIO ROBERTO - PB</t>
   </si>
   <si>
     <t>RUBEM E MEDEIROS PRODUTOS PARA SAUDE LTDA</t>
@@ -375,7 +375,7 @@
     <t>34191107900003800001090001356908120992717000</t>
   </si>
   <si>
-    <t>MALCA</t>
+    <t>MALCA - CE</t>
   </si>
   <si>
     <t>AGILE DISTRIBUIDORA LTDA</t>
@@ -417,7 +417,7 @@
     <t>00193121400003663840000003473568000002940717</t>
   </si>
   <si>
-    <t>JOSEMAR</t>
+    <t>JOSEMAR - BA</t>
   </si>
   <si>
     <t>FOCUS - COMERCIO DE MEDICAMENTOS LTDA</t>
@@ -501,66 +501,27 @@
     <t>34199139500005466661090002533378120992717000</t>
   </si>
   <si>
+    <t>NOVA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006017.4</t>
+  </si>
+  <si>
+    <t>00191146500015028000000003473568000003058217</t>
+  </si>
+  <si>
+    <t>01006215.3</t>
+  </si>
+  <si>
+    <t>00198146600005183090000003473568000003086417</t>
+  </si>
+  <si>
+    <t>01006204.2</t>
+  </si>
+  <si>
     <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
   </si>
   <si>
-    <t>01006305.1</t>
-  </si>
-  <si>
-    <t>NOVA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006017.4</t>
-  </si>
-  <si>
-    <t>00191146500015028000000003473568000003058217</t>
-  </si>
-  <si>
-    <t>01006034.4</t>
-  </si>
-  <si>
-    <t>34194146600012096001090002555228120992717000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
-  </si>
-  <si>
-    <t>01006259.2</t>
-  </si>
-  <si>
-    <t>00193146600001971600000003473568000003085817</t>
-  </si>
-  <si>
-    <t>01006215.3</t>
-  </si>
-  <si>
-    <t>00198146600005183090000003473568000003086417</t>
-  </si>
-  <si>
-    <t>01006204.2</t>
-  </si>
-  <si>
-    <t>01006205.2</t>
-  </si>
-  <si>
-    <t>00194146700004193280000003473568000003078217</t>
-  </si>
-  <si>
-    <t>VWL DIST. DE MED. E MAT. MEDICO-HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>01006092.4</t>
-  </si>
-  <si>
-    <t>00192146800002625000000003473568000003064817</t>
-  </si>
-  <si>
-    <t>01006207.2</t>
-  </si>
-  <si>
-    <t>01006305.2</t>
-  </si>
-  <si>
     <t>01006305.3</t>
   </si>
   <si>
@@ -582,7 +543,7 @@
     <t>01006508.1</t>
   </si>
   <si>
-    <t>KELLEN</t>
+    <t>KELLEN - MA</t>
   </si>
   <si>
     <t>NM DISTRIBUIDORA E SERVICOS LTDA</t>
@@ -606,76 +567,115 @@
     <t>34195148500001254011090002579818120992717000</t>
   </si>
   <si>
+    <t>01006508.2</t>
+  </si>
+  <si>
+    <t>ASPEN SERVICE COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01006387.2</t>
+  </si>
+  <si>
+    <t>01006395.2</t>
+  </si>
+  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006515.1</t>
-  </si>
-  <si>
-    <t>34193148800001416241090002593268120992717000</t>
+    <t>01006515.2</t>
+  </si>
+  <si>
+    <t>34197149500001416241090002593348120992717000</t>
+  </si>
+  <si>
+    <t>R5 SOLUCOES EM SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>01006572.1</t>
+  </si>
+  <si>
+    <t>01006508.3</t>
+  </si>
+  <si>
+    <t>01006204.4</t>
+  </si>
+  <si>
+    <t>01006205.4</t>
+  </si>
+  <si>
+    <t>00191149700004193280000003473568000003078417</t>
+  </si>
+  <si>
+    <t>01006585.1</t>
+  </si>
+  <si>
+    <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006433.2</t>
+  </si>
+  <si>
+    <t>34198149700031531501090002588648120992717000</t>
+  </si>
+  <si>
+    <t>01006350.3</t>
+  </si>
+  <si>
+    <t>34191149900001254021090002579998120992717000</t>
+  </si>
+  <si>
+    <t>01006595.1</t>
+  </si>
+  <si>
+    <t>00191150000000689500000003473568000003117217</t>
+  </si>
+  <si>
+    <t>01006395.3</t>
+  </si>
+  <si>
+    <t>MARCOS DUTRA - PI</t>
+  </si>
+  <si>
+    <t>MAIS SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>01006494.3</t>
+  </si>
+  <si>
+    <t>PI</t>
   </si>
   <si>
     <t>L G PRODUTOS HOSPITALARES LTDA</t>
   </si>
   <si>
-    <t>01006470.2</t>
-  </si>
-  <si>
-    <t>01006508.2</t>
-  </si>
-  <si>
-    <t>ASPEN SERVICE COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01006387.2</t>
-  </si>
-  <si>
-    <t>01006395.2</t>
-  </si>
-  <si>
-    <t>PROMED DIST. DE MEDIC E PROD. PARA SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>01006538.1</t>
-  </si>
-  <si>
-    <t>00191149100002068000000003473568000003104717</t>
-  </si>
-  <si>
-    <t>L G MED DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006520.1</t>
-  </si>
-  <si>
-    <t>01006536.1</t>
-  </si>
-  <si>
-    <t>00195149100007447560000003473568000003104017</t>
-  </si>
-  <si>
-    <t>01006357.4</t>
-  </si>
-  <si>
-    <t>00195149200003921600000003473568000003090817</t>
-  </si>
-  <si>
-    <t>ESTRELA COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
-  </si>
-  <si>
-    <t>01006263.2</t>
-  </si>
-  <si>
-    <t>00194149200005796930000003473568000003087617</t>
-  </si>
-  <si>
-    <t>VIAMED LTDA</t>
-  </si>
-  <si>
-    <t>01006359.4</t>
-  </si>
-  <si>
-    <t>34199149200001797941090002579578120992717000</t>
+    <t>01006633.1</t>
+  </si>
+  <si>
+    <t>00194150200000904480000003473568000003122017</t>
+  </si>
+  <si>
+    <t>01006515.3</t>
+  </si>
+  <si>
+    <t>34199150200001416241090002593428120992717000</t>
+  </si>
+  <si>
+    <t>01006572.2</t>
+  </si>
+  <si>
+    <t>DAYCOVAL</t>
+  </si>
+  <si>
+    <t>01006577.1</t>
+  </si>
+  <si>
+    <t>00194150200001400750000003473568000003120817</t>
+  </si>
+  <si>
+    <t>01006625.1</t>
+  </si>
+  <si>
+    <t>00194150200002570400000003473568000003121217</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -1170,7 +1170,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1200,7 +1200,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
@@ -1230,7 +1230,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
@@ -1260,7 +1260,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>847</v>
+        <v>857</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
@@ -1290,7 +1290,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
@@ -1320,7 +1320,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
@@ -1350,7 +1350,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>21</v>
@@ -1380,7 +1380,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
@@ -1410,7 +1410,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
@@ -1440,7 +1440,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>13</v>
@@ -1470,7 +1470,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>13</v>
@@ -1500,7 +1500,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>13</v>
@@ -1530,7 +1530,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>13</v>
@@ -1560,7 +1560,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>13</v>
@@ -1590,7 +1590,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
@@ -1620,7 +1620,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>13</v>
@@ -1650,7 +1650,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
@@ -1680,7 +1680,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>13</v>
@@ -1710,7 +1710,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>13</v>
@@ -1740,7 +1740,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>13</v>
@@ -1770,7 +1770,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>13</v>
@@ -1800,7 +1800,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>13</v>
@@ -1830,7 +1830,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>13</v>
@@ -1860,7 +1860,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>21</v>
@@ -1890,7 +1890,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>13</v>
@@ -1920,7 +1920,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>21</v>
@@ -1950,7 +1950,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>21</v>
@@ -1980,7 +1980,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>13</v>
@@ -2010,7 +2010,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>13</v>
@@ -2040,7 +2040,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>13</v>
@@ -2070,7 +2070,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>21</v>
@@ -2100,7 +2100,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>13</v>
@@ -2130,7 +2130,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>13</v>
@@ -2160,7 +2160,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>13</v>
@@ -2190,7 +2190,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>13</v>
@@ -2220,7 +2220,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>13</v>
@@ -2250,7 +2250,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>13</v>
@@ -2280,7 +2280,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>13</v>
@@ -2310,7 +2310,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>13</v>
@@ -2340,7 +2340,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>13</v>
@@ -2370,7 +2370,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>13</v>
@@ -2400,7 +2400,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>13</v>
@@ -2430,7 +2430,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>21</v>
@@ -2460,7 +2460,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>21</v>
@@ -2490,7 +2490,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>21</v>
@@ -2520,7 +2520,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>21</v>
@@ -2550,7 +2550,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>21</v>
@@ -2580,7 +2580,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>21</v>
@@ -2610,7 +2610,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>21</v>
@@ -2640,7 +2640,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>21</v>
@@ -2670,7 +2670,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>21</v>
@@ -2700,7 +2700,7 @@
         <v>38840.89</v>
       </c>
       <c r="F53" s="6">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
@@ -2726,7 +2726,7 @@
         <v>4480</v>
       </c>
       <c r="F54" s="6">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>21</v>
@@ -2756,7 +2756,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2782,7 +2782,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2808,7 +2808,7 @@
         <v>27216.799999999999</v>
       </c>
       <c r="F57" s="6">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2834,7 +2834,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>21</v>
@@ -2864,7 +2864,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>21</v>
@@ -2894,7 +2894,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>21</v>
@@ -2924,7 +2924,7 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>13</v>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>158</v>
@@ -2948,45 +2948,49 @@
         <v>159</v>
       </c>
       <c r="D62" s="4">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E62" s="5">
-        <v>1034.3800000000001</v>
+        <v>15028</v>
       </c>
       <c r="F62" s="6">
-        <v>29</v>
-      </c>
-      <c r="G62" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H62" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I62" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="J62" s="3"/>
     </row>
     <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D63" s="4">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="E63" s="5">
-        <v>15028</v>
+        <v>5183.09</v>
       </c>
       <c r="F63" s="6">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>162</v>
@@ -2998,89 +3002,77 @@
         <v>10</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>163</v>
       </c>
       <c r="D64" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E64" s="5">
-        <v>12096</v>
+        <v>15716</v>
       </c>
       <c r="F64" s="6">
-        <v>27</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I64" s="3" t="s">
-        <v>164</v>
-      </c>
+      <c r="I64" s="3"/>
       <c r="J64" s="3"/>
     </row>
     <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="D65" s="4">
-        <v>46176</v>
+        <v>46188</v>
       </c>
       <c r="E65" s="5">
-        <v>1971.6</v>
+        <v>828.8</v>
       </c>
       <c r="F65" s="6">
-        <v>27</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G65" s="3"/>
       <c r="H65" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>167</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="I65" s="3"/>
       <c r="J65" s="3"/>
     </row>
     <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D66" s="4">
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="E66" s="5">
-        <v>5183.09</v>
+        <v>21985.58</v>
       </c>
       <c r="F66" s="6">
-        <v>27</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G66" s="3"/>
       <c r="H66" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I66" s="3"/>
       <c r="J66" s="3"/>
     </row>
     <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3088,25 +3080,29 @@
         <v>10</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D67" s="4">
-        <v>46177</v>
+        <v>46192</v>
       </c>
       <c r="E67" s="5">
-        <v>15716</v>
+        <v>4193.28</v>
       </c>
       <c r="F67" s="6">
-        <v>26</v>
-      </c>
-      <c r="G67" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H67" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="3"/>
+      <c r="I67" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="J67" s="3"/>
     </row>
     <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3114,135 +3110,135 @@
         <v>10</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D68" s="4">
-        <v>46177</v>
+        <v>46192</v>
       </c>
       <c r="E68" s="5">
-        <v>4193.28</v>
+        <v>15716</v>
       </c>
       <c r="F68" s="6">
-        <v>26</v>
-      </c>
-      <c r="G68" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I68" s="3" t="s">
-        <v>172</v>
-      </c>
+      <c r="I68" s="3"/>
       <c r="J68" s="3"/>
     </row>
     <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D69" s="4">
-        <v>46178</v>
+        <v>46192</v>
       </c>
       <c r="E69" s="5">
-        <v>2625</v>
+        <v>7494.53</v>
       </c>
       <c r="F69" s="6">
-        <v>25</v>
-      </c>
-      <c r="G69" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>175</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I69" s="3"/>
       <c r="J69" s="3"/>
     </row>
     <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C70" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D70" s="4">
+        <v>46194</v>
+      </c>
+      <c r="E70" s="5">
+        <v>2800</v>
+      </c>
+      <c r="F70" s="6">
+        <v>19</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D70" s="4">
-        <v>46179</v>
-      </c>
-      <c r="E70" s="5">
-        <v>3667.76</v>
-      </c>
-      <c r="F70" s="6">
-        <v>24</v>
-      </c>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I70" s="3"/>
       <c r="J70" s="3"/>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D71" s="4">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="E71" s="5">
-        <v>828.8</v>
+        <v>1254.01</v>
       </c>
       <c r="F71" s="6">
-        <v>22</v>
-      </c>
-      <c r="G71" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H71" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I71" s="3"/>
+      <c r="I71" s="3" t="s">
+        <v>179</v>
+      </c>
       <c r="J71" s="3"/>
     </row>
     <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D72" s="4">
-        <v>46188</v>
+        <v>46199</v>
       </c>
       <c r="E72" s="5">
-        <v>828.8</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="F72" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
@@ -3252,16 +3248,16 @@
         <v>10</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D73" s="4">
-        <v>46190</v>
+        <v>46200</v>
       </c>
       <c r="E73" s="5">
-        <v>21985.58</v>
+        <v>13138.76</v>
       </c>
       <c r="F73" s="6">
         <v>13</v>
@@ -3278,357 +3274,357 @@
         <v>10</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D74" s="4">
-        <v>46192</v>
+        <v>46200</v>
       </c>
       <c r="E74" s="5">
-        <v>4193.28</v>
+        <v>12485</v>
       </c>
       <c r="F74" s="6">
-        <v>11</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I74" s="3"/>
       <c r="J74" s="3"/>
     </row>
     <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D75" s="4">
-        <v>46192</v>
+        <v>46205</v>
       </c>
       <c r="E75" s="5">
-        <v>15716</v>
+        <v>1416.24</v>
       </c>
       <c r="F75" s="6">
-        <v>11</v>
-      </c>
-      <c r="G75" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H75" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I75" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="J75" s="3"/>
     </row>
     <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D76" s="4">
-        <v>46192</v>
+        <v>46205</v>
       </c>
       <c r="E76" s="5">
-        <v>7494.53</v>
+        <v>5574</v>
       </c>
       <c r="F76" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
     </row>
     <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D77" s="4">
-        <v>46194</v>
+        <v>46206</v>
       </c>
       <c r="E77" s="5">
-        <v>2800</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="F77" s="6">
-        <v>9</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>189</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I77" s="3"/>
       <c r="J77" s="3"/>
     </row>
     <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="D78" s="4">
-        <v>46195</v>
+        <v>46207</v>
       </c>
       <c r="E78" s="5">
-        <v>1254.01</v>
+        <v>15716</v>
       </c>
       <c r="F78" s="6">
-        <v>8</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G78" s="3"/>
       <c r="H78" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>192</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I78" s="3"/>
       <c r="J78" s="3"/>
     </row>
     <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D79" s="4">
-        <v>46198</v>
+        <v>46207</v>
       </c>
       <c r="E79" s="5">
-        <v>1416.24</v>
+        <v>4193.28</v>
       </c>
       <c r="F79" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J79" s="3"/>
     </row>
     <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D80" s="4">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="E80" s="5">
-        <v>4989.6000000000004</v>
+        <v>7049.25</v>
       </c>
       <c r="F80" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
     </row>
     <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D81" s="4">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="E81" s="5">
-        <v>4676.8500000000004</v>
+        <v>31531.5</v>
       </c>
       <c r="F81" s="6">
-        <v>4</v>
-      </c>
-      <c r="G81" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H81" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I81" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="J81" s="3"/>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D82" s="4">
-        <v>46200</v>
+        <v>46209</v>
       </c>
       <c r="E82" s="5">
-        <v>13138.76</v>
+        <v>1254.02</v>
       </c>
       <c r="F82" s="6">
-        <v>3</v>
-      </c>
-      <c r="G82" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H82" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I82" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="J82" s="3"/>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D83" s="4">
-        <v>46200</v>
+        <v>46210</v>
       </c>
       <c r="E83" s="5">
-        <v>12485</v>
+        <v>689.5</v>
       </c>
       <c r="F83" s="6">
         <v>3</v>
       </c>
-      <c r="G83" s="3"/>
+      <c r="G83" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H83" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I83" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="J83" s="3"/>
     </row>
     <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>185</v>
+        <v>10</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D84" s="4">
-        <v>46201</v>
+        <v>46210</v>
       </c>
       <c r="E84" s="5">
-        <v>2068</v>
+        <v>12485</v>
       </c>
       <c r="F84" s="6">
-        <v>2</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G84" s="3"/>
       <c r="H84" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>204</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I84" s="3"/>
       <c r="J84" s="3"/>
     </row>
     <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D85" s="4">
-        <v>46201</v>
+        <v>46212</v>
       </c>
       <c r="E85" s="5">
-        <v>49153.88</v>
+        <v>3126.32</v>
       </c>
       <c r="F85" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" s="3"/>
       <c r="H85" s="3" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
     </row>
     <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D86" s="4">
-        <v>46201</v>
+        <v>46212</v>
       </c>
       <c r="E86" s="5">
-        <v>7447.56</v>
+        <v>904.48</v>
       </c>
       <c r="F86" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>188</v>
+        <v>66</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>208</v>
@@ -3637,28 +3633,28 @@
     </row>
     <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>209</v>
       </c>
       <c r="D87" s="4">
-        <v>46202</v>
+        <v>46212</v>
       </c>
       <c r="E87" s="5">
-        <v>3921.6</v>
+        <v>1416.24</v>
       </c>
       <c r="F87" s="6">
         <v>1</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>188</v>
+        <v>66</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>210</v>
@@ -3667,63 +3663,91 @@
     </row>
     <row r="88" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="D88" s="4">
-        <v>46202</v>
+        <v>46212</v>
       </c>
       <c r="E88" s="5">
-        <v>5796.93</v>
+        <v>5574</v>
       </c>
       <c r="F88" s="6">
         <v>1</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>213</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="I88" s="3"/>
       <c r="J88" s="3"/>
     </row>
     <row r="89" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D89" s="4">
-        <v>46202</v>
+        <v>46212</v>
       </c>
       <c r="E89" s="5">
-        <v>1797.94</v>
+        <v>1400.75</v>
       </c>
       <c r="F89" s="6">
         <v>1</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I89" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J89" s="3"/>
+    </row>
+    <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D90" s="4">
+        <v>46212</v>
+      </c>
+      <c r="E90" s="5">
+        <v>2570.4</v>
+      </c>
+      <c r="F90" s="6">
+        <v>1</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I90" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="J89" s="3"/>
+      <c r="J90" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7708DF05-1B7F-4E69-960F-A0571B162890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="202">
   <si>
     <t>Funcionário</t>
   </si>
@@ -624,31 +636,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -667,14 +678,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -697,119 +702,381 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
-  <dimension ref="A1:J86"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J85"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
-    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
-    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
-    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
-    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="26.28515625" customWidth="true"/>
-    <col max="8" min="8" style="1" width="3.7109375" customWidth="true"/>
-    <col max="9" min="9" style="1" width="60.5703125" customWidth="true"/>
-    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
-    <col max="16384" min="11" style="1" width="12.140625"/>
+    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="60.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -841,7 +1108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -851,13 +1118,13 @@
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>45326</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>9391.78</v>
-      </c>
-      <c r="F2" s="6" t="n">
+      <c r="E2" s="5">
+        <v>9391.7800000000007</v>
+      </c>
+      <c r="F2" s="6">
         <v>901</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -871,7 +1138,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -881,13 +1148,13 @@
       <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>45346</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5">
         <v>5418</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="6">
         <v>881</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -901,7 +1168,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -911,13 +1178,13 @@
       <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>45350</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1264.87</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="E4" s="5">
+        <v>1264.8699999999999</v>
+      </c>
+      <c r="F4" s="6">
         <v>877</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -931,7 +1198,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -941,13 +1208,13 @@
       <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>45356</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5">
         <v>5418</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="6">
         <v>871</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -961,7 +1228,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -971,13 +1238,13 @@
       <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>45362</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5">
         <v>384</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="6">
         <v>865</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -991,7 +1258,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1001,13 +1268,13 @@
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>45364</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5">
         <v>816</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="6">
         <v>863</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1021,7 +1288,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1031,13 +1298,13 @@
       <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>45378</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5">
         <v>816</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="6">
         <v>849</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1051,7 +1318,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -1061,13 +1328,13 @@
       <c r="C9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>45463</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5">
         <v>1674.52</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="6">
         <v>764</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1081,7 +1348,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -1091,13 +1358,13 @@
       <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>45493</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5">
         <v>873.6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="6">
         <v>734</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -1111,7 +1378,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1121,13 +1388,13 @@
       <c r="C11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>45523</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5">
         <v>873.6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="6">
         <v>704</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -1141,7 +1408,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -1151,13 +1418,13 @@
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>45600</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5">
         <v>2000</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="6">
         <v>627</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1171,7 +1438,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>40</v>
       </c>
@@ -1181,13 +1448,13 @@
       <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>45607</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5">
         <v>3204.34</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="6">
         <v>620</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -1201,7 +1468,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1211,13 +1478,13 @@
       <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>45608</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F14" s="6">
         <v>619</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1231,7 +1498,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -1241,13 +1508,13 @@
       <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>45614</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="5">
         <v>2000</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="6">
         <v>613</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -1261,7 +1528,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
@@ -1271,13 +1538,13 @@
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>45615</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F16" s="6">
         <v>612</v>
       </c>
       <c r="G16" s="3" t="s">
@@ -1291,7 +1558,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -1301,13 +1568,13 @@
       <c r="C17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>45617</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="5">
         <v>1843.87</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="6">
         <v>610</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -1321,7 +1588,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
@@ -1331,13 +1598,13 @@
       <c r="C18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>45622</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F18" s="6" t="n">
+      <c r="E18" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F18" s="6">
         <v>605</v>
       </c>
       <c r="G18" s="3" t="s">
@@ -1351,7 +1618,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>46</v>
       </c>
@@ -1361,13 +1628,13 @@
       <c r="C19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>45622</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F19" s="6" t="n">
+      <c r="E19" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F19" s="6">
         <v>605</v>
       </c>
       <c r="G19" s="3" t="s">
@@ -1381,7 +1648,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
@@ -1391,13 +1658,13 @@
       <c r="C20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>45624</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="5">
         <v>1843.88</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="6">
         <v>603</v>
       </c>
       <c r="G20" s="3" t="s">
@@ -1411,7 +1678,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>63</v>
       </c>
@@ -1421,13 +1688,13 @@
       <c r="C21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>45688</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>1118.4</v>
-      </c>
-      <c r="F21" s="6" t="n">
+      <c r="E21" s="5">
+        <v>1118.4000000000001</v>
+      </c>
+      <c r="F21" s="6">
         <v>539</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -1441,7 +1708,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -1451,13 +1718,13 @@
       <c r="C22" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>45695</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="6">
         <v>532</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -1471,7 +1738,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -1481,13 +1748,13 @@
       <c r="C23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>45699</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="5">
         <v>2330</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="6">
         <v>528</v>
       </c>
       <c r="G23" s="3" t="s">
@@ -1501,7 +1768,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -1511,13 +1778,13 @@
       <c r="C24" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>45702</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="6">
         <v>525</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -1531,7 +1798,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
@@ -1541,13 +1808,13 @@
       <c r="C25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>45705</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="5">
         <v>2541</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="6">
         <v>522</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -1561,7 +1828,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
@@ -1571,13 +1838,13 @@
       <c r="C26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>45709</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="6">
         <v>518</v>
       </c>
       <c r="G26" s="3" t="s">
@@ -1591,7 +1858,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>40</v>
       </c>
@@ -1601,13 +1868,13 @@
       <c r="C27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>45712</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="5">
         <v>2541</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="6">
         <v>515</v>
       </c>
       <c r="G27" s="3" t="s">
@@ -1621,7 +1888,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
@@ -1631,13 +1898,13 @@
       <c r="C28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>45726</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="5">
         <v>2541</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="6">
         <v>501</v>
       </c>
       <c r="G28" s="3" t="s">
@@ -1651,7 +1918,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
@@ -1661,13 +1928,13 @@
       <c r="C29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4">
         <v>45727</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="6">
         <v>500</v>
       </c>
       <c r="G29" s="3" t="s">
@@ -1681,7 +1948,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
@@ -1691,13 +1958,13 @@
       <c r="C30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>45734</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="6">
         <v>493</v>
       </c>
       <c r="G30" s="3" t="s">
@@ -1711,7 +1978,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>46</v>
       </c>
@@ -1721,13 +1988,13 @@
       <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>45734</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="6">
         <v>493</v>
       </c>
       <c r="G31" s="3" t="s">
@@ -1741,7 +2008,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -1751,13 +2018,13 @@
       <c r="C32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>45740</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="5">
         <v>2541</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="6">
         <v>487</v>
       </c>
       <c r="G32" s="3" t="s">
@@ -1771,7 +2038,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -1781,13 +2048,13 @@
       <c r="C33" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>45741</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="6">
         <v>486</v>
       </c>
       <c r="G33" s="3" t="s">
@@ -1801,7 +2068,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>46</v>
       </c>
@@ -1811,13 +2078,13 @@
       <c r="C34" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>45741</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="6">
         <v>486</v>
       </c>
       <c r="G34" s="3" t="s">
@@ -1831,7 +2098,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>46</v>
       </c>
@@ -1841,13 +2108,13 @@
       <c r="C35" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4">
         <v>45748</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="6">
         <v>479</v>
       </c>
       <c r="G35" s="3" t="s">
@@ -1861,7 +2128,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>40</v>
       </c>
@@ -1871,13 +2138,13 @@
       <c r="C36" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4">
         <v>45748</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="5">
         <v>7562.76</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="6">
         <v>479</v>
       </c>
       <c r="G36" s="3" t="s">
@@ -1891,7 +2158,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
@@ -1901,13 +2168,13 @@
       <c r="C37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4">
         <v>45755</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="6">
         <v>472</v>
       </c>
       <c r="G37" s="3" t="s">
@@ -1921,7 +2188,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>46</v>
       </c>
@@ -1931,13 +2198,13 @@
       <c r="C38" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="4">
         <v>45761</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="5">
         <v>6169.53</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="6">
         <v>466</v>
       </c>
       <c r="G38" s="3" t="s">
@@ -1951,7 +2218,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>46</v>
       </c>
@@ -1961,13 +2228,13 @@
       <c r="C39" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="4">
         <v>45768</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="5">
         <v>3850</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="6">
         <v>459</v>
       </c>
       <c r="G39" s="3" t="s">
@@ -1981,7 +2248,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>46</v>
       </c>
@@ -1991,13 +2258,13 @@
       <c r="C40" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="4">
         <v>45775</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="5">
         <v>3850</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="6">
         <v>452</v>
       </c>
       <c r="G40" s="3" t="s">
@@ -2011,7 +2278,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>46</v>
       </c>
@@ -2021,13 +2288,13 @@
       <c r="C41" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="4">
         <v>45775</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="5">
         <v>6089.41</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="6">
         <v>452</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -2041,7 +2308,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>46</v>
       </c>
@@ -2051,13 +2318,13 @@
       <c r="C42" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="4">
         <v>45782</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="5">
         <v>3800</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="6">
         <v>445</v>
       </c>
       <c r="G42" s="3" t="s">
@@ -2071,7 +2338,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>46</v>
       </c>
@@ -2081,13 +2348,13 @@
       <c r="C43" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="4">
         <v>45789</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="5">
         <v>3800</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="6">
         <v>438</v>
       </c>
       <c r="G43" s="3" t="s">
@@ -2101,7 +2368,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>116</v>
       </c>
@@ -2111,13 +2378,13 @@
       <c r="C44" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="4">
         <v>45789</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="5">
         <v>1143.54</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="6">
         <v>438</v>
       </c>
       <c r="G44" s="3" t="s">
@@ -2131,7 +2398,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>116</v>
       </c>
@@ -2141,13 +2408,13 @@
       <c r="C45" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="4">
         <v>45796</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="5">
         <v>2287.06</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="6">
         <v>431</v>
       </c>
       <c r="G45" s="3" t="s">
@@ -2161,7 +2428,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
@@ -2171,13 +2438,13 @@
       <c r="C46" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="4">
         <v>45896</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="5">
         <v>4572.62</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="6">
         <v>331</v>
       </c>
       <c r="G46" s="3" t="s">
@@ -2191,7 +2458,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
@@ -2201,13 +2468,13 @@
       <c r="C47" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="4">
         <v>45910</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="6">
         <v>317</v>
       </c>
       <c r="G47" s="3" t="s">
@@ -2221,7 +2488,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>40</v>
       </c>
@@ -2231,13 +2498,13 @@
       <c r="C48" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="4">
         <v>45924</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="6">
         <v>303</v>
       </c>
       <c r="G48" s="3" t="s">
@@ -2251,7 +2518,7 @@
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>130</v>
       </c>
@@ -2261,13 +2528,13 @@
       <c r="C49" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="4">
         <v>45947</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="5">
         <v>3867.34</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="6">
         <v>280</v>
       </c>
       <c r="G49" s="3" t="s">
@@ -2281,7 +2548,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
@@ -2291,13 +2558,13 @@
       <c r="C50" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="4">
         <v>45954</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="6">
         <v>273</v>
       </c>
       <c r="G50" s="3" t="s">
@@ -2311,7 +2578,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>130</v>
       </c>
@@ -2321,13 +2588,13 @@
       <c r="C51" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="4">
         <v>45961</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F51" s="6">
         <v>266</v>
       </c>
       <c r="G51" s="3" t="s">
@@ -2341,7 +2608,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>130</v>
       </c>
@@ -2351,13 +2618,13 @@
       <c r="C52" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="4">
         <v>45968</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F52" s="6">
         <v>259</v>
       </c>
       <c r="G52" s="3" t="s">
@@ -2371,7 +2638,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>116</v>
       </c>
@@ -2381,13 +2648,13 @@
       <c r="C53" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="4">
         <v>45980</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E53" s="5">
         <v>4480</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F53" s="6">
         <v>247</v>
       </c>
       <c r="G53" s="3" t="s">
@@ -2401,7 +2668,7 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>130</v>
       </c>
@@ -2411,13 +2678,13 @@
       <c r="C54" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="4">
         <v>45980</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E54" s="5">
         <v>38840.89</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F54" s="6">
         <v>247</v>
       </c>
       <c r="G54" s="3"/>
@@ -2427,7 +2694,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>130</v>
       </c>
@@ -2437,13 +2704,13 @@
       <c r="C55" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="4">
         <v>45987</v>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>33844.16</v>
-      </c>
-      <c r="F55" s="6" t="n">
+      <c r="E55" s="5">
+        <v>33844.160000000003</v>
+      </c>
+      <c r="F55" s="6">
         <v>240</v>
       </c>
       <c r="G55" s="3"/>
@@ -2453,7 +2720,7 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>116</v>
       </c>
@@ -2463,13 +2730,13 @@
       <c r="C56" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="4">
         <v>45989</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="5">
         <v>3220</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F56" s="6">
         <v>238</v>
       </c>
       <c r="G56" s="3"/>
@@ -2479,7 +2746,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>130</v>
       </c>
@@ -2489,13 +2756,13 @@
       <c r="C57" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="4">
         <v>45994</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="5">
         <v>14483.06</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="6">
         <v>233</v>
       </c>
       <c r="G57" s="3"/>
@@ -2505,7 +2772,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2515,13 +2782,13 @@
       <c r="C58" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="4">
         <v>46090</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="5">
         <v>806.34</v>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F58" s="6">
         <v>137</v>
       </c>
       <c r="G58" s="3" t="s">
@@ -2535,7 +2802,7 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>18</v>
       </c>
@@ -2545,13 +2812,13 @@
       <c r="C59" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="4">
         <v>46097</v>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E59" s="5">
         <v>503.28</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F59" s="6">
         <v>130</v>
       </c>
       <c r="G59" s="3" t="s">
@@ -2565,7 +2832,7 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>18</v>
       </c>
@@ -2575,13 +2842,13 @@
       <c r="C60" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="4">
         <v>46104</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="5">
         <v>503.28</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F60" s="6">
         <v>123</v>
       </c>
       <c r="G60" s="3" t="s">
@@ -2595,7 +2862,7 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>10</v>
       </c>
@@ -2605,13 +2872,13 @@
       <c r="C61" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="4">
         <v>46105</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="5">
         <v>5466.66</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F61" s="6">
         <v>122</v>
       </c>
       <c r="G61" s="3" t="s">
@@ -2625,7 +2892,7 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>10</v>
       </c>
@@ -2635,13 +2902,13 @@
       <c r="C62" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="4">
         <v>46175</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E62" s="5">
         <v>15028</v>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F62" s="6">
         <v>52</v>
       </c>
       <c r="G62" s="3" t="s">
@@ -2655,7 +2922,7 @@
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>130</v>
       </c>
@@ -2665,13 +2932,13 @@
       <c r="C63" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="4">
         <v>46176</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="5">
         <v>5183.09</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="6">
         <v>51</v>
       </c>
       <c r="G63" s="3" t="s">
@@ -2685,7 +2952,7 @@
       </c>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>10</v>
       </c>
@@ -2695,13 +2962,13 @@
       <c r="C64" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="4">
         <v>46177</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="5">
         <v>15716</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="6">
         <v>50</v>
       </c>
       <c r="G64" s="3"/>
@@ -2711,7 +2978,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>10</v>
       </c>
@@ -2721,13 +2988,13 @@
       <c r="C65" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="4">
         <v>46192</v>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E65" s="5">
         <v>15716</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="6">
         <v>35</v>
       </c>
       <c r="G65" s="3"/>
@@ -2737,7 +3004,7 @@
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>10</v>
       </c>
@@ -2747,13 +3014,13 @@
       <c r="C66" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="4">
         <v>46192</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="5">
         <v>4193.28</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="F66" s="6">
         <v>35</v>
       </c>
       <c r="G66" s="3" t="s">
@@ -2767,7 +3034,7 @@
       </c>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>130</v>
       </c>
@@ -2777,13 +3044,13 @@
       <c r="C67" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="4">
         <v>46192</v>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E67" s="5">
         <v>7494.53</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" s="6">
         <v>35</v>
       </c>
       <c r="G67" s="3"/>
@@ -2793,7 +3060,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>18</v>
       </c>
@@ -2803,13 +3070,13 @@
       <c r="C68" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="4">
         <v>46195</v>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E68" s="5">
         <v>1254.01</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" s="6">
         <v>32</v>
       </c>
       <c r="G68" s="3" t="s">
@@ -2823,7 +3090,7 @@
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>130</v>
       </c>
@@ -2833,13 +3100,13 @@
       <c r="C69" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="4">
         <v>46199</v>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="F69" s="6" t="n">
+      <c r="E69" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="F69" s="6">
         <v>28</v>
       </c>
       <c r="G69" s="3"/>
@@ -2849,7 +3116,7 @@
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>10</v>
       </c>
@@ -2859,13 +3126,13 @@
       <c r="C70" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="4">
         <v>46200</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="5">
         <v>13138.76</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="F70" s="6">
         <v>27</v>
       </c>
       <c r="G70" s="3"/>
@@ -2875,7 +3142,7 @@
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>130</v>
       </c>
@@ -2885,13 +3152,13 @@
       <c r="C71" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="4">
         <v>46206</v>
       </c>
-      <c r="E71" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="F71" s="6" t="n">
+      <c r="E71" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="F71" s="6">
         <v>21</v>
       </c>
       <c r="G71" s="3"/>
@@ -2901,7 +3168,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>10</v>
       </c>
@@ -2911,13 +3178,13 @@
       <c r="C72" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="4">
         <v>46207</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E72" s="5">
         <v>4193.28</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="6">
         <v>20</v>
       </c>
       <c r="G72" s="3" t="s">
@@ -2931,7 +3198,7 @@
       </c>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>10</v>
       </c>
@@ -2941,13 +3208,13 @@
       <c r="C73" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="4">
         <v>46207</v>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="5">
         <v>7049.25</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" s="6">
         <v>20</v>
       </c>
       <c r="G73" s="3"/>
@@ -2957,7 +3224,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>10</v>
       </c>
@@ -2967,13 +3234,13 @@
       <c r="C74" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="4">
         <v>46207</v>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E74" s="5">
         <v>15716</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="6">
         <v>20</v>
       </c>
       <c r="G74" s="3"/>
@@ -2983,7 +3250,7 @@
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>18</v>
       </c>
@@ -2993,13 +3260,13 @@
       <c r="C75" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="4">
         <v>46209</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E75" s="5">
         <v>1254.02</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="F75" s="6">
         <v>18</v>
       </c>
       <c r="G75" s="3" t="s">
@@ -3013,7 +3280,7 @@
       </c>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>10</v>
       </c>
@@ -3023,13 +3290,13 @@
       <c r="C76" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="4">
         <v>46210</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="5">
         <v>12485</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="6">
         <v>17</v>
       </c>
       <c r="G76" s="3"/>
@@ -3039,7 +3306,7 @@
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>10</v>
       </c>
@@ -3049,13 +3316,13 @@
       <c r="C77" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="4">
         <v>46215</v>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="E77" s="5">
         <v>13138.76</v>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="F77" s="6">
         <v>12</v>
       </c>
       <c r="G77" s="3"/>
@@ -3065,7 +3332,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>184</v>
       </c>
@@ -3075,13 +3342,13 @@
       <c r="C78" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="4">
         <v>46219</v>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E78" s="5">
         <v>3126.32</v>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="F78" s="6">
         <v>8</v>
       </c>
       <c r="G78" s="3"/>
@@ -3091,7 +3358,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
     </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>10</v>
       </c>
@@ -3101,13 +3368,13 @@
       <c r="C79" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="4">
         <v>46220</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E79" s="5">
         <v>12485</v>
       </c>
-      <c r="F79" s="6" t="n">
+      <c r="F79" s="6">
         <v>7</v>
       </c>
       <c r="G79" s="3"/>
@@ -3117,7 +3384,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>18</v>
       </c>
@@ -3127,13 +3394,13 @@
       <c r="C80" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="4">
         <v>46220</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="E80" s="5">
         <v>526.24</v>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="F80" s="6">
         <v>7</v>
       </c>
       <c r="G80" s="3" t="s">
@@ -3147,7 +3414,7 @@
       </c>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>18</v>
       </c>
@@ -3157,13 +3424,13 @@
       <c r="C81" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" s="4">
         <v>46222</v>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E81" s="5">
         <v>31531.5</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="F81" s="6">
         <v>5</v>
       </c>
       <c r="G81" s="3" t="s">
@@ -3177,7 +3444,7 @@
       </c>
       <c r="J81" s="3"/>
     </row>
-    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>10</v>
       </c>
@@ -3187,13 +3454,13 @@
       <c r="C82" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="4">
         <v>46222</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E82" s="5">
         <v>3996.72</v>
       </c>
-      <c r="F82" s="6" t="n">
+      <c r="F82" s="6">
         <v>5</v>
       </c>
       <c r="G82" s="3"/>
@@ -3203,7 +3470,7 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>18</v>
       </c>
@@ -3213,13 +3480,13 @@
       <c r="C83" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="D83" s="4">
         <v>46223</v>
       </c>
-      <c r="E83" s="5" t="n">
+      <c r="E83" s="5">
         <v>1400</v>
       </c>
-      <c r="F83" s="6" t="n">
+      <c r="F83" s="6">
         <v>4</v>
       </c>
       <c r="G83" s="3" t="s">
@@ -3233,7 +3500,7 @@
       </c>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>18</v>
       </c>
@@ -3243,13 +3510,13 @@
       <c r="C84" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="D84" s="4">
         <v>46224</v>
       </c>
-      <c r="E84" s="5" t="n">
+      <c r="E84" s="5">
         <v>689.5</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" s="6">
         <v>3</v>
       </c>
       <c r="G84" s="3" t="s">
@@ -3263,7 +3530,7 @@
       </c>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>184</v>
       </c>
@@ -3273,13 +3540,13 @@
       <c r="C85" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" s="4">
         <v>46226</v>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E85" s="5">
         <v>3126.32</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F85" s="6">
         <v>1</v>
       </c>
       <c r="G85" s="3"/>
@@ -3289,21 +3556,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
     </row>
-    <row r="86" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A86" s="7"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="9" t="n">
-        <v>460642.02</v>
-      </c>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="10"/>
-    </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7708DF05-1B7F-4E69-960F-A0571B162890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FA6418-495E-43CC-82D1-F495B83E1B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="208">
   <si>
     <t>Funcionário</t>
   </si>
@@ -531,24 +531,9 @@
     <t>01006508.1</t>
   </si>
   <si>
-    <t>CAMEDIC COMERCIAL E SERVIÇOS DE PROD MED HOSP EIRE</t>
-  </si>
-  <si>
-    <t>01006350.2</t>
-  </si>
-  <si>
-    <t>34195148500001254011090002579818120992717000</t>
-  </si>
-  <si>
     <t>01006508.2</t>
   </si>
   <si>
-    <t>ASPEN SERVICE COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01006387.2</t>
-  </si>
-  <si>
     <t>01006508.3</t>
   </si>
   <si>
@@ -564,73 +549,106 @@
     <t>01006204.4</t>
   </si>
   <si>
-    <t>01006350.3</t>
-  </si>
-  <si>
-    <t>34191149900001254021090002579998120992717000</t>
+    <t>01006585.2</t>
+  </si>
+  <si>
+    <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>01006433.3</t>
+  </si>
+  <si>
+    <t>34193151200031531501090002588728120992717000</t>
+  </si>
+  <si>
+    <t>01006681.1</t>
+  </si>
+  <si>
+    <t>DAYCOVAL</t>
+  </si>
+  <si>
+    <t>70793151800003516480001121205064100656760355</t>
+  </si>
+  <si>
+    <t>ESTRELA COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01006263.3</t>
+  </si>
+  <si>
+    <t>00195152300005796940000003473568000003087717</t>
   </si>
   <si>
     <t>JMC COMERCIAL LTDA</t>
   </si>
   <si>
-    <t>01006395.3</t>
-  </si>
-  <si>
-    <t>01006387.3</t>
+    <t>01006580.3</t>
+  </si>
+  <si>
+    <t>BRADESCO</t>
+  </si>
+  <si>
+    <t>23792152500002520200435090000000103200304920</t>
+  </si>
+  <si>
+    <t>FLEX HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>01006586.4</t>
+  </si>
+  <si>
+    <t>00191152700011700000000003473568000003114517</t>
+  </si>
+  <si>
+    <t>01006585.3</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01006718.3</t>
+  </si>
+  <si>
+    <t>70791152700001400000001121205064100656761015</t>
+  </si>
+  <si>
+    <t>MULTIMAIS ATACADO LTDA</t>
+  </si>
+  <si>
+    <t>01006782.2</t>
+  </si>
+  <si>
+    <t>70791152800002400000001121205064100656762856</t>
   </si>
   <si>
     <t>MARCOS DUTRA - PI</t>
   </si>
   <si>
-    <t>MAIS SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>01006494.4</t>
+    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006753.2</t>
   </si>
   <si>
     <t>PI</t>
   </si>
   <si>
-    <t>01006395.4</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01006645.1</t>
-  </si>
-  <si>
-    <t>DAYCOVAL</t>
-  </si>
-  <si>
-    <t>70795151000000526240001121205064100656760637</t>
-  </si>
-  <si>
-    <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>01006433.3</t>
-  </si>
-  <si>
-    <t>34193151200031531501090002588728120992717000</t>
-  </si>
-  <si>
-    <t>01006585.2</t>
-  </si>
-  <si>
-    <t>01006718.1</t>
-  </si>
-  <si>
-    <t>70791151300001400000001121205064100656760991</t>
-  </si>
-  <si>
-    <t>01006595.3</t>
-  </si>
-  <si>
-    <t>00199151400000689500000003473568000003117417</t>
-  </si>
-  <si>
-    <t>01006494.5</t>
+    <t>00191152800000860000000003473568000003128717</t>
+  </si>
+  <si>
+    <t>MONTALVAO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01006713.2</t>
+  </si>
+  <si>
+    <t>70797152800003300000001121205064100656761239</t>
+  </si>
+  <si>
+    <t>01006816.1</t>
+  </si>
+  <si>
+    <t>00191152900002754000000003473568000003132917</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -1125,7 +1143,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>901</v>
+        <v>915</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1155,7 +1173,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>881</v>
+        <v>895</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
@@ -1185,7 +1203,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>877</v>
+        <v>891</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
@@ -1215,7 +1233,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
@@ -1245,7 +1263,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>865</v>
+        <v>879</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
@@ -1275,7 +1293,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
@@ -1305,7 +1323,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>21</v>
@@ -1335,7 +1353,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
@@ -1365,7 +1383,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>734</v>
+        <v>748</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
@@ -1395,7 +1413,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>13</v>
@@ -1425,7 +1443,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>627</v>
+        <v>641</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>13</v>
@@ -1455,7 +1473,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>13</v>
@@ -1485,7 +1503,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>619</v>
+        <v>633</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>13</v>
@@ -1515,7 +1533,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>13</v>
@@ -1545,7 +1563,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
@@ -1575,7 +1593,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>13</v>
@@ -1605,7 +1623,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
@@ -1635,7 +1653,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>13</v>
@@ -1665,7 +1683,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>13</v>
@@ -1695,7 +1713,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>13</v>
@@ -1725,7 +1743,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>13</v>
@@ -1755,7 +1773,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>13</v>
@@ -1785,7 +1803,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>13</v>
@@ -1815,7 +1833,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>21</v>
@@ -1845,7 +1863,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>13</v>
@@ -1875,7 +1893,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>21</v>
@@ -1905,7 +1923,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>21</v>
@@ -1935,7 +1953,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>13</v>
@@ -1965,7 +1983,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>13</v>
@@ -1995,7 +2013,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>13</v>
@@ -2025,7 +2043,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>21</v>
@@ -2055,7 +2073,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>13</v>
@@ -2085,7 +2103,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>13</v>
@@ -2115,7 +2133,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>13</v>
@@ -2145,7 +2163,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>13</v>
@@ -2175,7 +2193,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>13</v>
@@ -2205,7 +2223,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>13</v>
@@ -2235,7 +2253,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>13</v>
@@ -2265,7 +2283,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>13</v>
@@ -2295,7 +2313,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>13</v>
@@ -2325,7 +2343,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>13</v>
@@ -2355,7 +2373,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>13</v>
@@ -2385,7 +2403,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>21</v>
@@ -2415,7 +2433,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>21</v>
@@ -2445,7 +2463,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>21</v>
@@ -2475,7 +2493,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>21</v>
@@ -2505,7 +2523,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>21</v>
@@ -2535,7 +2553,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>21</v>
@@ -2565,7 +2583,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>21</v>
@@ -2595,7 +2613,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>21</v>
@@ -2625,7 +2643,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>21</v>
@@ -2655,7 +2673,7 @@
         <v>4480</v>
       </c>
       <c r="F53" s="6">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>21</v>
@@ -2685,7 +2703,7 @@
         <v>38840.89</v>
       </c>
       <c r="F54" s="6">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
@@ -2711,7 +2729,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2737,7 +2755,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2763,7 +2781,7 @@
         <v>14483.06</v>
       </c>
       <c r="F57" s="6">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2789,7 +2807,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>21</v>
@@ -2819,7 +2837,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>21</v>
@@ -2849,7 +2867,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>21</v>
@@ -2879,7 +2897,7 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>13</v>
@@ -2909,7 +2927,7 @@
         <v>15028</v>
       </c>
       <c r="F62" s="6">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>21</v>
@@ -2939,7 +2957,7 @@
         <v>5183.09</v>
       </c>
       <c r="F63" s="6">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>21</v>
@@ -2969,7 +2987,7 @@
         <v>15716</v>
       </c>
       <c r="F64" s="6">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
@@ -2995,7 +3013,7 @@
         <v>15716</v>
       </c>
       <c r="F65" s="6">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3" t="s">
@@ -3021,7 +3039,7 @@
         <v>4193.28</v>
       </c>
       <c r="F66" s="6">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>21</v>
@@ -3051,7 +3069,7 @@
         <v>7494.53</v>
       </c>
       <c r="F67" s="6">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
@@ -3062,32 +3080,28 @@
     </row>
     <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="D68" s="4">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="E68" s="5">
-        <v>1254.01</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="F68" s="6">
-        <v>32</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>170</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="I68" s="3"/>
       <c r="J68" s="3"/>
     </row>
     <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3098,16 +3112,16 @@
         <v>143</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D69" s="4">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="E69" s="5">
         <v>4676.8500000000004</v>
       </c>
       <c r="F69" s="6">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
@@ -3121,49 +3135,53 @@
         <v>10</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D70" s="4">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="E70" s="5">
-        <v>13138.76</v>
+        <v>4193.28</v>
       </c>
       <c r="F70" s="6">
-        <v>27</v>
-      </c>
-      <c r="G70" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H70" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I70" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="J70" s="3"/>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D71" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E71" s="5">
-        <v>4676.8500000000004</v>
+        <v>7049.25</v>
       </c>
       <c r="F71" s="6">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
@@ -3176,26 +3194,22 @@
         <v>158</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D72" s="4">
         <v>46207</v>
       </c>
       <c r="E72" s="5">
-        <v>4193.28</v>
+        <v>15716</v>
       </c>
       <c r="F72" s="6">
-        <v>20</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>176</v>
-      </c>
+      <c r="I72" s="3"/>
       <c r="J72" s="3"/>
     </row>
     <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3206,16 +3220,16 @@
         <v>158</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D73" s="4">
-        <v>46207</v>
+        <v>46222</v>
       </c>
       <c r="E73" s="5">
-        <v>7049.25</v>
+        <v>3996.72</v>
       </c>
       <c r="F73" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3" t="s">
@@ -3226,28 +3240,32 @@
     </row>
     <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D74" s="4">
-        <v>46207</v>
+        <v>46222</v>
       </c>
       <c r="E74" s="5">
-        <v>15716</v>
+        <v>31531.5</v>
       </c>
       <c r="F74" s="6">
-        <v>20</v>
-      </c>
-      <c r="G74" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H74" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I74" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="J74" s="3"/>
     </row>
     <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3255,22 +3273,22 @@
         <v>18</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D75" s="4">
+        <v>46228</v>
+      </c>
+      <c r="E75" s="5">
+        <v>3516.48</v>
+      </c>
+      <c r="F75" s="6">
+        <v>13</v>
+      </c>
+      <c r="G75" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="D75" s="4">
-        <v>46209</v>
-      </c>
-      <c r="E75" s="5">
-        <v>1254.02</v>
-      </c>
-      <c r="F75" s="6">
-        <v>18</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>66</v>
@@ -3291,19 +3309,23 @@
         <v>182</v>
       </c>
       <c r="D76" s="4">
-        <v>46210</v>
+        <v>46233</v>
       </c>
       <c r="E76" s="5">
-        <v>12485</v>
+        <v>5796.94</v>
       </c>
       <c r="F76" s="6">
-        <v>17</v>
-      </c>
-      <c r="G76" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H76" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I76" s="3"/>
+      <c r="I76" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="J76" s="3"/>
     </row>
     <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3311,51 +3333,59 @@
         <v>10</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D77" s="4">
-        <v>46215</v>
+        <v>46235</v>
       </c>
       <c r="E77" s="5">
-        <v>13138.76</v>
+        <v>2520.1999999999998</v>
       </c>
       <c r="F77" s="6">
-        <v>12</v>
-      </c>
-      <c r="G77" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="H77" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I77" s="3"/>
+      <c r="I77" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="J77" s="3"/>
     </row>
     <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>184</v>
+        <v>10</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D78" s="4">
-        <v>46219</v>
+        <v>46237</v>
       </c>
       <c r="E78" s="5">
-        <v>3126.32</v>
+        <v>11700</v>
       </c>
       <c r="F78" s="6">
-        <v>8</v>
-      </c>
-      <c r="G78" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H78" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="I78" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="J78" s="3"/>
     </row>
     <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3363,23 +3393,23 @@
         <v>10</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D79" s="4">
-        <v>46220</v>
+        <v>46237</v>
       </c>
       <c r="E79" s="5">
-        <v>12485</v>
+        <v>3996.72</v>
       </c>
       <c r="F79" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
@@ -3389,114 +3419,118 @@
         <v>18</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D80" s="4">
-        <v>46220</v>
+        <v>46237</v>
       </c>
       <c r="E80" s="5">
-        <v>526.24</v>
+        <v>1400</v>
       </c>
       <c r="F80" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>66</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J80" s="3"/>
     </row>
     <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D81" s="4">
-        <v>46222</v>
+        <v>46238</v>
       </c>
       <c r="E81" s="5">
-        <v>31531.5</v>
+        <v>2400</v>
       </c>
       <c r="F81" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>13</v>
+        <v>179</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J81" s="3"/>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D82" s="4">
-        <v>46222</v>
+        <v>46238</v>
       </c>
       <c r="E82" s="5">
-        <v>3996.72</v>
+        <v>860</v>
       </c>
       <c r="F82" s="6">
-        <v>5</v>
-      </c>
-      <c r="G82" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H82" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I82" s="3"/>
+        <v>201</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="J82" s="3"/>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D83" s="4">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="E83" s="5">
-        <v>1400</v>
+        <v>3300</v>
       </c>
       <c r="F83" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="J83" s="3"/>
     </row>
@@ -3505,19 +3539,19 @@
         <v>18</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D84" s="4">
-        <v>46224</v>
+        <v>46239</v>
       </c>
       <c r="E84" s="5">
-        <v>689.5</v>
+        <v>2754</v>
       </c>
       <c r="F84" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>21</v>
@@ -3526,35 +3560,9 @@
         <v>66</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="J84" s="3"/>
-    </row>
-    <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D85" s="4">
-        <v>46226</v>
-      </c>
-      <c r="E85" s="5">
-        <v>3126.32</v>
-      </c>
-      <c r="F85" s="6">
-        <v>1</v>
-      </c>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,31 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FA6418-495E-43CC-82D1-F495B83E1B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr refMode="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
   <si>
     <t>Funcionário</t>
   </si>
@@ -510,12 +498,6 @@
     <t>00191146500015028000000003473568000003058217</t>
   </si>
   <si>
-    <t>01006215.3</t>
-  </si>
-  <si>
-    <t>00198146600005183090000003473568000003086417</t>
-  </si>
-  <si>
     <t>01006204.2</t>
   </si>
   <si>
@@ -591,15 +573,6 @@
     <t>23792152500002520200435090000000103200304920</t>
   </si>
   <si>
-    <t>FLEX HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006586.4</t>
-  </si>
-  <si>
-    <t>00191152700011700000000003473568000003114517</t>
-  </si>
-  <si>
     <t>01006585.3</t>
   </si>
   <si>
@@ -649,35 +622,42 @@
   </si>
   <si>
     <t>00191152900002754000000003473568000003132917</t>
+  </si>
+  <si>
+    <t>01005217.6</t>
+  </si>
+  <si>
+    <t>23792153100010174450435090000000107600304920</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
+    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -696,8 +676,14 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -720,381 +706,119 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA0A0A0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA0A0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+  <cellXfs count="11">
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
+      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
+      <protection hidden="false" locked="true"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
   <dimension ref="A1:J84"/>
-  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="60.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.140625" style="1"/>
+    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
+    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
+    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
+    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
+    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
+    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
+    <col max="7" min="7" style="1" width="26.28515625" customWidth="true"/>
+    <col max="8" min="8" style="1" width="3.7109375" customWidth="true"/>
+    <col max="9" min="9" style="1" width="60.5703125" customWidth="true"/>
+    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
+    <col max="16384" min="11" style="1" width="12.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1126,7 +850,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1136,14 +860,14 @@
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="4" t="n">
         <v>45326</v>
       </c>
-      <c r="E2" s="5">
-        <v>9391.7800000000007</v>
-      </c>
-      <c r="F2" s="6">
-        <v>915</v>
+      <c r="E2" s="5" t="n">
+        <v>9391.78</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>918</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1156,7 +880,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -1166,14 +890,14 @@
       <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="4" t="n">
         <v>45346</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="F3" s="6">
-        <v>895</v>
+      <c r="F3" s="6" t="n">
+        <v>898</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
@@ -1186,7 +910,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -1196,14 +920,14 @@
       <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="4" t="n">
         <v>45350</v>
       </c>
-      <c r="E4" s="5">
-        <v>1264.8699999999999</v>
-      </c>
-      <c r="F4" s="6">
-        <v>891</v>
+      <c r="E4" s="5" t="n">
+        <v>1264.87</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>894</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
@@ -1216,7 +940,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1226,14 +950,14 @@
       <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="4" t="n">
         <v>45356</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="5" t="n">
         <v>5418</v>
       </c>
-      <c r="F5" s="6">
-        <v>885</v>
+      <c r="F5" s="6" t="n">
+        <v>888</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
@@ -1246,7 +970,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -1256,14 +980,14 @@
       <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="4" t="n">
         <v>45362</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="5" t="n">
         <v>384</v>
       </c>
-      <c r="F6" s="6">
-        <v>879</v>
+      <c r="F6" s="6" t="n">
+        <v>882</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
@@ -1276,7 +1000,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1286,14 +1010,14 @@
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="n">
         <v>45364</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="F7" s="6">
-        <v>877</v>
+      <c r="F7" s="6" t="n">
+        <v>880</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
@@ -1306,7 +1030,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1316,14 +1040,14 @@
       <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="4" t="n">
         <v>45378</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="5" t="n">
         <v>816</v>
       </c>
-      <c r="F8" s="6">
-        <v>863</v>
+      <c r="F8" s="6" t="n">
+        <v>866</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>21</v>
@@ -1336,7 +1060,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -1346,14 +1070,14 @@
       <c r="C9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="4" t="n">
         <v>45463</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5" t="n">
         <v>1674.52</v>
       </c>
-      <c r="F9" s="6">
-        <v>778</v>
+      <c r="F9" s="6" t="n">
+        <v>781</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
@@ -1366,7 +1090,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -1376,14 +1100,14 @@
       <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="4" t="n">
         <v>45493</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="F10" s="6">
-        <v>748</v>
+      <c r="F10" s="6" t="n">
+        <v>751</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
@@ -1396,7 +1120,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1406,14 +1130,14 @@
       <c r="C11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="4" t="n">
         <v>45523</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5" t="n">
         <v>873.6</v>
       </c>
-      <c r="F11" s="6">
-        <v>718</v>
+      <c r="F11" s="6" t="n">
+        <v>721</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>13</v>
@@ -1426,7 +1150,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -1436,14 +1160,14 @@
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="4" t="n">
         <v>45600</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="F12" s="6">
-        <v>641</v>
+      <c r="F12" s="6" t="n">
+        <v>644</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>13</v>
@@ -1456,7 +1180,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A13" s="3" t="s">
         <v>40</v>
       </c>
@@ -1466,14 +1190,14 @@
       <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="4" t="n">
         <v>45607</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="5" t="n">
         <v>3204.34</v>
       </c>
-      <c r="F13" s="6">
-        <v>634</v>
+      <c r="F13" s="6" t="n">
+        <v>637</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>13</v>
@@ -1486,7 +1210,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1496,14 +1220,14 @@
       <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="4" t="n">
         <v>45608</v>
       </c>
-      <c r="E14" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="F14" s="6">
-        <v>633</v>
+      <c r="E14" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>636</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>13</v>
@@ -1516,7 +1240,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -1526,14 +1250,14 @@
       <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="4" t="n">
         <v>45614</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="F15" s="6">
-        <v>627</v>
+      <c r="F15" s="6" t="n">
+        <v>630</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>13</v>
@@ -1546,7 +1270,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
@@ -1556,14 +1280,14 @@
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="4" t="n">
         <v>45615</v>
       </c>
-      <c r="E16" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="F16" s="6">
-        <v>626</v>
+      <c r="E16" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>629</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
@@ -1576,7 +1300,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -1586,14 +1310,14 @@
       <c r="C17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="4" t="n">
         <v>45617</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="5" t="n">
         <v>1843.87</v>
       </c>
-      <c r="F17" s="6">
-        <v>624</v>
+      <c r="F17" s="6" t="n">
+        <v>627</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>13</v>
@@ -1606,7 +1330,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
@@ -1616,14 +1340,14 @@
       <c r="C18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E18" s="5">
-        <v>1216.8599999999999</v>
-      </c>
-      <c r="F18" s="6">
-        <v>619</v>
+      <c r="E18" s="5" t="n">
+        <v>1216.86</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>622</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
@@ -1636,7 +1360,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A19" s="3" t="s">
         <v>46</v>
       </c>
@@ -1646,14 +1370,14 @@
       <c r="C19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="4" t="n">
         <v>45622</v>
       </c>
-      <c r="E19" s="5">
-        <v>4439.8999999999996</v>
-      </c>
-      <c r="F19" s="6">
-        <v>619</v>
+      <c r="E19" s="5" t="n">
+        <v>4439.9</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>622</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>13</v>
@@ -1666,7 +1390,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
@@ -1676,14 +1400,14 @@
       <c r="C20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="4" t="n">
         <v>45624</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="5" t="n">
         <v>1843.88</v>
       </c>
-      <c r="F20" s="6">
-        <v>617</v>
+      <c r="F20" s="6" t="n">
+        <v>620</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>13</v>
@@ -1696,7 +1420,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A21" s="3" t="s">
         <v>63</v>
       </c>
@@ -1706,14 +1430,14 @@
       <c r="C21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="4" t="n">
         <v>45688</v>
       </c>
-      <c r="E21" s="5">
-        <v>1118.4000000000001</v>
-      </c>
-      <c r="F21" s="6">
-        <v>553</v>
+      <c r="E21" s="5" t="n">
+        <v>1118.4</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>556</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>13</v>
@@ -1726,7 +1450,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -1736,14 +1460,14 @@
       <c r="C22" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="4" t="n">
         <v>45695</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="F22" s="6">
-        <v>546</v>
+      <c r="F22" s="6" t="n">
+        <v>549</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>13</v>
@@ -1756,7 +1480,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -1766,14 +1490,14 @@
       <c r="C23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="4" t="n">
         <v>45699</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="5" t="n">
         <v>2330</v>
       </c>
-      <c r="F23" s="6">
-        <v>542</v>
+      <c r="F23" s="6" t="n">
+        <v>545</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>13</v>
@@ -1786,7 +1510,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -1796,14 +1520,14 @@
       <c r="C24" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="4" t="n">
         <v>45702</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="F24" s="6">
-        <v>539</v>
+      <c r="F24" s="6" t="n">
+        <v>542</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>13</v>
@@ -1816,7 +1540,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
@@ -1826,14 +1550,14 @@
       <c r="C25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="4" t="n">
         <v>45705</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F25" s="6">
-        <v>536</v>
+      <c r="F25" s="6" t="n">
+        <v>539</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>21</v>
@@ -1846,7 +1570,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
@@ -1856,14 +1580,14 @@
       <c r="C26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="4" t="n">
         <v>45709</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="5" t="n">
         <v>3296.8</v>
       </c>
-      <c r="F26" s="6">
-        <v>532</v>
+      <c r="F26" s="6" t="n">
+        <v>535</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>13</v>
@@ -1876,7 +1600,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A27" s="3" t="s">
         <v>40</v>
       </c>
@@ -1886,14 +1610,14 @@
       <c r="C27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="4" t="n">
         <v>45712</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F27" s="6">
-        <v>529</v>
+      <c r="F27" s="6" t="n">
+        <v>532</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>21</v>
@@ -1906,7 +1630,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
@@ -1916,14 +1640,14 @@
       <c r="C28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="4" t="n">
         <v>45726</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F28" s="6">
-        <v>515</v>
+      <c r="F28" s="6" t="n">
+        <v>518</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>21</v>
@@ -1936,7 +1660,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
@@ -1946,14 +1670,14 @@
       <c r="C29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="4" t="n">
         <v>45727</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="F29" s="6">
-        <v>514</v>
+      <c r="F29" s="6" t="n">
+        <v>517</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>13</v>
@@ -1966,7 +1690,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
@@ -1976,14 +1700,14 @@
       <c r="C30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="4" t="n">
         <v>45734</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="F30" s="6">
-        <v>507</v>
+      <c r="F30" s="6" t="n">
+        <v>510</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>13</v>
@@ -1996,7 +1720,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A31" s="3" t="s">
         <v>46</v>
       </c>
@@ -2006,14 +1730,14 @@
       <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="4" t="n">
         <v>45734</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F31" s="6">
-        <v>507</v>
+      <c r="F31" s="6" t="n">
+        <v>510</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>13</v>
@@ -2026,7 +1750,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -2036,14 +1760,14 @@
       <c r="C32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="4" t="n">
         <v>45740</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="5" t="n">
         <v>2541</v>
       </c>
-      <c r="F32" s="6">
-        <v>501</v>
+      <c r="F32" s="6" t="n">
+        <v>504</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>21</v>
@@ -2056,7 +1780,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -2066,14 +1790,14 @@
       <c r="C33" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="5" t="n">
         <v>7562.78</v>
       </c>
-      <c r="F33" s="6">
-        <v>500</v>
+      <c r="F33" s="6" t="n">
+        <v>503</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>13</v>
@@ -2086,7 +1810,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A34" s="3" t="s">
         <v>46</v>
       </c>
@@ -2096,14 +1820,14 @@
       <c r="C34" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="4" t="n">
         <v>45741</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F34" s="6">
-        <v>500</v>
+      <c r="F34" s="6" t="n">
+        <v>503</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>13</v>
@@ -2116,7 +1840,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A35" s="3" t="s">
         <v>46</v>
       </c>
@@ -2126,14 +1850,14 @@
       <c r="C35" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F35" s="6">
-        <v>493</v>
+      <c r="F35" s="6" t="n">
+        <v>496</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>13</v>
@@ -2146,7 +1870,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A36" s="3" t="s">
         <v>40</v>
       </c>
@@ -2156,14 +1880,14 @@
       <c r="C36" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="5" t="n">
         <v>7562.76</v>
       </c>
-      <c r="F36" s="6">
-        <v>493</v>
+      <c r="F36" s="6" t="n">
+        <v>496</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>13</v>
@@ -2176,7 +1900,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
@@ -2186,14 +1910,14 @@
       <c r="C37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="4" t="n">
         <v>45755</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="5" t="n">
         <v>1154.56</v>
       </c>
-      <c r="F37" s="6">
-        <v>486</v>
+      <c r="F37" s="6" t="n">
+        <v>489</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>13</v>
@@ -2206,7 +1930,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A38" s="3" t="s">
         <v>46</v>
       </c>
@@ -2216,14 +1940,14 @@
       <c r="C38" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="4" t="n">
         <v>45761</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="5" t="n">
         <v>6169.53</v>
       </c>
-      <c r="F38" s="6">
-        <v>480</v>
+      <c r="F38" s="6" t="n">
+        <v>483</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>13</v>
@@ -2236,7 +1960,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A39" s="3" t="s">
         <v>46</v>
       </c>
@@ -2246,14 +1970,14 @@
       <c r="C39" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="4" t="n">
         <v>45768</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="F39" s="6">
-        <v>473</v>
+      <c r="F39" s="6" t="n">
+        <v>476</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>13</v>
@@ -2266,7 +1990,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A40" s="3" t="s">
         <v>46</v>
       </c>
@@ -2276,14 +2000,14 @@
       <c r="C40" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="F40" s="6">
-        <v>466</v>
+      <c r="F40" s="6" t="n">
+        <v>469</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>13</v>
@@ -2296,7 +2020,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A41" s="3" t="s">
         <v>46</v>
       </c>
@@ -2306,14 +2030,14 @@
       <c r="C41" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="4" t="n">
         <v>45775</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="5" t="n">
         <v>6089.41</v>
       </c>
-      <c r="F41" s="6">
-        <v>466</v>
+      <c r="F41" s="6" t="n">
+        <v>469</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>13</v>
@@ -2326,7 +2050,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A42" s="3" t="s">
         <v>46</v>
       </c>
@@ -2336,14 +2060,14 @@
       <c r="C42" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="F42" s="6">
-        <v>459</v>
+      <c r="F42" s="6" t="n">
+        <v>462</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>13</v>
@@ -2356,7 +2080,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A43" s="3" t="s">
         <v>46</v>
       </c>
@@ -2366,14 +2090,14 @@
       <c r="C43" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="F43" s="6">
-        <v>452</v>
+      <c r="F43" s="6" t="n">
+        <v>455</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>13</v>
@@ -2386,7 +2110,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A44" s="3" t="s">
         <v>116</v>
       </c>
@@ -2396,14 +2120,14 @@
       <c r="C44" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="4" t="n">
         <v>45789</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="5" t="n">
         <v>1143.54</v>
       </c>
-      <c r="F44" s="6">
-        <v>452</v>
+      <c r="F44" s="6" t="n">
+        <v>455</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>21</v>
@@ -2416,7 +2140,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A45" s="3" t="s">
         <v>116</v>
       </c>
@@ -2426,14 +2150,14 @@
       <c r="C45" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="4" t="n">
         <v>45796</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="5" t="n">
         <v>2287.06</v>
       </c>
-      <c r="F45" s="6">
-        <v>445</v>
+      <c r="F45" s="6" t="n">
+        <v>448</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>21</v>
@@ -2446,7 +2170,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
@@ -2456,14 +2180,14 @@
       <c r="C46" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="4" t="n">
         <v>45896</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="5" t="n">
         <v>4572.62</v>
       </c>
-      <c r="F46" s="6">
-        <v>345</v>
+      <c r="F46" s="6" t="n">
+        <v>348</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>21</v>
@@ -2476,7 +2200,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
@@ -2486,14 +2210,14 @@
       <c r="C47" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="4" t="n">
         <v>45910</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="F47" s="6">
-        <v>331</v>
+      <c r="F47" s="6" t="n">
+        <v>334</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>21</v>
@@ -2506,7 +2230,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A48" s="3" t="s">
         <v>40</v>
       </c>
@@ -2516,14 +2240,14 @@
       <c r="C48" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="4" t="n">
         <v>45924</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="5" t="n">
         <v>3663.84</v>
       </c>
-      <c r="F48" s="6">
-        <v>317</v>
+      <c r="F48" s="6" t="n">
+        <v>320</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>21</v>
@@ -2536,7 +2260,7 @@
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A49" s="3" t="s">
         <v>130</v>
       </c>
@@ -2546,14 +2270,14 @@
       <c r="C49" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="4" t="n">
         <v>45947</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="5" t="n">
         <v>3867.34</v>
       </c>
-      <c r="F49" s="6">
-        <v>294</v>
+      <c r="F49" s="6" t="n">
+        <v>297</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>21</v>
@@ -2566,7 +2290,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
@@ -2576,14 +2300,14 @@
       <c r="C50" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="4" t="n">
         <v>45954</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="F50" s="6">
-        <v>287</v>
+      <c r="F50" s="6" t="n">
+        <v>290</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>21</v>
@@ -2596,7 +2320,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A51" s="3" t="s">
         <v>130</v>
       </c>
@@ -2606,14 +2330,14 @@
       <c r="C51" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="4" t="n">
         <v>45961</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="F51" s="6">
-        <v>280</v>
+      <c r="F51" s="6" t="n">
+        <v>283</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>21</v>
@@ -2626,7 +2350,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A52" s="3" t="s">
         <v>130</v>
       </c>
@@ -2636,14 +2360,14 @@
       <c r="C52" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="4" t="n">
         <v>45968</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="5" t="n">
         <v>2144.59</v>
       </c>
-      <c r="F52" s="6">
-        <v>273</v>
+      <c r="F52" s="6" t="n">
+        <v>276</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>21</v>
@@ -2656,7 +2380,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A53" s="3" t="s">
         <v>116</v>
       </c>
@@ -2666,14 +2390,14 @@
       <c r="C53" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="4" t="n">
         <v>45980</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E53" s="5" t="n">
         <v>4480</v>
       </c>
-      <c r="F53" s="6">
-        <v>261</v>
+      <c r="F53" s="6" t="n">
+        <v>264</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>21</v>
@@ -2686,7 +2410,7 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A54" s="3" t="s">
         <v>130</v>
       </c>
@@ -2696,14 +2420,14 @@
       <c r="C54" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="4" t="n">
         <v>45980</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="5" t="n">
         <v>38840.89</v>
       </c>
-      <c r="F54" s="6">
-        <v>261</v>
+      <c r="F54" s="6" t="n">
+        <v>264</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
@@ -2712,7 +2436,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A55" s="3" t="s">
         <v>130</v>
       </c>
@@ -2722,14 +2446,14 @@
       <c r="C55" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="4" t="n">
         <v>45987</v>
       </c>
-      <c r="E55" s="5">
-        <v>33844.160000000003</v>
-      </c>
-      <c r="F55" s="6">
-        <v>254</v>
+      <c r="E55" s="5" t="n">
+        <v>33844.16</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>257</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2738,7 +2462,7 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A56" s="3" t="s">
         <v>116</v>
       </c>
@@ -2748,14 +2472,14 @@
       <c r="C56" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="4" t="n">
         <v>45989</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="5" t="n">
         <v>3220</v>
       </c>
-      <c r="F56" s="6">
-        <v>252</v>
+      <c r="F56" s="6" t="n">
+        <v>255</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2764,7 +2488,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A57" s="3" t="s">
         <v>130</v>
       </c>
@@ -2774,14 +2498,14 @@
       <c r="C57" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="4" t="n">
         <v>45994</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="5" t="n">
         <v>14483.06</v>
       </c>
-      <c r="F57" s="6">
-        <v>247</v>
+      <c r="F57" s="6" t="n">
+        <v>250</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2790,7 +2514,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2800,14 +2524,14 @@
       <c r="C58" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="4" t="n">
         <v>46090</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="5" t="n">
         <v>806.34</v>
       </c>
-      <c r="F58" s="6">
-        <v>151</v>
+      <c r="F58" s="6" t="n">
+        <v>154</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>21</v>
@@ -2820,7 +2544,7 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A59" s="3" t="s">
         <v>18</v>
       </c>
@@ -2830,14 +2554,14 @@
       <c r="C59" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="4" t="n">
         <v>46097</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="F59" s="6">
-        <v>144</v>
+      <c r="F59" s="6" t="n">
+        <v>147</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>21</v>
@@ -2850,7 +2574,7 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A60" s="3" t="s">
         <v>18</v>
       </c>
@@ -2860,14 +2584,14 @@
       <c r="C60" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="4" t="n">
         <v>46104</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="5" t="n">
         <v>503.28</v>
       </c>
-      <c r="F60" s="6">
-        <v>137</v>
+      <c r="F60" s="6" t="n">
+        <v>140</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>21</v>
@@ -2880,7 +2604,7 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A61" s="3" t="s">
         <v>10</v>
       </c>
@@ -2890,14 +2614,14 @@
       <c r="C61" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="4" t="n">
         <v>46105</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="5" t="n">
         <v>5466.66</v>
       </c>
-      <c r="F61" s="6">
-        <v>136</v>
+      <c r="F61" s="6" t="n">
+        <v>139</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>13</v>
@@ -2910,7 +2634,7 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A62" s="3" t="s">
         <v>10</v>
       </c>
@@ -2920,14 +2644,14 @@
       <c r="C62" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="4" t="n">
         <v>46175</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="5" t="n">
         <v>15028</v>
       </c>
-      <c r="F62" s="6">
-        <v>66</v>
+      <c r="F62" s="6" t="n">
+        <v>69</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>21</v>
@@ -2940,37 +2664,33 @@
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A63" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D63" s="4">
-        <v>46176</v>
-      </c>
-      <c r="E63" s="5">
-        <v>5183.09</v>
-      </c>
-      <c r="F63" s="6">
-        <v>65</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="D63" s="4" t="n">
+        <v>46177</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>15716</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>162</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I63" s="3"/>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A64" s="3" t="s">
         <v>10</v>
       </c>
@@ -2978,16 +2698,16 @@
         <v>158</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D64" s="4">
-        <v>46177</v>
-      </c>
-      <c r="E64" s="5">
+        <v>162</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>46192</v>
+      </c>
+      <c r="E64" s="5" t="n">
         <v>15716</v>
       </c>
-      <c r="F64" s="6">
-        <v>64</v>
+      <c r="F64" s="6" t="n">
+        <v>52</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
@@ -2996,7 +2716,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A65" s="3" t="s">
         <v>10</v>
       </c>
@@ -3004,55 +2724,55 @@
         <v>158</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D65" s="4">
+        <v>163</v>
+      </c>
+      <c r="D65" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="E65" s="5">
-        <v>15716</v>
-      </c>
-      <c r="F65" s="6">
-        <v>49</v>
-      </c>
-      <c r="G65" s="3"/>
+      <c r="E65" s="5" t="n">
+        <v>4193.28</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H65" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I65" s="3"/>
+      <c r="I65" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A66" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="E66" s="5">
-        <v>4193.28</v>
-      </c>
-      <c r="F66" s="6">
+      <c r="E66" s="5" t="n">
+        <v>7494.53</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>166</v>
-      </c>
+      <c r="I66" s="3"/>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A67" s="3" t="s">
         <v>130</v>
       </c>
@@ -3060,16 +2780,16 @@
         <v>143</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D67" s="4">
-        <v>46192</v>
-      </c>
-      <c r="E67" s="5">
-        <v>7494.53</v>
-      </c>
-      <c r="F67" s="6">
-        <v>49</v>
+        <v>166</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>4676.85</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>45</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
@@ -3078,7 +2798,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A68" s="3" t="s">
         <v>130</v>
       </c>
@@ -3086,16 +2806,16 @@
         <v>143</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D68" s="4">
-        <v>46199</v>
-      </c>
-      <c r="E68" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="F68" s="6">
-        <v>42</v>
+        <v>167</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>4676.85</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
@@ -3104,33 +2824,37 @@
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A69" s="3" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>46207</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>4193.28</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D69" s="4">
-        <v>46206</v>
-      </c>
-      <c r="E69" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="F69" s="6">
-        <v>35</v>
-      </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I69" s="3"/>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A70" s="3" t="s">
         <v>10</v>
       </c>
@@ -3140,27 +2864,23 @@
       <c r="C70" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="4" t="n">
         <v>46207</v>
       </c>
-      <c r="E70" s="5">
-        <v>4193.28</v>
-      </c>
-      <c r="F70" s="6">
-        <v>34</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="E70" s="5" t="n">
+        <v>7049.25</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I70" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="I70" s="3"/>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A71" s="3" t="s">
         <v>10</v>
       </c>
@@ -3168,16 +2888,16 @@
         <v>158</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D71" s="4">
+        <v>171</v>
+      </c>
+      <c r="D71" s="4" t="n">
         <v>46207</v>
       </c>
-      <c r="E71" s="5">
-        <v>7049.25</v>
-      </c>
-      <c r="F71" s="6">
-        <v>34</v>
+      <c r="E71" s="5" t="n">
+        <v>15716</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>37</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
@@ -3186,7 +2906,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A72" s="3" t="s">
         <v>10</v>
       </c>
@@ -3194,16 +2914,16 @@
         <v>158</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D72" s="4">
-        <v>46207</v>
-      </c>
-      <c r="E72" s="5">
-        <v>15716</v>
-      </c>
-      <c r="F72" s="6">
-        <v>34</v>
+        <v>172</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>46222</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>3996.72</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>22</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
@@ -3212,359 +2932,347 @@
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A73" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73" s="4" t="n">
         <v>46222</v>
       </c>
-      <c r="E73" s="5">
-        <v>3996.72</v>
-      </c>
-      <c r="F73" s="6">
-        <v>19</v>
-      </c>
-      <c r="G73" s="3"/>
+      <c r="E73" s="5" t="n">
+        <v>31531.5</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="H73" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I73" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A74" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D74" s="4">
-        <v>46222</v>
-      </c>
-      <c r="E74" s="5">
-        <v>31531.5</v>
-      </c>
-      <c r="F74" s="6">
-        <v>19</v>
+      <c r="D74" s="4" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>3516.48</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>66</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A75" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D75" s="4">
-        <v>46228</v>
-      </c>
-      <c r="E75" s="5">
-        <v>3516.48</v>
-      </c>
-      <c r="F75" s="6">
-        <v>13</v>
+        <v>180</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>5796.94</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A76" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D76" s="4">
-        <v>46233</v>
-      </c>
-      <c r="E76" s="5">
-        <v>5796.94</v>
-      </c>
-      <c r="F76" s="6">
-        <v>8</v>
+        <v>183</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>2520.2</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A77" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D77" s="4">
-        <v>46235</v>
-      </c>
-      <c r="E77" s="5">
-        <v>2520.1999999999998</v>
-      </c>
-      <c r="F77" s="6">
-        <v>6</v>
-      </c>
-      <c r="G77" s="3" t="s">
         <v>186</v>
       </c>
+      <c r="D77" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>3996.72</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+    </row>
+    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A78" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J77" s="3"/>
-    </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D78" s="4">
-        <v>46237</v>
-      </c>
-      <c r="E78" s="5">
-        <v>11700</v>
-      </c>
-      <c r="F78" s="6">
-        <v>4</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I78" s="3" t="s">
+      <c r="J78" s="3"/>
+    </row>
+    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A79" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="J78" s="3"/>
-    </row>
-    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D79" s="4">
-        <v>46237</v>
-      </c>
-      <c r="E79" s="5">
-        <v>3996.72</v>
-      </c>
-      <c r="F79" s="6">
-        <v>4</v>
-      </c>
-      <c r="G79" s="3"/>
+      <c r="D79" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="H79" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I79" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A80" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>860</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J80" s="3"/>
+    </row>
+    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J81" s="3"/>
+    </row>
+    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
+      <c r="A82" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D80" s="4">
-        <v>46237</v>
-      </c>
-      <c r="E80" s="5">
-        <v>1400</v>
-      </c>
-      <c r="F80" s="6">
-        <v>4</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J80" s="3"/>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D81" s="4">
-        <v>46238</v>
-      </c>
-      <c r="E81" s="5">
-        <v>2400</v>
-      </c>
-      <c r="F81" s="6">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J81" s="3"/>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="B82" s="3" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D82" s="4">
-        <v>46238</v>
-      </c>
-      <c r="E82" s="5">
-        <v>860</v>
-      </c>
-      <c r="F82" s="6">
-        <v>3</v>
+        <v>201</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>2754</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>202</v>
       </c>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
       <c r="A83" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>10174.45</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I83" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D83" s="4">
-        <v>46238</v>
-      </c>
-      <c r="E83" s="5">
-        <v>3300</v>
-      </c>
-      <c r="F83" s="6">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D84" s="4">
-        <v>46239</v>
-      </c>
-      <c r="E84" s="5">
-        <v>2754</v>
-      </c>
-      <c r="F84" s="6">
-        <v>2</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J84" s="3"/>
+    <row r="84" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A84" s="7"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="9" t="n">
+        <v>429553.79</v>
+      </c>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="10"/>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup orientation="default" cellComments="none"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fábio\Desktop\dados planilhas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71B202F-F8AC-49C6-B933-92631AE89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr refMode="A1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="208">
   <si>
     <t>Funcionário</t>
   </si>
@@ -561,103 +568,111 @@
     <t>00195152300005796940000003473568000003087717</t>
   </si>
   <si>
-    <t>JMC COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01006580.3</t>
+    <t>01006585.3</t>
+  </si>
+  <si>
+    <t>ATACAMED COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>01006816.1</t>
+  </si>
+  <si>
+    <t>00191152900002754000000003473568000003132917</t>
+  </si>
+  <si>
+    <t>01005217.6</t>
   </si>
   <si>
     <t>BRADESCO</t>
   </si>
   <si>
-    <t>23792152500002520200435090000000103200304920</t>
-  </si>
-  <si>
-    <t>01006585.3</t>
-  </si>
-  <si>
-    <t>ATACAMED COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>01006718.3</t>
-  </si>
-  <si>
-    <t>70791152700001400000001121205064100656761015</t>
+    <t>23792153100010174450435090000000107600304920</t>
+  </si>
+  <si>
+    <t>CRALAB SAUDE ATACADO LTDA</t>
+  </si>
+  <si>
+    <t>01006847.1</t>
+  </si>
+  <si>
+    <t>70791153400005352330001121205064100656763250</t>
   </si>
   <si>
     <t>MULTIMAIS ATACADO LTDA</t>
   </si>
   <si>
-    <t>01006782.2</t>
-  </si>
-  <si>
-    <t>70791152800002400000001121205064100656762856</t>
+    <t>01006782.3</t>
+  </si>
+  <si>
+    <t>70791153500002400000001121205064100656762864</t>
+  </si>
+  <si>
+    <t>01006816.2</t>
+  </si>
+  <si>
+    <t>00197153600002754000000003473568000003133017</t>
   </si>
   <si>
     <t>MARCOS DUTRA - PI</t>
   </si>
   <si>
-    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>01006753.2</t>
+    <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
+  </si>
+  <si>
+    <t>01006872.1</t>
   </si>
   <si>
     <t>PI</t>
   </si>
   <si>
-    <t>00191152800000860000000003473568000003128717</t>
+    <t>70798153700003419960001121205064100656763540</t>
   </si>
   <si>
     <t>MONTALVAO COMERCIAL LTDA</t>
   </si>
   <si>
-    <t>01006713.2</t>
-  </si>
-  <si>
-    <t>70797152800003300000001121205064100656761239</t>
-  </si>
-  <si>
-    <t>01006816.1</t>
-  </si>
-  <si>
-    <t>00191152900002754000000003473568000003132917</t>
-  </si>
-  <si>
-    <t>01005217.6</t>
-  </si>
-  <si>
-    <t>23792153100010174450435090000000107600304920</t>
+    <t>01006713.3</t>
+  </si>
+  <si>
+    <t>70792153800003300000001121205064100656761247</t>
+  </si>
+  <si>
+    <t>MAIS SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>01006873.1</t>
+  </si>
+  <si>
+    <t>34191153800009358701090002603088120992717000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/MM/yyyy" numFmtId="164"/>
-    <numFmt formatCode="###,###,##0.00" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Segoe UI"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -676,14 +691,8 @@
         <bgColor rgb="FF7EA6D1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -706,119 +715,361 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0A0A0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFA0A0A0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0A0A0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0A0A0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" shrinkToFit="false" wrapText="false"/>
-      <protection hidden="false" locked="true"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="1" fillId="4" fontId="1" numFmtId="165" xfId="0">
-      <alignment horizontal="right" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="true" applyNumberFormat="true" applyFont="true" applyProtection="true" borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="top" textRotation="0" shrinkToFit="false" wrapText="true"/>
-      <protection hidden="false" locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J84"/>
-  <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col max="1" min="1" style="1" width="22.28515625" customWidth="true"/>
-    <col max="2" min="2" style="1" width="30.28515625" customWidth="true"/>
-    <col max="3" min="3" style="1" width="12.85546875" customWidth="true"/>
-    <col max="4" min="4" style="1" width="24.7109375" customWidth="true"/>
-    <col max="5" min="5" style="1" width="27.28515625" customWidth="true"/>
-    <col max="6" min="6" style="1" width="9.140625" customWidth="true"/>
-    <col max="7" min="7" style="1" width="26.28515625" customWidth="true"/>
-    <col max="8" min="8" style="1" width="3.7109375" customWidth="true"/>
-    <col max="9" min="9" style="1" width="60.5703125" customWidth="true"/>
-    <col max="10" min="10" style="1" width="26.28515625" customWidth="true"/>
-    <col max="16384" min="11" style="1" width="12.140625"/>
+    <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="60.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="true" ht="27" customFormat="true" s="1">
+    <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -850,7 +1101,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -860,14 +1111,14 @@
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>45326</v>
       </c>
-      <c r="E2" s="5" t="n">
-        <v>9391.78</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>918</v>
+      <c r="E2" s="5">
+        <v>9391.7800000000007</v>
+      </c>
+      <c r="F2" s="6">
+        <v>925</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -880,7 +1131,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -890,14 +1141,14 @@
       <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>45346</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5">
         <v>5418</v>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>898</v>
+      <c r="F3" s="6">
+        <v>905</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
@@ -910,7 +1161,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -920,14 +1171,14 @@
       <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>45350</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>1264.87</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>894</v>
+      <c r="E4" s="5">
+        <v>1264.8699999999999</v>
+      </c>
+      <c r="F4" s="6">
+        <v>901</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
@@ -940,7 +1191,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -950,14 +1201,14 @@
       <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>45356</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5">
         <v>5418</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>888</v>
+      <c r="F5" s="6">
+        <v>895</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>13</v>
@@ -970,7 +1221,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -980,14 +1231,14 @@
       <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>45362</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5">
         <v>384</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>882</v>
+      <c r="F6" s="6">
+        <v>889</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
@@ -1000,7 +1251,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1010,14 +1261,14 @@
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>45364</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5">
         <v>816</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>880</v>
+      <c r="F7" s="6">
+        <v>887</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
@@ -1030,7 +1281,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1040,14 +1291,14 @@
       <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>45378</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="5">
         <v>816</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>866</v>
+      <c r="F8" s="6">
+        <v>873</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>21</v>
@@ -1060,7 +1311,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -1070,14 +1321,14 @@
       <c r="C9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>45463</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5">
         <v>1674.52</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>781</v>
+      <c r="F9" s="6">
+        <v>788</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
@@ -1090,7 +1341,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -1100,14 +1351,14 @@
       <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>45493</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5">
         <v>873.6</v>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>751</v>
+      <c r="F10" s="6">
+        <v>758</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>13</v>
@@ -1120,7 +1371,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1130,14 +1381,14 @@
       <c r="C11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>45523</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5">
         <v>873.6</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>721</v>
+      <c r="F11" s="6">
+        <v>728</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>13</v>
@@ -1150,7 +1401,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>40</v>
       </c>
@@ -1160,14 +1411,14 @@
       <c r="C12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>45600</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5">
         <v>2000</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>644</v>
+      <c r="F12" s="6">
+        <v>651</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>13</v>
@@ -1180,7 +1431,7 @@
       </c>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>40</v>
       </c>
@@ -1190,14 +1441,14 @@
       <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>45607</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5">
         <v>3204.34</v>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>637</v>
+      <c r="F13" s="6">
+        <v>644</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>13</v>
@@ -1210,7 +1461,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1220,14 +1471,14 @@
       <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>45608</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>636</v>
+      <c r="E14" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F14" s="6">
+        <v>643</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>13</v>
@@ -1240,7 +1491,7 @@
       </c>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
@@ -1250,14 +1501,14 @@
       <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>45614</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="5">
         <v>2000</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>630</v>
+      <c r="F15" s="6">
+        <v>637</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>13</v>
@@ -1270,7 +1521,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
@@ -1280,14 +1531,14 @@
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>45615</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>629</v>
+      <c r="E16" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F16" s="6">
+        <v>636</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
@@ -1300,7 +1551,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
@@ -1310,14 +1561,14 @@
       <c r="C17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>45617</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="5">
         <v>1843.87</v>
       </c>
-      <c r="F17" s="6" t="n">
-        <v>627</v>
+      <c r="F17" s="6">
+        <v>634</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>13</v>
@@ -1330,7 +1581,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
@@ -1340,14 +1591,14 @@
       <c r="C18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>45622</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1216.86</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>622</v>
+      <c r="E18" s="5">
+        <v>1216.8599999999999</v>
+      </c>
+      <c r="F18" s="6">
+        <v>629</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
@@ -1360,7 +1611,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>46</v>
       </c>
@@ -1370,14 +1621,14 @@
       <c r="C19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>45622</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>4439.9</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>622</v>
+      <c r="E19" s="5">
+        <v>4439.8999999999996</v>
+      </c>
+      <c r="F19" s="6">
+        <v>629</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>13</v>
@@ -1390,7 +1641,7 @@
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
@@ -1400,14 +1651,14 @@
       <c r="C20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>45624</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="5">
         <v>1843.88</v>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>620</v>
+      <c r="F20" s="6">
+        <v>627</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>13</v>
@@ -1420,7 +1671,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>63</v>
       </c>
@@ -1430,14 +1681,14 @@
       <c r="C21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>45688</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>1118.4</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>556</v>
+      <c r="E21" s="5">
+        <v>1118.4000000000001</v>
+      </c>
+      <c r="F21" s="6">
+        <v>563</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>13</v>
@@ -1450,7 +1701,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
@@ -1460,14 +1711,14 @@
       <c r="C22" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>45695</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F22" s="6" t="n">
-        <v>549</v>
+      <c r="F22" s="6">
+        <v>556</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>13</v>
@@ -1480,7 +1731,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
@@ -1490,14 +1741,14 @@
       <c r="C23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>45699</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="5">
         <v>2330</v>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>545</v>
+      <c r="F23" s="6">
+        <v>552</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>13</v>
@@ -1510,7 +1761,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -1520,14 +1771,14 @@
       <c r="C24" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>45702</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>542</v>
+      <c r="F24" s="6">
+        <v>549</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>13</v>
@@ -1540,7 +1791,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
@@ -1550,14 +1801,14 @@
       <c r="C25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>45705</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="5">
         <v>2541</v>
       </c>
-      <c r="F25" s="6" t="n">
-        <v>539</v>
+      <c r="F25" s="6">
+        <v>546</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>21</v>
@@ -1570,7 +1821,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
@@ -1580,14 +1831,14 @@
       <c r="C26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>45709</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="5">
         <v>3296.8</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>535</v>
+      <c r="F26" s="6">
+        <v>542</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>13</v>
@@ -1600,7 +1851,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>40</v>
       </c>
@@ -1610,14 +1861,14 @@
       <c r="C27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>45712</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="5">
         <v>2541</v>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>532</v>
+      <c r="F27" s="6">
+        <v>539</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>21</v>
@@ -1630,7 +1881,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
@@ -1640,14 +1891,14 @@
       <c r="C28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>45726</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="5">
         <v>2541</v>
       </c>
-      <c r="F28" s="6" t="n">
-        <v>518</v>
+      <c r="F28" s="6">
+        <v>525</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>21</v>
@@ -1660,7 +1911,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
@@ -1670,14 +1921,14 @@
       <c r="C29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4">
         <v>45727</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F29" s="6" t="n">
-        <v>517</v>
+      <c r="F29" s="6">
+        <v>524</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>13</v>
@@ -1690,7 +1941,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
@@ -1700,14 +1951,14 @@
       <c r="C30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>45734</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F30" s="6" t="n">
-        <v>510</v>
+      <c r="F30" s="6">
+        <v>517</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>13</v>
@@ -1720,7 +1971,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>46</v>
       </c>
@@ -1730,14 +1981,14 @@
       <c r="C31" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>45734</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F31" s="6" t="n">
-        <v>510</v>
+      <c r="F31" s="6">
+        <v>517</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>13</v>
@@ -1750,7 +2001,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -1760,14 +2011,14 @@
       <c r="C32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>45740</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="5">
         <v>2541</v>
       </c>
-      <c r="F32" s="6" t="n">
-        <v>504</v>
+      <c r="F32" s="6">
+        <v>511</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>21</v>
@@ -1780,7 +2031,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
@@ -1790,14 +2041,14 @@
       <c r="C33" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>45741</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="5">
         <v>7562.78</v>
       </c>
-      <c r="F33" s="6" t="n">
-        <v>503</v>
+      <c r="F33" s="6">
+        <v>510</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>13</v>
@@ -1810,7 +2061,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>46</v>
       </c>
@@ -1820,14 +2071,14 @@
       <c r="C34" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>45741</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F34" s="6" t="n">
-        <v>503</v>
+      <c r="F34" s="6">
+        <v>510</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>13</v>
@@ -1840,7 +2091,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>46</v>
       </c>
@@ -1850,14 +2101,14 @@
       <c r="C35" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4">
         <v>45748</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F35" s="6" t="n">
-        <v>496</v>
+      <c r="F35" s="6">
+        <v>503</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>13</v>
@@ -1870,7 +2121,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>40</v>
       </c>
@@ -1880,14 +2131,14 @@
       <c r="C36" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4">
         <v>45748</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="5">
         <v>7562.76</v>
       </c>
-      <c r="F36" s="6" t="n">
-        <v>496</v>
+      <c r="F36" s="6">
+        <v>503</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>13</v>
@@ -1900,7 +2151,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>46</v>
       </c>
@@ -1910,14 +2161,14 @@
       <c r="C37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4">
         <v>45755</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="5">
         <v>1154.56</v>
       </c>
-      <c r="F37" s="6" t="n">
-        <v>489</v>
+      <c r="F37" s="6">
+        <v>496</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>13</v>
@@ -1930,7 +2181,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>46</v>
       </c>
@@ -1940,14 +2191,14 @@
       <c r="C38" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="4">
         <v>45761</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="5">
         <v>6169.53</v>
       </c>
-      <c r="F38" s="6" t="n">
-        <v>483</v>
+      <c r="F38" s="6">
+        <v>490</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>13</v>
@@ -1960,7 +2211,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>46</v>
       </c>
@@ -1970,14 +2221,14 @@
       <c r="C39" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="4">
         <v>45768</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="5">
         <v>3850</v>
       </c>
-      <c r="F39" s="6" t="n">
-        <v>476</v>
+      <c r="F39" s="6">
+        <v>483</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>13</v>
@@ -1990,7 +2241,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>46</v>
       </c>
@@ -2000,14 +2251,14 @@
       <c r="C40" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="4">
         <v>45775</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="5">
         <v>3850</v>
       </c>
-      <c r="F40" s="6" t="n">
-        <v>469</v>
+      <c r="F40" s="6">
+        <v>476</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>13</v>
@@ -2020,7 +2271,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>46</v>
       </c>
@@ -2030,14 +2281,14 @@
       <c r="C41" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="4">
         <v>45775</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="5">
         <v>6089.41</v>
       </c>
-      <c r="F41" s="6" t="n">
-        <v>469</v>
+      <c r="F41" s="6">
+        <v>476</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>13</v>
@@ -2050,7 +2301,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>46</v>
       </c>
@@ -2060,14 +2311,14 @@
       <c r="C42" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="4">
         <v>45782</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="5">
         <v>3800</v>
       </c>
-      <c r="F42" s="6" t="n">
-        <v>462</v>
+      <c r="F42" s="6">
+        <v>469</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>13</v>
@@ -2080,7 +2331,7 @@
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>46</v>
       </c>
@@ -2090,14 +2341,14 @@
       <c r="C43" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="4">
         <v>45789</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="5">
         <v>3800</v>
       </c>
-      <c r="F43" s="6" t="n">
-        <v>455</v>
+      <c r="F43" s="6">
+        <v>462</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>13</v>
@@ -2110,7 +2361,7 @@
       </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>116</v>
       </c>
@@ -2120,14 +2371,14 @@
       <c r="C44" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="4">
         <v>45789</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="5">
         <v>1143.54</v>
       </c>
-      <c r="F44" s="6" t="n">
-        <v>455</v>
+      <c r="F44" s="6">
+        <v>462</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>21</v>
@@ -2140,7 +2391,7 @@
       </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>116</v>
       </c>
@@ -2150,14 +2401,14 @@
       <c r="C45" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="4">
         <v>45796</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="5">
         <v>2287.06</v>
       </c>
-      <c r="F45" s="6" t="n">
-        <v>448</v>
+      <c r="F45" s="6">
+        <v>455</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>21</v>
@@ -2170,7 +2421,7 @@
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
@@ -2180,14 +2431,14 @@
       <c r="C46" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="4">
         <v>45896</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="5">
         <v>4572.62</v>
       </c>
-      <c r="F46" s="6" t="n">
-        <v>348</v>
+      <c r="F46" s="6">
+        <v>355</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>21</v>
@@ -2200,7 +2451,7 @@
       </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
@@ -2210,14 +2461,14 @@
       <c r="C47" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="4">
         <v>45910</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F47" s="6" t="n">
-        <v>334</v>
+      <c r="F47" s="6">
+        <v>341</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>21</v>
@@ -2230,7 +2481,7 @@
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>40</v>
       </c>
@@ -2240,14 +2491,14 @@
       <c r="C48" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="4">
         <v>45924</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="5">
         <v>3663.84</v>
       </c>
-      <c r="F48" s="6" t="n">
-        <v>320</v>
+      <c r="F48" s="6">
+        <v>327</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>21</v>
@@ -2260,7 +2511,7 @@
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>130</v>
       </c>
@@ -2270,14 +2521,14 @@
       <c r="C49" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="4">
         <v>45947</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="5">
         <v>3867.34</v>
       </c>
-      <c r="F49" s="6" t="n">
-        <v>297</v>
+      <c r="F49" s="6">
+        <v>304</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>21</v>
@@ -2290,7 +2541,7 @@
       </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
@@ -2300,14 +2551,14 @@
       <c r="C50" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="4">
         <v>45954</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E50" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F50" s="6" t="n">
-        <v>290</v>
+      <c r="F50" s="6">
+        <v>297</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>21</v>
@@ -2320,7 +2571,7 @@
       </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>130</v>
       </c>
@@ -2330,14 +2581,14 @@
       <c r="C51" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="4">
         <v>45961</v>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="E51" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F51" s="6" t="n">
-        <v>283</v>
+      <c r="F51" s="6">
+        <v>290</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>21</v>
@@ -2350,7 +2601,7 @@
       </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>130</v>
       </c>
@@ -2360,14 +2611,14 @@
       <c r="C52" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="4">
         <v>45968</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E52" s="5">
         <v>2144.59</v>
       </c>
-      <c r="F52" s="6" t="n">
-        <v>276</v>
+      <c r="F52" s="6">
+        <v>283</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>21</v>
@@ -2380,7 +2631,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>116</v>
       </c>
@@ -2390,14 +2641,14 @@
       <c r="C53" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="4">
         <v>45980</v>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="E53" s="5">
         <v>4480</v>
       </c>
-      <c r="F53" s="6" t="n">
-        <v>264</v>
+      <c r="F53" s="6">
+        <v>271</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>21</v>
@@ -2410,7 +2661,7 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>130</v>
       </c>
@@ -2420,14 +2671,14 @@
       <c r="C54" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="4">
         <v>45980</v>
       </c>
-      <c r="E54" s="5" t="n">
+      <c r="E54" s="5">
         <v>38840.89</v>
       </c>
-      <c r="F54" s="6" t="n">
-        <v>264</v>
+      <c r="F54" s="6">
+        <v>271</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
@@ -2436,7 +2687,7 @@
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>130</v>
       </c>
@@ -2446,14 +2697,14 @@
       <c r="C55" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="4">
         <v>45987</v>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>33844.16</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>257</v>
+      <c r="E55" s="5">
+        <v>33844.160000000003</v>
+      </c>
+      <c r="F55" s="6">
+        <v>264</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2462,7 +2713,7 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>116</v>
       </c>
@@ -2472,14 +2723,14 @@
       <c r="C56" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="4">
         <v>45989</v>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E56" s="5">
         <v>3220</v>
       </c>
-      <c r="F56" s="6" t="n">
-        <v>255</v>
+      <c r="F56" s="6">
+        <v>262</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2488,7 +2739,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>130</v>
       </c>
@@ -2498,14 +2749,14 @@
       <c r="C57" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="4">
         <v>45994</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="E57" s="5">
         <v>14483.06</v>
       </c>
-      <c r="F57" s="6" t="n">
-        <v>250</v>
+      <c r="F57" s="6">
+        <v>257</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2514,7 +2765,7 @@
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>18</v>
       </c>
@@ -2524,14 +2775,14 @@
       <c r="C58" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="4">
         <v>46090</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E58" s="5">
         <v>806.34</v>
       </c>
-      <c r="F58" s="6" t="n">
-        <v>154</v>
+      <c r="F58" s="6">
+        <v>161</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>21</v>
@@ -2544,7 +2795,7 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>18</v>
       </c>
@@ -2554,14 +2805,14 @@
       <c r="C59" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="4">
         <v>46097</v>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E59" s="5">
         <v>503.28</v>
       </c>
-      <c r="F59" s="6" t="n">
-        <v>147</v>
+      <c r="F59" s="6">
+        <v>154</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>21</v>
@@ -2574,7 +2825,7 @@
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>18</v>
       </c>
@@ -2584,14 +2835,14 @@
       <c r="C60" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="4">
         <v>46104</v>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E60" s="5">
         <v>503.28</v>
       </c>
-      <c r="F60" s="6" t="n">
-        <v>140</v>
+      <c r="F60" s="6">
+        <v>147</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>21</v>
@@ -2604,7 +2855,7 @@
       </c>
       <c r="J60" s="3"/>
     </row>
-    <row r="61" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>10</v>
       </c>
@@ -2614,14 +2865,14 @@
       <c r="C61" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="4">
         <v>46105</v>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E61" s="5">
         <v>5466.66</v>
       </c>
-      <c r="F61" s="6" t="n">
-        <v>139</v>
+      <c r="F61" s="6">
+        <v>146</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>13</v>
@@ -2634,7 +2885,7 @@
       </c>
       <c r="J61" s="3"/>
     </row>
-    <row r="62" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>10</v>
       </c>
@@ -2644,14 +2895,14 @@
       <c r="C62" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="4">
         <v>46175</v>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E62" s="5">
         <v>15028</v>
       </c>
-      <c r="F62" s="6" t="n">
-        <v>69</v>
+      <c r="F62" s="6">
+        <v>76</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>21</v>
@@ -2664,7 +2915,7 @@
       </c>
       <c r="J62" s="3"/>
     </row>
-    <row r="63" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>10</v>
       </c>
@@ -2674,14 +2925,14 @@
       <c r="C63" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="4">
         <v>46177</v>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="E63" s="5">
         <v>15716</v>
       </c>
-      <c r="F63" s="6" t="n">
-        <v>67</v>
+      <c r="F63" s="6">
+        <v>74</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
@@ -2690,7 +2941,7 @@
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
     </row>
-    <row r="64" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>10</v>
       </c>
@@ -2700,14 +2951,14 @@
       <c r="C64" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="4">
         <v>46192</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E64" s="5">
         <v>15716</v>
       </c>
-      <c r="F64" s="6" t="n">
-        <v>52</v>
+      <c r="F64" s="6">
+        <v>59</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
@@ -2716,7 +2967,7 @@
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>10</v>
       </c>
@@ -2726,14 +2977,14 @@
       <c r="C65" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="4">
         <v>46192</v>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E65" s="5">
         <v>4193.28</v>
       </c>
-      <c r="F65" s="6" t="n">
-        <v>52</v>
+      <c r="F65" s="6">
+        <v>59</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>21</v>
@@ -2746,7 +2997,7 @@
       </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>130</v>
       </c>
@@ -2756,14 +3007,14 @@
       <c r="C66" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="4">
         <v>46192</v>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E66" s="5">
         <v>7494.53</v>
       </c>
-      <c r="F66" s="6" t="n">
-        <v>52</v>
+      <c r="F66" s="6">
+        <v>59</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3" t="s">
@@ -2772,7 +3023,7 @@
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
     </row>
-    <row r="67" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>130</v>
       </c>
@@ -2782,14 +3033,14 @@
       <c r="C67" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="4">
         <v>46199</v>
       </c>
-      <c r="E67" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>45</v>
+      <c r="E67" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="F67" s="6">
+        <v>52</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
@@ -2798,7 +3049,7 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>130</v>
       </c>
@@ -2808,14 +3059,14 @@
       <c r="C68" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="4">
         <v>46206</v>
       </c>
-      <c r="E68" s="5" t="n">
-        <v>4676.85</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>38</v>
+      <c r="E68" s="5">
+        <v>4676.8500000000004</v>
+      </c>
+      <c r="F68" s="6">
+        <v>45</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
@@ -2824,7 +3075,7 @@
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>10</v>
       </c>
@@ -2834,14 +3085,14 @@
       <c r="C69" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="4">
         <v>46207</v>
       </c>
-      <c r="E69" s="5" t="n">
+      <c r="E69" s="5">
         <v>4193.28</v>
       </c>
-      <c r="F69" s="6" t="n">
-        <v>37</v>
+      <c r="F69" s="6">
+        <v>44</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>21</v>
@@ -2854,7 +3105,7 @@
       </c>
       <c r="J69" s="3"/>
     </row>
-    <row r="70" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>10</v>
       </c>
@@ -2864,14 +3115,14 @@
       <c r="C70" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="4">
         <v>46207</v>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E70" s="5">
         <v>7049.25</v>
       </c>
-      <c r="F70" s="6" t="n">
-        <v>37</v>
+      <c r="F70" s="6">
+        <v>44</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
@@ -2880,7 +3131,7 @@
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
     </row>
-    <row r="71" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>10</v>
       </c>
@@ -2890,14 +3141,14 @@
       <c r="C71" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="4">
         <v>46207</v>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E71" s="5">
         <v>15716</v>
       </c>
-      <c r="F71" s="6" t="n">
-        <v>37</v>
+      <c r="F71" s="6">
+        <v>44</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
@@ -2906,7 +3157,7 @@
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>10</v>
       </c>
@@ -2916,14 +3167,14 @@
       <c r="C72" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="4">
         <v>46222</v>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E72" s="5">
         <v>3996.72</v>
       </c>
-      <c r="F72" s="6" t="n">
-        <v>22</v>
+      <c r="F72" s="6">
+        <v>29</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
@@ -2932,7 +3183,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>18</v>
       </c>
@@ -2942,14 +3193,14 @@
       <c r="C73" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="4">
         <v>46222</v>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="E73" s="5">
         <v>31531.5</v>
       </c>
-      <c r="F73" s="6" t="n">
-        <v>22</v>
+      <c r="F73" s="6">
+        <v>29</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>13</v>
@@ -2962,7 +3213,7 @@
       </c>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>18</v>
       </c>
@@ -2972,14 +3223,14 @@
       <c r="C74" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="4">
         <v>46228</v>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E74" s="5">
         <v>3516.48</v>
       </c>
-      <c r="F74" s="6" t="n">
-        <v>16</v>
+      <c r="F74" s="6">
+        <v>23</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>177</v>
@@ -2992,7 +3243,7 @@
       </c>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>10</v>
       </c>
@@ -3002,14 +3253,14 @@
       <c r="C75" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="4">
         <v>46233</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E75" s="5">
         <v>5796.94</v>
       </c>
-      <c r="F75" s="6" t="n">
-        <v>11</v>
+      <c r="F75" s="6">
+        <v>18</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>21</v>
@@ -3022,257 +3273,273 @@
       </c>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" customHeight="true" ht="14.25" customFormat="true" s="1">
+    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="4">
+        <v>46237</v>
+      </c>
+      <c r="E76" s="5">
+        <v>3996.72</v>
+      </c>
+      <c r="F76" s="6">
+        <v>14</v>
+      </c>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+    </row>
+    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D76" s="4" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>2520.2</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G76" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I76" s="3" t="s">
+      <c r="D77" s="4">
+        <v>46239</v>
+      </c>
+      <c r="E77" s="5">
+        <v>2754</v>
+      </c>
+      <c r="F77" s="6">
+        <v>12</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J76" s="3"/>
-    </row>
-    <row r="77" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A77" s="3" t="s">
+      <c r="J77" s="3"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D78" s="4">
+        <v>46241</v>
+      </c>
+      <c r="E78" s="5">
+        <v>10174.450000000001</v>
+      </c>
+      <c r="F78" s="6">
         <v>10</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>46237</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>3996.72</v>
-      </c>
-      <c r="F77" s="6" t="n">
+      <c r="G78" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J78" s="3"/>
+    </row>
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D79" s="4">
+        <v>46244</v>
+      </c>
+      <c r="E79" s="5">
+        <v>5352.33</v>
+      </c>
+      <c r="F79" s="6">
         <v>7</v>
-      </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-    </row>
-    <row r="78" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A78" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>46237</v>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J78" s="3"/>
-    </row>
-    <row r="79" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A79" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F79" s="6" t="n">
-        <v>6</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H79" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J79" s="3"/>
+    </row>
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D80" s="4">
+        <v>46245</v>
+      </c>
+      <c r="E80" s="5">
+        <v>2400</v>
+      </c>
+      <c r="F80" s="6">
+        <v>6</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I79" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J79" s="3"/>
-    </row>
-    <row r="80" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A80" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B80" s="3" t="s">
+      <c r="I80" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="J80" s="3"/>
+    </row>
+    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D80" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>860</v>
-      </c>
-      <c r="F80" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G80" s="3" t="s">
+      <c r="D81" s="4">
+        <v>46246</v>
+      </c>
+      <c r="E81" s="5">
+        <v>2754</v>
+      </c>
+      <c r="F81" s="6">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="H81" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I81" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="J81" s="3"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="J80" s="3"/>
-    </row>
-    <row r="81" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A81" s="3" t="s">
+      <c r="B82" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D82" s="4">
+        <v>46247</v>
+      </c>
+      <c r="E82" s="5">
+        <v>3419.96</v>
+      </c>
+      <c r="F82" s="6">
+        <v>4</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J82" s="3"/>
+    </row>
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>3300</v>
-      </c>
-      <c r="F81" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J81" s="3"/>
-    </row>
-    <row r="82" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A82" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>2754</v>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I82" s="3" t="s">
+      <c r="B83" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="J82" s="3"/>
-    </row>
-    <row r="83" customHeight="true" ht="14.25" customFormat="true" s="1">
-      <c r="A83" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D83" s="4" t="n">
-        <v>46241</v>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>10174.45</v>
-      </c>
-      <c r="F83" s="6" t="n">
+      <c r="D83" s="4">
+        <v>46248</v>
+      </c>
+      <c r="E83" s="5">
+        <v>3300</v>
+      </c>
+      <c r="F83" s="6">
         <v>3</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>204</v>
       </c>
       <c r="J83" s="3"/>
     </row>
-    <row r="84" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A84" s="7"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="9" t="n">
-        <v>429553.79</v>
-      </c>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="10"/>
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D84" s="4">
+        <v>46248</v>
+      </c>
+      <c r="E84" s="5">
+        <v>9358.7000000000007</v>
+      </c>
+      <c r="F84" s="6">
+        <v>3</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J84" s="3"/>
     </row>
   </sheetData>
-  <pageSetup orientation="default" cellComments="none"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fábio\Desktop\dados planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71B202F-F8AC-49C6-B933-92631AE89DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA40ACDA-2EAD-4C48-AD8C-E7375CD3F1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XLS_Grid_LANCAMENTO A RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="207">
   <si>
     <t>Funcionário</t>
   </si>
@@ -46,6 +51,9 @@
     <t>UF</t>
   </si>
   <si>
+    <t>Grupo Econômico</t>
+  </si>
+  <si>
     <t>Cod.Barras - Boleto</t>
   </si>
   <si>
@@ -496,27 +504,6 @@
     <t>34199139500005466661090002533378120992717000</t>
   </si>
   <si>
-    <t>NOVA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>01006017.4</t>
-  </si>
-  <si>
-    <t>00191146500015028000000003473568000003058217</t>
-  </si>
-  <si>
-    <t>01006204.2</t>
-  </si>
-  <si>
-    <t>01006204.3</t>
-  </si>
-  <si>
-    <t>01006205.3</t>
-  </si>
-  <si>
-    <t>00192148200004193280000003473568000003078317</t>
-  </si>
-  <si>
     <t>01006508.1</t>
   </si>
   <si>
@@ -526,21 +513,6 @@
     <t>01006508.3</t>
   </si>
   <si>
-    <t>01006205.4</t>
-  </si>
-  <si>
-    <t>00191149700004193280000003473568000003078417</t>
-  </si>
-  <si>
-    <t>01006585.1</t>
-  </si>
-  <si>
-    <t>01006204.4</t>
-  </si>
-  <si>
-    <t>01006585.2</t>
-  </si>
-  <si>
     <t>GRADUAL COMERCIO E SERVICOS LTDA</t>
   </si>
   <si>
@@ -568,82 +540,112 @@
     <t>00195152300005796940000003473568000003087717</t>
   </si>
   <si>
-    <t>01006585.3</t>
-  </si>
-  <si>
     <t>ATACAMED COMERCIO LTDA</t>
   </si>
   <si>
-    <t>01006816.1</t>
-  </si>
-  <si>
-    <t>00191152900002754000000003473568000003132917</t>
-  </si>
-  <si>
-    <t>01005217.6</t>
-  </si>
-  <si>
-    <t>BRADESCO</t>
-  </si>
-  <si>
-    <t>23792153100010174450435090000000107600304920</t>
-  </si>
-  <si>
-    <t>CRALAB SAUDE ATACADO LTDA</t>
-  </si>
-  <si>
-    <t>01006847.1</t>
-  </si>
-  <si>
-    <t>70791153400005352330001121205064100656763250</t>
+    <t>01006816.2</t>
+  </si>
+  <si>
+    <t>00197153600002754000000003473568000003133017</t>
+  </si>
+  <si>
+    <t>MARCOS DUTRA - PI</t>
+  </si>
+  <si>
+    <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
+  </si>
+  <si>
+    <t>01006872.1</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>70798153700003419960001121205064100656763540</t>
+  </si>
+  <si>
+    <t>MONTALVAO COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>01006713.3</t>
+  </si>
+  <si>
+    <t>JMC</t>
+  </si>
+  <si>
+    <t>70792153800003300000001121205064100656761247</t>
+  </si>
+  <si>
+    <t>ALIANCA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006753.4</t>
+  </si>
+  <si>
+    <t>00191154200000860000000003473568000003128917</t>
+  </si>
+  <si>
+    <t>01006941.1</t>
+  </si>
+  <si>
+    <t>00191154200002818370000003473568000003141017</t>
   </si>
   <si>
     <t>MULTIMAIS ATACADO LTDA</t>
   </si>
   <si>
-    <t>01006782.3</t>
-  </si>
-  <si>
-    <t>70791153500002400000001121205064100656762864</t>
-  </si>
-  <si>
-    <t>01006816.2</t>
-  </si>
-  <si>
-    <t>00197153600002754000000003473568000003133017</t>
-  </si>
-  <si>
-    <t>MARCOS DUTRA - PI</t>
-  </si>
-  <si>
-    <t>M. A. M COMERCIO E DISTRIBUIDORA DE MEDICAMENTOS L</t>
-  </si>
-  <si>
-    <t>01006872.1</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>70798153700003419960001121205064100656763540</t>
-  </si>
-  <si>
-    <t>MONTALVAO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>01006713.3</t>
-  </si>
-  <si>
-    <t>70792153800003300000001121205064100656761247</t>
-  </si>
-  <si>
-    <t>MAIS SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>01006873.1</t>
-  </si>
-  <si>
-    <t>34191153800009358701090002603088120992717000</t>
+    <t>01006782.4</t>
+  </si>
+  <si>
+    <t>70791154200002400000001121205064100656762872</t>
+  </si>
+  <si>
+    <t>REALMED COMERCIO DE PRODUTOS MEDICOS E HOSPITALARE</t>
+  </si>
+  <si>
+    <t>01006951.1</t>
+  </si>
+  <si>
+    <t>00196154300000982710000003473568000003141817</t>
+  </si>
+  <si>
+    <t>01006816.3</t>
+  </si>
+  <si>
+    <t>00191154300002754000000003473568000003133117</t>
+  </si>
+  <si>
+    <t>PARNAMIRIM HOSPITALAR E MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006970.1</t>
+  </si>
+  <si>
+    <t>00193154300003066000000003473568000003141517</t>
+  </si>
+  <si>
+    <t>PLENA DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01006787.1</t>
+  </si>
+  <si>
+    <t>70799154300000875250001121205064100656762096</t>
+  </si>
+  <si>
+    <t>RAMON ANTONIO NUNES DA SILVA</t>
+  </si>
+  <si>
+    <t>01006944.1</t>
+  </si>
+  <si>
+    <t>00194154400002549410000003473568000003142117</t>
+  </si>
+  <si>
+    <t>01006872.2</t>
+  </si>
+  <si>
+    <t>70791154400003419960001121205064100656763557</t>
   </si>
 </sst>
 </file>
@@ -663,13 +665,13 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -721,22 +723,22 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,39 +769,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -851,7 +853,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -962,13 +964,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -977,6 +972,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1041,11 +1043,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1053,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -1064,12 +1086,13 @@
     <col min="6" max="6" width="9.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="26.28515625" style="1" customWidth="1"/>
     <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="60.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.28515625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.140625" style="1"/>
+    <col min="9" max="9" width="43.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="26.28515625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="12.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1100,16 +1123,19 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4">
         <v>45326</v>
@@ -1118,28 +1144,29 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4">
         <v>45346</v>
@@ -1148,28 +1175,29 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="4">
         <v>45350</v>
@@ -1178,28 +1206,29 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="4">
         <v>45356</v>
@@ -1208,28 +1237,29 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="4">
         <v>45362</v>
@@ -1238,28 +1268,29 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="3"/>
-    </row>
-    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4">
         <v>45364</v>
@@ -1268,28 +1299,29 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="4">
         <v>45378</v>
@@ -1298,28 +1330,29 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="4">
         <v>45463</v>
@@ -1328,28 +1361,29 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="4">
         <v>45493</v>
@@ -1358,28 +1392,29 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="4">
         <v>45523</v>
@@ -1388,28 +1423,29 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="4">
         <v>45600</v>
@@ -1418,28 +1454,29 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="4">
         <v>45607</v>
@@ -1448,28 +1485,29 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="4">
         <v>45608</v>
@@ -1478,28 +1516,29 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="3"/>
+      <c r="J14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="4">
         <v>45614</v>
@@ -1508,28 +1547,29 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="4">
         <v>45615</v>
@@ -1538,28 +1578,29 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" s="4">
         <v>45617</v>
@@ -1568,28 +1609,29 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="4">
         <v>45622</v>
@@ -1598,28 +1640,29 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="4">
         <v>45622</v>
@@ -1628,28 +1671,29 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" s="4">
         <v>45624</v>
@@ -1658,28 +1702,29 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="4">
         <v>45688</v>
@@ -1688,28 +1733,29 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D22" s="4">
         <v>45695</v>
@@ -1718,28 +1764,29 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D23" s="4">
         <v>45699</v>
@@ -1748,28 +1795,29 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" s="4">
         <v>45702</v>
@@ -1778,28 +1826,29 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D25" s="4">
         <v>45705</v>
@@ -1808,28 +1857,29 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D26" s="4">
         <v>45709</v>
@@ -1838,28 +1888,29 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D27" s="4">
         <v>45712</v>
@@ -1868,28 +1919,29 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D28" s="4">
         <v>45726</v>
@@ -1898,28 +1950,29 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D29" s="4">
         <v>45727</v>
@@ -1928,28 +1981,29 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J29" s="3"/>
-    </row>
-    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D30" s="4">
         <v>45734</v>
@@ -1958,28 +2012,29 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J30" s="3"/>
-    </row>
-    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" s="4">
         <v>45734</v>
@@ -1988,28 +2043,29 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J31" s="3"/>
-    </row>
-    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K31" s="3"/>
+    </row>
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D32" s="4">
         <v>45740</v>
@@ -2018,28 +2074,29 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D33" s="4">
         <v>45741</v>
@@ -2048,28 +2105,29 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J33" s="3"/>
-    </row>
-    <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K33" s="3"/>
+    </row>
+    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D34" s="4">
         <v>45741</v>
@@ -2078,28 +2136,29 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J34" s="3"/>
-    </row>
-    <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D35" s="4">
         <v>45748</v>
@@ -2108,28 +2167,29 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J35" s="3"/>
-    </row>
-    <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K35" s="3"/>
+    </row>
+    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D36" s="4">
         <v>45748</v>
@@ -2138,28 +2198,29 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J36" s="3"/>
-    </row>
-    <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K36" s="3"/>
+    </row>
+    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D37" s="4">
         <v>45755</v>
@@ -2168,28 +2229,29 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J37" s="3"/>
-    </row>
-    <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K37" s="3"/>
+    </row>
+    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D38" s="4">
         <v>45761</v>
@@ -2198,28 +2260,29 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J38" s="3"/>
-    </row>
-    <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K38" s="3"/>
+    </row>
+    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D39" s="4">
         <v>45768</v>
@@ -2228,28 +2291,29 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="J39" s="3"/>
-    </row>
-    <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K39" s="3"/>
+    </row>
+    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D40" s="4">
         <v>45775</v>
@@ -2258,28 +2322,29 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J40" s="3"/>
-    </row>
-    <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D41" s="4">
         <v>45775</v>
@@ -2288,28 +2353,29 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="J41" s="3"/>
-    </row>
-    <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K41" s="3"/>
+    </row>
+    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D42" s="4">
         <v>45782</v>
@@ -2318,28 +2384,29 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J42" s="3"/>
-    </row>
-    <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K42" s="3"/>
+    </row>
+    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D43" s="4">
         <v>45789</v>
@@ -2348,28 +2415,29 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J43" s="3"/>
-    </row>
-    <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K43" s="3"/>
+    </row>
+    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D44" s="4">
         <v>45789</v>
@@ -2378,28 +2446,29 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I44" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J44" s="3"/>
-    </row>
-    <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I44" s="3"/>
+      <c r="J44" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K44" s="3"/>
+    </row>
+    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D45" s="4">
         <v>45796</v>
@@ -2408,28 +2477,29 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J45" s="3"/>
-    </row>
-    <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K45" s="3"/>
+    </row>
+    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D46" s="4">
         <v>45896</v>
@@ -2438,28 +2508,29 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J46" s="3"/>
-    </row>
-    <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K46" s="3"/>
+    </row>
+    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D47" s="4">
         <v>45910</v>
@@ -2468,28 +2539,29 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J47" s="3"/>
-    </row>
-    <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K47" s="3"/>
+    </row>
+    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D48" s="4">
         <v>45924</v>
@@ -2498,28 +2570,29 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J48" s="3"/>
-    </row>
-    <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K48" s="3"/>
+    </row>
+    <row r="49" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D49" s="4">
         <v>45947</v>
@@ -2528,28 +2601,29 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J49" s="3"/>
-    </row>
-    <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K49" s="3"/>
+    </row>
+    <row r="50" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D50" s="4">
         <v>45954</v>
@@ -2558,28 +2632,29 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="J50" s="3"/>
-    </row>
-    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K50" s="3"/>
+    </row>
+    <row r="51" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D51" s="4">
         <v>45961</v>
@@ -2588,28 +2663,29 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J51" s="3"/>
-    </row>
-    <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K51" s="3"/>
+    </row>
+    <row r="52" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D52" s="4">
         <v>45968</v>
@@ -2618,28 +2694,29 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J52" s="3"/>
-    </row>
-    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K52" s="3"/>
+    </row>
+    <row r="53" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D53" s="4">
         <v>45980</v>
@@ -2648,28 +2725,29 @@
         <v>4480</v>
       </c>
       <c r="F53" s="6">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J53" s="3"/>
-    </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K53" s="3"/>
+    </row>
+    <row r="54" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D54" s="4">
         <v>45980</v>
@@ -2678,24 +2756,25 @@
         <v>38840.89</v>
       </c>
       <c r="F54" s="6">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
-    </row>
-    <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K54" s="3"/>
+    </row>
+    <row r="55" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D55" s="4">
         <v>45987</v>
@@ -2704,24 +2783,25 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-    </row>
-    <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K55" s="3"/>
+    </row>
+    <row r="56" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D56" s="4">
         <v>45989</v>
@@ -2730,24 +2810,25 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-    </row>
-    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K56" s="3"/>
+    </row>
+    <row r="57" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D57" s="4">
         <v>45994</v>
@@ -2756,24 +2837,25 @@
         <v>14483.06</v>
       </c>
       <c r="F57" s="6">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
-    </row>
-    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K57" s="3"/>
+    </row>
+    <row r="58" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D58" s="4">
         <v>46090</v>
@@ -2782,28 +2864,29 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="J58" s="3"/>
-    </row>
-    <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="K58" s="3"/>
+    </row>
+    <row r="59" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D59" s="4">
         <v>46097</v>
@@ -2812,28 +2895,29 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
+        <v>158</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K59" s="3"/>
+    </row>
+    <row r="60" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J59" s="3"/>
-    </row>
-    <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="D60" s="4">
         <v>46104</v>
@@ -2842,28 +2926,29 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J60" s="3"/>
-    </row>
-    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K60" s="3"/>
+    </row>
+    <row r="61" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D61" s="4">
         <v>46105</v>
@@ -2872,672 +2957,567 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J61" s="3"/>
-    </row>
-    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K61" s="3"/>
+    </row>
+    <row r="62" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>159</v>
       </c>
       <c r="D62" s="4">
-        <v>46175</v>
+        <v>46192</v>
       </c>
       <c r="E62" s="5">
-        <v>15028</v>
+        <v>7494.53</v>
       </c>
       <c r="F62" s="6">
-        <v>76</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I62" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+    </row>
+    <row r="63" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J62" s="3"/>
-    </row>
-    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="D63" s="4">
-        <v>46177</v>
+        <v>46199</v>
       </c>
       <c r="E63" s="5">
-        <v>15716</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="F63" s="6">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
-    </row>
-    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K63" s="3"/>
+    </row>
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D64" s="4">
-        <v>46192</v>
+        <v>46206</v>
       </c>
       <c r="E64" s="5">
-        <v>15716</v>
+        <v>4676.8500000000004</v>
       </c>
       <c r="F64" s="6">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-    </row>
-    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K64" s="3"/>
+    </row>
+    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>163</v>
       </c>
       <c r="D65" s="4">
-        <v>46192</v>
+        <v>46222</v>
       </c>
       <c r="E65" s="5">
-        <v>4193.28</v>
+        <v>31531.5</v>
       </c>
       <c r="F65" s="6">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I65" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="J65" s="3"/>
-    </row>
-    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K65" s="3"/>
+    </row>
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>165</v>
       </c>
       <c r="D66" s="4">
-        <v>46192</v>
+        <v>46228</v>
       </c>
       <c r="E66" s="5">
-        <v>7494.53</v>
+        <v>3516.48</v>
       </c>
       <c r="F66" s="6">
-        <v>59</v>
-      </c>
-      <c r="G66" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="H66" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-    </row>
-    <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J66" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K66" s="3"/>
+    </row>
+    <row r="67" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D67" s="4">
+        <v>46233</v>
+      </c>
+      <c r="E67" s="5">
+        <v>5796.94</v>
+      </c>
+      <c r="F67" s="6">
+        <v>22</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="K67" s="3"/>
+    </row>
+    <row r="68" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46246</v>
+      </c>
+      <c r="E68" s="5">
+        <v>2754</v>
+      </c>
+      <c r="F68" s="6">
+        <v>9</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K68" s="3"/>
+    </row>
+    <row r="69" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D69" s="4">
+        <v>46247</v>
+      </c>
+      <c r="E69" s="5">
+        <v>3419.96</v>
+      </c>
+      <c r="F69" s="6">
+        <v>8</v>
+      </c>
+      <c r="G69" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D67" s="4">
-        <v>46199</v>
-      </c>
-      <c r="E67" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="F67" s="6">
-        <v>52</v>
-      </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-    </row>
-    <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D68" s="4">
-        <v>46206</v>
-      </c>
-      <c r="E68" s="5">
-        <v>4676.8500000000004</v>
-      </c>
-      <c r="F68" s="6">
-        <v>45</v>
-      </c>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-    </row>
-    <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D69" s="4">
-        <v>46207</v>
-      </c>
-      <c r="E69" s="5">
-        <v>4193.28</v>
-      </c>
-      <c r="F69" s="6">
-        <v>44</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="H69" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J69" s="3"/>
-    </row>
-    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K69" s="3"/>
+    </row>
+    <row r="70" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D70" s="4">
-        <v>46207</v>
+        <v>46248</v>
       </c>
       <c r="E70" s="5">
-        <v>7049.25</v>
+        <v>3300</v>
       </c>
       <c r="F70" s="6">
-        <v>44</v>
-      </c>
-      <c r="G70" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="H70" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-    </row>
-    <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K70" s="3"/>
+    </row>
+    <row r="71" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D71" s="4">
+        <v>46252</v>
+      </c>
+      <c r="E71" s="5">
+        <v>860</v>
+      </c>
+      <c r="F71" s="6">
+        <v>3</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K71" s="3"/>
+    </row>
+    <row r="72" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D72" s="4">
+        <v>46252</v>
+      </c>
+      <c r="E72" s="5">
+        <v>2818.37</v>
+      </c>
+      <c r="F72" s="6">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K72" s="3"/>
+    </row>
+    <row r="73" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D73" s="4">
+        <v>46252</v>
+      </c>
+      <c r="E73" s="5">
+        <v>2400</v>
+      </c>
+      <c r="F73" s="6">
+        <v>3</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K73" s="3"/>
+    </row>
+    <row r="74" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D74" s="4">
+        <v>46253</v>
+      </c>
+      <c r="E74" s="5">
+        <v>982.71</v>
+      </c>
+      <c r="F74" s="6">
+        <v>2</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K74" s="3"/>
+    </row>
+    <row r="75" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D71" s="4">
-        <v>46207</v>
-      </c>
-      <c r="E71" s="5">
-        <v>15716</v>
-      </c>
-      <c r="F71" s="6">
-        <v>44</v>
-      </c>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-    </row>
-    <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D72" s="4">
-        <v>46222</v>
-      </c>
-      <c r="E72" s="5">
-        <v>3996.72</v>
-      </c>
-      <c r="F72" s="6">
-        <v>29</v>
-      </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-    </row>
-    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C73" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D75" s="4">
+        <v>46253</v>
+      </c>
+      <c r="E75" s="5">
+        <v>2754</v>
+      </c>
+      <c r="F75" s="6">
+        <v>2</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K75" s="3"/>
+    </row>
+    <row r="76" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D76" s="4">
+        <v>46253</v>
+      </c>
+      <c r="E76" s="5">
+        <v>3066</v>
+      </c>
+      <c r="F76" s="6">
+        <v>2</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K76" s="3"/>
+    </row>
+    <row r="77" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D77" s="4">
+        <v>46253</v>
+      </c>
+      <c r="E77" s="5">
+        <v>875.25</v>
+      </c>
+      <c r="F77" s="6">
+        <v>2</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K77" s="3"/>
+    </row>
+    <row r="78" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D78" s="4">
+        <v>46254</v>
+      </c>
+      <c r="E78" s="5">
+        <v>2549.41</v>
+      </c>
+      <c r="F78" s="6">
+        <v>1</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K78" s="3"/>
+    </row>
+    <row r="79" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D73" s="4">
-        <v>46222</v>
-      </c>
-      <c r="E73" s="5">
-        <v>31531.5</v>
-      </c>
-      <c r="F73" s="6">
-        <v>29</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I73" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J73" s="3"/>
-    </row>
-    <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D74" s="4">
-        <v>46228</v>
-      </c>
-      <c r="E74" s="5">
-        <v>3516.48</v>
-      </c>
-      <c r="F74" s="6">
-        <v>23</v>
-      </c>
-      <c r="G74" s="3" t="s">
+      <c r="C79" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D79" s="4">
+        <v>46254</v>
+      </c>
+      <c r="E79" s="5">
+        <v>3419.96</v>
+      </c>
+      <c r="F79" s="6">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J74" s="3"/>
-    </row>
-    <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D75" s="4">
-        <v>46233</v>
-      </c>
-      <c r="E75" s="5">
-        <v>5796.94</v>
-      </c>
-      <c r="F75" s="6">
-        <v>18</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J75" s="3"/>
-    </row>
-    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D76" s="4">
-        <v>46237</v>
-      </c>
-      <c r="E76" s="5">
-        <v>3996.72</v>
-      </c>
-      <c r="F76" s="6">
-        <v>14</v>
-      </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-    </row>
-    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D77" s="4">
-        <v>46239</v>
-      </c>
-      <c r="E77" s="5">
-        <v>2754</v>
-      </c>
-      <c r="F77" s="6">
-        <v>12</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J77" s="3"/>
-    </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D78" s="4">
-        <v>46241</v>
-      </c>
-      <c r="E78" s="5">
-        <v>10174.450000000001</v>
-      </c>
-      <c r="F78" s="6">
-        <v>10</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="J78" s="3"/>
-    </row>
-    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D79" s="4">
-        <v>46244</v>
-      </c>
-      <c r="E79" s="5">
-        <v>5352.33</v>
-      </c>
-      <c r="F79" s="6">
-        <v>7</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J79" s="3"/>
-    </row>
-    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D80" s="4">
-        <v>46245</v>
-      </c>
-      <c r="E80" s="5">
-        <v>2400</v>
-      </c>
-      <c r="F80" s="6">
-        <v>6</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J80" s="3"/>
-    </row>
-    <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D81" s="4">
-        <v>46246</v>
-      </c>
-      <c r="E81" s="5">
-        <v>2754</v>
-      </c>
-      <c r="F81" s="6">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="J81" s="3"/>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D82" s="4">
-        <v>46247</v>
-      </c>
-      <c r="E82" s="5">
-        <v>3419.96</v>
-      </c>
-      <c r="F82" s="6">
-        <v>4</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J82" s="3"/>
-    </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D83" s="4">
-        <v>46248</v>
-      </c>
-      <c r="E83" s="5">
-        <v>3300</v>
-      </c>
-      <c r="F83" s="6">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J83" s="3"/>
-    </row>
-    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C84" s="3" t="s">
+      <c r="I79" s="3"/>
+      <c r="J79" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D84" s="4">
-        <v>46248</v>
-      </c>
-      <c r="E84" s="5">
-        <v>9358.7000000000007</v>
-      </c>
-      <c r="F84" s="6">
-        <v>3</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J84" s="3"/>
+      <c r="K79" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
+++ b/dados/XLS_Grid_LANCAMENTO A RECEBER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS\Desktop\dados planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA40ACDA-2EAD-4C48-AD8C-E7375CD3F1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC04F91-D2D8-4599-86D0-B5C8CB0C0CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="210">
   <si>
     <t>Funcionário</t>
   </si>
@@ -646,6 +646,15 @@
   </si>
   <si>
     <t>70791154400003419960001121205064100656763557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOE MED COMERCIO DE PRODUTOS MEDICOS HOSPITALARES </t>
+  </si>
+  <si>
+    <t>01006793.2</t>
+  </si>
+  <si>
+    <t>34196154500003800001090002597718120992717000</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" style="1" customWidth="1"/>
@@ -1144,7 +1153,7 @@
         <v>9391.7800000000007</v>
       </c>
       <c r="F2" s="6">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>14</v>
@@ -1175,7 +1184,7 @@
         <v>5418</v>
       </c>
       <c r="F3" s="6">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>14</v>
@@ -1206,7 +1215,7 @@
         <v>1264.8699999999999</v>
       </c>
       <c r="F4" s="6">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>22</v>
@@ -1237,7 +1246,7 @@
         <v>5418</v>
       </c>
       <c r="F5" s="6">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>14</v>
@@ -1268,7 +1277,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>22</v>
@@ -1299,7 +1308,7 @@
         <v>816</v>
       </c>
       <c r="F7" s="6">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>22</v>
@@ -1330,7 +1339,7 @@
         <v>816</v>
       </c>
       <c r="F8" s="6">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>22</v>
@@ -1361,7 +1370,7 @@
         <v>1674.52</v>
       </c>
       <c r="F9" s="6">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>14</v>
@@ -1392,7 +1401,7 @@
         <v>873.6</v>
       </c>
       <c r="F10" s="6">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>14</v>
@@ -1423,7 +1432,7 @@
         <v>873.6</v>
       </c>
       <c r="F11" s="6">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>14</v>
@@ -1454,7 +1463,7 @@
         <v>2000</v>
       </c>
       <c r="F12" s="6">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>14</v>
@@ -1485,7 +1494,7 @@
         <v>3204.34</v>
       </c>
       <c r="F13" s="6">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>14</v>
@@ -1516,7 +1525,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F14" s="6">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>14</v>
@@ -1547,7 +1556,7 @@
         <v>2000</v>
       </c>
       <c r="F15" s="6">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>14</v>
@@ -1578,7 +1587,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F16" s="6">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>14</v>
@@ -1609,7 +1618,7 @@
         <v>1843.87</v>
       </c>
       <c r="F17" s="6">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>14</v>
@@ -1640,7 +1649,7 @@
         <v>1216.8599999999999</v>
       </c>
       <c r="F18" s="6">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>14</v>
@@ -1671,7 +1680,7 @@
         <v>4439.8999999999996</v>
       </c>
       <c r="F19" s="6">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>14</v>
@@ -1702,7 +1711,7 @@
         <v>1843.88</v>
       </c>
       <c r="F20" s="6">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>14</v>
@@ -1733,7 +1742,7 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="F21" s="6">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>14</v>
@@ -1764,7 +1773,7 @@
         <v>3296.8</v>
       </c>
       <c r="F22" s="6">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>14</v>
@@ -1795,7 +1804,7 @@
         <v>2330</v>
       </c>
       <c r="F23" s="6">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>14</v>
@@ -1826,7 +1835,7 @@
         <v>3296.8</v>
       </c>
       <c r="F24" s="6">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>14</v>
@@ -1857,7 +1866,7 @@
         <v>2541</v>
       </c>
       <c r="F25" s="6">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>22</v>
@@ -1888,7 +1897,7 @@
         <v>3296.8</v>
       </c>
       <c r="F26" s="6">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>14</v>
@@ -1919,7 +1928,7 @@
         <v>2541</v>
       </c>
       <c r="F27" s="6">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>22</v>
@@ -1950,7 +1959,7 @@
         <v>2541</v>
       </c>
       <c r="F28" s="6">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>22</v>
@@ -1981,7 +1990,7 @@
         <v>7562.78</v>
       </c>
       <c r="F29" s="6">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>14</v>
@@ -2012,7 +2021,7 @@
         <v>7562.78</v>
       </c>
       <c r="F30" s="6">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>14</v>
@@ -2043,7 +2052,7 @@
         <v>1154.56</v>
       </c>
       <c r="F31" s="6">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>14</v>
@@ -2074,7 +2083,7 @@
         <v>2541</v>
       </c>
       <c r="F32" s="6">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>22</v>
@@ -2105,7 +2114,7 @@
         <v>7562.78</v>
       </c>
       <c r="F33" s="6">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>14</v>
@@ -2136,7 +2145,7 @@
         <v>1154.56</v>
       </c>
       <c r="F34" s="6">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>14</v>
@@ -2167,7 +2176,7 @@
         <v>1154.56</v>
       </c>
       <c r="F35" s="6">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>14</v>
@@ -2198,7 +2207,7 @@
         <v>7562.76</v>
       </c>
       <c r="F36" s="6">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>14</v>
@@ -2229,7 +2238,7 @@
         <v>1154.56</v>
       </c>
       <c r="F37" s="6">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>14</v>
@@ -2260,7 +2269,7 @@
         <v>6169.53</v>
       </c>
       <c r="F38" s="6">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>14</v>
@@ -2291,7 +2300,7 @@
         <v>3850</v>
       </c>
       <c r="F39" s="6">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>14</v>
@@ -2322,7 +2331,7 @@
         <v>3850</v>
       </c>
       <c r="F40" s="6">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>14</v>
@@ -2353,7 +2362,7 @@
         <v>6089.41</v>
       </c>
       <c r="F41" s="6">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>14</v>
@@ -2384,7 +2393,7 @@
         <v>3800</v>
       </c>
       <c r="F42" s="6">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>14</v>
@@ -2415,7 +2424,7 @@
         <v>3800</v>
       </c>
       <c r="F43" s="6">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>14</v>
@@ -2446,7 +2455,7 @@
         <v>1143.54</v>
       </c>
       <c r="F44" s="6">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>22</v>
@@ -2477,7 +2486,7 @@
         <v>2287.06</v>
       </c>
       <c r="F45" s="6">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>22</v>
@@ -2508,7 +2517,7 @@
         <v>4572.62</v>
       </c>
       <c r="F46" s="6">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>22</v>
@@ -2539,7 +2548,7 @@
         <v>3663.84</v>
       </c>
       <c r="F47" s="6">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>22</v>
@@ -2570,7 +2579,7 @@
         <v>3663.84</v>
       </c>
       <c r="F48" s="6">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>22</v>
@@ -2601,7 +2610,7 @@
         <v>3867.34</v>
       </c>
       <c r="F49" s="6">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>22</v>
@@ -2632,7 +2641,7 @@
         <v>2144.59</v>
       </c>
       <c r="F50" s="6">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>22</v>
@@ -2663,7 +2672,7 @@
         <v>2144.59</v>
       </c>
       <c r="F51" s="6">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>22</v>
@@ -2694,7 +2703,7 @@
         <v>2144.59</v>
       </c>
       <c r="F52" s="6">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>22</v>
@@ -2725,7 +2734,7 @@
         <v>4480</v>
       </c>
       <c r="F53" s="6">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>22</v>
@@ -2756,7 +2765,7 @@
         <v>38840.89</v>
       </c>
       <c r="F54" s="6">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
@@ -2783,7 +2792,7 @@
         <v>33844.160000000003</v>
       </c>
       <c r="F55" s="6">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
@@ -2810,7 +2819,7 @@
         <v>3220</v>
       </c>
       <c r="F56" s="6">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -2837,7 +2846,7 @@
         <v>14483.06</v>
       </c>
       <c r="F57" s="6">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -2864,7 +2873,7 @@
         <v>806.34</v>
       </c>
       <c r="F58" s="6">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>22</v>
@@ -2895,7 +2904,7 @@
         <v>503.28</v>
       </c>
       <c r="F59" s="6">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>22</v>
@@ -2926,7 +2935,7 @@
         <v>503.28</v>
       </c>
       <c r="F60" s="6">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>22</v>
@@ -2957,7 +2966,7 @@
         <v>5466.66</v>
       </c>
       <c r="F61" s="6">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>14</v>
@@ -2988,7 +2997,7 @@
         <v>7494.53</v>
       </c>
       <c r="F62" s="6">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
@@ -3015,7 +3024,7 @@
         